--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sitewide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JobG8 categories" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LIVE" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NOT LIVE" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Sitewide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="JobG8 categories" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="LIVE" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="NOT LIVE" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sitewide'!$A$1:$B$9</definedName>
@@ -2278,38 +2278,36 @@
       <c r="B2" s="2" t="inlineStr"/>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2 / 2.2 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>4 / 3.8 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/8</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>1 / 1.0 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -2319,32 +2317,28 @@
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr"/>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>0 / 3.5 / 3/11</t>
-        </is>
+      <c r="C3" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>7 / 1.7 / 1/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>2 / 0.7 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr"/>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>2 / 0.5 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>1 / 0.2 / 0/5</t>
-        </is>
+      <c r="I3" s="5" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -2354,32 +2348,28 @@
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1 / 1.0 / 0/11</t>
-        </is>
+      <c r="C4" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3 / 2.9 / 1/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7 / 2.6 / 1/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2 / 1.8 / 0/8</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5 / 2.0 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -2389,36 +2379,32 @@
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr"/>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>0 / 0.7 / 0/11</t>
-        </is>
+      <c r="C5" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>1 / 2.0 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/8</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>6 / 2.4 / 1/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -2428,40 +2414,36 @@
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr"/>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0 / 0.1 / 0/11</t>
-        </is>
+      <c r="C6" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3 / 2.5 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6 / 2.6 / 1/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3 / 4.5 / 2/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/8</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1 / 1.0 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -2471,40 +2453,36 @@
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr"/>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>0 / 0.6 / 0/11</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>3 / 1.5 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>3 / 1.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>3 / 1.8 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -2516,38 +2494,36 @@
       <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1 / 1.4 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6 / 2.1 / 1/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2 / 1.3 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>7 / 4.7 / 2/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/8</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -2557,40 +2533,36 @@
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr"/>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>0 / 1.5 / 0/11</t>
-        </is>
+      <c r="C9" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>0 / 2.0 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2 / 1.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>6 / 2.2 / 1/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>1 / 2.2 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/8</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>1 / 0.2 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -2600,40 +2572,36 @@
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0 / 1.5 / 0/11</t>
-        </is>
+      <c r="C10" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="11">
@@ -2642,44 +2610,40 @@
           <t>Cumbria - North</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>1 / 1.6 / 0/11</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>0 / 2.8 / 3/11</t>
-        </is>
+      <c r="B11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2689,40 +2653,38 @@
           <t>Cumbria - South</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>1 / 1.1 / 0/11</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2 / 0.6 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2734,43 +2696,39 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>1 / 1.8 / 0/11</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>1 / 0.8 / 0/11</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -2780,40 +2738,36 @@
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>0 / 0.4 / 0/11</t>
-        </is>
+      <c r="C14" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3 / 2.5 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2 / 0.6 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2 / 0.9 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2 / 3.2 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3 / 1.4 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -2823,35 +2777,33 @@
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr"/>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>0 / 0.1 / 0/11</t>
-        </is>
+      <c r="C15" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>5 / 3.2 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>3 / 2.1 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>6 / 1.2 / 1/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr"/>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>3 / 1.0 / 0/5</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2862,40 +2814,36 @@
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>1 / 1.0 / 0/11</t>
-        </is>
+      <c r="C16" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5 / 3.9 / 2/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3 / 1.4 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1 / 3.2 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1 / 0.2 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -2907,34 +2855,32 @@
       <c r="B17" s="4" t="inlineStr"/>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>5 / 2.1 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>6 / 2.8 / 1/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>4 / 5.7 / 2/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/8</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>4 / 2.0 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -2944,35 +2890,33 @@
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>0 / 0.2 / 0/11</t>
-        </is>
+      <c r="C18" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4 / 1.4 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8 / 2.9 / 1/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2 / 1.2 / 0/8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3 / 1.6 / 0/5</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2983,28 +2927,24 @@
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr"/>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>2 / 1.3 / 0/11</t>
-        </is>
+      <c r="C19" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="D19" s="4" t="inlineStr"/>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>3 / 3.9 / 2/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>3 / 3.7 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>3 / 2.2 / 0/5</t>
-        </is>
+      <c r="I19" s="5" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -3013,45 +2953,41 @@
           <t>Greater Manchester - North</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>3 / 3.1 / 1/11</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/8</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1 / 0.2 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -3061,40 +2997,36 @@
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr"/>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>0 / 0.8 / 0/11</t>
-        </is>
+      <c r="C21" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>2 / 0.2 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>3 / 0.6 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -3104,40 +3036,36 @@
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/8</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>1 / 1.0 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -3150,27 +3078,27 @@
       <c r="C23" s="4" t="inlineStr"/>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>14 / 7.4 / 7/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>0 / 1.7 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>10 / 5.0 / 2/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>1 / 2.8 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>4 / 3.5 / 0/8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr"/>
@@ -3181,44 +3109,42 @@
           <t>Herefordshire</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>0 / 1.4 / 0/11</t>
-        </is>
+      <c r="B24" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0 / 1.2 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3229,40 +3155,36 @@
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr"/>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>3 / 2.3 / 0/11</t>
-        </is>
+      <c r="C25" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>10 / 4.0 / 1/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>1 / 1.6 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>9 / 2.1 / 1/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/8</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>4 / 1.6 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -3275,33 +3197,31 @@
       <c r="C26" s="2" t="inlineStr"/>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>8 / 4.5 / 1/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3 / 4.3 / 2/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7 / 2.8 / 1/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1 / 3.2 / 1/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2 / 1.6 / 0/8</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>2 / 0.8 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -3310,44 +3230,42 @@
           <t>Lancashire - Blackpool &amp; Fylde</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>1 / 0.8 / 0/11</t>
-        </is>
+      <c r="B27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>2 / 0.9 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3357,45 +3275,39 @@
           <t>Lancashire - Central</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>3 / 2.8 / 0/11</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>0 / 0.2 / 0/11</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/8</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -3404,44 +3316,40 @@
           <t>Lancashire - East</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>3 / 2.5 / 0/11</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>0 / 0.7 / 0/11</t>
-        </is>
+      <c r="B29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>3 / 1.1 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3453,42 +3361,40 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/11</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>0 / 1.2 / 0/11</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3500,42 +3406,42 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>0 / 1.3 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3546,40 +3452,36 @@
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr"/>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>0 / 0.1 / 0/11</t>
-        </is>
+      <c r="C32" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>3 / 1.6 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2 / 1.3 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2 / 3.0 / 1/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2 / 0.9 / 0/8</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>3 / 3.0 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="33">
@@ -3589,40 +3491,36 @@
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr"/>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>0 / 1.7 / 0/11</t>
-        </is>
+      <c r="C33" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>4 / 1.2 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>3 / 1.6 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>3 / 2.7 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>1 / 2.8 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>1 / 1.4 / 0/8</t>
-        </is>
-      </c>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>2 / 1.0 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -3638,7 +3536,7 @@
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>10 / 5.2 / 2/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
@@ -3651,40 +3549,36 @@
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr"/>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>0 / 0.4 / 0/11</t>
-        </is>
+      <c r="C35" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>6 / 2.0 / 1/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/8</t>
-        </is>
-      </c>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -3695,42 +3589,40 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/10</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/10</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3742,42 +3634,42 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>1 / 2.0 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>1 / 1.7 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3787,45 +3679,39 @@
           <t>Merseyside - Wirral</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>1 / 1.5 / 0/11</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>0 / 0.5 / 0/11</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3 / 0.6 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>1 / 1.0 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -3835,36 +3721,32 @@
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr"/>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>0 / 1.1 / 0/11</t>
-        </is>
+      <c r="C39" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr"/>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>2 / 1.6 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>2 / 4.2 / 2/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/8</t>
-        </is>
-      </c>
-      <c r="I39" s="4" t="inlineStr">
-        <is>
-          <t>1 / 0.8 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -3878,24 +3760,22 @@
       <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>6 / 4.1 / 1/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/8</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>4 / 2.4 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="41">
@@ -3904,44 +3784,40 @@
           <t>North Scotland</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>6 / 5.6 / 4/10</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/10</t>
-        </is>
+      <c r="B41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>6 / 3.0 / 1/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3951,45 +3827,39 @@
           <t>North Wales - East</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>5 / 4.5 / 1/10</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>0 / 0.2 / 0/10</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>1 / 1.3 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>1 / 1.0 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -4000,43 +3870,39 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>3 / 1.8 / 0/10</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/10</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/8</t>
-        </is>
-      </c>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>1 / 0.4 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -4046,40 +3912,36 @@
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
+      <c r="C44" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>11 / 3.6 / 1/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1 / 1.3 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>6 / 2.2 / 1/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>2 / 3.3 / 2/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>3 / 2.5 / 1/8</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>1 / 0.2 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -4089,35 +3951,33 @@
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr"/>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>1 / 1.8 / 0/10</t>
-        </is>
+      <c r="C45" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr"/>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/5</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -4127,45 +3987,41 @@
           <t>Northern Ireland - West</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>4 / 4.1 / 0/10</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>3 / 1.0 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -4175,36 +4031,32 @@
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr"/>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>1 / 0.5 / 0/11</t>
-        </is>
+      <c r="C47" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>3 / 1.8 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>2 / 2.1 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>4 / 2.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>1 / 3.7 / 2/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
-      <c r="I47" s="4" t="inlineStr">
-        <is>
-          <t>1 / 1.0 / 0/5</t>
-        </is>
+      <c r="I47" s="5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -4217,33 +4069,31 @@
       <c r="C48" s="2" t="inlineStr"/>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>5 / 3.0 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2 / 1.7 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>10 / 4.6 / 2/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>1 / 2.8 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/8</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>3 / 0.8 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -4254,42 +4104,42 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -4301,42 +4151,42 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -4347,40 +4197,36 @@
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr"/>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>0 / 0.1 / 0/10</t>
-        </is>
+      <c r="C51" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>4 / 2.2 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>4 / 2.4 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/8</t>
-        </is>
-      </c>
-      <c r="I51" s="4" t="inlineStr">
-        <is>
-          <t>1 / 0.2 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -4389,45 +4235,39 @@
           <t>Scotland Central - Falkirk &amp; Stirling</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>2 / 2.8 / 0/10</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/10</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -4438,42 +4278,40 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/10</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/10</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>2 / 1.0 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -4483,44 +4321,42 @@
           <t>Scotland Central - Tayside</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>5 / 3.8 / 0/10</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/5</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -4532,43 +4368,41 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
-      <c r="I55" s="4" t="inlineStr">
-        <is>
-          <t>1 / 0.6 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -4578,40 +4412,36 @@
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/10</t>
-        </is>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>4 / 3.1 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/8</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>3 / 2.4 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -4620,45 +4450,41 @@
           <t>Scotland West - Lanarkshire</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>0 / 0.5 / 0/10</t>
-        </is>
+      <c r="B57" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
-      <c r="I57" s="4" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -4669,43 +4495,39 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/10</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/10</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -4715,35 +4537,33 @@
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr"/>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>0 / 1.8 / 0/11</t>
-        </is>
+      <c r="C59" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0 / 1.1 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>2 / 1.7 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr"/>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>2 / 1.9 / 0/8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -4754,40 +4574,36 @@
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>1 / 3.5 / 3/11</t>
-        </is>
+      <c r="C60" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>2 / 1.3 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>4 / 0.6 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>2 / 3.3 / 1/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/8</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>2 / 0.4 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -4797,34 +4613,32 @@
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr"/>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>0 / 0.2 / 0/11</t>
-        </is>
+      <c r="C61" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1 / 1.4 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>2 / 1.2 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>3 / 2.5 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr"/>
@@ -4836,35 +4650,33 @@
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>0 / 0.9 / 0/11</t>
-        </is>
+      <c r="C62" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>3 / 1.6 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2 / 0.3 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>1 / 1.8 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/5</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -4878,23 +4690,23 @@
       <c r="C63" s="4" t="inlineStr"/>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>6 / 4.5 / 4/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>5 / 4.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr"/>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>5 / 5.2 / 2/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>3 / 2.0 / 0/8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr"/>
@@ -4909,33 +4721,31 @@
       <c r="C64" s="2" t="inlineStr"/>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>7 / 3.6 / 1/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>4 / 2.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>5 / 2.6 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>4 / 4.2 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>6 / 5.8 / 6/8</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>4 / 2.8 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -4946,43 +4756,41 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
-      <c r="I65" s="4" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4991,44 +4799,40 @@
           <t>Wales - West</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>3 / 1.9 / 0/10</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/10</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5038,44 +4842,40 @@
           <t>Wales South - Cardiff &amp; Vale</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>5 / 4.1 / 1/10</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/10</t>
-        </is>
+      <c r="B67" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>3 / 1.7 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>2 / 1.3 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>2 / 0.9 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>0 / 1.2 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5087,42 +4887,42 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>1 / 2.7 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>2 / 1.3 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5132,45 +4932,39 @@
           <t>Wales South - Swansea Bay</t>
         </is>
       </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>1 / 2.9 / 1/10</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>0 / 0.1 / 0/10</t>
-        </is>
+      <c r="B69" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>1 / 1.8 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
-      <c r="I69" s="4" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="70">
@@ -5181,43 +4975,39 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>2 / 1.4 / 1/10</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/10</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>4 / 2.6 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="71">
@@ -5229,30 +5019,28 @@
       <c r="B71" s="4" t="inlineStr"/>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>11 / 4.0 / 1/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>3 / 3.9 / 2/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr"/>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>3 / 2.7 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
-      <c r="I71" s="4" t="inlineStr">
-        <is>
-          <t>5 / 3.4 / 0/5</t>
-        </is>
+      <c r="I71" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -5262,39 +5050,37 @@
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr"/>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>1 / 1.1 / 0/11</t>
-        </is>
+      <c r="C72" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>3 / 1.1 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>1 / 1.3 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/5</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5305,40 +5091,36 @@
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr"/>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
+      <c r="C73" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>6 / 1.3 / 1/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>5 / 2.4 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>3 / 2.2 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>3 / 3.1 / 0/8</t>
-        </is>
-      </c>
-      <c r="I73" s="4" t="inlineStr">
-        <is>
-          <t>2 / 0.4 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -5351,33 +5133,31 @@
       <c r="C74" s="2" t="inlineStr"/>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>3 / 2.0 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>4 / 3.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>3 / 1.1 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>0 / 2.7 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/8</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>1 / 1.0 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="75">
@@ -5387,40 +5167,36 @@
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr"/>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>0 / 1.3 / 0/11</t>
-        </is>
+      <c r="C75" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>1 / 2.1 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>2 / 0.4 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>3 / 1.6 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.8 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/8</t>
-        </is>
-      </c>
-      <c r="I75" s="4" t="inlineStr">
-        <is>
-          <t>1 / 0.4 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -5430,40 +5206,36 @@
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr"/>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>0 / 0.7 / 0/11</t>
-        </is>
+      <c r="C76" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>0 / 1.2 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>2 / 1.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2 / 0.4 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>2 / 4.0 / 0/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/8</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>4 / 2.8 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="77">
@@ -5473,36 +5245,32 @@
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr"/>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>1 / 3.5 / 0/11</t>
-        </is>
+      <c r="C77" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>3 / 0.9 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>12 / 2.7 / 1/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr"/>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/8</t>
-        </is>
-      </c>
-      <c r="I77" s="4" t="inlineStr">
-        <is>
-          <t>2 / 1.0 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -5515,33 +5283,31 @@
       <c r="C78" s="2" t="inlineStr"/>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>4 / 2.0 / 0/11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>4 / 3.1 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>6 / 2.0 / 1/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>0 / 2.3 / 2/6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>2 / 1.0 / 0/5</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="79">
@@ -5555,20 +5321,18 @@
       <c r="D79" s="4" t="inlineStr"/>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>4 / 4.0 / 0/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>15 / 5.4 / 3/9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr"/>
       <c r="H79" s="4" t="inlineStr"/>
-      <c r="I79" s="4" t="inlineStr">
-        <is>
-          <t>3 / 2.6 / 0/5</t>
-        </is>
+      <c r="I79" s="5" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sitewide'!$A$1:$B$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'JobG8 categories'!$A$1:$B$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'JobG8 categories'!$A$1:$C$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'LIVE'!$A$1:$I$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOT LIVE'!$A$1:$I$79</definedName>
   </definedNames>
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,8 +37,14 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <color rgb="00000000"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +59,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F3F6F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -73,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -89,6 +100,30 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -566,11 +601,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -584,6 +620,11 @@
           <t>Jobs received</t>
         </is>
       </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Ontap jobs</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -594,6 +635,7 @@
       <c r="B2" s="3" t="n">
         <v>2547</v>
       </c>
+      <c r="C2" s="7" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -604,6 +646,7 @@
       <c r="B3" s="5" t="n">
         <v>920</v>
       </c>
+      <c r="C3" s="7" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -614,6 +657,7 @@
       <c r="B4" s="3" t="n">
         <v>669</v>
       </c>
+      <c r="C4" s="7" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -624,6 +668,7 @@
       <c r="B5" s="5" t="n">
         <v>267</v>
       </c>
+      <c r="C5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -634,6 +679,7 @@
       <c r="B6" s="3" t="n">
         <v>125</v>
       </c>
+      <c r="C6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -644,6 +690,7 @@
       <c r="B7" s="5" t="n">
         <v>116</v>
       </c>
+      <c r="C7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -654,6 +701,7 @@
       <c r="B8" s="3" t="n">
         <v>108</v>
       </c>
+      <c r="C8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -664,6 +712,7 @@
       <c r="B9" s="5" t="n">
         <v>107</v>
       </c>
+      <c r="C9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -674,6 +723,7 @@
       <c r="B10" s="3" t="n">
         <v>101</v>
       </c>
+      <c r="C10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -684,6 +734,7 @@
       <c r="B11" s="5" t="n">
         <v>99</v>
       </c>
+      <c r="C11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -694,6 +745,7 @@
       <c r="B12" s="3" t="n">
         <v>84</v>
       </c>
+      <c r="C12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -704,6 +756,7 @@
       <c r="B13" s="5" t="n">
         <v>83</v>
       </c>
+      <c r="C13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -714,6 +767,7 @@
       <c r="B14" s="3" t="n">
         <v>65</v>
       </c>
+      <c r="C14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -724,6 +778,7 @@
       <c r="B15" s="5" t="n">
         <v>29</v>
       </c>
+      <c r="C15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -734,6 +789,7 @@
       <c r="B16" s="3" t="n">
         <v>23</v>
       </c>
+      <c r="C16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -744,9 +800,21 @@
       <c r="B17" s="5" t="n">
         <v>11</v>
       </c>
+      <c r="C17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Total JobG8 jobs received</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="n">
+        <v>5354</v>
+      </c>
+      <c r="C18" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B17"/>
+  <autoFilter ref="A1:C18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2212,14 +2280,14 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -2269,3069 +2337,3069 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Bedfordshire</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="n">
+      <c r="B2" s="10" t="inlineStr"/>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I2" s="11" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Berkshire</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr"/>
-      <c r="C3" s="5" t="n">
+      <c r="B3" s="12" t="inlineStr"/>
+      <c r="C3" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="5" t="n">
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr"/>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr"/>
+      <c r="I3" s="13" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Bristol &amp; Bath</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="3" t="n">
+      <c r="B4" s="10" t="inlineStr"/>
+      <c r="C4" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="n">
+      <c r="D4" s="10" t="inlineStr"/>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr"/>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I4" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Buckinghamshire</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr"/>
-      <c r="C5" s="5" t="n">
+      <c r="B5" s="12" t="inlineStr"/>
+      <c r="C5" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="n">
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr"/>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Cambridgeshire</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr"/>
-      <c r="C6" s="3" t="n">
+      <c r="B6" s="10" t="inlineStr"/>
+      <c r="C6" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="n">
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Cheshire - East</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr"/>
-      <c r="C7" s="5" t="n">
+      <c r="B7" s="12" t="inlineStr"/>
+      <c r="C7" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="n">
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I7" s="13" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Cheshire - Warrington &amp; Halton</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr"/>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="n">
+      <c r="B8" s="10" t="inlineStr"/>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Cheshire - West</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr"/>
-      <c r="C9" s="5" t="n">
+      <c r="B9" s="12" t="inlineStr"/>
+      <c r="C9" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="n">
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>Cornwall</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr"/>
-      <c r="C10" s="3" t="n">
+      <c r="B10" s="10" t="inlineStr"/>
+      <c r="C10" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="n">
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="n">
         <v>55</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Cumbria - North</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Cumbria - South</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr"/>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Cumbria - West</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="n">
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="n">
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I13" s="13" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Derbyshire</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr"/>
-      <c r="C14" s="3" t="n">
+      <c r="B14" s="10" t="inlineStr"/>
+      <c r="C14" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="n">
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I14" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Devon</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr"/>
-      <c r="C15" s="5" t="n">
+      <c r="B15" s="12" t="inlineStr"/>
+      <c r="C15" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr"/>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Dorset</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr"/>
-      <c r="C16" s="3" t="n">
+      <c r="B16" s="10" t="inlineStr"/>
+      <c r="C16" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="n">
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I16" s="11" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>Essex</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr"/>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="n">
+      <c r="B17" s="12" t="inlineStr"/>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr"/>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I17" s="13" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>Gloucestershire</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr"/>
-      <c r="C18" s="3" t="n">
+      <c r="B18" s="10" t="inlineStr"/>
+      <c r="C18" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr"/>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr"/>
-      <c r="C19" s="5" t="n">
+      <c r="B19" s="12" t="inlineStr"/>
+      <c r="C19" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr"/>
-      <c r="I19" s="5" t="n">
+      <c r="D19" s="12" t="inlineStr"/>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr"/>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="inlineStr"/>
+      <c r="I19" s="13" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>Greater Manchester - North</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B20" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="n">
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I20" s="11" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>Greater Manchester - South</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr"/>
-      <c r="C21" s="5" t="n">
+      <c r="B21" s="12" t="inlineStr"/>
+      <c r="C21" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="n">
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I21" s="13" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>Greater Manchester - Wigan &amp; Bolton</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr"/>
-      <c r="C22" s="3" t="n">
+      <c r="B22" s="10" t="inlineStr"/>
+      <c r="C22" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="n">
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>Hampshire</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr"/>
-      <c r="C23" s="4" t="inlineStr"/>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr"/>
+      <c r="C23" s="12" t="inlineStr"/>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I23" s="12" t="inlineStr"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>Herefordshire</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n">
+      <c r="B24" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>Hertfordshire</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr"/>
-      <c r="C25" s="5" t="n">
+      <c r="B25" s="12" t="inlineStr"/>
+      <c r="C25" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="n">
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I25" s="13" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>Kent</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr"/>
-      <c r="C26" s="2" t="inlineStr"/>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="n">
+      <c r="B26" s="10" t="inlineStr"/>
+      <c r="C26" s="10" t="inlineStr"/>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I26" s="11" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>Lancashire - Blackpool &amp; Fylde</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B27" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I27" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>Lancashire - Central</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n">
+      <c r="B28" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="C28" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="n">
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I28" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>Lancashire - East</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B29" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C29" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I29" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>Lancashire - North</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="n">
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>Lancashire - West</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H31" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I31" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>Leicestershire</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr"/>
-      <c r="C32" s="3" t="n">
+      <c r="B32" s="10" t="inlineStr"/>
+      <c r="C32" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="n">
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I32" s="11" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>Lincolnshire</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr"/>
-      <c r="C33" s="5" t="n">
+      <c r="B33" s="12" t="inlineStr"/>
+      <c r="C33" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="n">
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H33" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I33" s="13" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>London</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr"/>
-      <c r="C34" s="2" t="inlineStr"/>
-      <c r="D34" s="2" t="inlineStr"/>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr"/>
+      <c r="C34" s="10" t="inlineStr"/>
+      <c r="D34" s="10" t="inlineStr"/>
+      <c r="E34" s="10" t="inlineStr"/>
+      <c r="F34" s="10" t="inlineStr"/>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr"/>
+      <c r="I34" s="10" t="inlineStr"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>Merseyside - Liverpool</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr"/>
-      <c r="C35" s="5" t="n">
+      <c r="B35" s="12" t="inlineStr"/>
+      <c r="C35" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="n">
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H35" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I35" s="13" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>Merseyside - Sefton</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="n">
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t>Merseyside - St Helens &amp; Knowsley</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H37" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I37" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>Merseyside - Wirral</t>
         </is>
       </c>
-      <c r="B38" s="3" t="n">
+      <c r="B38" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="C38" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="n">
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I38" s="11" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
         <is>
           <t>Norfolk</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr"/>
-      <c r="C39" s="5" t="n">
+      <c r="B39" s="12" t="inlineStr"/>
+      <c r="C39" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr"/>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I39" s="5" t="n">
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr"/>
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H39" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I39" s="13" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>North East</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr"/>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr"/>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="n">
+      <c r="B40" s="10" t="inlineStr"/>
+      <c r="C40" s="10" t="inlineStr"/>
+      <c r="D40" s="10" t="inlineStr"/>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="inlineStr"/>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="n">
         <v>75</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="12" t="inlineStr">
         <is>
           <t>North Scotland</t>
         </is>
       </c>
-      <c r="B41" s="5" t="n">
+      <c r="B41" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C41" s="5" t="n">
+      <c r="C41" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I41" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>North Wales - East</t>
         </is>
       </c>
-      <c r="B42" s="3" t="n">
+      <c r="B42" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="C42" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="n">
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H42" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I42" s="11" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="12" t="inlineStr">
         <is>
           <t>North Wales - West</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="n">
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I43" s="5" t="n">
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H43" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I43" s="13" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>Northamptonshire</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr"/>
-      <c r="C44" s="3" t="n">
+      <c r="B44" s="10" t="inlineStr"/>
+      <c r="C44" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="n">
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I44" s="11" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="12" t="inlineStr">
         <is>
           <t>Northern Ireland - East</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr"/>
-      <c r="C45" s="5" t="n">
+      <c r="B45" s="12" t="inlineStr"/>
+      <c r="C45" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G45" s="4" t="inlineStr"/>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I45" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="12" t="inlineStr"/>
+      <c r="H45" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I45" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>Northern Ireland - West</t>
         </is>
       </c>
-      <c r="B46" s="3" t="n">
+      <c r="B46" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="n">
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H46" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I46" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="12" t="inlineStr">
         <is>
           <t>Nottinghamshire</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr"/>
-      <c r="C47" s="5" t="n">
+      <c r="B47" s="12" t="inlineStr"/>
+      <c r="C47" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G47" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H47" s="4" t="inlineStr"/>
-      <c r="I47" s="5" t="n">
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H47" s="12" t="inlineStr"/>
+      <c r="I47" s="13" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>Oxfordshire</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr"/>
-      <c r="C48" s="2" t="inlineStr"/>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="n">
+      <c r="B48" s="10" t="inlineStr"/>
+      <c r="C48" s="10" t="inlineStr"/>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H48" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I48" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="12" t="inlineStr">
         <is>
           <t>Rutland</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G49" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H49" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I49" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H49" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I49" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="10" t="inlineStr">
         <is>
           <t>Scotland - Borders</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F50" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H50" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="12" t="inlineStr">
         <is>
           <t>Scotland Central - Edinburgh &amp; Lothians</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr"/>
-      <c r="C51" s="5" t="n">
+      <c r="B51" s="12" t="inlineStr"/>
+      <c r="C51" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G51" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I51" s="5" t="n">
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E51" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H51" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I51" s="13" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>Scotland Central - Falkirk &amp; Stirling</t>
         </is>
       </c>
-      <c r="B52" s="3" t="n">
+      <c r="B52" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="C52" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I52" s="3" t="n">
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F52" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G52" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H52" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I52" s="11" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="12" t="inlineStr">
         <is>
           <t>Scotland Central - Fife</t>
         </is>
       </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="n">
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C53" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G53" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H53" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I53" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E53" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G53" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H53" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I53" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>Scotland Central - Tayside</t>
         </is>
       </c>
-      <c r="B54" s="3" t="n">
+      <c r="B54" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E54" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F54" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G54" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H54" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I54" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="12" t="inlineStr">
         <is>
           <t>Scotland West - Ayrshire</t>
         </is>
       </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G55" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I55" s="5" t="n">
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G55" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H55" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I55" s="13" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>Scotland West - Glasgow</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr"/>
-      <c r="C56" s="3" t="n">
+      <c r="B56" s="10" t="inlineStr"/>
+      <c r="C56" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I56" s="3" t="n">
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E56" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F56" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G56" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H56" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I56" s="11" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="12" t="inlineStr">
         <is>
           <t>Scotland West - Lanarkshire</t>
         </is>
       </c>
-      <c r="B57" s="5" t="n">
+      <c r="B57" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G57" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H57" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I57" s="5" t="n">
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E57" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F57" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G57" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H57" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I57" s="13" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="10" t="inlineStr">
         <is>
           <t>Scotland West - Renfrewshire &amp; Inverclyde</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="n">
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I58" s="3" t="n">
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E58" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F58" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G58" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H58" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I58" s="11" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="12" t="inlineStr">
         <is>
           <t>Shropshire</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr"/>
-      <c r="C59" s="5" t="n">
+      <c r="B59" s="12" t="inlineStr"/>
+      <c r="C59" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G59" s="4" t="inlineStr"/>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I59" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E59" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F59" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G59" s="12" t="inlineStr"/>
+      <c r="H59" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I59" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="10" t="inlineStr">
         <is>
           <t>Somerset</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr"/>
-      <c r="C60" s="3" t="n">
+      <c r="B60" s="10" t="inlineStr"/>
+      <c r="C60" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I60" s="3" t="n">
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E60" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F60" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G60" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H60" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I60" s="11" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="12" t="inlineStr">
         <is>
           <t>Staffordshire</t>
         </is>
       </c>
-      <c r="B61" s="4" t="inlineStr"/>
-      <c r="C61" s="5" t="n">
+      <c r="B61" s="12" t="inlineStr"/>
+      <c r="C61" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G61" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H61" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I61" s="4" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="D61" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E61" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F61" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G61" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H61" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I61" s="12" t="inlineStr"/>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="10" t="inlineStr">
         <is>
           <t>Suffolk</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr"/>
-      <c r="C62" s="3" t="n">
+      <c r="B62" s="10" t="inlineStr"/>
+      <c r="C62" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr"/>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E62" s="10" t="inlineStr"/>
+      <c r="F62" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G62" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H62" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I62" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="12" t="inlineStr">
         <is>
           <t>Surrey</t>
         </is>
       </c>
-      <c r="B63" s="4" t="inlineStr"/>
-      <c r="C63" s="4" t="inlineStr"/>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr"/>
-      <c r="G63" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H63" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I63" s="4" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="B63" s="12" t="inlineStr"/>
+      <c r="C63" s="12" t="inlineStr"/>
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E63" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F63" s="12" t="inlineStr"/>
+      <c r="G63" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H63" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I63" s="12" t="inlineStr"/>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="10" t="inlineStr">
         <is>
           <t>Sussex</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr"/>
-      <c r="C64" s="2" t="inlineStr"/>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I64" s="3" t="n">
+      <c r="B64" s="10" t="inlineStr"/>
+      <c r="C64" s="10" t="inlineStr"/>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F64" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G64" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H64" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I64" s="11" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="12" t="inlineStr">
         <is>
           <t>Wales - Mid</t>
         </is>
       </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G65" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I65" s="5" t="n">
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E65" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F65" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G65" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H65" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I65" s="13" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="10" t="inlineStr">
         <is>
           <t>Wales - West</t>
         </is>
       </c>
-      <c r="B66" s="3" t="n">
+      <c r="B66" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C66" s="3" t="n">
+      <c r="C66" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F66" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G66" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H66" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I66" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="12" t="inlineStr">
         <is>
           <t>Wales South - Cardiff &amp; Vale</t>
         </is>
       </c>
-      <c r="B67" s="5" t="n">
+      <c r="B67" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C67" s="5" t="n">
+      <c r="C67" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D67" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I67" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E67" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F67" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G67" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H67" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I67" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="10" t="inlineStr">
         <is>
           <t>Wales South - Gwent</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E68" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F68" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G68" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H68" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I68" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="12" t="inlineStr">
         <is>
           <t>Wales South - Swansea Bay</t>
         </is>
       </c>
-      <c r="B69" s="5" t="n">
+      <c r="B69" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C69" s="5" t="n">
+      <c r="C69" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G69" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H69" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I69" s="5" t="n">
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F69" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I69" s="13" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="10" t="inlineStr">
         <is>
           <t>Wales South - Valleys</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="n">
+      <c r="B70" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C70" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I70" s="3" t="n">
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="11" t="n">
         <v>19</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="12" t="inlineStr">
         <is>
           <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
-      <c r="B71" s="4" t="inlineStr"/>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr"/>
-      <c r="G71" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="4" t="inlineStr"/>
-      <c r="I71" s="5" t="n">
+      <c r="B71" s="12" t="inlineStr"/>
+      <c r="C71" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="12" t="inlineStr"/>
+      <c r="G71" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="12" t="inlineStr"/>
+      <c r="I71" s="13" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="10" t="inlineStr">
         <is>
           <t>West Midlands - Black Country</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr"/>
-      <c r="C72" s="3" t="n">
+      <c r="B72" s="10" t="inlineStr"/>
+      <c r="C72" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="4" t="inlineStr">
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="12" t="inlineStr">
         <is>
           <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
-      <c r="B73" s="4" t="inlineStr"/>
-      <c r="C73" s="5" t="n">
+      <c r="B73" s="12" t="inlineStr"/>
+      <c r="C73" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I73" s="5" t="n">
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="13" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="10" t="inlineStr">
         <is>
           <t>Wiltshire</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr"/>
-      <c r="C74" s="2" t="inlineStr"/>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="3" t="n">
+      <c r="B74" s="10" t="inlineStr"/>
+      <c r="C74" s="10" t="inlineStr"/>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="11" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="4" t="inlineStr">
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="12" t="inlineStr">
         <is>
           <t>Worcestershire</t>
         </is>
       </c>
-      <c r="B75" s="4" t="inlineStr"/>
-      <c r="C75" s="5" t="n">
+      <c r="B75" s="12" t="inlineStr"/>
+      <c r="C75" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="D75" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G75" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H75" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I75" s="5" t="n">
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E75" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F75" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H75" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I75" s="13" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="10" t="inlineStr">
         <is>
           <t>Yorkshire - East</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr"/>
-      <c r="C76" s="3" t="n">
+      <c r="B76" s="10" t="inlineStr"/>
+      <c r="C76" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I76" s="3" t="n">
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F76" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H76" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I76" s="11" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="4" t="inlineStr">
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="12" t="inlineStr">
         <is>
           <t>Yorkshire - North</t>
         </is>
       </c>
-      <c r="B77" s="4" t="inlineStr"/>
-      <c r="C77" s="5" t="n">
+      <c r="B77" s="12" t="inlineStr"/>
+      <c r="C77" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="D77" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G77" s="4" t="inlineStr"/>
-      <c r="H77" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I77" s="5" t="n">
+      <c r="D77" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E77" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="12" t="inlineStr"/>
+      <c r="H77" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I77" s="13" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="10" t="inlineStr">
         <is>
           <t>Yorkshire - South</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr"/>
-      <c r="C78" s="2" t="inlineStr"/>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I78" s="3" t="n">
+      <c r="B78" s="10" t="inlineStr"/>
+      <c r="C78" s="10" t="inlineStr"/>
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="11" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="4" t="inlineStr">
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="12" t="inlineStr">
         <is>
           <t>Yorkshire - West</t>
         </is>
       </c>
-      <c r="B79" s="4" t="inlineStr"/>
-      <c r="C79" s="4" t="inlineStr"/>
-      <c r="D79" s="4" t="inlineStr"/>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="4" t="inlineStr"/>
-      <c r="H79" s="4" t="inlineStr"/>
-      <c r="I79" s="5" t="n">
+      <c r="B79" s="12" t="inlineStr"/>
+      <c r="C79" s="12" t="inlineStr"/>
+      <c r="D79" s="12" t="inlineStr"/>
+      <c r="E79" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="12" t="inlineStr"/>
+      <c r="H79" s="12" t="inlineStr"/>
+      <c r="I79" s="13" t="n">
         <v>5</v>
       </c>
     </row>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sitewide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="JobG8 categories" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="LIVE" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="NOT LIVE" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sitewide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JobG8 categories" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LIVE" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NOT LIVE" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sitewide'!$A$1:$B$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'JobG8 categories'!$A$1:$C$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'JobG8 categories'!$A$1:$C$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'LIVE'!$A$1:$I$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOT LIVE'!$A$1:$I$79</definedName>
   </definedNames>
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -104,6 +104,9 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -116,14 +119,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -516,7 +513,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1671</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="3">
@@ -536,7 +533,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5">
@@ -546,7 +543,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1722</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="6">
@@ -601,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -635,7 +632,9 @@
       <c r="B2" s="3" t="n">
         <v>2547</v>
       </c>
-      <c r="C2" s="7" t="inlineStr"/>
+      <c r="C2" s="7" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -646,7 +645,9 @@
       <c r="B3" s="5" t="n">
         <v>920</v>
       </c>
-      <c r="C3" s="7" t="inlineStr"/>
+      <c r="C3" s="7" t="n">
+        <v>511</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -657,7 +658,9 @@
       <c r="B4" s="3" t="n">
         <v>669</v>
       </c>
-      <c r="C4" s="7" t="inlineStr"/>
+      <c r="C4" s="7" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -668,7 +671,9 @@
       <c r="B5" s="5" t="n">
         <v>267</v>
       </c>
-      <c r="C5" s="7" t="inlineStr"/>
+      <c r="C5" s="7" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -679,7 +684,9 @@
       <c r="B6" s="3" t="n">
         <v>125</v>
       </c>
-      <c r="C6" s="7" t="inlineStr"/>
+      <c r="C6" s="7" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -690,7 +697,9 @@
       <c r="B7" s="5" t="n">
         <v>116</v>
       </c>
-      <c r="C7" s="7" t="inlineStr"/>
+      <c r="C7" s="7" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -701,7 +710,9 @@
       <c r="B8" s="3" t="n">
         <v>108</v>
       </c>
-      <c r="C8" s="7" t="inlineStr"/>
+      <c r="C8" s="7" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -712,7 +723,9 @@
       <c r="B9" s="5" t="n">
         <v>107</v>
       </c>
-      <c r="C9" s="7" t="inlineStr"/>
+      <c r="C9" s="7" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -723,7 +736,9 @@
       <c r="B10" s="3" t="n">
         <v>101</v>
       </c>
-      <c r="C10" s="7" t="inlineStr"/>
+      <c r="C10" s="7" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -734,7 +749,9 @@
       <c r="B11" s="5" t="n">
         <v>99</v>
       </c>
-      <c r="C11" s="7" t="inlineStr"/>
+      <c r="C11" s="7" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -745,7 +762,9 @@
       <c r="B12" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="C12" s="7" t="inlineStr"/>
+      <c r="C12" s="7" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -756,7 +775,9 @@
       <c r="B13" s="5" t="n">
         <v>83</v>
       </c>
-      <c r="C13" s="7" t="inlineStr"/>
+      <c r="C13" s="7" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -767,7 +788,9 @@
       <c r="B14" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="C14" s="7" t="inlineStr"/>
+      <c r="C14" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -778,7 +801,7 @@
       <c r="B15" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="C15" s="7" t="inlineStr"/>
+      <c r="C15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -789,7 +812,7 @@
       <c r="B16" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="C16" s="7" t="inlineStr"/>
+      <c r="C16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -800,21 +823,36 @@
       <c r="B17" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="C17" s="7" t="inlineStr"/>
+      <c r="C17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>Total JobG8 jobs received</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="n">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Published JobG8 ID absent from current feed</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Total Ontap JobG8 jobs published today</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n">
         <v>5354</v>
       </c>
-      <c r="C18" s="8" t="inlineStr"/>
+      <c r="C19" s="10" t="n">
+        <v>1308</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C18"/>
+  <autoFilter ref="A1:C19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1571,7 +1609,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>1</v>
@@ -2338,44 +2376,46 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>Bedfordshire</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr"/>
-      <c r="C2" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G2" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H2" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I2" s="11" t="n">
-        <v>2</v>
+      <c r="B2" s="11" t="inlineStr"/>
+      <c r="C2" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/11</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>2 / 2.2 / 0/11</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>4 / 3.8 / 0/9</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>1 / 1.1 / 0/9</t>
+        </is>
+      </c>
+      <c r="G2" s="11" t="inlineStr">
+        <is>
+          <t>1 / 0.7 / 0/6</t>
+        </is>
+      </c>
+      <c r="H2" s="11" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="I2" s="11" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
@@ -2385,59 +2425,67 @@
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr"/>
-      <c r="C3" s="13" t="n">
-        <v>2</v>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>0 / 3.5 / 3/11</t>
+        </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7 / 1.7 / 1/11</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 0.7 / 0/9</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr"/>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 0.5 / 0/6</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr"/>
-      <c r="I3" s="13" t="n">
-        <v>7</v>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>1 / 0.2 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Bristol &amp; Bath</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr"/>
-      <c r="C4" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" s="10" t="inlineStr"/>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="10" t="inlineStr"/>
-      <c r="H4" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I4" s="11" t="n">
-        <v>1</v>
+      <c r="B4" s="11" t="inlineStr"/>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr"/>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>3 / 2.9 / 1/9</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>7 / 2.6 / 1/9</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr"/>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>2 / 1.8 / 0/8</t>
+        </is>
+      </c>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
+          <t>5 / 2.0 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -2447,71 +2495,79 @@
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr"/>
-      <c r="C5" s="13" t="n">
-        <v>2</v>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>0 / 0.7 / 0/11</t>
+        </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.6 / 0/11</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.0 / 0/9</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr"/>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 2.0 / 0/6</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I5" s="13" t="n">
-        <v>4</v>
+          <t>1 / 0.8 / 0/8</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>6 / 2.4 / 1/5</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Cambridgeshire</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr"/>
-      <c r="C6" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I6" s="11" t="n">
-        <v>2</v>
+      <c r="B6" s="11" t="inlineStr"/>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/11</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>3 / 2.5 / 0/11</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>1 / 1.2 / 0/9</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>6 / 2.6 / 1/9</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>3 / 4.5 / 2/6</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/8</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -2521,77 +2577,83 @@
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr"/>
-      <c r="C7" s="13" t="n">
-        <v>0</v>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>0 / 0.6 / 0/11</t>
+        </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 1.5 / 0/11</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.2 / 0/9</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 1.0 / 0/9</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I7" s="13" t="n">
-        <v>2</v>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>3 / 1.8 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Cheshire - Warrington &amp; Halton</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr"/>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I8" s="11" t="n">
-        <v>1</v>
+      <c r="B8" s="11" t="inlineStr"/>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>1 / 1.4 / 0/11</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>6 / 2.1 / 1/11</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>2 / 1.3 / 0/9</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>1 / 0.3 / 0/9</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>7 / 4.7 / 2/6</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/8</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -2601,75 +2663,83 @@
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr"/>
-      <c r="C9" s="13" t="n">
-        <v>1</v>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>0 / 1.5 / 0/11</t>
+        </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 2.0 / 0/11</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 1.0 / 0/9</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6 / 2.2 / 1/9</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 2.2 / 0/6</t>
         </is>
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I9" s="13" t="n">
-        <v>1</v>
+          <t>1 / 0.2 / 0/8</t>
+        </is>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>1 / 0.2 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Cornwall</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr"/>
-      <c r="C10" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I10" s="11" t="n">
-        <v>55</v>
+      <c r="B10" s="11" t="inlineStr"/>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>0 / 1.5 / 0/11</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>1 / 0.5 / 0/11</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/9</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/9</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.3 / 0/6</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -2678,81 +2748,87 @@
           <t>Cumbria - North</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="13" t="n">
-        <v>2</v>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>1 / 1.6 / 0/11</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>0 / 2.8 / 3/11</t>
+        </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.2 / 0/6</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
       <c r="I11" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Cumbria - South</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="10" t="inlineStr"/>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I12" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>1 / 1.1 / 0/11</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr"/>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>1 / 0.7 / 0/11</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/9</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>2 / 0.6 / 0/9</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.7 / 0/6</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>1 / 0.1 / 0/8</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
@@ -2764,78 +2840,86 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="n">
-        <v>2</v>
+          <t>1 / 1.8 / 0/11</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>1 / 0.8 / 0/11</t>
+        </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.5 / 0/6</t>
         </is>
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I13" s="13" t="n">
-        <v>1</v>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Derbyshire</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr"/>
-      <c r="C14" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I14" s="11" t="n">
-        <v>1</v>
+      <c r="B14" s="11" t="inlineStr"/>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.4 / 0/11</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>3 / 2.5 / 0/11</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>2 / 0.6 / 0/9</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>2 / 0.9 / 0/9</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>2 / 3.2 / 0/6</t>
+        </is>
+      </c>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="I14" s="11" t="inlineStr">
+        <is>
+          <t>3 / 1.4 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -2845,73 +2929,79 @@
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr"/>
-      <c r="C15" s="13" t="n">
-        <v>1</v>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/11</t>
+        </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5 / 3.2 / 0/11</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 2.1 / 0/9</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6 / 1.2 / 1/9</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr"/>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 1.1 / 0/8</t>
         </is>
       </c>
       <c r="I15" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 1.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>Dorset</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr"/>
-      <c r="C16" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H16" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I16" s="11" t="n">
-        <v>3</v>
+      <c r="B16" s="11" t="inlineStr"/>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>5 / 3.9 / 2/11</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/9</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>3 / 1.4 / 0/9</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>1 / 3.2 / 0/6</t>
+        </is>
+      </c>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="I16" s="11" t="inlineStr">
+        <is>
+          <t>1 / 0.2 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -2923,68 +3013,72 @@
       <c r="B17" s="12" t="inlineStr"/>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.7 / 0/11</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5 / 2.1 / 0/11</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr"/>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6 / 2.8 / 1/9</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4 / 5.7 / 2/6</t>
         </is>
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I17" s="13" t="n">
-        <v>3</v>
+          <t>1 / 1.1 / 0/8</t>
+        </is>
+      </c>
+      <c r="I17" s="12" t="inlineStr">
+        <is>
+          <t>4 / 2.0 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Gloucestershire</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr"/>
-      <c r="C18" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G18" s="10" t="inlineStr"/>
-      <c r="H18" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B18" s="11" t="inlineStr"/>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/11</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>4 / 1.4 / 0/11</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/9</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>8 / 2.9 / 1/9</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr"/>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>2 / 1.2 / 0/8</t>
+        </is>
+      </c>
+      <c r="I18" s="11" t="inlineStr">
+        <is>
+          <t>3 / 1.6 / 0/5</t>
         </is>
       </c>
     </row>
@@ -2995,67 +3089,75 @@
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr"/>
-      <c r="C19" s="13" t="n">
-        <v>2</v>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>2 / 1.3 / 0/11</t>
+        </is>
       </c>
       <c r="D19" s="12" t="inlineStr"/>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 3.9 / 2/9</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr"/>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 3.7 / 0/6</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr"/>
-      <c r="I19" s="13" t="n">
-        <v>8</v>
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>3 / 2.2 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Greater Manchester - North</t>
         </is>
       </c>
-      <c r="B20" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E20" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H20" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I20" s="11" t="n">
-        <v>4</v>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>3 / 3.1 / 1/11</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/11</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/9</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/9</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/6</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/8</t>
+        </is>
+      </c>
+      <c r="I20" s="11" t="inlineStr">
+        <is>
+          <t>1 / 0.2 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -3065,75 +3167,83 @@
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr"/>
-      <c r="C21" s="13" t="n">
-        <v>1</v>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>0 / 0.8 / 0/11</t>
+        </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.7 / 0/11</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.4 / 0/9</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 0.2 / 0/9</t>
         </is>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I21" s="13" t="n">
-        <v>5</v>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="I21" s="12" t="inlineStr">
+        <is>
+          <t>3 / 0.6 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>Greater Manchester - Wigan &amp; Bolton</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr"/>
-      <c r="C22" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E22" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F22" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I22" s="11" t="n">
-        <v>2</v>
+      <c r="B22" s="11" t="inlineStr"/>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>1 / 0.7 / 0/11</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>1 / 0.3 / 0/9</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/9</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.3 / 0/6</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -3146,73 +3256,75 @@
       <c r="C23" s="12" t="inlineStr"/>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14 / 7.4 / 7/11</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 1.7 / 0/9</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10 / 5.0 / 2/9</t>
         </is>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 2.8 / 0/6</t>
         </is>
       </c>
       <c r="H23" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4 / 3.5 / 0/8</t>
         </is>
       </c>
       <c r="I23" s="12" t="inlineStr"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>Herefordshire</t>
         </is>
       </c>
-      <c r="B24" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E24" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G24" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H24" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I24" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>0 / 1.4 / 0/11</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/11</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>1 / 0.1 / 0/9</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/9</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>0 / 1.2 / 0/6</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="I24" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
@@ -3223,73 +3335,79 @@
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr"/>
-      <c r="C25" s="13" t="n">
-        <v>1</v>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>3 / 2.3 / 0/11</t>
+        </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10 / 4.0 / 1/11</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.6 / 0/9</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9 / 2.1 / 1/9</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.0 / 0/6</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I25" s="13" t="n">
-        <v>5</v>
+          <t>1 / 0.2 / 0/8</t>
+        </is>
+      </c>
+      <c r="I25" s="12" t="inlineStr">
+        <is>
+          <t>4 / 1.6 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>Kent</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr"/>
-      <c r="C26" s="10" t="inlineStr"/>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E26" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H26" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I26" s="11" t="n">
-        <v>4</v>
+      <c r="B26" s="11" t="inlineStr"/>
+      <c r="C26" s="11" t="inlineStr"/>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>8 / 4.5 / 1/11</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>3 / 4.3 / 2/9</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>7 / 2.8 / 1/9</t>
+        </is>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>1 / 3.2 / 1/6</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>2 / 1.6 / 0/8</t>
+        </is>
+      </c>
+      <c r="I26" s="11" t="inlineStr">
+        <is>
+          <t>2 / 0.8 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
@@ -3298,84 +3416,92 @@
           <t>Lancashire - Blackpool &amp; Fylde</t>
         </is>
       </c>
-      <c r="B27" s="13" t="n">
-        <v>0</v>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>1 / 0.8 / 0/11</t>
+        </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 0.9 / 0/9</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.3 / 0/6</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
       <c r="I27" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>Lancashire - Central</t>
         </is>
       </c>
-      <c r="B28" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E28" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F28" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G28" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H28" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I28" s="11" t="n">
-        <v>1</v>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>3 / 2.8 / 0/11</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/11</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>1 / 0.3 / 0/11</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/9</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/9</t>
+        </is>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>1 / 0.5 / 0/6</t>
+        </is>
+      </c>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/8</t>
+        </is>
+      </c>
+      <c r="I28" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -3384,85 +3510,91 @@
           <t>Lancashire - East</t>
         </is>
       </c>
-      <c r="B29" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" s="13" t="n">
-        <v>3</v>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>3 / 2.5 / 0/11</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>0 / 0.7 / 0/11</t>
+        </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.3 / 0/11</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.2 / 0/9</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 1.1 / 0/9</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.2 / 0/6</t>
         </is>
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
       <c r="I29" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>Lancashire - North</t>
         </is>
       </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="D30" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E30" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G30" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I30" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>0 / 1.2 / 0/11</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/9</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/9</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/6</t>
+        </is>
+      </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="I30" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
@@ -3474,82 +3606,86 @@
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 1.3 / 0/10</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.1 / 0/10</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.2 / 0/10</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>Leicestershire</t>
         </is>
       </c>
-      <c r="B32" s="10" t="inlineStr"/>
-      <c r="C32" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E32" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F32" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G32" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H32" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I32" s="11" t="n">
-        <v>5</v>
+      <c r="B32" s="11" t="inlineStr"/>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/11</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>3 / 1.6 / 0/11</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>2 / 1.3 / 0/9</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>1 / 0.9 / 0/9</t>
+        </is>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>2 / 3.0 / 1/6</t>
+        </is>
+      </c>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>2 / 0.9 / 0/8</t>
+        </is>
+      </c>
+      <c r="I32" s="11" t="inlineStr">
+        <is>
+          <t>3 / 3.0 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
@@ -3559,56 +3695,60 @@
         </is>
       </c>
       <c r="B33" s="12" t="inlineStr"/>
-      <c r="C33" s="13" t="n">
-        <v>2</v>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>0 / 1.7 / 0/11</t>
+        </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4 / 1.2 / 0/11</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 1.6 / 0/9</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 2.7 / 0/9</t>
         </is>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 2.8 / 0/6</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I33" s="13" t="n">
-        <v>2</v>
+          <t>1 / 1.4 / 0/8</t>
+        </is>
+      </c>
+      <c r="I33" s="12" t="inlineStr">
+        <is>
+          <t>2 / 1.0 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>London</t>
         </is>
       </c>
-      <c r="B34" s="10" t="inlineStr"/>
-      <c r="C34" s="10" t="inlineStr"/>
-      <c r="D34" s="10" t="inlineStr"/>
-      <c r="E34" s="10" t="inlineStr"/>
-      <c r="F34" s="10" t="inlineStr"/>
-      <c r="G34" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H34" s="10" t="inlineStr"/>
-      <c r="I34" s="10" t="inlineStr"/>
+      <c r="B34" s="11" t="inlineStr"/>
+      <c r="C34" s="11" t="inlineStr"/>
+      <c r="D34" s="11" t="inlineStr"/>
+      <c r="E34" s="11" t="inlineStr"/>
+      <c r="F34" s="11" t="inlineStr"/>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>10 / 5.2 / 2/6</t>
+        </is>
+      </c>
+      <c r="H34" s="11" t="inlineStr"/>
+      <c r="I34" s="11" t="inlineStr"/>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="12" t="inlineStr">
@@ -3617,80 +3757,86 @@
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr"/>
-      <c r="C35" s="13" t="n">
-        <v>2</v>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>0 / 0.4 / 0/11</t>
+        </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.3 / 0/11</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.4 / 0/9</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6 / 2.0 / 1/9</t>
         </is>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.5 / 0/6</t>
         </is>
       </c>
       <c r="H35" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I35" s="13" t="n">
-        <v>0</v>
+          <t>0 / 0.1 / 0/8</t>
+        </is>
+      </c>
+      <c r="I35" s="12" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>Merseyside - Sefton</t>
         </is>
       </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C36" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E36" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F36" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G36" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H36" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I36" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/10</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/9</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/9</t>
+        </is>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/6</t>
+        </is>
+      </c>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="I36" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
@@ -3702,84 +3848,90 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 2.0 / 0/10</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.8 / 0/10</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.7 / 0/6</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
       <c r="I37" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>Merseyside - Wirral</t>
         </is>
       </c>
-      <c r="B38" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E38" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F38" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G38" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H38" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I38" s="11" t="n">
-        <v>2</v>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>1 / 1.5 / 0/11</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.5 / 0/11</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>1 / 0.3 / 0/9</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr">
+        <is>
+          <t>3 / 0.6 / 0/9</t>
+        </is>
+      </c>
+      <c r="G38" s="11" t="inlineStr">
+        <is>
+          <t>1 / 0.2 / 0/6</t>
+        </is>
+      </c>
+      <c r="H38" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="I38" s="11" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
@@ -3789,61 +3941,67 @@
         </is>
       </c>
       <c r="B39" s="12" t="inlineStr"/>
-      <c r="C39" s="13" t="n">
-        <v>2</v>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>0 / 1.1 / 0/11</t>
+        </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.7 / 0/11</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr"/>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 1.6 / 0/9</t>
         </is>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 4.2 / 2/6</t>
         </is>
       </c>
       <c r="H39" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I39" s="13" t="n">
-        <v>3</v>
+          <t>0 / 0.2 / 0/8</t>
+        </is>
+      </c>
+      <c r="I39" s="12" t="inlineStr">
+        <is>
+          <t>1 / 0.8 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>North East</t>
         </is>
       </c>
-      <c r="B40" s="10" t="inlineStr"/>
-      <c r="C40" s="10" t="inlineStr"/>
-      <c r="D40" s="10" t="inlineStr"/>
-      <c r="E40" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F40" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G40" s="10" t="inlineStr"/>
-      <c r="H40" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I40" s="11" t="n">
-        <v>75</v>
+      <c r="B40" s="11" t="inlineStr"/>
+      <c r="C40" s="11" t="inlineStr"/>
+      <c r="D40" s="11" t="inlineStr"/>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.9 / 0/9</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>6 / 4.1 / 1/9</t>
+        </is>
+      </c>
+      <c r="G40" s="11" t="inlineStr"/>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>1 / 1.1 / 0/8</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="inlineStr">
+        <is>
+          <t>4 / 2.4 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
@@ -3852,82 +4010,92 @@
           <t>North Scotland</t>
         </is>
       </c>
-      <c r="B41" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" s="13" t="n">
-        <v>0</v>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>6 / 5.6 / 4/10</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6 / 3.0 / 1/10</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.2 / 0/9</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.5 / 0/6</t>
         </is>
       </c>
       <c r="H41" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
       <c r="I41" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>North Wales - East</t>
         </is>
       </c>
-      <c r="B42" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C42" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E42" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F42" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G42" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H42" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I42" s="11" t="n">
-        <v>2</v>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>5 / 4.5 / 1/10</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/10</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>1 / 1.3 / 0/10</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/9</t>
+        </is>
+      </c>
+      <c r="F42" s="11" t="inlineStr">
+        <is>
+          <t>1 / 0.4 / 0/9</t>
+        </is>
+      </c>
+      <c r="G42" s="11" t="inlineStr">
+        <is>
+          <t>1 / 1.5 / 0/6</t>
+        </is>
+      </c>
+      <c r="H42" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="I42" s="11" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
@@ -3938,78 +4106,86 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C43" s="13" t="n">
-        <v>0</v>
+          <t>3 / 1.8 / 0/10</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I43" s="13" t="n">
-        <v>0</v>
+          <t>1 / 0.2 / 0/8</t>
+        </is>
+      </c>
+      <c r="I43" s="12" t="inlineStr">
+        <is>
+          <t>1 / 0.4 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>Northamptonshire</t>
         </is>
       </c>
-      <c r="B44" s="10" t="inlineStr"/>
-      <c r="C44" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E44" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F44" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G44" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H44" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I44" s="11" t="n">
-        <v>4</v>
+      <c r="B44" s="11" t="inlineStr"/>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>11 / 3.6 / 1/11</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>1 / 1.3 / 0/9</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t>6 / 2.2 / 1/9</t>
+        </is>
+      </c>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>2 / 3.3 / 2/6</t>
+        </is>
+      </c>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>3 / 2.5 / 1/8</t>
+        </is>
+      </c>
+      <c r="I44" s="11" t="inlineStr">
+        <is>
+          <t>1 / 0.2 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
@@ -4019,77 +4195,83 @@
         </is>
       </c>
       <c r="B45" s="12" t="inlineStr"/>
-      <c r="C45" s="13" t="n">
-        <v>1</v>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>1 / 1.8 / 0/10</t>
+        </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.2 / 0/9</t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="G45" s="12" t="inlineStr"/>
       <c r="H45" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.1 / 0/8</t>
         </is>
       </c>
       <c r="I45" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="10" t="inlineStr">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>Northern Ireland - West</t>
         </is>
       </c>
-      <c r="B46" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C46" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D46" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E46" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F46" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G46" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H46" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I46" s="11" t="n">
-        <v>1</v>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>4 / 4.1 / 0/10</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>3 / 1.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="E46" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/9</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/9</t>
+        </is>
+      </c>
+      <c r="G46" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/6</t>
+        </is>
+      </c>
+      <c r="H46" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="I46" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
@@ -4099,69 +4281,75 @@
         </is>
       </c>
       <c r="B47" s="12" t="inlineStr"/>
-      <c r="C47" s="13" t="n">
-        <v>1</v>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>1 / 0.5 / 0/11</t>
+        </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 1.8 / 0/11</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 2.1 / 0/9</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4 / 2.0 / 0/9</t>
         </is>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 3.7 / 2/6</t>
         </is>
       </c>
       <c r="H47" s="12" t="inlineStr"/>
-      <c r="I47" s="13" t="n">
-        <v>3</v>
+      <c r="I47" s="12" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="10" t="inlineStr">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>Oxfordshire</t>
         </is>
       </c>
-      <c r="B48" s="10" t="inlineStr"/>
-      <c r="C48" s="10" t="inlineStr"/>
-      <c r="D48" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E48" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F48" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G48" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H48" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I48" s="11" t="n">
-        <v>1</v>
+      <c r="B48" s="11" t="inlineStr"/>
+      <c r="C48" s="11" t="inlineStr"/>
+      <c r="D48" s="11" t="inlineStr">
+        <is>
+          <t>5 / 3.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>2 / 1.7 / 0/9</t>
+        </is>
+      </c>
+      <c r="F48" s="11" t="inlineStr">
+        <is>
+          <t>10 / 4.6 / 2/9</t>
+        </is>
+      </c>
+      <c r="G48" s="11" t="inlineStr">
+        <is>
+          <t>1 / 2.8 / 0/6</t>
+        </is>
+      </c>
+      <c r="H48" s="11" t="inlineStr">
+        <is>
+          <t>1 / 0.2 / 0/8</t>
+        </is>
+      </c>
+      <c r="I48" s="11" t="inlineStr">
+        <is>
+          <t>3 / 0.8 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
@@ -4172,89 +4360,89 @@
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
       <c r="H49" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
       <c r="I49" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="10" t="inlineStr">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>Scotland - Borders</t>
         </is>
       </c>
-      <c r="B50" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C50" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D50" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E50" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F50" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G50" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H50" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I50" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t>2 / 1.1 / 0/10</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/9</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/9</t>
+        </is>
+      </c>
+      <c r="G50" s="11" t="inlineStr">
+        <is>
+          <t>1 / 0.2 / 0/6</t>
+        </is>
+      </c>
+      <c r="H50" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="I50" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
@@ -4265,77 +4453,87 @@
         </is>
       </c>
       <c r="B51" s="12" t="inlineStr"/>
-      <c r="C51" s="13" t="n">
-        <v>1</v>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/10</t>
+        </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4 / 2.2 / 0/10</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4 / 2.4 / 0/9</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.1 / 0/9</t>
         </is>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.2 / 0/6</t>
         </is>
       </c>
       <c r="H51" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I51" s="13" t="n">
-        <v>2</v>
+          <t>1 / 0.4 / 0/8</t>
+        </is>
+      </c>
+      <c r="I51" s="12" t="inlineStr">
+        <is>
+          <t>1 / 0.2 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="10" t="inlineStr">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>Scotland Central - Falkirk &amp; Stirling</t>
         </is>
       </c>
-      <c r="B52" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C52" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D52" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E52" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F52" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G52" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H52" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I52" s="11" t="n">
-        <v>0</v>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>2 / 2.8 / 0/10</t>
+        </is>
+      </c>
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/9</t>
+        </is>
+      </c>
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/9</t>
+        </is>
+      </c>
+      <c r="G52" s="11" t="inlineStr">
+        <is>
+          <t>1 / 1.2 / 0/6</t>
+        </is>
+      </c>
+      <c r="H52" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="I52" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
@@ -4346,85 +4544,89 @@
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C53" s="13" t="n">
-        <v>0</v>
+          <t>2 / 1.5 / 0/10</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 1.0 / 0/10</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.7 / 0/6</t>
         </is>
       </c>
       <c r="H53" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
       <c r="I53" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="10" t="inlineStr">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t>Scotland Central - Tayside</t>
         </is>
       </c>
-      <c r="B54" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="C54" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D54" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E54" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F54" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G54" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H54" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I54" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>5 / 3.8 / 0/10</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/10</t>
+        </is>
+      </c>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>1 / 1.2 / 0/9</t>
+        </is>
+      </c>
+      <c r="F54" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/9</t>
+        </is>
+      </c>
+      <c r="G54" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.7 / 0/6</t>
+        </is>
+      </c>
+      <c r="H54" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="I54" s="11" t="inlineStr">
+        <is>
+          <t>1 / 0.2 / 0/5</t>
         </is>
       </c>
     </row>
@@ -4436,80 +4638,86 @@
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.5 / 0/10</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.4 / 0/9</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
       <c r="H55" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I55" s="13" t="n">
-        <v>0</v>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="I55" s="12" t="inlineStr">
+        <is>
+          <t>1 / 0.6 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="10" t="inlineStr">
+      <c r="A56" s="11" t="inlineStr">
         <is>
           <t>Scotland West - Glasgow</t>
         </is>
       </c>
-      <c r="B56" s="10" t="inlineStr"/>
-      <c r="C56" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E56" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F56" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G56" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H56" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I56" s="11" t="n">
-        <v>0</v>
+      <c r="B56" s="11" t="inlineStr"/>
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>4 / 3.1 / 0/10</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/9</t>
+        </is>
+      </c>
+      <c r="F56" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/9</t>
+        </is>
+      </c>
+      <c r="G56" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.3 / 0/6</t>
+        </is>
+      </c>
+      <c r="H56" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.6 / 0/8</t>
+        </is>
+      </c>
+      <c r="I56" s="11" t="inlineStr">
+        <is>
+          <t>3 / 2.4 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
@@ -4518,84 +4726,92 @@
           <t>Scotland West - Lanarkshire</t>
         </is>
       </c>
-      <c r="B57" s="13" t="n">
-        <v>1</v>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>0 / 0.5 / 0/10</t>
+        </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.1 / 0/10</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.4 / 0/10</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
       <c r="H57" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I57" s="13" t="n">
-        <v>0</v>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="I57" s="12" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="10" t="inlineStr">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t>Scotland West - Renfrewshire &amp; Inverclyde</t>
         </is>
       </c>
-      <c r="B58" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C58" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E58" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F58" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G58" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H58" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I58" s="11" t="n">
-        <v>0</v>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>1 / 0.4 / 0/10</t>
+        </is>
+      </c>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/9</t>
+        </is>
+      </c>
+      <c r="F58" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/9</t>
+        </is>
+      </c>
+      <c r="G58" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.7 / 0/6</t>
+        </is>
+      </c>
+      <c r="H58" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="I58" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
@@ -4605,73 +4821,79 @@
         </is>
       </c>
       <c r="B59" s="12" t="inlineStr"/>
-      <c r="C59" s="13" t="n">
-        <v>3</v>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>0 / 1.8 / 0/11</t>
+        </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 1.1 / 0/11</t>
         </is>
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 1.7 / 0/9</t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.3 / 0/9</t>
         </is>
       </c>
       <c r="G59" s="12" t="inlineStr"/>
       <c r="H59" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 1.9 / 0/8</t>
         </is>
       </c>
       <c r="I59" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="10" t="inlineStr">
+      <c r="A60" s="11" t="inlineStr">
         <is>
           <t>Somerset</t>
         </is>
       </c>
-      <c r="B60" s="10" t="inlineStr"/>
-      <c r="C60" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="D60" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E60" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F60" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G60" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H60" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I60" s="11" t="n">
-        <v>0</v>
+      <c r="B60" s="11" t="inlineStr"/>
+      <c r="C60" s="11" t="inlineStr">
+        <is>
+          <t>1 / 3.5 / 3/11</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>2 / 1.3 / 0/11</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>1 / 0.3 / 0/9</t>
+        </is>
+      </c>
+      <c r="F60" s="11" t="inlineStr">
+        <is>
+          <t>4 / 0.6 / 0/9</t>
+        </is>
+      </c>
+      <c r="G60" s="11" t="inlineStr">
+        <is>
+          <t>2 / 3.3 / 1/6</t>
+        </is>
+      </c>
+      <c r="H60" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/8</t>
+        </is>
+      </c>
+      <c r="I60" s="11" t="inlineStr">
+        <is>
+          <t>2 / 0.4 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
@@ -4681,70 +4903,74 @@
         </is>
       </c>
       <c r="B61" s="12" t="inlineStr"/>
-      <c r="C61" s="13" t="n">
-        <v>3</v>
+      <c r="C61" s="12" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/11</t>
+        </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.4 / 0/11</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 1.2 / 0/9</t>
         </is>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 2.5 / 0/6</t>
         </is>
       </c>
       <c r="H61" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.1 / 0/8</t>
         </is>
       </c>
       <c r="I61" s="12" t="inlineStr"/>
     </row>
     <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="10" t="inlineStr">
+      <c r="A62" s="11" t="inlineStr">
         <is>
           <t>Suffolk</t>
         </is>
       </c>
-      <c r="B62" s="10" t="inlineStr"/>
-      <c r="C62" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E62" s="10" t="inlineStr"/>
-      <c r="F62" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G62" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H62" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I62" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B62" s="11" t="inlineStr"/>
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.9 / 0/11</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>3 / 1.6 / 0/11</t>
+        </is>
+      </c>
+      <c r="E62" s="11" t="inlineStr"/>
+      <c r="F62" s="11" t="inlineStr">
+        <is>
+          <t>2 / 0.3 / 0/9</t>
+        </is>
+      </c>
+      <c r="G62" s="11" t="inlineStr">
+        <is>
+          <t>1 / 1.8 / 0/6</t>
+        </is>
+      </c>
+      <c r="H62" s="11" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="I62" s="11" t="inlineStr">
+        <is>
+          <t>1 / 0.4 / 0/5</t>
         </is>
       </c>
     </row>
@@ -4758,62 +4984,64 @@
       <c r="C63" s="12" t="inlineStr"/>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6 / 4.5 / 4/11</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5 / 4.0 / 0/9</t>
         </is>
       </c>
       <c r="F63" s="12" t="inlineStr"/>
       <c r="G63" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5 / 5.2 / 2/6</t>
         </is>
       </c>
       <c r="H63" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 2.0 / 0/8</t>
         </is>
       </c>
       <c r="I63" s="12" t="inlineStr"/>
     </row>
     <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="10" t="inlineStr">
+      <c r="A64" s="11" t="inlineStr">
         <is>
           <t>Sussex</t>
         </is>
       </c>
-      <c r="B64" s="10" t="inlineStr"/>
-      <c r="C64" s="10" t="inlineStr"/>
-      <c r="D64" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E64" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F64" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G64" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H64" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I64" s="11" t="n">
-        <v>4</v>
+      <c r="B64" s="11" t="inlineStr"/>
+      <c r="C64" s="11" t="inlineStr"/>
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>7 / 3.6 / 1/11</t>
+        </is>
+      </c>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>4 / 2.0 / 0/9</t>
+        </is>
+      </c>
+      <c r="F64" s="11" t="inlineStr">
+        <is>
+          <t>5 / 2.6 / 0/9</t>
+        </is>
+      </c>
+      <c r="G64" s="11" t="inlineStr">
+        <is>
+          <t>4 / 4.2 / 0/6</t>
+        </is>
+      </c>
+      <c r="H64" s="11" t="inlineStr">
+        <is>
+          <t>6 / 5.8 / 6/8</t>
+        </is>
+      </c>
+      <c r="I64" s="11" t="inlineStr">
+        <is>
+          <t>4 / 2.8 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -4824,83 +5052,89 @@
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.1 / 0/10</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="F65" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
       <c r="H65" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I65" s="13" t="n">
-        <v>1</v>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="I65" s="12" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="10" t="inlineStr">
+      <c r="A66" s="11" t="inlineStr">
         <is>
           <t>Wales - West</t>
         </is>
       </c>
-      <c r="B66" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C66" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D66" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E66" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F66" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G66" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H66" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I66" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t>3 / 1.9 / 0/10</t>
+        </is>
+      </c>
+      <c r="C66" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/9</t>
+        </is>
+      </c>
+      <c r="F66" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/9</t>
+        </is>
+      </c>
+      <c r="G66" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.7 / 0/6</t>
+        </is>
+      </c>
+      <c r="H66" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/8</t>
+        </is>
+      </c>
+      <c r="I66" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
@@ -4910,87 +5144,91 @@
           <t>Wales South - Cardiff &amp; Vale</t>
         </is>
       </c>
-      <c r="B67" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C67" s="13" t="n">
-        <v>1</v>
+      <c r="B67" s="12" t="inlineStr">
+        <is>
+          <t>5 / 4.1 / 1/10</t>
+        </is>
+      </c>
+      <c r="C67" s="12" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 1.7 / 0/10</t>
         </is>
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 1.3 / 0/9</t>
         </is>
       </c>
       <c r="F67" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 0.9 / 0/9</t>
         </is>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 1.2 / 0/6</t>
         </is>
       </c>
       <c r="H67" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
       <c r="I67" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="10" t="inlineStr">
+      <c r="A68" s="11" t="inlineStr">
         <is>
           <t>Wales South - Gwent</t>
         </is>
       </c>
-      <c r="B68" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C68" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D68" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E68" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F68" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G68" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H68" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I68" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t>1 / 2.7 / 0/10</t>
+        </is>
+      </c>
+      <c r="C68" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/10</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="inlineStr">
+        <is>
+          <t>1 / 0.3 / 0/10</t>
+        </is>
+      </c>
+      <c r="E68" s="11" t="inlineStr">
+        <is>
+          <t>2 / 1.3 / 0/9</t>
+        </is>
+      </c>
+      <c r="F68" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/9</t>
+        </is>
+      </c>
+      <c r="G68" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.7 / 0/6</t>
+        </is>
+      </c>
+      <c r="H68" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="I68" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
@@ -5000,82 +5238,92 @@
           <t>Wales South - Swansea Bay</t>
         </is>
       </c>
-      <c r="B69" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C69" s="13" t="n">
-        <v>1</v>
+      <c r="B69" s="12" t="inlineStr">
+        <is>
+          <t>1 / 2.9 / 1/10</t>
+        </is>
+      </c>
+      <c r="C69" s="12" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/10</t>
+        </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.8 / 0/10</t>
         </is>
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.7 / 0/9</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.3 / 0/6</t>
         </is>
       </c>
       <c r="H69" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I69" s="13" t="n">
-        <v>10</v>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="I69" s="12" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="10" t="inlineStr">
+      <c r="A70" s="11" t="inlineStr">
         <is>
           <t>Wales South - Valleys</t>
         </is>
       </c>
-      <c r="B70" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C70" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I70" s="11" t="n">
-        <v>19</v>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>2 / 1.4 / 1/10</t>
+        </is>
+      </c>
+      <c r="C70" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.3 / 0/10</t>
+        </is>
+      </c>
+      <c r="E70" s="11" t="inlineStr">
+        <is>
+          <t>4 / 2.6 / 0/9</t>
+        </is>
+      </c>
+      <c r="F70" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.4 / 0/9</t>
+        </is>
+      </c>
+      <c r="G70" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/6</t>
+        </is>
+      </c>
+      <c r="H70" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="I70" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
@@ -5087,68 +5335,72 @@
       <c r="B71" s="12" t="inlineStr"/>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.0 / 0/11</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11 / 4.0 / 1/11</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 3.9 / 2/9</t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr"/>
       <c r="G71" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 2.7 / 0/6</t>
         </is>
       </c>
       <c r="H71" s="12" t="inlineStr"/>
-      <c r="I71" s="13" t="n">
-        <v>1</v>
+      <c r="I71" s="12" t="inlineStr">
+        <is>
+          <t>5 / 3.4 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="10" t="inlineStr">
+      <c r="A72" s="11" t="inlineStr">
         <is>
           <t>West Midlands - Black Country</t>
         </is>
       </c>
-      <c r="B72" s="10" t="inlineStr"/>
-      <c r="C72" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D72" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I72" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B72" s="11" t="inlineStr"/>
+      <c r="C72" s="11" t="inlineStr">
+        <is>
+          <t>1 / 1.1 / 0/11</t>
+        </is>
+      </c>
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="E72" s="11" t="inlineStr">
+        <is>
+          <t>3 / 1.1 / 0/9</t>
+        </is>
+      </c>
+      <c r="F72" s="11" t="inlineStr">
+        <is>
+          <t>1 / 0.4 / 0/9</t>
+        </is>
+      </c>
+      <c r="G72" s="11" t="inlineStr">
+        <is>
+          <t>1 / 1.3 / 0/6</t>
+        </is>
+      </c>
+      <c r="H72" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="I72" s="11" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/5</t>
         </is>
       </c>
     </row>
@@ -5159,73 +5411,79 @@
         </is>
       </c>
       <c r="B73" s="12" t="inlineStr"/>
-      <c r="C73" s="13" t="n">
-        <v>4</v>
+      <c r="C73" s="12" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6 / 1.3 / 1/11</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.6 / 0/9</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5 / 2.4 / 0/9</t>
         </is>
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 2.2 / 0/6</t>
         </is>
       </c>
       <c r="H73" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I73" s="13" t="n">
-        <v>1</v>
+          <t>3 / 3.1 / 0/8</t>
+        </is>
+      </c>
+      <c r="I73" s="12" t="inlineStr">
+        <is>
+          <t>2 / 0.4 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="10" t="inlineStr">
+      <c r="A74" s="11" t="inlineStr">
         <is>
           <t>Wiltshire</t>
         </is>
       </c>
-      <c r="B74" s="10" t="inlineStr"/>
-      <c r="C74" s="10" t="inlineStr"/>
-      <c r="D74" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="11" t="n">
-        <v>4</v>
+      <c r="B74" s="11" t="inlineStr"/>
+      <c r="C74" s="11" t="inlineStr"/>
+      <c r="D74" s="11" t="inlineStr">
+        <is>
+          <t>3 / 2.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="E74" s="11" t="inlineStr">
+        <is>
+          <t>4 / 3.0 / 0/9</t>
+        </is>
+      </c>
+      <c r="F74" s="11" t="inlineStr">
+        <is>
+          <t>3 / 1.1 / 0/9</t>
+        </is>
+      </c>
+      <c r="G74" s="11" t="inlineStr">
+        <is>
+          <t>0 / 2.7 / 0/6</t>
+        </is>
+      </c>
+      <c r="H74" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.6 / 0/8</t>
+        </is>
+      </c>
+      <c r="I74" s="11" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -5235,75 +5493,83 @@
         </is>
       </c>
       <c r="B75" s="12" t="inlineStr"/>
-      <c r="C75" s="13" t="n">
-        <v>2</v>
+      <c r="C75" s="12" t="inlineStr">
+        <is>
+          <t>0 / 1.3 / 0/11</t>
+        </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 2.1 / 0/11</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 0.4 / 0/9</t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 1.6 / 0/9</t>
         </is>
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.8 / 0/6</t>
         </is>
       </c>
       <c r="H75" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I75" s="13" t="n">
-        <v>1</v>
+          <t>0 / 0.2 / 0/8</t>
+        </is>
+      </c>
+      <c r="I75" s="12" t="inlineStr">
+        <is>
+          <t>1 / 0.4 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="10" t="inlineStr">
+      <c r="A76" s="11" t="inlineStr">
         <is>
           <t>Yorkshire - East</t>
         </is>
       </c>
-      <c r="B76" s="10" t="inlineStr"/>
-      <c r="C76" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="D76" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E76" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F76" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G76" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H76" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I76" s="11" t="n">
-        <v>5</v>
+      <c r="B76" s="11" t="inlineStr"/>
+      <c r="C76" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.7 / 0/11</t>
+        </is>
+      </c>
+      <c r="D76" s="11" t="inlineStr">
+        <is>
+          <t>0 / 1.2 / 0/11</t>
+        </is>
+      </c>
+      <c r="E76" s="11" t="inlineStr">
+        <is>
+          <t>2 / 1.0 / 0/9</t>
+        </is>
+      </c>
+      <c r="F76" s="11" t="inlineStr">
+        <is>
+          <t>2 / 0.4 / 0/9</t>
+        </is>
+      </c>
+      <c r="G76" s="11" t="inlineStr">
+        <is>
+          <t>2 / 4.0 / 0/6</t>
+        </is>
+      </c>
+      <c r="H76" s="11" t="inlineStr">
+        <is>
+          <t>1 / 1.2 / 0/8</t>
+        </is>
+      </c>
+      <c r="I76" s="11" t="inlineStr">
+        <is>
+          <t>4 / 2.8 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -5313,69 +5579,75 @@
         </is>
       </c>
       <c r="B77" s="12" t="inlineStr"/>
-      <c r="C77" s="13" t="n">
-        <v>4</v>
+      <c r="C77" s="12" t="inlineStr">
+        <is>
+          <t>1 / 3.5 / 0/11</t>
+        </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 0.9 / 0/11</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.1 / 0/9</t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12 / 2.7 / 1/9</t>
         </is>
       </c>
       <c r="G77" s="12" t="inlineStr"/>
       <c r="H77" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I77" s="13" t="n">
-        <v>2</v>
+          <t>2 / 1.5 / 0/8</t>
+        </is>
+      </c>
+      <c r="I77" s="12" t="inlineStr">
+        <is>
+          <t>2 / 1.0 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="10" t="inlineStr">
+      <c r="A78" s="11" t="inlineStr">
         <is>
           <t>Yorkshire - South</t>
         </is>
       </c>
-      <c r="B78" s="10" t="inlineStr"/>
-      <c r="C78" s="10" t="inlineStr"/>
-      <c r="D78" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I78" s="11" t="n">
-        <v>11</v>
+      <c r="B78" s="11" t="inlineStr"/>
+      <c r="C78" s="11" t="inlineStr"/>
+      <c r="D78" s="11" t="inlineStr">
+        <is>
+          <t>4 / 2.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="E78" s="11" t="inlineStr">
+        <is>
+          <t>4 / 3.1 / 0/9</t>
+        </is>
+      </c>
+      <c r="F78" s="11" t="inlineStr">
+        <is>
+          <t>6 / 2.0 / 1/9</t>
+        </is>
+      </c>
+      <c r="G78" s="11" t="inlineStr">
+        <is>
+          <t>0 / 2.3 / 2/6</t>
+        </is>
+      </c>
+      <c r="H78" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="I78" s="11" t="inlineStr">
+        <is>
+          <t>2 / 1.0 / 0/5</t>
+        </is>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
@@ -5389,18 +5661,20 @@
       <c r="D79" s="12" t="inlineStr"/>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4 / 4.0 / 0/9</t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15 / 5.4 / 3/9</t>
         </is>
       </c>
       <c r="G79" s="12" t="inlineStr"/>
       <c r="H79" s="12" t="inlineStr"/>
-      <c r="I79" s="13" t="n">
-        <v>5</v>
+      <c r="I79" s="12" t="inlineStr">
+        <is>
+          <t>3 / 2.6 / 0/5</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sitewide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JobG8 categories" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LIVE" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NOT LIVE" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Sitewide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="JobG8 categories" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="LIVE" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="NOT LIVE" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sitewide'!$A$1:$B$9</definedName>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -2473,7 +2473,7 @@
       </c>
       <c r="F4" s="11" t="inlineStr">
         <is>
-          <t>7 / 2.6 / 1/9</t>
+          <t>8 / 2.7 / 1/9</t>
         </is>
       </c>
       <c r="G4" s="11" t="inlineStr"/>
@@ -2513,7 +2513,7 @@
       <c r="F5" s="12" t="inlineStr"/>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>1 / 2.0 / 0/6</t>
+          <t>2 / 2.2 / 0/6</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/11</t>
+          <t>2 / 0.6 / 0/11</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>5 / 1.0 / 0/5</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/11</t>
+          <t>0 / 0.7 / 0/11</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -2931,7 +2931,7 @@
       <c r="B15" s="12" t="inlineStr"/>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/11</t>
+          <t>1 / 0.2 / 0/11</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>4 / 5.7 / 2/6</t>
+          <t>5 / 5.8 / 2/6</t>
         </is>
       </c>
       <c r="H17" s="12" t="inlineStr">
@@ -3052,7 +3052,7 @@
       <c r="B18" s="11" t="inlineStr"/>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/11</t>
+          <t>1 / 0.3 / 0/11</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -3091,7 +3091,7 @@
       <c r="B19" s="12" t="inlineStr"/>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>2 / 1.3 / 0/11</t>
+          <t>1 / 1.2 / 0/11</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr"/>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/11</t>
+          <t>1 / 0.3 / 0/11</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/9</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
-          <t>1 / 3.2 / 1/6</t>
+          <t>0 / 3.0 / 1/6</t>
         </is>
       </c>
       <c r="H26" s="11" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/11</t>
+          <t>2 / 1.1 / 0/11</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>1 / 0.1 / 0/8</t>
         </is>
       </c>
       <c r="I30" s="11" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>3 / 1.6 / 0/11</t>
+          <t>2 / 1.5 / 0/11</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/9</t>
+          <t>2 / 1.0 / 0/9</t>
         </is>
       </c>
       <c r="G32" s="11" t="inlineStr">
@@ -3679,12 +3679,12 @@
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>2 / 0.9 / 0/8</t>
+          <t>1 / 0.8 / 0/8</t>
         </is>
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
-          <t>3 / 3.0 / 0/5</t>
+          <t>2 / 2.8 / 0/5</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>3 / 1.6 / 0/9</t>
+          <t>2 / 1.4 / 0/9</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>6 / 2.0 / 1/9</t>
+          <t>5 / 1.9 / 0/9</t>
         </is>
       </c>
       <c r="G35" s="12" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>3 / 0.6 / 0/9</t>
+          <t>2 / 0.4 / 0/9</t>
         </is>
       </c>
       <c r="G38" s="11" t="inlineStr">
@@ -3984,7 +3984,7 @@
       <c r="D40" s="11" t="inlineStr"/>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/9</t>
+          <t>1 / 1.0 / 0/9</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="I40" s="11" t="inlineStr">
         <is>
-          <t>4 / 2.4 / 0/5</t>
+          <t>30 / 7.6 / 1/5</t>
         </is>
       </c>
     </row>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 0/6</t>
+          <t>2 / 1.7 / 0/6</t>
         </is>
       </c>
       <c r="H41" s="12" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>1 / 1.3 / 0/10</t>
+          <t>2 / 1.4 / 0/10</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>11 / 3.6 / 1/11</t>
+          <t>10 / 3.5 / 1/11</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
-          <t>6 / 2.2 / 1/9</t>
+          <t>5 / 2.1 / 0/9</t>
         </is>
       </c>
       <c r="G44" s="11" t="inlineStr">
@@ -4283,7 +4283,7 @@
       <c r="B47" s="12" t="inlineStr"/>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/11</t>
+          <t>0 / 0.5 / 0/11</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/10</t>
+          <t>4 / 1.3 / 0/10</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>1 / 0.2 / 0/5</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>2 / 2.8 / 0/10</t>
+          <t>1 / 2.7 / 0/10</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>4 / 3.1 / 0/10</t>
+          <t>6 / 3.3 / 1/10</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="I56" s="11" t="inlineStr">
         <is>
-          <t>3 / 2.4 / 0/5</t>
+          <t>6 / 3.0 / 1/5</t>
         </is>
       </c>
     </row>
@@ -4862,7 +4862,7 @@
       <c r="B60" s="11" t="inlineStr"/>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>1 / 3.5 / 3/11</t>
+          <t>2 / 3.6 / 3/11</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="G60" s="11" t="inlineStr">
         <is>
-          <t>2 / 3.3 / 1/6</t>
+          <t>1 / 3.2 / 1/6</t>
         </is>
       </c>
       <c r="H60" s="11" t="inlineStr">
@@ -4995,7 +4995,7 @@
       <c r="F63" s="12" t="inlineStr"/>
       <c r="G63" s="12" t="inlineStr">
         <is>
-          <t>5 / 5.2 / 2/6</t>
+          <t>4 / 5.0 / 2/6</t>
         </is>
       </c>
       <c r="H63" s="12" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>5 / 4.1 / 1/10</t>
+          <t>8 / 4.4 / 2/10</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="I67" s="12" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>1 / 0.2 / 0/5</t>
         </is>
       </c>
     </row>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>1 / 2.9 / 1/10</t>
+          <t>3 / 3.1 / 1/10</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>2 / 1.4 / 1/10</t>
+          <t>10 / 2.2 / 2/10</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/10</t>
+          <t>1 / 0.4 / 0/10</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="I70" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>4 / 0.8 / 0/5</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
-          <t>3 / 1.6 / 0/9</t>
+          <t>2 / 1.4 / 0/9</t>
         </is>
       </c>
       <c r="G75" s="12" t="inlineStr">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="I78" s="11" t="inlineStr">
         <is>
-          <t>2 / 1.0 / 0/5</t>
+          <t>4 / 1.4 / 0/5</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
-          <t>15 / 5.4 / 3/9</t>
+          <t>16 / 5.6 / 3/9</t>
         </is>
       </c>
       <c r="G79" s="12" t="inlineStr"/>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -106,9 +106,6 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -626,118 +623,118 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>I.T. &amp; Communications</t>
+          <t>Sales &amp; Marketing</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2547</v>
+        <v>2619</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>28</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>I.T. &amp; Communications</t>
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>920</v>
+        <v>1618</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>511</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Medical</t>
+          <t>Administration</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>669</v>
+        <v>1304</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>30</v>
+        <v>682</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Sales &amp; Marketing</t>
+          <t>Healthcare &amp; Medical</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>267</v>
+        <v>830</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>HR / Recruitment</t>
+          <t>Call Centre / CustomerService</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>125</v>
+        <v>685</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>15</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Call Centre / CustomerService</t>
+          <t>Accounting</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>116</v>
+        <v>403</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Real Estate &amp; Property</t>
+          <t>HR / Recruitment</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>108</v>
+        <v>386</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Banking &amp; Financial Services</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>107</v>
+        <v>352</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Accounting</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>101</v>
+        <v>352</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11">
@@ -747,33 +744,33 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>99</v>
+        <v>330</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Consulting &amp; Corporate Strategy</t>
+          <t>Real Estate &amp; Property</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>84</v>
+        <v>231</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Advert / Media / Entertainment</t>
+          <t>Consulting &amp; Corporate Strategy</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>83</v>
+        <v>230</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>5</v>
@@ -782,37 +779,41 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Banking &amp; Financial Services</t>
+          <t>Advert / Media / Entertainment</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>65</v>
+        <v>184</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Executive Positions</t>
+          <t>Insurance &amp; Superannuation</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="C15" s="8" t="inlineStr"/>
+        <v>178</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Insurance &amp; Superannuation</t>
+          <t>Executive Positions</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="C16" s="8" t="inlineStr"/>
+        <v>177</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -821,9 +822,11 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="C17" s="8" t="inlineStr"/>
+        <v>121</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -835,19 +838,19 @@
         <v>0</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>612</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Total Ontap JobG8 jobs published today</t>
         </is>
       </c>
-      <c r="B19" s="10" t="n">
-        <v>5354</v>
-      </c>
-      <c r="C19" s="10" t="n">
+      <c r="B19" s="9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C19" s="9" t="n">
         <v>1308</v>
       </c>
     </row>
@@ -2376,3302 +2379,3302 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Bedfordshire</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr"/>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr"/>
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>0 / 0.2 / 0/11</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>2 / 2.2 / 0/11</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>4 / 3.8 / 0/9</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>1 / 1.1 / 0/9</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>1 / 0.7 / 0/6</t>
         </is>
       </c>
-      <c r="H2" s="11" t="inlineStr">
+      <c r="H2" s="10" t="inlineStr">
         <is>
           <t>1 / 1.0 / 0/8</t>
         </is>
       </c>
-      <c r="I2" s="11" t="inlineStr">
+      <c r="I2" s="10" t="inlineStr">
         <is>
           <t>1 / 1.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>Berkshire</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr"/>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr"/>
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>0 / 3.5 / 3/11</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>7 / 1.7 / 1/11</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>2 / 0.7 / 0/9</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr"/>
-      <c r="G3" s="12" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr"/>
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>2 / 0.5 / 0/6</t>
         </is>
       </c>
-      <c r="H3" s="12" t="inlineStr"/>
-      <c r="I3" s="12" t="inlineStr">
+      <c r="H3" s="11" t="inlineStr"/>
+      <c r="I3" s="11" t="inlineStr">
         <is>
           <t>1 / 0.2 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Bristol &amp; Bath</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr"/>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr"/>
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>1 / 1.0 / 0/11</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr"/>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr"/>
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>3 / 2.9 / 1/9</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>8 / 2.7 / 1/9</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr"/>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr"/>
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>2 / 1.8 / 0/8</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="I4" s="10" t="inlineStr">
         <is>
           <t>5 / 2.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Buckinghamshire</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr"/>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr"/>
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>0 / 0.7 / 0/11</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>1 / 0.6 / 0/11</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>1 / 1.0 / 0/9</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr"/>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr"/>
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>2 / 2.2 / 0/6</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr">
+      <c r="H5" s="11" t="inlineStr">
         <is>
           <t>1 / 0.8 / 0/8</t>
         </is>
       </c>
-      <c r="I5" s="12" t="inlineStr">
+      <c r="I5" s="11" t="inlineStr">
         <is>
           <t>6 / 2.4 / 1/5</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Cambridgeshire</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr"/>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr"/>
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>0 / 0.1 / 0/11</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>3 / 2.5 / 0/11</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>1 / 1.2 / 0/9</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>6 / 2.6 / 1/9</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>3 / 4.5 / 2/6</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>0 / 0.1 / 0/8</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>1 / 1.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Cheshire - East</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr"/>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr"/>
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>0 / 0.6 / 0/11</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>3 / 1.5 / 0/11</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>0 / 0.2 / 0/9</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>3 / 1.0 / 0/9</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="G7" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
-      <c r="H7" s="12" t="inlineStr">
+      <c r="H7" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
-      <c r="I7" s="12" t="inlineStr">
+      <c r="I7" s="11" t="inlineStr">
         <is>
           <t>3 / 1.8 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Cheshire - Warrington &amp; Halton</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr"/>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr"/>
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>1 / 1.4 / 0/11</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>6 / 2.1 / 1/11</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>2 / 1.3 / 0/9</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>1 / 0.3 / 0/9</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>7 / 4.7 / 2/6</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>0 / 0.1 / 0/8</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Cheshire - West</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr"/>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr"/>
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>0 / 1.5 / 0/11</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>0 / 2.0 / 0/11</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>2 / 1.0 / 0/9</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>6 / 2.2 / 1/9</t>
         </is>
       </c>
-      <c r="G9" s="12" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>1 / 2.2 / 0/6</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr">
+      <c r="H9" s="11" t="inlineStr">
         <is>
           <t>1 / 0.2 / 0/8</t>
         </is>
       </c>
-      <c r="I9" s="12" t="inlineStr">
+      <c r="I9" s="11" t="inlineStr">
         <is>
           <t>1 / 0.2 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>Cornwall</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr"/>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr"/>
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>0 / 1.5 / 0/11</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>2 / 0.6 / 0/11</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>0 / 0.2 / 0/9</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>0 / 0.3 / 0/6</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>5 / 1.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Cumbria - North</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>1 / 1.6 / 0/11</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>0 / 2.8 / 3/11</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="G11" s="12" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>0 / 0.2 / 0/6</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr">
+      <c r="H11" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
-      <c r="I11" s="12" t="inlineStr">
+      <c r="I11" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Cumbria - South</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>1 / 1.1 / 0/11</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr"/>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr"/>
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>1 / 0.7 / 0/11</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>2 / 0.6 / 0/9</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>0 / 0.7 / 0/6</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>1 / 0.1 / 0/8</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Cumbria - West</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>1 / 1.8 / 0/11</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>0 / 0.7 / 0/11</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="G13" s="12" t="inlineStr">
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>0 / 0.5 / 0/6</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr">
+      <c r="H13" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
-      <c r="I13" s="12" t="inlineStr">
+      <c r="I13" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Derbyshire</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr"/>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr"/>
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>0 / 0.4 / 0/11</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>3 / 2.5 / 0/11</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>2 / 0.6 / 0/9</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>2 / 0.9 / 0/9</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>2 / 3.2 / 0/6</t>
         </is>
       </c>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
-      <c r="I14" s="11" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>3 / 1.4 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Devon</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr"/>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr"/>
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>1 / 0.2 / 0/11</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>5 / 3.2 / 0/11</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>3 / 2.1 / 0/9</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>6 / 1.2 / 1/9</t>
         </is>
       </c>
-      <c r="G15" s="12" t="inlineStr"/>
-      <c r="H15" s="12" t="inlineStr">
+      <c r="G15" s="11" t="inlineStr"/>
+      <c r="H15" s="11" t="inlineStr">
         <is>
           <t>2 / 1.1 / 0/8</t>
         </is>
       </c>
-      <c r="I15" s="12" t="inlineStr">
+      <c r="I15" s="11" t="inlineStr">
         <is>
           <t>3 / 1.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Dorset</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr"/>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr"/>
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>1 / 1.0 / 0/11</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>5 / 3.9 / 2/11</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>0 / 0.2 / 0/9</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>3 / 1.4 / 0/9</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>1 / 3.2 / 0/6</t>
         </is>
       </c>
-      <c r="H16" s="11" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
-      <c r="I16" s="11" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr">
         <is>
           <t>1 / 0.2 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Essex</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr"/>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr"/>
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>1 / 0.7 / 0/11</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>5 / 2.1 / 0/11</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr"/>
-      <c r="F17" s="12" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr"/>
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>6 / 2.8 / 1/9</t>
         </is>
       </c>
-      <c r="G17" s="12" t="inlineStr">
+      <c r="G17" s="11" t="inlineStr">
         <is>
           <t>5 / 5.8 / 2/6</t>
         </is>
       </c>
-      <c r="H17" s="12" t="inlineStr">
+      <c r="H17" s="11" t="inlineStr">
         <is>
           <t>1 / 1.1 / 0/8</t>
         </is>
       </c>
-      <c r="I17" s="12" t="inlineStr">
+      <c r="I17" s="11" t="inlineStr">
         <is>
           <t>4 / 2.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>Gloucestershire</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr"/>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr"/>
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>1 / 0.3 / 0/11</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>4 / 1.4 / 0/11</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="10" t="inlineStr">
         <is>
           <t>8 / 2.9 / 1/9</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr"/>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="G18" s="10" t="inlineStr"/>
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>2 / 1.2 / 0/8</t>
         </is>
       </c>
-      <c r="I18" s="11" t="inlineStr">
+      <c r="I18" s="10" t="inlineStr">
         <is>
           <t>3 / 1.6 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr"/>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr"/>
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>1 / 1.2 / 0/11</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr"/>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr"/>
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>3 / 3.9 / 2/9</t>
         </is>
       </c>
-      <c r="F19" s="12" t="inlineStr"/>
-      <c r="G19" s="12" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr"/>
+      <c r="G19" s="11" t="inlineStr">
         <is>
           <t>3 / 3.7 / 0/6</t>
         </is>
       </c>
-      <c r="H19" s="12" t="inlineStr"/>
-      <c r="I19" s="12" t="inlineStr">
+      <c r="H19" s="11" t="inlineStr"/>
+      <c r="I19" s="11" t="inlineStr">
         <is>
           <t>3 / 2.2 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>Greater Manchester - North</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>3 / 3.1 / 1/11</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>0 / 0.2 / 0/11</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
-      <c r="H20" s="11" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>0 / 0.1 / 0/8</t>
         </is>
       </c>
-      <c r="I20" s="11" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>1 / 0.2 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Greater Manchester - South</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr"/>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr"/>
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>0 / 0.8 / 0/11</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>1 / 0.7 / 0/11</t>
         </is>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>1 / 0.4 / 0/9</t>
         </is>
       </c>
-      <c r="F21" s="12" t="inlineStr">
+      <c r="F21" s="11" t="inlineStr">
         <is>
           <t>2 / 0.2 / 0/9</t>
         </is>
       </c>
-      <c r="G21" s="12" t="inlineStr">
+      <c r="G21" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
-      <c r="H21" s="12" t="inlineStr">
+      <c r="H21" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
-      <c r="I21" s="12" t="inlineStr">
+      <c r="I21" s="11" t="inlineStr">
         <is>
           <t>3 / 0.6 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>Greater Manchester - Wigan &amp; Bolton</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr"/>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr"/>
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>1 / 0.7 / 0/11</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>1 / 0.3 / 0/9</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F22" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>0 / 0.3 / 0/6</t>
         </is>
       </c>
-      <c r="H22" s="11" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>1 / 1.0 / 0/8</t>
         </is>
       </c>
-      <c r="I22" s="11" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>1 / 1.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Hampshire</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr"/>
-      <c r="C23" s="12" t="inlineStr"/>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr"/>
+      <c r="C23" s="11" t="inlineStr"/>
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>14 / 7.4 / 7/11</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E23" s="11" t="inlineStr">
         <is>
           <t>0 / 1.7 / 0/9</t>
         </is>
       </c>
-      <c r="F23" s="12" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>10 / 5.0 / 2/9</t>
         </is>
       </c>
-      <c r="G23" s="12" t="inlineStr">
+      <c r="G23" s="11" t="inlineStr">
         <is>
           <t>1 / 2.8 / 0/6</t>
         </is>
       </c>
-      <c r="H23" s="12" t="inlineStr">
+      <c r="H23" s="11" t="inlineStr">
         <is>
           <t>4 / 3.5 / 0/8</t>
         </is>
       </c>
-      <c r="I23" s="12" t="inlineStr"/>
+      <c r="I23" s="11" t="inlineStr"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>Herefordshire</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>0 / 1.4 / 0/11</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>1 / 0.3 / 0/11</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>0 / 1.2 / 0/6</t>
         </is>
       </c>
-      <c r="H24" s="11" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
-      <c r="I24" s="11" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Hertfordshire</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr"/>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr"/>
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>3 / 2.3 / 0/11</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>10 / 4.0 / 1/11</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E25" s="11" t="inlineStr">
         <is>
           <t>1 / 1.6 / 0/9</t>
         </is>
       </c>
-      <c r="F25" s="12" t="inlineStr">
+      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>9 / 2.1 / 1/9</t>
         </is>
       </c>
-      <c r="G25" s="12" t="inlineStr">
+      <c r="G25" s="11" t="inlineStr">
         <is>
           <t>1 / 1.0 / 0/6</t>
         </is>
       </c>
-      <c r="H25" s="12" t="inlineStr">
+      <c r="H25" s="11" t="inlineStr">
         <is>
           <t>1 / 0.2 / 0/8</t>
         </is>
       </c>
-      <c r="I25" s="12" t="inlineStr">
+      <c r="I25" s="11" t="inlineStr">
         <is>
           <t>4 / 1.6 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>Kent</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr"/>
-      <c r="C26" s="11" t="inlineStr"/>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr"/>
+      <c r="C26" s="10" t="inlineStr"/>
+      <c r="D26" s="10" t="inlineStr">
         <is>
           <t>8 / 4.5 / 1/11</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="E26" s="10" t="inlineStr">
         <is>
           <t>3 / 4.3 / 2/9</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F26" s="10" t="inlineStr">
         <is>
           <t>7 / 2.8 / 1/9</t>
         </is>
       </c>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>0 / 3.0 / 1/6</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>2 / 1.6 / 0/8</t>
         </is>
       </c>
-      <c r="I26" s="11" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>2 / 0.8 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Lancashire - Blackpool &amp; Fylde</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>1 / 0.8 / 0/11</t>
         </is>
       </c>
-      <c r="C27" s="12" t="inlineStr">
+      <c r="C27" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D27" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
-      <c r="E27" s="12" t="inlineStr">
+      <c r="E27" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F27" s="12" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>2 / 0.9 / 0/9</t>
         </is>
       </c>
-      <c r="G27" s="12" t="inlineStr">
+      <c r="G27" s="11" t="inlineStr">
         <is>
           <t>1 / 0.3 / 0/6</t>
         </is>
       </c>
-      <c r="H27" s="12" t="inlineStr">
+      <c r="H27" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
-      <c r="I27" s="12" t="inlineStr">
+      <c r="I27" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>Lancashire - Central</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>3 / 2.8 / 0/11</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>0 / 0.2 / 0/11</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D28" s="10" t="inlineStr">
         <is>
           <t>1 / 0.3 / 0/11</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E28" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="F28" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="G28" s="10" t="inlineStr">
         <is>
           <t>1 / 0.5 / 0/6</t>
         </is>
       </c>
-      <c r="H28" s="11" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>0 / 0.2 / 0/8</t>
         </is>
       </c>
-      <c r="I28" s="11" t="inlineStr">
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="12" t="inlineStr">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Lancashire - East</t>
         </is>
       </c>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>3 / 2.5 / 0/11</t>
         </is>
       </c>
-      <c r="C29" s="12" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>0 / 0.7 / 0/11</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>0 / 0.3 / 0/11</t>
         </is>
       </c>
-      <c r="E29" s="12" t="inlineStr">
+      <c r="E29" s="11" t="inlineStr">
         <is>
           <t>0 / 0.2 / 0/9</t>
         </is>
       </c>
-      <c r="F29" s="12" t="inlineStr">
+      <c r="F29" s="11" t="inlineStr">
         <is>
           <t>3 / 1.1 / 0/9</t>
         </is>
       </c>
-      <c r="G29" s="12" t="inlineStr">
+      <c r="G29" s="11" t="inlineStr">
         <is>
           <t>1 / 1.2 / 0/6</t>
         </is>
       </c>
-      <c r="H29" s="12" t="inlineStr">
+      <c r="H29" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
-      <c r="I29" s="12" t="inlineStr">
+      <c r="I29" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>Lancashire - North</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>2 / 1.1 / 0/11</t>
         </is>
       </c>
-      <c r="C30" s="11" t="inlineStr">
+      <c r="C30" s="10" t="inlineStr">
         <is>
           <t>0 / 1.2 / 0/11</t>
         </is>
       </c>
-      <c r="D30" s="11" t="inlineStr">
+      <c r="D30" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
-      <c r="E30" s="11" t="inlineStr">
+      <c r="E30" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F30" s="11" t="inlineStr">
+      <c r="F30" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="G30" s="11" t="inlineStr">
+      <c r="G30" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
-      <c r="H30" s="11" t="inlineStr">
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>1 / 0.1 / 0/8</t>
         </is>
       </c>
-      <c r="I30" s="11" t="inlineStr">
+      <c r="I30" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="12" t="inlineStr">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Lancashire - West</t>
         </is>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>0 / 1.3 / 0/10</t>
         </is>
       </c>
-      <c r="C31" s="12" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>0 / 0.1 / 0/10</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D31" s="11" t="inlineStr">
         <is>
           <t>1 / 1.2 / 0/10</t>
         </is>
       </c>
-      <c r="E31" s="12" t="inlineStr">
+      <c r="E31" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F31" s="12" t="inlineStr">
+      <c r="F31" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="G31" s="12" t="inlineStr">
+      <c r="G31" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
-      <c r="H31" s="12" t="inlineStr">
+      <c r="H31" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
-      <c r="I31" s="12" t="inlineStr">
+      <c r="I31" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>Leicestershire</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr"/>
-      <c r="C32" s="11" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr"/>
+      <c r="C32" s="10" t="inlineStr">
         <is>
           <t>0 / 0.1 / 0/11</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="D32" s="10" t="inlineStr">
         <is>
           <t>2 / 1.5 / 0/11</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr">
+      <c r="E32" s="10" t="inlineStr">
         <is>
           <t>2 / 1.3 / 0/9</t>
         </is>
       </c>
-      <c r="F32" s="11" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr">
         <is>
           <t>2 / 1.0 / 0/9</t>
         </is>
       </c>
-      <c r="G32" s="11" t="inlineStr">
+      <c r="G32" s="10" t="inlineStr">
         <is>
           <t>2 / 3.0 / 1/6</t>
         </is>
       </c>
-      <c r="H32" s="11" t="inlineStr">
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>1 / 0.8 / 0/8</t>
         </is>
       </c>
-      <c r="I32" s="11" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>2 / 2.8 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="12" t="inlineStr">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>Lincolnshire</t>
         </is>
       </c>
-      <c r="B33" s="12" t="inlineStr"/>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr"/>
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>0 / 1.7 / 0/11</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D33" s="11" t="inlineStr">
         <is>
           <t>4 / 1.2 / 0/11</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="E33" s="11" t="inlineStr">
         <is>
           <t>2 / 1.4 / 0/9</t>
         </is>
       </c>
-      <c r="F33" s="12" t="inlineStr">
+      <c r="F33" s="11" t="inlineStr">
         <is>
           <t>3 / 2.7 / 0/9</t>
         </is>
       </c>
-      <c r="G33" s="12" t="inlineStr">
+      <c r="G33" s="11" t="inlineStr">
         <is>
           <t>1 / 2.8 / 0/6</t>
         </is>
       </c>
-      <c r="H33" s="12" t="inlineStr">
+      <c r="H33" s="11" t="inlineStr">
         <is>
           <t>1 / 1.4 / 0/8</t>
         </is>
       </c>
-      <c r="I33" s="12" t="inlineStr">
+      <c r="I33" s="11" t="inlineStr">
         <is>
           <t>2 / 1.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>London</t>
         </is>
       </c>
-      <c r="B34" s="11" t="inlineStr"/>
-      <c r="C34" s="11" t="inlineStr"/>
-      <c r="D34" s="11" t="inlineStr"/>
-      <c r="E34" s="11" t="inlineStr"/>
-      <c r="F34" s="11" t="inlineStr"/>
-      <c r="G34" s="11" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr"/>
+      <c r="C34" s="10" t="inlineStr"/>
+      <c r="D34" s="10" t="inlineStr"/>
+      <c r="E34" s="10" t="inlineStr"/>
+      <c r="F34" s="10" t="inlineStr"/>
+      <c r="G34" s="10" t="inlineStr">
         <is>
           <t>10 / 5.2 / 2/6</t>
         </is>
       </c>
-      <c r="H34" s="11" t="inlineStr"/>
-      <c r="I34" s="11" t="inlineStr"/>
+      <c r="H34" s="10" t="inlineStr"/>
+      <c r="I34" s="10" t="inlineStr"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="12" t="inlineStr">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>Merseyside - Liverpool</t>
         </is>
       </c>
-      <c r="B35" s="12" t="inlineStr"/>
-      <c r="C35" s="12" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr"/>
+      <c r="C35" s="11" t="inlineStr">
         <is>
           <t>0 / 0.4 / 0/11</t>
         </is>
       </c>
-      <c r="D35" s="12" t="inlineStr">
+      <c r="D35" s="11" t="inlineStr">
         <is>
           <t>0 / 0.3 / 0/11</t>
         </is>
       </c>
-      <c r="E35" s="12" t="inlineStr">
+      <c r="E35" s="11" t="inlineStr">
         <is>
           <t>1 / 0.4 / 0/9</t>
         </is>
       </c>
-      <c r="F35" s="12" t="inlineStr">
+      <c r="F35" s="11" t="inlineStr">
         <is>
           <t>5 / 1.9 / 0/9</t>
         </is>
       </c>
-      <c r="G35" s="12" t="inlineStr">
+      <c r="G35" s="11" t="inlineStr">
         <is>
           <t>1 / 0.5 / 0/6</t>
         </is>
       </c>
-      <c r="H35" s="12" t="inlineStr">
+      <c r="H35" s="11" t="inlineStr">
         <is>
           <t>0 / 0.1 / 0/8</t>
         </is>
       </c>
-      <c r="I35" s="12" t="inlineStr">
+      <c r="I35" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>Merseyside - Sefton</t>
         </is>
       </c>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>0 / 0.1 / 0/10</t>
         </is>
       </c>
-      <c r="C36" s="11" t="inlineStr">
+      <c r="C36" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="D36" s="11" t="inlineStr">
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="E36" s="11" t="inlineStr">
+      <c r="E36" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F36" s="11" t="inlineStr">
+      <c r="F36" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="G36" s="11" t="inlineStr">
+      <c r="G36" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
-      <c r="H36" s="11" t="inlineStr">
+      <c r="H36" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
-      <c r="I36" s="11" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="12" t="inlineStr">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>Merseyside - St Helens &amp; Knowsley</t>
         </is>
       </c>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>1 / 2.0 / 0/10</t>
         </is>
       </c>
-      <c r="C37" s="12" t="inlineStr">
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="D37" s="12" t="inlineStr">
+      <c r="D37" s="11" t="inlineStr">
         <is>
           <t>1 / 0.8 / 0/10</t>
         </is>
       </c>
-      <c r="E37" s="12" t="inlineStr">
+      <c r="E37" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F37" s="12" t="inlineStr">
+      <c r="F37" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="G37" s="12" t="inlineStr">
+      <c r="G37" s="11" t="inlineStr">
         <is>
           <t>1 / 1.7 / 0/6</t>
         </is>
       </c>
-      <c r="H37" s="12" t="inlineStr">
+      <c r="H37" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
-      <c r="I37" s="12" t="inlineStr">
+      <c r="I37" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>Merseyside - Wirral</t>
         </is>
       </c>
-      <c r="B38" s="11" t="inlineStr">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>1 / 1.5 / 0/11</t>
         </is>
       </c>
-      <c r="C38" s="11" t="inlineStr">
+      <c r="C38" s="10" t="inlineStr">
         <is>
           <t>0 / 0.5 / 0/11</t>
         </is>
       </c>
-      <c r="D38" s="11" t="inlineStr">
+      <c r="D38" s="10" t="inlineStr">
         <is>
           <t>1 / 1.0 / 0/11</t>
         </is>
       </c>
-      <c r="E38" s="11" t="inlineStr">
+      <c r="E38" s="10" t="inlineStr">
         <is>
           <t>1 / 0.3 / 0/9</t>
         </is>
       </c>
-      <c r="F38" s="11" t="inlineStr">
+      <c r="F38" s="10" t="inlineStr">
         <is>
           <t>2 / 0.4 / 0/9</t>
         </is>
       </c>
-      <c r="G38" s="11" t="inlineStr">
+      <c r="G38" s="10" t="inlineStr">
         <is>
           <t>1 / 0.2 / 0/6</t>
         </is>
       </c>
-      <c r="H38" s="11" t="inlineStr">
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
-      <c r="I38" s="11" t="inlineStr">
+      <c r="I38" s="10" t="inlineStr">
         <is>
           <t>1 / 1.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="12" t="inlineStr">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Norfolk</t>
         </is>
       </c>
-      <c r="B39" s="12" t="inlineStr"/>
-      <c r="C39" s="12" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr"/>
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>0 / 1.1 / 0/11</t>
         </is>
       </c>
-      <c r="D39" s="12" t="inlineStr">
+      <c r="D39" s="11" t="inlineStr">
         <is>
           <t>0 / 0.7 / 0/11</t>
         </is>
       </c>
-      <c r="E39" s="12" t="inlineStr"/>
-      <c r="F39" s="12" t="inlineStr">
+      <c r="E39" s="11" t="inlineStr"/>
+      <c r="F39" s="11" t="inlineStr">
         <is>
           <t>2 / 1.6 / 0/9</t>
         </is>
       </c>
-      <c r="G39" s="12" t="inlineStr">
+      <c r="G39" s="11" t="inlineStr">
         <is>
           <t>2 / 4.2 / 2/6</t>
         </is>
       </c>
-      <c r="H39" s="12" t="inlineStr">
+      <c r="H39" s="11" t="inlineStr">
         <is>
           <t>0 / 0.2 / 0/8</t>
         </is>
       </c>
-      <c r="I39" s="12" t="inlineStr">
+      <c r="I39" s="11" t="inlineStr">
         <is>
           <t>1 / 0.8 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="11" t="inlineStr">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>North East</t>
         </is>
       </c>
-      <c r="B40" s="11" t="inlineStr"/>
-      <c r="C40" s="11" t="inlineStr"/>
-      <c r="D40" s="11" t="inlineStr"/>
-      <c r="E40" s="11" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr"/>
+      <c r="C40" s="10" t="inlineStr"/>
+      <c r="D40" s="10" t="inlineStr"/>
+      <c r="E40" s="10" t="inlineStr">
         <is>
           <t>1 / 1.0 / 0/9</t>
         </is>
       </c>
-      <c r="F40" s="11" t="inlineStr">
+      <c r="F40" s="10" t="inlineStr">
         <is>
           <t>6 / 4.1 / 1/9</t>
         </is>
       </c>
-      <c r="G40" s="11" t="inlineStr"/>
-      <c r="H40" s="11" t="inlineStr">
+      <c r="G40" s="10" t="inlineStr"/>
+      <c r="H40" s="10" t="inlineStr">
         <is>
           <t>1 / 1.1 / 0/8</t>
         </is>
       </c>
-      <c r="I40" s="11" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>30 / 7.6 / 1/5</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="12" t="inlineStr">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>North Scotland</t>
         </is>
       </c>
-      <c r="B41" s="12" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>6 / 5.6 / 4/10</t>
         </is>
       </c>
-      <c r="C41" s="12" t="inlineStr">
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="D41" s="12" t="inlineStr">
+      <c r="D41" s="11" t="inlineStr">
         <is>
           <t>6 / 3.0 / 1/10</t>
         </is>
       </c>
-      <c r="E41" s="12" t="inlineStr">
+      <c r="E41" s="11" t="inlineStr">
         <is>
           <t>0 / 0.2 / 0/9</t>
         </is>
       </c>
-      <c r="F41" s="12" t="inlineStr">
+      <c r="F41" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="G41" s="12" t="inlineStr">
+      <c r="G41" s="11" t="inlineStr">
         <is>
           <t>2 / 1.7 / 0/6</t>
         </is>
       </c>
-      <c r="H41" s="12" t="inlineStr">
+      <c r="H41" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
-      <c r="I41" s="12" t="inlineStr">
+      <c r="I41" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="11" t="inlineStr">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>North Wales - East</t>
         </is>
       </c>
-      <c r="B42" s="11" t="inlineStr">
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>5 / 4.5 / 1/10</t>
         </is>
       </c>
-      <c r="C42" s="11" t="inlineStr">
+      <c r="C42" s="10" t="inlineStr">
         <is>
           <t>0 / 0.2 / 0/10</t>
         </is>
       </c>
-      <c r="D42" s="11" t="inlineStr">
+      <c r="D42" s="10" t="inlineStr">
         <is>
           <t>2 / 1.4 / 0/10</t>
         </is>
       </c>
-      <c r="E42" s="11" t="inlineStr">
+      <c r="E42" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F42" s="11" t="inlineStr">
+      <c r="F42" s="10" t="inlineStr">
         <is>
           <t>1 / 0.4 / 0/9</t>
         </is>
       </c>
-      <c r="G42" s="11" t="inlineStr">
+      <c r="G42" s="10" t="inlineStr">
         <is>
           <t>1 / 1.5 / 0/6</t>
         </is>
       </c>
-      <c r="H42" s="11" t="inlineStr">
+      <c r="H42" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
-      <c r="I42" s="11" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>1 / 1.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="12" t="inlineStr">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t>North Wales - West</t>
         </is>
       </c>
-      <c r="B43" s="12" t="inlineStr">
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t>3 / 1.8 / 0/10</t>
         </is>
       </c>
-      <c r="C43" s="12" t="inlineStr">
+      <c r="C43" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="D43" s="12" t="inlineStr">
+      <c r="D43" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="E43" s="12" t="inlineStr">
+      <c r="E43" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F43" s="12" t="inlineStr">
+      <c r="F43" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="G43" s="12" t="inlineStr">
+      <c r="G43" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
-      <c r="H43" s="12" t="inlineStr">
+      <c r="H43" s="11" t="inlineStr">
         <is>
           <t>1 / 0.2 / 0/8</t>
         </is>
       </c>
-      <c r="I43" s="12" t="inlineStr">
+      <c r="I43" s="11" t="inlineStr">
         <is>
           <t>1 / 0.4 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="11" t="inlineStr">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>Northamptonshire</t>
         </is>
       </c>
-      <c r="B44" s="11" t="inlineStr"/>
-      <c r="C44" s="11" t="inlineStr">
+      <c r="B44" s="10" t="inlineStr"/>
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
-      <c r="D44" s="11" t="inlineStr">
+      <c r="D44" s="10" t="inlineStr">
         <is>
           <t>10 / 3.5 / 1/11</t>
         </is>
       </c>
-      <c r="E44" s="11" t="inlineStr">
+      <c r="E44" s="10" t="inlineStr">
         <is>
           <t>1 / 1.3 / 0/9</t>
         </is>
       </c>
-      <c r="F44" s="11" t="inlineStr">
+      <c r="F44" s="10" t="inlineStr">
         <is>
           <t>5 / 2.1 / 0/9</t>
         </is>
       </c>
-      <c r="G44" s="11" t="inlineStr">
+      <c r="G44" s="10" t="inlineStr">
         <is>
           <t>2 / 3.3 / 2/6</t>
         </is>
       </c>
-      <c r="H44" s="11" t="inlineStr">
+      <c r="H44" s="10" t="inlineStr">
         <is>
           <t>3 / 2.5 / 1/8</t>
         </is>
       </c>
-      <c r="I44" s="11" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>1 / 0.2 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="12" t="inlineStr">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>Northern Ireland - East</t>
         </is>
       </c>
-      <c r="B45" s="12" t="inlineStr"/>
-      <c r="C45" s="12" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr"/>
+      <c r="C45" s="11" t="inlineStr">
         <is>
           <t>1 / 1.8 / 0/10</t>
         </is>
       </c>
-      <c r="D45" s="12" t="inlineStr">
+      <c r="D45" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="E45" s="12" t="inlineStr">
+      <c r="E45" s="11" t="inlineStr">
         <is>
           <t>1 / 1.2 / 0/9</t>
         </is>
       </c>
-      <c r="F45" s="12" t="inlineStr">
+      <c r="F45" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="G45" s="12" t="inlineStr"/>
-      <c r="H45" s="12" t="inlineStr">
+      <c r="G45" s="11" t="inlineStr"/>
+      <c r="H45" s="11" t="inlineStr">
         <is>
           <t>0 / 0.1 / 0/8</t>
         </is>
       </c>
-      <c r="I45" s="12" t="inlineStr">
+      <c r="I45" s="11" t="inlineStr">
         <is>
           <t>1 / 1.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="11" t="inlineStr">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>Northern Ireland - West</t>
         </is>
       </c>
-      <c r="B46" s="11" t="inlineStr">
+      <c r="B46" s="10" t="inlineStr">
         <is>
           <t>4 / 4.1 / 0/10</t>
         </is>
       </c>
-      <c r="C46" s="11" t="inlineStr">
+      <c r="C46" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="D46" s="11" t="inlineStr">
+      <c r="D46" s="10" t="inlineStr">
         <is>
           <t>3 / 1.0 / 0/10</t>
         </is>
       </c>
-      <c r="E46" s="11" t="inlineStr">
+      <c r="E46" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F46" s="11" t="inlineStr">
+      <c r="F46" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="G46" s="11" t="inlineStr">
+      <c r="G46" s="10" t="inlineStr">
         <is>
           <t>0 / 0.2 / 0/6</t>
         </is>
       </c>
-      <c r="H46" s="11" t="inlineStr">
+      <c r="H46" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
-      <c r="I46" s="11" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="12" t="inlineStr">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>Nottinghamshire</t>
         </is>
       </c>
-      <c r="B47" s="12" t="inlineStr"/>
-      <c r="C47" s="12" t="inlineStr">
+      <c r="B47" s="11" t="inlineStr"/>
+      <c r="C47" s="11" t="inlineStr">
         <is>
           <t>0 / 0.5 / 0/11</t>
         </is>
       </c>
-      <c r="D47" s="12" t="inlineStr">
+      <c r="D47" s="11" t="inlineStr">
         <is>
           <t>3 / 1.8 / 0/11</t>
         </is>
       </c>
-      <c r="E47" s="12" t="inlineStr">
+      <c r="E47" s="11" t="inlineStr">
         <is>
           <t>2 / 2.1 / 0/9</t>
         </is>
       </c>
-      <c r="F47" s="12" t="inlineStr">
+      <c r="F47" s="11" t="inlineStr">
         <is>
           <t>4 / 2.0 / 0/9</t>
         </is>
       </c>
-      <c r="G47" s="12" t="inlineStr">
+      <c r="G47" s="11" t="inlineStr">
         <is>
           <t>1 / 3.7 / 2/6</t>
         </is>
       </c>
-      <c r="H47" s="12" t="inlineStr"/>
-      <c r="I47" s="12" t="inlineStr">
+      <c r="H47" s="11" t="inlineStr"/>
+      <c r="I47" s="11" t="inlineStr">
         <is>
           <t>1 / 1.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="11" t="inlineStr">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>Oxfordshire</t>
         </is>
       </c>
-      <c r="B48" s="11" t="inlineStr"/>
-      <c r="C48" s="11" t="inlineStr"/>
-      <c r="D48" s="11" t="inlineStr">
+      <c r="B48" s="10" t="inlineStr"/>
+      <c r="C48" s="10" t="inlineStr"/>
+      <c r="D48" s="10" t="inlineStr">
         <is>
           <t>5 / 3.0 / 0/11</t>
         </is>
       </c>
-      <c r="E48" s="11" t="inlineStr">
+      <c r="E48" s="10" t="inlineStr">
         <is>
           <t>2 / 1.7 / 0/9</t>
         </is>
       </c>
-      <c r="F48" s="11" t="inlineStr">
+      <c r="F48" s="10" t="inlineStr">
         <is>
           <t>10 / 4.6 / 2/9</t>
         </is>
       </c>
-      <c r="G48" s="11" t="inlineStr">
+      <c r="G48" s="10" t="inlineStr">
         <is>
           <t>1 / 2.8 / 0/6</t>
         </is>
       </c>
-      <c r="H48" s="11" t="inlineStr">
+      <c r="H48" s="10" t="inlineStr">
         <is>
           <t>1 / 0.2 / 0/8</t>
         </is>
       </c>
-      <c r="I48" s="11" t="inlineStr">
+      <c r="I48" s="10" t="inlineStr">
         <is>
           <t>3 / 0.8 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="12" t="inlineStr">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>Rutland</t>
         </is>
       </c>
-      <c r="B49" s="12" t="inlineStr">
+      <c r="B49" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
-      <c r="C49" s="12" t="inlineStr">
+      <c r="C49" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
-      <c r="D49" s="12" t="inlineStr">
+      <c r="D49" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
-      <c r="E49" s="12" t="inlineStr">
+      <c r="E49" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F49" s="12" t="inlineStr">
+      <c r="F49" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="G49" s="12" t="inlineStr">
+      <c r="G49" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
-      <c r="H49" s="12" t="inlineStr">
+      <c r="H49" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
-      <c r="I49" s="12" t="inlineStr">
+      <c r="I49" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="11" t="inlineStr">
+      <c r="A50" s="10" t="inlineStr">
         <is>
           <t>Scotland - Borders</t>
         </is>
       </c>
-      <c r="B50" s="11" t="inlineStr">
+      <c r="B50" s="10" t="inlineStr">
         <is>
           <t>4 / 1.3 / 0/10</t>
         </is>
       </c>
-      <c r="C50" s="11" t="inlineStr">
+      <c r="C50" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="D50" s="11" t="inlineStr">
+      <c r="D50" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="E50" s="11" t="inlineStr">
+      <c r="E50" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F50" s="11" t="inlineStr">
+      <c r="F50" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="G50" s="11" t="inlineStr">
+      <c r="G50" s="10" t="inlineStr">
         <is>
           <t>1 / 0.2 / 0/6</t>
         </is>
       </c>
-      <c r="H50" s="11" t="inlineStr">
+      <c r="H50" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
-      <c r="I50" s="11" t="inlineStr">
+      <c r="I50" s="10" t="inlineStr">
         <is>
           <t>1 / 0.2 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="12" t="inlineStr">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t>Scotland Central - Edinburgh &amp; Lothians</t>
         </is>
       </c>
-      <c r="B51" s="12" t="inlineStr"/>
-      <c r="C51" s="12" t="inlineStr">
+      <c r="B51" s="11" t="inlineStr"/>
+      <c r="C51" s="11" t="inlineStr">
         <is>
           <t>0 / 0.1 / 0/10</t>
         </is>
       </c>
-      <c r="D51" s="12" t="inlineStr">
+      <c r="D51" s="11" t="inlineStr">
         <is>
           <t>4 / 2.2 / 0/10</t>
         </is>
       </c>
-      <c r="E51" s="12" t="inlineStr">
+      <c r="E51" s="11" t="inlineStr">
         <is>
           <t>4 / 2.4 / 0/9</t>
         </is>
       </c>
-      <c r="F51" s="12" t="inlineStr">
+      <c r="F51" s="11" t="inlineStr">
         <is>
           <t>1 / 0.1 / 0/9</t>
         </is>
       </c>
-      <c r="G51" s="12" t="inlineStr">
+      <c r="G51" s="11" t="inlineStr">
         <is>
           <t>1 / 1.2 / 0/6</t>
         </is>
       </c>
-      <c r="H51" s="12" t="inlineStr">
+      <c r="H51" s="11" t="inlineStr">
         <is>
           <t>1 / 0.4 / 0/8</t>
         </is>
       </c>
-      <c r="I51" s="12" t="inlineStr">
+      <c r="I51" s="11" t="inlineStr">
         <is>
           <t>1 / 0.2 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="11" t="inlineStr">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>Scotland Central - Falkirk &amp; Stirling</t>
         </is>
       </c>
-      <c r="B52" s="11" t="inlineStr">
+      <c r="B52" s="10" t="inlineStr">
         <is>
           <t>1 / 2.7 / 0/10</t>
         </is>
       </c>
-      <c r="C52" s="11" t="inlineStr">
+      <c r="C52" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="D52" s="11" t="inlineStr">
+      <c r="D52" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="E52" s="11" t="inlineStr">
+      <c r="E52" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F52" s="11" t="inlineStr">
+      <c r="F52" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="G52" s="11" t="inlineStr">
+      <c r="G52" s="10" t="inlineStr">
         <is>
           <t>1 / 1.2 / 0/6</t>
         </is>
       </c>
-      <c r="H52" s="11" t="inlineStr">
+      <c r="H52" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
-      <c r="I52" s="11" t="inlineStr">
+      <c r="I52" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="12" t="inlineStr">
+      <c r="A53" s="11" t="inlineStr">
         <is>
           <t>Scotland Central - Fife</t>
         </is>
       </c>
-      <c r="B53" s="12" t="inlineStr">
+      <c r="B53" s="11" t="inlineStr">
         <is>
           <t>2 / 1.5 / 0/10</t>
         </is>
       </c>
-      <c r="C53" s="12" t="inlineStr">
+      <c r="C53" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="D53" s="12" t="inlineStr">
+      <c r="D53" s="11" t="inlineStr">
         <is>
           <t>2 / 1.0 / 0/10</t>
         </is>
       </c>
-      <c r="E53" s="12" t="inlineStr">
+      <c r="E53" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F53" s="12" t="inlineStr">
+      <c r="F53" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="G53" s="12" t="inlineStr">
+      <c r="G53" s="11" t="inlineStr">
         <is>
           <t>0 / 0.7 / 0/6</t>
         </is>
       </c>
-      <c r="H53" s="12" t="inlineStr">
+      <c r="H53" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
-      <c r="I53" s="12" t="inlineStr">
+      <c r="I53" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="11" t="inlineStr">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>Scotland Central - Tayside</t>
         </is>
       </c>
-      <c r="B54" s="11" t="inlineStr">
+      <c r="B54" s="10" t="inlineStr">
         <is>
           <t>5 / 3.8 / 0/10</t>
         </is>
       </c>
-      <c r="C54" s="11" t="inlineStr">
+      <c r="C54" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="D54" s="11" t="inlineStr">
+      <c r="D54" s="10" t="inlineStr">
         <is>
           <t>0 / 0.2 / 0/10</t>
         </is>
       </c>
-      <c r="E54" s="11" t="inlineStr">
+      <c r="E54" s="10" t="inlineStr">
         <is>
           <t>1 / 1.2 / 0/9</t>
         </is>
       </c>
-      <c r="F54" s="11" t="inlineStr">
+      <c r="F54" s="10" t="inlineStr">
         <is>
           <t>0 / 0.2 / 0/9</t>
         </is>
       </c>
-      <c r="G54" s="11" t="inlineStr">
+      <c r="G54" s="10" t="inlineStr">
         <is>
           <t>0 / 0.7 / 0/6</t>
         </is>
       </c>
-      <c r="H54" s="11" t="inlineStr">
+      <c r="H54" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
-      <c r="I54" s="11" t="inlineStr">
+      <c r="I54" s="10" t="inlineStr">
         <is>
           <t>1 / 0.2 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="12" t="inlineStr">
+      <c r="A55" s="11" t="inlineStr">
         <is>
           <t>Scotland West - Ayrshire</t>
         </is>
       </c>
-      <c r="B55" s="12" t="inlineStr">
+      <c r="B55" s="11" t="inlineStr">
         <is>
           <t>1 / 0.5 / 0/10</t>
         </is>
       </c>
-      <c r="C55" s="12" t="inlineStr">
+      <c r="C55" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="D55" s="12" t="inlineStr">
+      <c r="D55" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="E55" s="12" t="inlineStr">
+      <c r="E55" s="11" t="inlineStr">
         <is>
           <t>1 / 0.4 / 0/9</t>
         </is>
       </c>
-      <c r="F55" s="12" t="inlineStr">
+      <c r="F55" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="G55" s="12" t="inlineStr">
+      <c r="G55" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
-      <c r="H55" s="12" t="inlineStr">
+      <c r="H55" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
-      <c r="I55" s="12" t="inlineStr">
+      <c r="I55" s="11" t="inlineStr">
         <is>
           <t>1 / 0.6 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="11" t="inlineStr">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>Scotland West - Glasgow</t>
         </is>
       </c>
-      <c r="B56" s="11" t="inlineStr"/>
-      <c r="C56" s="11" t="inlineStr">
+      <c r="B56" s="10" t="inlineStr"/>
+      <c r="C56" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="D56" s="11" t="inlineStr">
+      <c r="D56" s="10" t="inlineStr">
         <is>
           <t>6 / 3.3 / 1/10</t>
         </is>
       </c>
-      <c r="E56" s="11" t="inlineStr">
+      <c r="E56" s="10" t="inlineStr">
         <is>
           <t>0 / 0.2 / 0/9</t>
         </is>
       </c>
-      <c r="F56" s="11" t="inlineStr">
+      <c r="F56" s="10" t="inlineStr">
         <is>
           <t>0 / 0.2 / 0/9</t>
         </is>
       </c>
-      <c r="G56" s="11" t="inlineStr">
+      <c r="G56" s="10" t="inlineStr">
         <is>
           <t>0 / 0.3 / 0/6</t>
         </is>
       </c>
-      <c r="H56" s="11" t="inlineStr">
+      <c r="H56" s="10" t="inlineStr">
         <is>
           <t>0 / 0.6 / 0/8</t>
         </is>
       </c>
-      <c r="I56" s="11" t="inlineStr">
+      <c r="I56" s="10" t="inlineStr">
         <is>
           <t>6 / 3.0 / 1/5</t>
         </is>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="12" t="inlineStr">
+      <c r="A57" s="11" t="inlineStr">
         <is>
           <t>Scotland West - Lanarkshire</t>
         </is>
       </c>
-      <c r="B57" s="12" t="inlineStr">
+      <c r="B57" s="11" t="inlineStr">
         <is>
           <t>0 / 0.5 / 0/10</t>
         </is>
       </c>
-      <c r="C57" s="12" t="inlineStr">
+      <c r="C57" s="11" t="inlineStr">
         <is>
           <t>0 / 0.1 / 0/10</t>
         </is>
       </c>
-      <c r="D57" s="12" t="inlineStr">
+      <c r="D57" s="11" t="inlineStr">
         <is>
           <t>0 / 0.4 / 0/10</t>
         </is>
       </c>
-      <c r="E57" s="12" t="inlineStr">
+      <c r="E57" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F57" s="12" t="inlineStr">
+      <c r="F57" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="G57" s="12" t="inlineStr">
+      <c r="G57" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
-      <c r="H57" s="12" t="inlineStr">
+      <c r="H57" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
-      <c r="I57" s="12" t="inlineStr">
+      <c r="I57" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="11" t="inlineStr">
+      <c r="A58" s="10" t="inlineStr">
         <is>
           <t>Scotland West - Renfrewshire &amp; Inverclyde</t>
         </is>
       </c>
-      <c r="B58" s="11" t="inlineStr">
+      <c r="B58" s="10" t="inlineStr">
         <is>
           <t>1 / 1.0 / 0/10</t>
         </is>
       </c>
-      <c r="C58" s="11" t="inlineStr">
+      <c r="C58" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="D58" s="11" t="inlineStr">
+      <c r="D58" s="10" t="inlineStr">
         <is>
           <t>1 / 0.4 / 0/10</t>
         </is>
       </c>
-      <c r="E58" s="11" t="inlineStr">
+      <c r="E58" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F58" s="11" t="inlineStr">
+      <c r="F58" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="G58" s="11" t="inlineStr">
+      <c r="G58" s="10" t="inlineStr">
         <is>
           <t>0 / 0.7 / 0/6</t>
         </is>
       </c>
-      <c r="H58" s="11" t="inlineStr">
+      <c r="H58" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
-      <c r="I58" s="11" t="inlineStr">
+      <c r="I58" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="12" t="inlineStr">
+      <c r="A59" s="11" t="inlineStr">
         <is>
           <t>Shropshire</t>
         </is>
       </c>
-      <c r="B59" s="12" t="inlineStr"/>
-      <c r="C59" s="12" t="inlineStr">
+      <c r="B59" s="11" t="inlineStr"/>
+      <c r="C59" s="11" t="inlineStr">
         <is>
           <t>0 / 1.8 / 0/11</t>
         </is>
       </c>
-      <c r="D59" s="12" t="inlineStr">
+      <c r="D59" s="11" t="inlineStr">
         <is>
           <t>0 / 1.1 / 0/11</t>
         </is>
       </c>
-      <c r="E59" s="12" t="inlineStr">
+      <c r="E59" s="11" t="inlineStr">
         <is>
           <t>2 / 1.7 / 0/9</t>
         </is>
       </c>
-      <c r="F59" s="12" t="inlineStr">
+      <c r="F59" s="11" t="inlineStr">
         <is>
           <t>1 / 0.3 / 0/9</t>
         </is>
       </c>
-      <c r="G59" s="12" t="inlineStr"/>
-      <c r="H59" s="12" t="inlineStr">
+      <c r="G59" s="11" t="inlineStr"/>
+      <c r="H59" s="11" t="inlineStr">
         <is>
           <t>2 / 1.9 / 0/8</t>
         </is>
       </c>
-      <c r="I59" s="12" t="inlineStr">
+      <c r="I59" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="11" t="inlineStr">
+      <c r="A60" s="10" t="inlineStr">
         <is>
           <t>Somerset</t>
         </is>
       </c>
-      <c r="B60" s="11" t="inlineStr"/>
-      <c r="C60" s="11" t="inlineStr">
+      <c r="B60" s="10" t="inlineStr"/>
+      <c r="C60" s="10" t="inlineStr">
         <is>
           <t>2 / 3.6 / 3/11</t>
         </is>
       </c>
-      <c r="D60" s="11" t="inlineStr">
+      <c r="D60" s="10" t="inlineStr">
         <is>
           <t>2 / 1.3 / 0/11</t>
         </is>
       </c>
-      <c r="E60" s="11" t="inlineStr">
+      <c r="E60" s="10" t="inlineStr">
         <is>
           <t>1 / 0.3 / 0/9</t>
         </is>
       </c>
-      <c r="F60" s="11" t="inlineStr">
+      <c r="F60" s="10" t="inlineStr">
         <is>
           <t>4 / 0.6 / 0/9</t>
         </is>
       </c>
-      <c r="G60" s="11" t="inlineStr">
+      <c r="G60" s="10" t="inlineStr">
         <is>
           <t>1 / 3.2 / 1/6</t>
         </is>
       </c>
-      <c r="H60" s="11" t="inlineStr">
+      <c r="H60" s="10" t="inlineStr">
         <is>
           <t>0 / 0.1 / 0/8</t>
         </is>
       </c>
-      <c r="I60" s="11" t="inlineStr">
+      <c r="I60" s="10" t="inlineStr">
         <is>
           <t>2 / 0.4 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="12" t="inlineStr">
+      <c r="A61" s="11" t="inlineStr">
         <is>
           <t>Staffordshire</t>
         </is>
       </c>
-      <c r="B61" s="12" t="inlineStr"/>
-      <c r="C61" s="12" t="inlineStr">
+      <c r="B61" s="11" t="inlineStr"/>
+      <c r="C61" s="11" t="inlineStr">
         <is>
           <t>0 / 0.2 / 0/11</t>
         </is>
       </c>
-      <c r="D61" s="12" t="inlineStr">
+      <c r="D61" s="11" t="inlineStr">
         <is>
           <t>1 / 1.4 / 0/11</t>
         </is>
       </c>
-      <c r="E61" s="12" t="inlineStr">
+      <c r="E61" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F61" s="12" t="inlineStr">
+      <c r="F61" s="11" t="inlineStr">
         <is>
           <t>2 / 1.2 / 0/9</t>
         </is>
       </c>
-      <c r="G61" s="12" t="inlineStr">
+      <c r="G61" s="11" t="inlineStr">
         <is>
           <t>3 / 2.5 / 0/6</t>
         </is>
       </c>
-      <c r="H61" s="12" t="inlineStr">
+      <c r="H61" s="11" t="inlineStr">
         <is>
           <t>0 / 0.1 / 0/8</t>
         </is>
       </c>
-      <c r="I61" s="12" t="inlineStr"/>
+      <c r="I61" s="11" t="inlineStr"/>
     </row>
     <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="11" t="inlineStr">
+      <c r="A62" s="10" t="inlineStr">
         <is>
           <t>Suffolk</t>
         </is>
       </c>
-      <c r="B62" s="11" t="inlineStr"/>
-      <c r="C62" s="11" t="inlineStr">
+      <c r="B62" s="10" t="inlineStr"/>
+      <c r="C62" s="10" t="inlineStr">
         <is>
           <t>0 / 0.9 / 0/11</t>
         </is>
       </c>
-      <c r="D62" s="11" t="inlineStr">
+      <c r="D62" s="10" t="inlineStr">
         <is>
           <t>3 / 1.6 / 0/11</t>
         </is>
       </c>
-      <c r="E62" s="11" t="inlineStr"/>
-      <c r="F62" s="11" t="inlineStr">
+      <c r="E62" s="10" t="inlineStr"/>
+      <c r="F62" s="10" t="inlineStr">
         <is>
           <t>2 / 0.3 / 0/9</t>
         </is>
       </c>
-      <c r="G62" s="11" t="inlineStr">
+      <c r="G62" s="10" t="inlineStr">
         <is>
           <t>1 / 1.8 / 0/6</t>
         </is>
       </c>
-      <c r="H62" s="11" t="inlineStr">
+      <c r="H62" s="10" t="inlineStr">
         <is>
           <t>1 / 1.0 / 0/8</t>
         </is>
       </c>
-      <c r="I62" s="11" t="inlineStr">
+      <c r="I62" s="10" t="inlineStr">
         <is>
           <t>1 / 0.4 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="12" t="inlineStr">
+      <c r="A63" s="11" t="inlineStr">
         <is>
           <t>Surrey</t>
         </is>
       </c>
-      <c r="B63" s="12" t="inlineStr"/>
-      <c r="C63" s="12" t="inlineStr"/>
-      <c r="D63" s="12" t="inlineStr">
+      <c r="B63" s="11" t="inlineStr"/>
+      <c r="C63" s="11" t="inlineStr"/>
+      <c r="D63" s="11" t="inlineStr">
         <is>
           <t>6 / 4.5 / 4/11</t>
         </is>
       </c>
-      <c r="E63" s="12" t="inlineStr">
+      <c r="E63" s="11" t="inlineStr">
         <is>
           <t>5 / 4.0 / 0/9</t>
         </is>
       </c>
-      <c r="F63" s="12" t="inlineStr"/>
-      <c r="G63" s="12" t="inlineStr">
+      <c r="F63" s="11" t="inlineStr"/>
+      <c r="G63" s="11" t="inlineStr">
         <is>
           <t>4 / 5.0 / 2/6</t>
         </is>
       </c>
-      <c r="H63" s="12" t="inlineStr">
+      <c r="H63" s="11" t="inlineStr">
         <is>
           <t>3 / 2.0 / 0/8</t>
         </is>
       </c>
-      <c r="I63" s="12" t="inlineStr"/>
+      <c r="I63" s="11" t="inlineStr"/>
     </row>
     <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="11" t="inlineStr">
+      <c r="A64" s="10" t="inlineStr">
         <is>
           <t>Sussex</t>
         </is>
       </c>
-      <c r="B64" s="11" t="inlineStr"/>
-      <c r="C64" s="11" t="inlineStr"/>
-      <c r="D64" s="11" t="inlineStr">
+      <c r="B64" s="10" t="inlineStr"/>
+      <c r="C64" s="10" t="inlineStr"/>
+      <c r="D64" s="10" t="inlineStr">
         <is>
           <t>7 / 3.6 / 1/11</t>
         </is>
       </c>
-      <c r="E64" s="11" t="inlineStr">
+      <c r="E64" s="10" t="inlineStr">
         <is>
           <t>4 / 2.0 / 0/9</t>
         </is>
       </c>
-      <c r="F64" s="11" t="inlineStr">
+      <c r="F64" s="10" t="inlineStr">
         <is>
           <t>5 / 2.6 / 0/9</t>
         </is>
       </c>
-      <c r="G64" s="11" t="inlineStr">
+      <c r="G64" s="10" t="inlineStr">
         <is>
           <t>4 / 4.2 / 0/6</t>
         </is>
       </c>
-      <c r="H64" s="11" t="inlineStr">
+      <c r="H64" s="10" t="inlineStr">
         <is>
           <t>6 / 5.8 / 6/8</t>
         </is>
       </c>
-      <c r="I64" s="11" t="inlineStr">
+      <c r="I64" s="10" t="inlineStr">
         <is>
           <t>4 / 2.8 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="12" t="inlineStr">
+      <c r="A65" s="11" t="inlineStr">
         <is>
           <t>Wales - Mid</t>
         </is>
       </c>
-      <c r="B65" s="12" t="inlineStr">
+      <c r="B65" s="11" t="inlineStr">
         <is>
           <t>0 / 0.1 / 0/10</t>
         </is>
       </c>
-      <c r="C65" s="12" t="inlineStr">
+      <c r="C65" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="D65" s="12" t="inlineStr">
+      <c r="D65" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="E65" s="12" t="inlineStr">
+      <c r="E65" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F65" s="12" t="inlineStr">
+      <c r="F65" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="G65" s="12" t="inlineStr">
+      <c r="G65" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
-      <c r="H65" s="12" t="inlineStr">
+      <c r="H65" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
-      <c r="I65" s="12" t="inlineStr">
+      <c r="I65" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="11" t="inlineStr">
+      <c r="A66" s="10" t="inlineStr">
         <is>
           <t>Wales - West</t>
         </is>
       </c>
-      <c r="B66" s="11" t="inlineStr">
+      <c r="B66" s="10" t="inlineStr">
         <is>
           <t>3 / 1.9 / 0/10</t>
         </is>
       </c>
-      <c r="C66" s="11" t="inlineStr">
+      <c r="C66" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="D66" s="11" t="inlineStr">
+      <c r="D66" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="E66" s="11" t="inlineStr">
+      <c r="E66" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F66" s="11" t="inlineStr">
+      <c r="F66" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="G66" s="11" t="inlineStr">
+      <c r="G66" s="10" t="inlineStr">
         <is>
           <t>0 / 0.7 / 0/6</t>
         </is>
       </c>
-      <c r="H66" s="11" t="inlineStr">
+      <c r="H66" s="10" t="inlineStr">
         <is>
           <t>0 / 0.1 / 0/8</t>
         </is>
       </c>
-      <c r="I66" s="11" t="inlineStr">
+      <c r="I66" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="12" t="inlineStr">
+      <c r="A67" s="11" t="inlineStr">
         <is>
           <t>Wales South - Cardiff &amp; Vale</t>
         </is>
       </c>
-      <c r="B67" s="12" t="inlineStr">
+      <c r="B67" s="11" t="inlineStr">
         <is>
           <t>8 / 4.4 / 2/10</t>
         </is>
       </c>
-      <c r="C67" s="12" t="inlineStr">
+      <c r="C67" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="D67" s="12" t="inlineStr">
+      <c r="D67" s="11" t="inlineStr">
         <is>
           <t>3 / 1.7 / 0/10</t>
         </is>
       </c>
-      <c r="E67" s="12" t="inlineStr">
+      <c r="E67" s="11" t="inlineStr">
         <is>
           <t>2 / 1.3 / 0/9</t>
         </is>
       </c>
-      <c r="F67" s="12" t="inlineStr">
+      <c r="F67" s="11" t="inlineStr">
         <is>
           <t>2 / 0.9 / 0/9</t>
         </is>
       </c>
-      <c r="G67" s="12" t="inlineStr">
+      <c r="G67" s="11" t="inlineStr">
         <is>
           <t>0 / 1.2 / 0/6</t>
         </is>
       </c>
-      <c r="H67" s="12" t="inlineStr">
+      <c r="H67" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
-      <c r="I67" s="12" t="inlineStr">
+      <c r="I67" s="11" t="inlineStr">
         <is>
           <t>1 / 0.2 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="11" t="inlineStr">
+      <c r="A68" s="10" t="inlineStr">
         <is>
           <t>Wales South - Gwent</t>
         </is>
       </c>
-      <c r="B68" s="11" t="inlineStr">
+      <c r="B68" s="10" t="inlineStr">
         <is>
           <t>1 / 2.7 / 0/10</t>
         </is>
       </c>
-      <c r="C68" s="11" t="inlineStr">
+      <c r="C68" s="10" t="inlineStr">
         <is>
           <t>0 / 0.1 / 0/10</t>
         </is>
       </c>
-      <c r="D68" s="11" t="inlineStr">
+      <c r="D68" s="10" t="inlineStr">
         <is>
           <t>1 / 0.3 / 0/10</t>
         </is>
       </c>
-      <c r="E68" s="11" t="inlineStr">
+      <c r="E68" s="10" t="inlineStr">
         <is>
           <t>2 / 1.3 / 0/9</t>
         </is>
       </c>
-      <c r="F68" s="11" t="inlineStr">
+      <c r="F68" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="G68" s="11" t="inlineStr">
+      <c r="G68" s="10" t="inlineStr">
         <is>
           <t>0 / 0.7 / 0/6</t>
         </is>
       </c>
-      <c r="H68" s="11" t="inlineStr">
+      <c r="H68" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
-      <c r="I68" s="11" t="inlineStr">
+      <c r="I68" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="12" t="inlineStr">
+      <c r="A69" s="11" t="inlineStr">
         <is>
           <t>Wales South - Swansea Bay</t>
         </is>
       </c>
-      <c r="B69" s="12" t="inlineStr">
+      <c r="B69" s="11" t="inlineStr">
         <is>
           <t>3 / 3.1 / 1/10</t>
         </is>
       </c>
-      <c r="C69" s="12" t="inlineStr">
+      <c r="C69" s="11" t="inlineStr">
         <is>
           <t>0 / 0.1 / 0/10</t>
         </is>
       </c>
-      <c r="D69" s="12" t="inlineStr">
+      <c r="D69" s="11" t="inlineStr">
         <is>
           <t>1 / 1.8 / 0/10</t>
         </is>
       </c>
-      <c r="E69" s="12" t="inlineStr">
+      <c r="E69" s="11" t="inlineStr">
         <is>
           <t>1 / 0.7 / 0/9</t>
         </is>
       </c>
-      <c r="F69" s="12" t="inlineStr">
+      <c r="F69" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="G69" s="12" t="inlineStr">
+      <c r="G69" s="11" t="inlineStr">
         <is>
           <t>0 / 0.3 / 0/6</t>
         </is>
       </c>
-      <c r="H69" s="12" t="inlineStr">
+      <c r="H69" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
-      <c r="I69" s="12" t="inlineStr">
+      <c r="I69" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="11" t="inlineStr">
+      <c r="A70" s="10" t="inlineStr">
         <is>
           <t>Wales South - Valleys</t>
         </is>
       </c>
-      <c r="B70" s="11" t="inlineStr">
+      <c r="B70" s="10" t="inlineStr">
         <is>
           <t>10 / 2.2 / 2/10</t>
         </is>
       </c>
-      <c r="C70" s="11" t="inlineStr">
+      <c r="C70" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="D70" s="11" t="inlineStr">
+      <c r="D70" s="10" t="inlineStr">
         <is>
           <t>1 / 0.4 / 0/10</t>
         </is>
       </c>
-      <c r="E70" s="11" t="inlineStr">
+      <c r="E70" s="10" t="inlineStr">
         <is>
           <t>4 / 2.6 / 0/9</t>
         </is>
       </c>
-      <c r="F70" s="11" t="inlineStr">
+      <c r="F70" s="10" t="inlineStr">
         <is>
           <t>0 / 0.4 / 0/9</t>
         </is>
       </c>
-      <c r="G70" s="11" t="inlineStr">
+      <c r="G70" s="10" t="inlineStr">
         <is>
           <t>0 / 0.2 / 0/6</t>
         </is>
       </c>
-      <c r="H70" s="11" t="inlineStr">
+      <c r="H70" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
-      <c r="I70" s="11" t="inlineStr">
+      <c r="I70" s="10" t="inlineStr">
         <is>
           <t>4 / 0.8 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="12" t="inlineStr">
+      <c r="A71" s="11" t="inlineStr">
         <is>
           <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
-      <c r="B71" s="12" t="inlineStr"/>
-      <c r="C71" s="12" t="inlineStr">
+      <c r="B71" s="11" t="inlineStr"/>
+      <c r="C71" s="11" t="inlineStr">
         <is>
           <t>1 / 1.0 / 0/11</t>
         </is>
       </c>
-      <c r="D71" s="12" t="inlineStr">
+      <c r="D71" s="11" t="inlineStr">
         <is>
           <t>11 / 4.0 / 1/11</t>
         </is>
       </c>
-      <c r="E71" s="12" t="inlineStr">
+      <c r="E71" s="11" t="inlineStr">
         <is>
           <t>3 / 3.9 / 2/9</t>
         </is>
       </c>
-      <c r="F71" s="12" t="inlineStr"/>
-      <c r="G71" s="12" t="inlineStr">
+      <c r="F71" s="11" t="inlineStr"/>
+      <c r="G71" s="11" t="inlineStr">
         <is>
           <t>3 / 2.7 / 0/6</t>
         </is>
       </c>
-      <c r="H71" s="12" t="inlineStr"/>
-      <c r="I71" s="12" t="inlineStr">
+      <c r="H71" s="11" t="inlineStr"/>
+      <c r="I71" s="11" t="inlineStr">
         <is>
           <t>5 / 3.4 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="11" t="inlineStr">
+      <c r="A72" s="10" t="inlineStr">
         <is>
           <t>West Midlands - Black Country</t>
         </is>
       </c>
-      <c r="B72" s="11" t="inlineStr"/>
-      <c r="C72" s="11" t="inlineStr">
+      <c r="B72" s="10" t="inlineStr"/>
+      <c r="C72" s="10" t="inlineStr">
         <is>
           <t>1 / 1.1 / 0/11</t>
         </is>
       </c>
-      <c r="D72" s="11" t="inlineStr">
+      <c r="D72" s="10" t="inlineStr">
         <is>
           <t>1 / 1.0 / 0/11</t>
         </is>
       </c>
-      <c r="E72" s="11" t="inlineStr">
+      <c r="E72" s="10" t="inlineStr">
         <is>
           <t>3 / 1.1 / 0/9</t>
         </is>
       </c>
-      <c r="F72" s="11" t="inlineStr">
+      <c r="F72" s="10" t="inlineStr">
         <is>
           <t>1 / 0.4 / 0/9</t>
         </is>
       </c>
-      <c r="G72" s="11" t="inlineStr">
+      <c r="G72" s="10" t="inlineStr">
         <is>
           <t>1 / 1.3 / 0/6</t>
         </is>
       </c>
-      <c r="H72" s="11" t="inlineStr">
+      <c r="H72" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
-      <c r="I72" s="11" t="inlineStr">
+      <c r="I72" s="10" t="inlineStr">
         <is>
           <t>1 / 1.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="12" t="inlineStr">
+      <c r="A73" s="11" t="inlineStr">
         <is>
           <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
-      <c r="B73" s="12" t="inlineStr"/>
-      <c r="C73" s="12" t="inlineStr">
+      <c r="B73" s="11" t="inlineStr"/>
+      <c r="C73" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
-      <c r="D73" s="12" t="inlineStr">
+      <c r="D73" s="11" t="inlineStr">
         <is>
           <t>6 / 1.3 / 1/11</t>
         </is>
       </c>
-      <c r="E73" s="12" t="inlineStr">
+      <c r="E73" s="11" t="inlineStr">
         <is>
           <t>1 / 0.6 / 0/9</t>
         </is>
       </c>
-      <c r="F73" s="12" t="inlineStr">
+      <c r="F73" s="11" t="inlineStr">
         <is>
           <t>5 / 2.4 / 0/9</t>
         </is>
       </c>
-      <c r="G73" s="12" t="inlineStr">
+      <c r="G73" s="11" t="inlineStr">
         <is>
           <t>3 / 2.2 / 0/6</t>
         </is>
       </c>
-      <c r="H73" s="12" t="inlineStr">
+      <c r="H73" s="11" t="inlineStr">
         <is>
           <t>3 / 3.1 / 0/8</t>
         </is>
       </c>
-      <c r="I73" s="12" t="inlineStr">
+      <c r="I73" s="11" t="inlineStr">
         <is>
           <t>2 / 0.4 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="11" t="inlineStr">
+      <c r="A74" s="10" t="inlineStr">
         <is>
           <t>Wiltshire</t>
         </is>
       </c>
-      <c r="B74" s="11" t="inlineStr"/>
-      <c r="C74" s="11" t="inlineStr"/>
-      <c r="D74" s="11" t="inlineStr">
+      <c r="B74" s="10" t="inlineStr"/>
+      <c r="C74" s="10" t="inlineStr"/>
+      <c r="D74" s="10" t="inlineStr">
         <is>
           <t>3 / 2.0 / 0/11</t>
         </is>
       </c>
-      <c r="E74" s="11" t="inlineStr">
+      <c r="E74" s="10" t="inlineStr">
         <is>
           <t>4 / 3.0 / 0/9</t>
         </is>
       </c>
-      <c r="F74" s="11" t="inlineStr">
+      <c r="F74" s="10" t="inlineStr">
         <is>
           <t>3 / 1.1 / 0/9</t>
         </is>
       </c>
-      <c r="G74" s="11" t="inlineStr">
+      <c r="G74" s="10" t="inlineStr">
         <is>
           <t>0 / 2.7 / 0/6</t>
         </is>
       </c>
-      <c r="H74" s="11" t="inlineStr">
+      <c r="H74" s="10" t="inlineStr">
         <is>
           <t>0 / 0.6 / 0/8</t>
         </is>
       </c>
-      <c r="I74" s="11" t="inlineStr">
+      <c r="I74" s="10" t="inlineStr">
         <is>
           <t>1 / 1.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="12" t="inlineStr">
+      <c r="A75" s="11" t="inlineStr">
         <is>
           <t>Worcestershire</t>
         </is>
       </c>
-      <c r="B75" s="12" t="inlineStr"/>
-      <c r="C75" s="12" t="inlineStr">
+      <c r="B75" s="11" t="inlineStr"/>
+      <c r="C75" s="11" t="inlineStr">
         <is>
           <t>0 / 1.3 / 0/11</t>
         </is>
       </c>
-      <c r="D75" s="12" t="inlineStr">
+      <c r="D75" s="11" t="inlineStr">
         <is>
           <t>1 / 2.1 / 0/11</t>
         </is>
       </c>
-      <c r="E75" s="12" t="inlineStr">
+      <c r="E75" s="11" t="inlineStr">
         <is>
           <t>2 / 0.4 / 0/9</t>
         </is>
       </c>
-      <c r="F75" s="12" t="inlineStr">
+      <c r="F75" s="11" t="inlineStr">
         <is>
           <t>2 / 1.4 / 0/9</t>
         </is>
       </c>
-      <c r="G75" s="12" t="inlineStr">
+      <c r="G75" s="11" t="inlineStr">
         <is>
           <t>0 / 0.8 / 0/6</t>
         </is>
       </c>
-      <c r="H75" s="12" t="inlineStr">
+      <c r="H75" s="11" t="inlineStr">
         <is>
           <t>0 / 0.2 / 0/8</t>
         </is>
       </c>
-      <c r="I75" s="12" t="inlineStr">
+      <c r="I75" s="11" t="inlineStr">
         <is>
           <t>1 / 0.4 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="11" t="inlineStr">
+      <c r="A76" s="10" t="inlineStr">
         <is>
           <t>Yorkshire - East</t>
         </is>
       </c>
-      <c r="B76" s="11" t="inlineStr"/>
-      <c r="C76" s="11" t="inlineStr">
+      <c r="B76" s="10" t="inlineStr"/>
+      <c r="C76" s="10" t="inlineStr">
         <is>
           <t>0 / 0.7 / 0/11</t>
         </is>
       </c>
-      <c r="D76" s="11" t="inlineStr">
+      <c r="D76" s="10" t="inlineStr">
         <is>
           <t>0 / 1.2 / 0/11</t>
         </is>
       </c>
-      <c r="E76" s="11" t="inlineStr">
+      <c r="E76" s="10" t="inlineStr">
         <is>
           <t>2 / 1.0 / 0/9</t>
         </is>
       </c>
-      <c r="F76" s="11" t="inlineStr">
+      <c r="F76" s="10" t="inlineStr">
         <is>
           <t>2 / 0.4 / 0/9</t>
         </is>
       </c>
-      <c r="G76" s="11" t="inlineStr">
+      <c r="G76" s="10" t="inlineStr">
         <is>
           <t>2 / 4.0 / 0/6</t>
         </is>
       </c>
-      <c r="H76" s="11" t="inlineStr">
+      <c r="H76" s="10" t="inlineStr">
         <is>
           <t>1 / 1.2 / 0/8</t>
         </is>
       </c>
-      <c r="I76" s="11" t="inlineStr">
+      <c r="I76" s="10" t="inlineStr">
         <is>
           <t>4 / 2.8 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="12" t="inlineStr">
+      <c r="A77" s="11" t="inlineStr">
         <is>
           <t>Yorkshire - North</t>
         </is>
       </c>
-      <c r="B77" s="12" t="inlineStr"/>
-      <c r="C77" s="12" t="inlineStr">
+      <c r="B77" s="11" t="inlineStr"/>
+      <c r="C77" s="11" t="inlineStr">
         <is>
           <t>1 / 3.5 / 0/11</t>
         </is>
       </c>
-      <c r="D77" s="12" t="inlineStr">
+      <c r="D77" s="11" t="inlineStr">
         <is>
           <t>3 / 0.9 / 0/11</t>
         </is>
       </c>
-      <c r="E77" s="12" t="inlineStr">
+      <c r="E77" s="11" t="inlineStr">
         <is>
           <t>0 / 0.1 / 0/9</t>
         </is>
       </c>
-      <c r="F77" s="12" t="inlineStr">
+      <c r="F77" s="11" t="inlineStr">
         <is>
           <t>12 / 2.7 / 1/9</t>
         </is>
       </c>
-      <c r="G77" s="12" t="inlineStr"/>
-      <c r="H77" s="12" t="inlineStr">
+      <c r="G77" s="11" t="inlineStr"/>
+      <c r="H77" s="11" t="inlineStr">
         <is>
           <t>2 / 1.5 / 0/8</t>
         </is>
       </c>
-      <c r="I77" s="12" t="inlineStr">
+      <c r="I77" s="11" t="inlineStr">
         <is>
           <t>2 / 1.0 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="11" t="inlineStr">
+      <c r="A78" s="10" t="inlineStr">
         <is>
           <t>Yorkshire - South</t>
         </is>
       </c>
-      <c r="B78" s="11" t="inlineStr"/>
-      <c r="C78" s="11" t="inlineStr"/>
-      <c r="D78" s="11" t="inlineStr">
+      <c r="B78" s="10" t="inlineStr"/>
+      <c r="C78" s="10" t="inlineStr"/>
+      <c r="D78" s="10" t="inlineStr">
         <is>
           <t>4 / 2.0 / 0/11</t>
         </is>
       </c>
-      <c r="E78" s="11" t="inlineStr">
+      <c r="E78" s="10" t="inlineStr">
         <is>
           <t>4 / 3.1 / 0/9</t>
         </is>
       </c>
-      <c r="F78" s="11" t="inlineStr">
+      <c r="F78" s="10" t="inlineStr">
         <is>
           <t>6 / 2.0 / 1/9</t>
         </is>
       </c>
-      <c r="G78" s="11" t="inlineStr">
+      <c r="G78" s="10" t="inlineStr">
         <is>
           <t>0 / 2.3 / 2/6</t>
         </is>
       </c>
-      <c r="H78" s="11" t="inlineStr">
+      <c r="H78" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
-      <c r="I78" s="11" t="inlineStr">
+      <c r="I78" s="10" t="inlineStr">
         <is>
           <t>4 / 1.4 / 0/5</t>
         </is>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="12" t="inlineStr">
+      <c r="A79" s="11" t="inlineStr">
         <is>
           <t>Yorkshire - West</t>
         </is>
       </c>
-      <c r="B79" s="12" t="inlineStr"/>
-      <c r="C79" s="12" t="inlineStr"/>
-      <c r="D79" s="12" t="inlineStr"/>
-      <c r="E79" s="12" t="inlineStr">
+      <c r="B79" s="11" t="inlineStr"/>
+      <c r="C79" s="11" t="inlineStr"/>
+      <c r="D79" s="11" t="inlineStr"/>
+      <c r="E79" s="11" t="inlineStr">
         <is>
           <t>4 / 4.0 / 0/9</t>
         </is>
       </c>
-      <c r="F79" s="12" t="inlineStr">
+      <c r="F79" s="11" t="inlineStr">
         <is>
           <t>16 / 5.6 / 3/9</t>
         </is>
       </c>
-      <c r="G79" s="12" t="inlineStr"/>
-      <c r="H79" s="12" t="inlineStr"/>
-      <c r="I79" s="12" t="inlineStr">
+      <c r="G79" s="11" t="inlineStr"/>
+      <c r="H79" s="11" t="inlineStr"/>
+      <c r="I79" s="11" t="inlineStr">
         <is>
           <t>3 / 2.6 / 0/5</t>
         </is>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1670</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="3">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>362</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1721</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="6">
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="4" t="inlineStr"/>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr"/>
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
       <c r="D15" s="4" t="inlineStr"/>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C23" s="5" t="n">
         <v>6</v>
@@ -1355,7 +1355,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
       <c r="D25" s="4" t="inlineStr"/>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
       <c r="D35" s="4" t="inlineStr"/>
@@ -1591,7 +1591,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C39" s="4" t="inlineStr"/>
       <c r="D39" s="4" t="inlineStr"/>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>1</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C47" s="4" t="inlineStr"/>
       <c r="D47" s="4" t="inlineStr"/>
@@ -1965,7 +1965,7 @@
         </is>
       </c>
       <c r="B61" s="5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C61" s="4" t="inlineStr"/>
       <c r="D61" s="4" t="inlineStr"/>
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C62" s="2" t="inlineStr"/>
       <c r="D62" s="2" t="inlineStr"/>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C64" s="3" t="n">
         <v>3</v>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="B73" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C73" s="4" t="inlineStr"/>
       <c r="D73" s="4" t="inlineStr"/>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="B75" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C75" s="4" t="inlineStr"/>
       <c r="D75" s="4" t="inlineStr"/>
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         </is>
       </c>
       <c r="B79" s="5" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C79" s="5" t="n">
         <v>1</v>
@@ -2387,37 +2387,37 @@
       <c r="B2" s="10" t="inlineStr"/>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/11</t>
+          <t>0 / 0.2 / 0/12</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
-          <t>2 / 2.2 / 0/11</t>
+          <t>2 / 2.2 / 0/12</t>
         </is>
       </c>
       <c r="E2" s="10" t="inlineStr">
         <is>
-          <t>4 / 3.8 / 0/9</t>
+          <t>4 / 3.8 / 0/10</t>
         </is>
       </c>
       <c r="F2" s="10" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/9</t>
+          <t>1 / 1.1 / 0/10</t>
         </is>
       </c>
       <c r="G2" s="10" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/6</t>
+          <t>1 / 0.7 / 0/7</t>
         </is>
       </c>
       <c r="H2" s="10" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/8</t>
+          <t>1 / 1.0 / 0/9</t>
         </is>
       </c>
       <c r="I2" s="10" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/5</t>
+          <t>1 / 1.0 / 0/6</t>
         </is>
       </c>
     </row>
@@ -2430,29 +2430,29 @@
       <c r="B3" s="11" t="inlineStr"/>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>0 / 3.5 / 3/11</t>
+          <t>0 / 3.2 / 3/12</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr">
         <is>
-          <t>7 / 1.7 / 1/11</t>
+          <t>8 / 2.2 / 2/12</t>
         </is>
       </c>
       <c r="E3" s="11" t="inlineStr">
         <is>
-          <t>2 / 0.7 / 0/9</t>
+          <t>2 / 0.8 / 0/10</t>
         </is>
       </c>
       <c r="F3" s="11" t="inlineStr"/>
       <c r="G3" s="11" t="inlineStr">
         <is>
-          <t>2 / 0.5 / 0/6</t>
+          <t>2 / 0.7 / 0/7</t>
         </is>
       </c>
       <c r="H3" s="11" t="inlineStr"/>
       <c r="I3" s="11" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/5</t>
+          <t>1 / 0.3 / 0/6</t>
         </is>
       </c>
     </row>
@@ -2465,29 +2465,29 @@
       <c r="B4" s="10" t="inlineStr"/>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/11</t>
+          <t>0 / 0.9 / 0/12</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr"/>
       <c r="E4" s="10" t="inlineStr">
         <is>
-          <t>3 / 2.9 / 1/9</t>
+          <t>3 / 2.9 / 1/10</t>
         </is>
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>8 / 2.7 / 1/9</t>
+          <t>8 / 3.2 / 2/10</t>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr"/>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>2 / 1.8 / 0/8</t>
+          <t>2 / 1.8 / 0/9</t>
         </is>
       </c>
       <c r="I4" s="10" t="inlineStr">
         <is>
-          <t>5 / 2.0 / 0/5</t>
+          <t>4 / 2.3 / 0/6</t>
         </is>
       </c>
     </row>
@@ -2500,33 +2500,33 @@
       <c r="B5" s="11" t="inlineStr"/>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/11</t>
+          <t>0 / 0.7 / 0/12</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/11</t>
+          <t>1 / 0.7 / 0/12</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/9</t>
+          <t>1 / 1.0 / 0/10</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr"/>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>2 / 2.2 / 0/6</t>
+          <t>2 / 2.1 / 0/7</t>
         </is>
       </c>
       <c r="H5" s="11" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/8</t>
+          <t>1 / 0.8 / 0/9</t>
         </is>
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>6 / 2.4 / 1/5</t>
+          <t>5 / 2.8 / 1/6</t>
         </is>
       </c>
     </row>
@@ -2539,37 +2539,37 @@
       <c r="B6" s="10" t="inlineStr"/>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/11</t>
+          <t>0 / 0.1 / 0/12</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>3 / 2.5 / 0/11</t>
+          <t>3 / 2.6 / 0/12</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/9</t>
+          <t>1 / 1.2 / 0/10</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>6 / 2.6 / 1/9</t>
+          <t>6 / 2.9 / 2/10</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>3 / 4.5 / 2/6</t>
+          <t>3 / 4.3 / 2/7</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/8</t>
+          <t>0 / 0.1 / 0/9</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/5</t>
+          <t>1 / 1.0 / 0/6</t>
         </is>
       </c>
     </row>
@@ -2582,37 +2582,37 @@
       <c r="B7" s="11" t="inlineStr"/>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/11</t>
+          <t>0 / 0.6 / 0/12</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>3 / 1.5 / 0/11</t>
+          <t>3 / 1.7 / 0/12</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/9</t>
+          <t>0 / 0.2 / 0/10</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>3 / 1.0 / 0/9</t>
+          <t>2 / 1.1 / 0/10</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/6</t>
+          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>3 / 1.8 / 0/5</t>
+          <t>3 / 2.0 / 0/6</t>
         </is>
       </c>
     </row>
@@ -2625,37 +2625,37 @@
       <c r="B8" s="10" t="inlineStr"/>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>1 / 1.4 / 0/11</t>
+          <t>1 / 1.3 / 0/12</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>6 / 2.1 / 1/11</t>
+          <t>5 / 2.3 / 1/12</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>2 / 1.3 / 0/9</t>
+          <t>2 / 1.4 / 0/10</t>
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/9</t>
+          <t>1 / 0.4 / 0/10</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>7 / 4.7 / 2/6</t>
+          <t>7 / 5.0 / 3/7</t>
         </is>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/8</t>
+          <t>0 / 0.1 / 0/9</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
     </row>
@@ -2668,37 +2668,37 @@
       <c r="B9" s="11" t="inlineStr"/>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>0 / 1.5 / 0/11</t>
+          <t>0 / 1.3 / 0/12</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>0 / 2.0 / 0/11</t>
+          <t>0 / 1.8 / 0/12</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>2 / 1.0 / 0/9</t>
+          <t>2 / 1.1 / 0/10</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>6 / 2.2 / 1/9</t>
+          <t>6 / 2.6 / 2/10</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>1 / 2.2 / 0/6</t>
+          <t>1 / 2.0 / 0/7</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/8</t>
+          <t>1 / 0.3 / 0/9</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/5</t>
+          <t>1 / 0.3 / 0/6</t>
         </is>
       </c>
     </row>
@@ -2711,37 +2711,37 @@
       <c r="B10" s="10" t="inlineStr"/>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>0 / 1.5 / 0/11</t>
+          <t>0 / 1.3 / 0/12</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>2 / 0.6 / 0/11</t>
+          <t>2 / 0.8 / 0/12</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/10</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>0 / 0.3 / 0/7</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>0 / 0.2 / 0/9</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>0 / 0.3 / 0/6</t>
-        </is>
-      </c>
-      <c r="H10" s="10" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
       <c r="I10" s="10" t="inlineStr">
         <is>
-          <t>5 / 1.0 / 0/5</t>
+          <t>31 / 6.0 / 1/6</t>
         </is>
       </c>
     </row>
@@ -2753,42 +2753,42 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>1 / 1.6 / 0/11</t>
+          <t>1 / 1.6 / 0/12</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>0 / 2.8 / 3/11</t>
+          <t>0 / 2.6 / 3/12</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/7</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/9</t>
-        </is>
-      </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>0 / 0.2 / 0/6</t>
-        </is>
-      </c>
-      <c r="H11" s="11" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
     </row>
@@ -2800,38 +2800,38 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/11</t>
+          <t>1 / 1.1 / 0/12</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr"/>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/11</t>
+          <t>1 / 0.8 / 0/12</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>2 / 0.6 / 0/9</t>
+          <t>2 / 0.7 / 0/10</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/6</t>
+          <t>0 / 0.6 / 0/7</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/8</t>
+          <t>1 / 0.2 / 0/9</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
     </row>
@@ -2843,42 +2843,42 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>1 / 1.8 / 0/11</t>
+          <t>0 / 1.7 / 0/12</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/11</t>
+          <t>0 / 0.7 / 0/12</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.4 / 0/7</t>
+        </is>
+      </c>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/9</t>
-        </is>
-      </c>
-      <c r="G13" s="11" t="inlineStr">
-        <is>
-          <t>0 / 0.5 / 0/6</t>
-        </is>
-      </c>
-      <c r="H13" s="11" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
     </row>
@@ -2891,37 +2891,37 @@
       <c r="B14" s="10" t="inlineStr"/>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/11</t>
+          <t>0 / 0.3 / 0/12</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>3 / 2.5 / 0/11</t>
+          <t>3 / 2.5 / 0/12</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>2 / 0.6 / 0/9</t>
+          <t>2 / 0.7 / 0/10</t>
         </is>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>2 / 0.9 / 0/9</t>
+          <t>3 / 1.1 / 0/10</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>2 / 3.2 / 0/6</t>
+          <t>2 / 3.0 / 0/7</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
-          <t>3 / 1.4 / 0/5</t>
+          <t>3 / 1.7 / 0/6</t>
         </is>
       </c>
     </row>
@@ -2934,33 +2934,33 @@
       <c r="B15" s="11" t="inlineStr"/>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/11</t>
+          <t>3 / 0.4 / 0/12</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>5 / 3.2 / 0/11</t>
+          <t>5 / 3.3 / 0/12</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>3 / 2.1 / 0/9</t>
+          <t>3 / 2.2 / 0/10</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>6 / 1.2 / 1/9</t>
+          <t>6 / 1.7 / 2/10</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr"/>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/8</t>
+          <t>1 / 1.1 / 0/9</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>3 / 1.0 / 0/5</t>
+          <t>2 / 1.2 / 0/6</t>
         </is>
       </c>
     </row>
@@ -2973,37 +2973,37 @@
       <c r="B16" s="10" t="inlineStr"/>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/11</t>
+          <t>1 / 1.0 / 0/12</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>5 / 3.9 / 2/11</t>
+          <t>4 / 3.9 / 2/12</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/9</t>
+          <t>0 / 0.2 / 0/10</t>
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>3 / 1.4 / 0/9</t>
+          <t>3 / 1.6 / 0/10</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>1 / 3.2 / 0/6</t>
+          <t>1 / 2.9 / 0/7</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/5</t>
+          <t>1 / 0.3 / 0/6</t>
         </is>
       </c>
     </row>
@@ -3016,33 +3016,33 @@
       <c r="B17" s="11" t="inlineStr"/>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/11</t>
+          <t>0 / 0.7 / 0/12</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>5 / 2.1 / 0/11</t>
+          <t>5 / 2.3 / 0/12</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr"/>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>6 / 2.8 / 1/9</t>
+          <t>5 / 3.0 / 1/10</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
-          <t>5 / 5.8 / 2/6</t>
+          <t>5 / 5.7 / 2/7</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/8</t>
+          <t>1 / 1.1 / 0/9</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>4 / 2.0 / 0/5</t>
+          <t>4 / 2.3 / 0/6</t>
         </is>
       </c>
     </row>
@@ -3055,33 +3055,33 @@
       <c r="B18" s="10" t="inlineStr"/>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/11</t>
+          <t>1 / 0.3 / 0/12</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>4 / 1.4 / 0/11</t>
+          <t>4 / 1.6 / 0/12</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>8 / 2.9 / 1/9</t>
+          <t>7 / 3.3 / 2/10</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr"/>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>2 / 1.2 / 0/8</t>
+          <t>1 / 1.2 / 0/9</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
-          <t>3 / 1.6 / 0/5</t>
+          <t>3 / 1.8 / 0/6</t>
         </is>
       </c>
     </row>
@@ -3094,25 +3094,25 @@
       <c r="B19" s="11" t="inlineStr"/>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/11</t>
+          <t>1 / 1.2 / 0/12</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr"/>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>3 / 3.9 / 2/9</t>
+          <t>4 / 3.9 / 2/10</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr"/>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>3 / 3.7 / 0/6</t>
+          <t>4 / 3.7 / 0/7</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr"/>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>3 / 2.2 / 0/5</t>
+          <t>3 / 2.3 / 0/6</t>
         </is>
       </c>
     </row>
@@ -3124,42 +3124,42 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>3 / 3.1 / 1/11</t>
+          <t>3 / 3.1 / 1/12</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/11</t>
+          <t>0 / 0.2 / 0/12</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/6</t>
+          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/8</t>
+          <t>0 / 0.1 / 0/9</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/5</t>
+          <t>1 / 0.3 / 0/6</t>
         </is>
       </c>
     </row>
@@ -3172,37 +3172,37 @@
       <c r="B21" s="11" t="inlineStr"/>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.8 / 0/11</t>
+          <t>0 / 0.8 / 0/12</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/11</t>
+          <t>1 / 0.8 / 0/12</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/9</t>
+          <t>1 / 0.5 / 0/10</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>2 / 0.2 / 0/9</t>
+          <t>2 / 0.4 / 0/10</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/6</t>
+          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>3 / 0.6 / 0/5</t>
+          <t>3 / 1.0 / 0/6</t>
         </is>
       </c>
     </row>
@@ -3215,37 +3215,37 @@
       <c r="B22" s="10" t="inlineStr"/>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/11</t>
+          <t>1 / 0.8 / 0/12</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/9</t>
+          <t>1 / 0.4 / 0/10</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/6</t>
+          <t>0 / 0.3 / 0/7</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/8</t>
+          <t>1 / 1.0 / 0/9</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/5</t>
+          <t>1 / 1.0 / 0/6</t>
         </is>
       </c>
     </row>
@@ -3259,27 +3259,27 @@
       <c r="C23" s="11" t="inlineStr"/>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>14 / 7.4 / 7/11</t>
+          <t>14 / 7.9 / 8/12</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>0 / 1.7 / 0/9</t>
+          <t>0 / 1.5 / 0/10</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>10 / 5.0 / 2/9</t>
+          <t>10 / 5.5 / 3/10</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>1 / 2.8 / 0/6</t>
+          <t>1 / 2.6 / 0/7</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>4 / 3.5 / 0/8</t>
+          <t>4 / 3.6 / 0/9</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr"/>
@@ -3292,42 +3292,42 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>0 / 1.4 / 0/11</t>
+          <t>0 / 1.2 / 0/12</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/11</t>
+          <t>1 / 0.3 / 0/12</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>0 / 1.0 / 0/7</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/9</t>
-        </is>
-      </c>
-      <c r="G24" s="10" t="inlineStr">
-        <is>
-          <t>0 / 1.2 / 0/6</t>
-        </is>
-      </c>
-      <c r="H24" s="10" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
       <c r="I24" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
     </row>
@@ -3340,37 +3340,37 @@
       <c r="B25" s="11" t="inlineStr"/>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>3 / 2.3 / 0/11</t>
+          <t>3 / 2.3 / 0/12</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>10 / 4.0 / 1/11</t>
+          <t>9 / 4.4 / 2/12</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>1 / 1.6 / 0/9</t>
+          <t>2 / 1.6 / 0/10</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>9 / 2.1 / 1/9</t>
+          <t>9 / 2.8 / 2/10</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/6</t>
+          <t>1 / 1.0 / 0/7</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/8</t>
+          <t>1 / 0.3 / 0/9</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>4 / 1.6 / 0/5</t>
+          <t>3 / 1.8 / 0/6</t>
         </is>
       </c>
     </row>
@@ -3384,32 +3384,32 @@
       <c r="C26" s="10" t="inlineStr"/>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>8 / 4.5 / 1/11</t>
+          <t>9 / 4.9 / 2/12</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>3 / 4.3 / 2/9</t>
+          <t>3 / 4.2 / 2/10</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>7 / 2.8 / 1/9</t>
+          <t>7 / 3.2 / 2/10</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>0 / 3.0 / 1/6</t>
+          <t>0 / 2.6 / 1/7</t>
         </is>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>2 / 1.6 / 0/8</t>
+          <t>2 / 1.7 / 0/9</t>
         </is>
       </c>
       <c r="I26" s="10" t="inlineStr">
         <is>
-          <t>2 / 0.8 / 0/5</t>
+          <t>3 / 1.2 / 0/6</t>
         </is>
       </c>
     </row>
@@ -3421,42 +3421,42 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/11</t>
+          <t>0 / 0.8 / 0/12</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>2 / 1.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.3 / 0/7</t>
+        </is>
+      </c>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
-        <is>
-          <t>2 / 0.9 / 0/9</t>
-        </is>
-      </c>
-      <c r="G27" s="11" t="inlineStr">
-        <is>
-          <t>1 / 0.3 / 0/6</t>
-        </is>
-      </c>
-      <c r="H27" s="11" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
     </row>
@@ -3468,42 +3468,42 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>3 / 2.8 / 0/11</t>
+          <t>3 / 2.8 / 0/12</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/11</t>
+          <t>0 / 0.2 / 0/12</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/11</t>
+          <t>1 / 0.3 / 0/12</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/6</t>
+          <t>1 / 0.6 / 0/7</t>
         </is>
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/8</t>
+          <t>0 / 0.2 / 0/9</t>
         </is>
       </c>
       <c r="I28" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
     </row>
@@ -3515,42 +3515,42 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>3 / 2.5 / 0/11</t>
+          <t>3 / 2.5 / 0/12</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/11</t>
+          <t>0 / 0.7 / 0/12</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/11</t>
+          <t>0 / 0.2 / 0/12</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/9</t>
+          <t>0 / 0.2 / 0/10</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>3 / 1.1 / 0/9</t>
+          <t>3 / 1.3 / 0/10</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/6</t>
+          <t>1 / 1.1 / 0/7</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
     </row>
@@ -3562,42 +3562,42 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/11</t>
+          <t>2 / 1.2 / 0/12</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>0 / 1.2 / 0/11</t>
+          <t>0 / 1.1 / 0/12</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/7</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0.2 / 0/9</t>
+        </is>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/6</t>
-        </is>
-      </c>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0.1 / 0/8</t>
-        </is>
-      </c>
-      <c r="I30" s="10" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
@@ -3609,42 +3609,42 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>0 / 1.3 / 0/10</t>
+          <t>0 / 1.2 / 0/11</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/10</t>
+          <t>0 / 0.1 / 0/11</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/10</t>
+          <t>1 / 1.2 / 0/11</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F31" s="11" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/9</t>
-        </is>
-      </c>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="I31" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/6</t>
-        </is>
-      </c>
-      <c r="H31" s="11" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
-      <c r="I31" s="11" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
@@ -3657,37 +3657,37 @@
       <c r="B32" s="10" t="inlineStr"/>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/11</t>
+          <t>0 / 0.1 / 0/12</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/11</t>
+          <t>2 / 1.6 / 0/12</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>2 / 1.3 / 0/9</t>
+          <t>2 / 1.4 / 0/10</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>2 / 1.0 / 0/9</t>
+          <t>2 / 1.1 / 0/10</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>2 / 3.0 / 1/6</t>
+          <t>2 / 2.9 / 1/7</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/8</t>
+          <t>1 / 0.8 / 0/9</t>
         </is>
       </c>
       <c r="I32" s="10" t="inlineStr">
         <is>
-          <t>2 / 2.8 / 0/5</t>
+          <t>2 / 2.7 / 0/6</t>
         </is>
       </c>
     </row>
@@ -3700,37 +3700,37 @@
       <c r="B33" s="11" t="inlineStr"/>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>0 / 1.7 / 0/11</t>
+          <t>0 / 1.6 / 0/12</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>4 / 1.2 / 0/11</t>
+          <t>5 / 1.5 / 0/12</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
+          <t>2 / 1.5 / 0/10</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>3 / 2.7 / 0/10</t>
+        </is>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>1 / 2.6 / 0/7</t>
+        </is>
+      </c>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
           <t>2 / 1.4 / 0/9</t>
         </is>
       </c>
-      <c r="F33" s="11" t="inlineStr">
-        <is>
-          <t>3 / 2.7 / 0/9</t>
-        </is>
-      </c>
-      <c r="G33" s="11" t="inlineStr">
-        <is>
-          <t>1 / 2.8 / 0/6</t>
-        </is>
-      </c>
-      <c r="H33" s="11" t="inlineStr">
-        <is>
-          <t>1 / 1.4 / 0/8</t>
-        </is>
-      </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>2 / 1.0 / 0/5</t>
+          <t>1 / 1.0 / 0/6</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       <c r="F34" s="10" t="inlineStr"/>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>10 / 5.2 / 2/6</t>
+          <t>7 / 5.4 / 3/7</t>
         </is>
       </c>
       <c r="H34" s="10" t="inlineStr"/>
@@ -3762,37 +3762,37 @@
       <c r="B35" s="11" t="inlineStr"/>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/11</t>
+          <t>0 / 0.3 / 0/12</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/11</t>
+          <t>0 / 0.2 / 0/12</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/9</t>
+          <t>1 / 0.5 / 0/10</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>5 / 1.9 / 0/9</t>
+          <t>6 / 2.3 / 1/10</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/6</t>
+          <t>1 / 0.6 / 0/7</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/8</t>
+          <t>0 / 0.1 / 0/9</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
     </row>
@@ -3804,42 +3804,42 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/10</t>
+          <t>0 / 0.1 / 0/11</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="F36" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="E36" s="10" t="inlineStr">
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F36" s="10" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/9</t>
-        </is>
-      </c>
-      <c r="G36" s="10" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/6</t>
-        </is>
-      </c>
-      <c r="H36" s="10" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
-      <c r="I36" s="10" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
@@ -3851,42 +3851,42 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>1 / 2.0 / 0/10</t>
+          <t>1 / 1.9 / 0/11</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>1 / 0.8 / 0/11</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="D37" s="11" t="inlineStr">
-        <is>
-          <t>1 / 0.8 / 0/10</t>
-        </is>
-      </c>
-      <c r="E37" s="11" t="inlineStr">
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
+          <t>1 / 1.6 / 0/7</t>
+        </is>
+      </c>
+      <c r="H37" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F37" s="11" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/9</t>
-        </is>
-      </c>
-      <c r="G37" s="11" t="inlineStr">
-        <is>
-          <t>1 / 1.7 / 0/6</t>
-        </is>
-      </c>
-      <c r="H37" s="11" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
     </row>
@@ -3898,42 +3898,42 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 0/11</t>
+          <t>1 / 1.5 / 0/12</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/11</t>
+          <t>0 / 0.4 / 0/12</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/11</t>
+          <t>1 / 1.0 / 0/12</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/9</t>
+          <t>1 / 0.4 / 0/10</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>2 / 0.4 / 0/9</t>
+          <t>2 / 0.6 / 0/10</t>
         </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/6</t>
+          <t>1 / 0.3 / 0/7</t>
         </is>
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/5</t>
+          <t>1 / 1.0 / 0/6</t>
         </is>
       </c>
     </row>
@@ -3946,33 +3946,33 @@
       <c r="B39" s="11" t="inlineStr"/>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>0 / 1.1 / 0/11</t>
+          <t>0 / 1.0 / 0/12</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/11</t>
+          <t>0 / 0.7 / 0/12</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr"/>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>2 / 1.6 / 0/9</t>
+          <t>2 / 1.6 / 0/10</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
-          <t>2 / 4.2 / 2/6</t>
+          <t>2 / 3.9 / 2/7</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/8</t>
+          <t>0 / 0.2 / 0/9</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/5</t>
+          <t>1 / 0.8 / 0/6</t>
         </is>
       </c>
     </row>
@@ -3987,23 +3987,23 @@
       <c r="D40" s="10" t="inlineStr"/>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/9</t>
+          <t>1 / 1.0 / 0/10</t>
         </is>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>6 / 4.1 / 1/9</t>
+          <t>6 / 4.3 / 2/10</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr"/>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/8</t>
+          <t>1 / 1.1 / 0/9</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>30 / 7.6 / 1/5</t>
+          <t>78 / 19.3 / 2/6</t>
         </is>
       </c>
     </row>
@@ -4015,42 +4015,42 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>6 / 5.6 / 4/10</t>
+          <t>5 / 5.5 / 4/11</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>6 / 3.3 / 2/11</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/10</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="D41" s="11" t="inlineStr">
-        <is>
-          <t>6 / 3.0 / 1/10</t>
-        </is>
-      </c>
-      <c r="E41" s="11" t="inlineStr">
-        <is>
-          <t>0 / 0.2 / 0/9</t>
-        </is>
-      </c>
-      <c r="F41" s="11" t="inlineStr">
+      <c r="G41" s="11" t="inlineStr">
+        <is>
+          <t>1 / 1.6 / 0/7</t>
+        </is>
+      </c>
+      <c r="H41" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="G41" s="11" t="inlineStr">
-        <is>
-          <t>2 / 1.7 / 0/6</t>
-        </is>
-      </c>
-      <c r="H41" s="11" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
     </row>
@@ -4062,42 +4062,42 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>5 / 4.5 / 1/10</t>
+          <t>5 / 4.5 / 1/11</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/10</t>
+          <t>0 / 0.2 / 0/11</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>2 / 1.4 / 0/10</t>
+          <t>2 / 1.5 / 0/11</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0.5 / 0/10</t>
+        </is>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>1 / 1.4 / 0/7</t>
+        </is>
+      </c>
+      <c r="H42" s="10" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F42" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0.4 / 0/9</t>
-        </is>
-      </c>
-      <c r="G42" s="10" t="inlineStr">
-        <is>
-          <t>1 / 1.5 / 0/6</t>
-        </is>
-      </c>
-      <c r="H42" s="10" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
       <c r="I42" s="10" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/5</t>
+          <t>1 / 1.0 / 0/6</t>
         </is>
       </c>
     </row>
@@ -4109,42 +4109,42 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>3 / 1.8 / 0/10</t>
+          <t>3 / 1.9 / 0/11</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="D43" s="11" t="inlineStr">
+      <c r="F43" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/9</t>
-        </is>
-      </c>
-      <c r="F43" s="11" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/9</t>
-        </is>
-      </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/6</t>
+          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/8</t>
+          <t>1 / 0.3 / 0/9</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/5</t>
+          <t>1 / 0.5 / 0/6</t>
         </is>
       </c>
     </row>
@@ -4157,37 +4157,37 @@
       <c r="B44" s="10" t="inlineStr"/>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>10 / 3.5 / 1/11</t>
+          <t>10 / 4.1 / 2/12</t>
         </is>
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
-          <t>1 / 1.3 / 0/9</t>
+          <t>1 / 1.3 / 0/10</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>5 / 2.1 / 0/9</t>
+          <t>3 / 2.2 / 0/10</t>
         </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>2 / 3.3 / 2/6</t>
+          <t>2 / 3.1 / 2/7</t>
         </is>
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>3 / 2.5 / 1/8</t>
+          <t>3 / 2.6 / 1/9</t>
         </is>
       </c>
       <c r="I44" s="10" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/5</t>
+          <t>1 / 0.3 / 0/6</t>
         </is>
       </c>
     </row>
@@ -4200,33 +4200,33 @@
       <c r="B45" s="11" t="inlineStr"/>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>1 / 1.8 / 0/10</t>
+          <t>1 / 1.7 / 0/11</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>1 / 1.2 / 0/10</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/10</t>
-        </is>
-      </c>
-      <c r="E45" s="11" t="inlineStr">
-        <is>
-          <t>1 / 1.2 / 0/9</t>
-        </is>
-      </c>
-      <c r="F45" s="11" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr"/>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/8</t>
+          <t>0 / 0.1 / 0/9</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/5</t>
+          <t>1 / 1.0 / 0/6</t>
         </is>
       </c>
     </row>
@@ -4238,42 +4238,42 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>4 / 4.1 / 0/10</t>
+          <t>4 / 4.1 / 0/11</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>3 / 1.2 / 0/11</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="D46" s="10" t="inlineStr">
-        <is>
-          <t>3 / 1.0 / 0/10</t>
-        </is>
-      </c>
-      <c r="E46" s="10" t="inlineStr">
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="G46" s="10" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/7</t>
+        </is>
+      </c>
+      <c r="H46" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F46" s="10" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/9</t>
-        </is>
-      </c>
-      <c r="G46" s="10" t="inlineStr">
-        <is>
-          <t>0 / 0.2 / 0/6</t>
-        </is>
-      </c>
-      <c r="H46" s="10" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
       <c r="I46" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
     </row>
@@ -4286,33 +4286,33 @@
       <c r="B47" s="11" t="inlineStr"/>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/11</t>
+          <t>0 / 0.4 / 0/12</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>3 / 1.8 / 0/11</t>
+          <t>4 / 2.0 / 0/12</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>2 / 2.1 / 0/9</t>
+          <t>2 / 2.1 / 0/10</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>4 / 2.0 / 0/9</t>
+          <t>4 / 2.2 / 0/10</t>
         </is>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
-          <t>1 / 3.7 / 2/6</t>
+          <t>1 / 3.3 / 2/7</t>
         </is>
       </c>
       <c r="H47" s="11" t="inlineStr"/>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/5</t>
+          <t>1 / 1.0 / 0/6</t>
         </is>
       </c>
     </row>
@@ -4326,32 +4326,32 @@
       <c r="C48" s="10" t="inlineStr"/>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>5 / 3.0 / 0/11</t>
+          <t>4 / 3.1 / 0/12</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr">
         <is>
-          <t>2 / 1.7 / 0/9</t>
+          <t>2 / 1.7 / 0/10</t>
         </is>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>10 / 4.6 / 2/9</t>
+          <t>9 / 5.0 / 3/10</t>
         </is>
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>1 / 2.8 / 0/6</t>
+          <t>1 / 2.6 / 0/7</t>
         </is>
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/8</t>
+          <t>1 / 0.3 / 0/9</t>
         </is>
       </c>
       <c r="I48" s="10" t="inlineStr">
         <is>
-          <t>3 / 0.8 / 0/5</t>
+          <t>3 / 1.2 / 0/6</t>
         </is>
       </c>
     </row>
@@ -4363,42 +4363,42 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="F49" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="G49" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
+        </is>
+      </c>
+      <c r="H49" s="11" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F49" s="11" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/9</t>
-        </is>
-      </c>
-      <c r="G49" s="11" t="inlineStr">
+      <c r="I49" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/6</t>
-        </is>
-      </c>
-      <c r="H49" s="11" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
-      <c r="I49" s="11" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
@@ -4410,42 +4410,42 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>4 / 1.3 / 0/10</t>
+          <t>3 / 1.5 / 0/11</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="D50" s="10" t="inlineStr">
+      <c r="F50" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="E50" s="10" t="inlineStr">
+      <c r="G50" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0.3 / 0/7</t>
+        </is>
+      </c>
+      <c r="H50" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F50" s="10" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/9</t>
-        </is>
-      </c>
-      <c r="G50" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0.2 / 0/6</t>
-        </is>
-      </c>
-      <c r="H50" s="10" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
       <c r="I50" s="10" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/5</t>
+          <t>0 / 0.2 / 0/6</t>
         </is>
       </c>
     </row>
@@ -4458,37 +4458,37 @@
       <c r="B51" s="11" t="inlineStr"/>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/10</t>
+          <t>0 / 0.1 / 0/11</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>4 / 2.2 / 0/10</t>
+          <t>3 / 2.3 / 0/11</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>4 / 2.4 / 0/9</t>
+          <t>3 / 2.5 / 0/10</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/9</t>
+          <t>1 / 0.2 / 0/10</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/6</t>
+          <t>1 / 1.1 / 0/7</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/8</t>
+          <t>1 / 0.4 / 0/9</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/5</t>
+          <t>1 / 0.3 / 0/6</t>
         </is>
       </c>
     </row>
@@ -4500,42 +4500,42 @@
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>1 / 2.7 / 0/10</t>
+          <t>1 / 2.5 / 0/11</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="D52" s="10" t="inlineStr">
+      <c r="F52" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="E52" s="10" t="inlineStr">
+      <c r="G52" s="10" t="inlineStr">
+        <is>
+          <t>1 / 1.1 / 0/7</t>
+        </is>
+      </c>
+      <c r="H52" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F52" s="10" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/9</t>
-        </is>
-      </c>
-      <c r="G52" s="10" t="inlineStr">
-        <is>
-          <t>1 / 1.2 / 0/6</t>
-        </is>
-      </c>
-      <c r="H52" s="10" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
       <c r="I52" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
     </row>
@@ -4547,42 +4547,42 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/10</t>
+          <t>2 / 1.5 / 0/11</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>2 / 1.1 / 0/11</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="D53" s="11" t="inlineStr">
-        <is>
-          <t>2 / 1.0 / 0/10</t>
-        </is>
-      </c>
-      <c r="E53" s="11" t="inlineStr">
+      <c r="F53" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="G53" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.6 / 0/7</t>
+        </is>
+      </c>
+      <c r="H53" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F53" s="11" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/9</t>
-        </is>
-      </c>
-      <c r="G53" s="11" t="inlineStr">
-        <is>
-          <t>0 / 0.7 / 0/6</t>
-        </is>
-      </c>
-      <c r="H53" s="11" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
     </row>
@@ -4594,42 +4594,42 @@
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>5 / 3.8 / 0/10</t>
+          <t>5 / 3.9 / 0/11</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/10</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
+          <t>0 / 0.2 / 0/11</t>
+        </is>
+      </c>
+      <c r="E54" s="10" t="inlineStr">
+        <is>
+          <t>1 / 1.2 / 0/10</t>
+        </is>
+      </c>
+      <c r="F54" s="10" t="inlineStr">
+        <is>
           <t>0 / 0.2 / 0/10</t>
         </is>
       </c>
-      <c r="E54" s="10" t="inlineStr">
-        <is>
-          <t>1 / 1.2 / 0/9</t>
-        </is>
-      </c>
-      <c r="F54" s="10" t="inlineStr">
-        <is>
-          <t>0 / 0.2 / 0/9</t>
-        </is>
-      </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/6</t>
+          <t>0 / 0.6 / 0/7</t>
         </is>
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="I54" s="10" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/5</t>
+          <t>1 / 0.3 / 0/6</t>
         </is>
       </c>
     </row>
@@ -4641,42 +4641,42 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
+          <t>1 / 0.5 / 0/11</t>
+        </is>
+      </c>
+      <c r="C55" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
           <t>1 / 0.5 / 0/10</t>
         </is>
       </c>
-      <c r="C55" s="11" t="inlineStr">
+      <c r="F55" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="D55" s="11" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/10</t>
-        </is>
-      </c>
-      <c r="E55" s="11" t="inlineStr">
-        <is>
-          <t>1 / 0.4 / 0/9</t>
-        </is>
-      </c>
-      <c r="F55" s="11" t="inlineStr">
+      <c r="G55" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
+        </is>
+      </c>
+      <c r="H55" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="G55" s="11" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/6</t>
-        </is>
-      </c>
-      <c r="H55" s="11" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/5</t>
+          <t>1 / 0.7 / 0/6</t>
         </is>
       </c>
     </row>
@@ -4689,37 +4689,37 @@
       <c r="B56" s="10" t="inlineStr"/>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/10</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>6 / 3.3 / 1/10</t>
+          <t>7 / 3.6 / 2/11</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/9</t>
+          <t>0 / 0.2 / 0/10</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/9</t>
+          <t>0 / 0.2 / 0/10</t>
         </is>
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/6</t>
+          <t>0 / 0.3 / 0/7</t>
         </is>
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/8</t>
+          <t>0 / 0.6 / 0/9</t>
         </is>
       </c>
       <c r="I56" s="10" t="inlineStr">
         <is>
-          <t>6 / 3.0 / 1/5</t>
+          <t>10 / 4.2 / 2/6</t>
         </is>
       </c>
     </row>
@@ -4731,42 +4731,42 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/10</t>
+          <t>0 / 0.5 / 0/11</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/10</t>
+          <t>0 / 0.1 / 0/11</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/10</t>
+          <t>0 / 0.4 / 0/11</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="F57" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="G57" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
+        </is>
+      </c>
+      <c r="H57" s="11" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F57" s="11" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/9</t>
-        </is>
-      </c>
-      <c r="G57" s="11" t="inlineStr">
+      <c r="I57" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/6</t>
-        </is>
-      </c>
-      <c r="H57" s="11" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
-      <c r="I57" s="11" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
@@ -4778,42 +4778,42 @@
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/10</t>
+          <t>1 / 1.0 / 0/11</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0.5 / 0/11</t>
+        </is>
+      </c>
+      <c r="E58" s="10" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="D58" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0.4 / 0/10</t>
-        </is>
-      </c>
-      <c r="E58" s="10" t="inlineStr">
+      <c r="F58" s="10" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="G58" s="10" t="inlineStr">
+        <is>
+          <t>0 / 0.6 / 0/7</t>
+        </is>
+      </c>
+      <c r="H58" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F58" s="10" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/9</t>
-        </is>
-      </c>
-      <c r="G58" s="10" t="inlineStr">
-        <is>
-          <t>0 / 0.7 / 0/6</t>
-        </is>
-      </c>
-      <c r="H58" s="10" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
       <c r="I58" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
     </row>
@@ -4826,33 +4826,33 @@
       <c r="B59" s="11" t="inlineStr"/>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>0 / 1.8 / 0/11</t>
+          <t>0 / 1.7 / 0/12</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>0 / 1.1 / 0/11</t>
+          <t>0 / 1.0 / 0/12</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>2 / 1.7 / 0/9</t>
+          <t>3 / 1.8 / 0/10</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/9</t>
+          <t>1 / 0.4 / 0/10</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr"/>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>2 / 1.9 / 0/8</t>
+          <t>2 / 1.9 / 0/9</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
     </row>
@@ -4865,37 +4865,37 @@
       <c r="B60" s="10" t="inlineStr"/>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>2 / 3.6 / 3/11</t>
+          <t>2 / 3.5 / 3/12</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>2 / 1.3 / 0/11</t>
+          <t>3 / 1.4 / 0/12</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/9</t>
+          <t>1 / 0.4 / 0/10</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>4 / 0.6 / 0/9</t>
+          <t>4 / 0.9 / 0/10</t>
         </is>
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>1 / 3.2 / 1/6</t>
+          <t>1 / 2.9 / 1/7</t>
         </is>
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/8</t>
+          <t>0 / 0.1 / 0/9</t>
         </is>
       </c>
       <c r="I60" s="10" t="inlineStr">
         <is>
-          <t>2 / 0.4 / 0/5</t>
+          <t>2 / 0.7 / 0/6</t>
         </is>
       </c>
     </row>
@@ -4908,32 +4908,32 @@
       <c r="B61" s="11" t="inlineStr"/>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/11</t>
+          <t>1 / 0.2 / 0/12</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>1 / 1.4 / 0/11</t>
+          <t>2 / 1.4 / 0/12</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>2 / 1.2 / 0/9</t>
+          <t>2 / 1.3 / 0/10</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
         <is>
-          <t>3 / 2.5 / 0/6</t>
+          <t>3 / 2.6 / 0/7</t>
         </is>
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/8</t>
+          <t>0 / 0.1 / 0/9</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr"/>
@@ -4947,33 +4947,33 @@
       <c r="B62" s="10" t="inlineStr"/>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/11</t>
+          <t>1 / 0.9 / 0/12</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>3 / 1.6 / 0/11</t>
+          <t>3 / 1.8 / 0/12</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr"/>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>2 / 0.3 / 0/9</t>
+          <t>2 / 0.5 / 0/10</t>
         </is>
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>1 / 1.8 / 0/6</t>
+          <t>1 / 1.7 / 0/7</t>
         </is>
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/8</t>
+          <t>1 / 1.0 / 0/9</t>
         </is>
       </c>
       <c r="I62" s="10" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/5</t>
+          <t>1 / 0.5 / 0/6</t>
         </is>
       </c>
     </row>
@@ -4987,23 +4987,23 @@
       <c r="C63" s="11" t="inlineStr"/>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>6 / 4.5 / 4/11</t>
+          <t>6 / 4.6 / 5/12</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>5 / 4.0 / 0/9</t>
+          <t>5 / 4.1 / 0/10</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr"/>
       <c r="G63" s="11" t="inlineStr">
         <is>
-          <t>4 / 5.0 / 2/6</t>
+          <t>4 / 4.9 / 2/7</t>
         </is>
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>3 / 2.0 / 0/8</t>
+          <t>3 / 2.1 / 0/9</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr"/>
@@ -5018,32 +5018,32 @@
       <c r="C64" s="10" t="inlineStr"/>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>7 / 3.6 / 1/11</t>
+          <t>7 / 3.9 / 2/12</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>4 / 2.0 / 0/9</t>
+          <t>4 / 2.2 / 0/10</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>5 / 2.6 / 0/9</t>
+          <t>4 / 2.7 / 0/10</t>
         </is>
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t>4 / 4.2 / 0/6</t>
+          <t>4 / 4.1 / 0/7</t>
         </is>
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>6 / 5.8 / 6/8</t>
+          <t>5 / 5.7 / 6/9</t>
         </is>
       </c>
       <c r="I64" s="10" t="inlineStr">
         <is>
-          <t>4 / 2.8 / 0/5</t>
+          <t>4 / 3.0 / 0/6</t>
         </is>
       </c>
     </row>
@@ -5055,42 +5055,42 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/10</t>
+          <t>0 / 0.1 / 0/11</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="D65" s="11" t="inlineStr">
+      <c r="F65" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="E65" s="11" t="inlineStr">
+      <c r="G65" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
+        </is>
+      </c>
+      <c r="H65" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="F65" s="11" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/9</t>
-        </is>
-      </c>
-      <c r="G65" s="11" t="inlineStr">
+      <c r="I65" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/6</t>
-        </is>
-      </c>
-      <c r="H65" s="11" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
-      <c r="I65" s="11" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/5</t>
         </is>
       </c>
     </row>
@@ -5102,42 +5102,42 @@
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>3 / 1.9 / 0/10</t>
+          <t>4 / 2.1 / 0/11</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="D66" s="10" t="inlineStr">
+      <c r="F66" s="10" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="E66" s="10" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/9</t>
-        </is>
-      </c>
-      <c r="F66" s="10" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/9</t>
-        </is>
-      </c>
       <c r="G66" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/6</t>
+          <t>0 / 0.6 / 0/7</t>
         </is>
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/8</t>
+          <t>1 / 0.2 / 0/9</t>
         </is>
       </c>
       <c r="I66" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
     </row>
@@ -5149,42 +5149,42 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>8 / 4.4 / 2/10</t>
+          <t>9 / 4.8 / 3/11</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/10</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>3 / 1.7 / 0/10</t>
+          <t>3 / 1.8 / 0/11</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>2 / 1.3 / 0/9</t>
+          <t>2 / 1.4 / 0/10</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>2 / 0.9 / 0/9</t>
+          <t>2 / 1.0 / 0/10</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr">
         <is>
-          <t>0 / 1.2 / 0/6</t>
+          <t>0 / 1.0 / 0/7</t>
         </is>
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/5</t>
+          <t>2 / 0.5 / 0/6</t>
         </is>
       </c>
     </row>
@@ -5196,42 +5196,42 @@
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>1 / 2.7 / 0/10</t>
+          <t>1 / 2.5 / 0/11</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/10</t>
+          <t>0 / 0.1 / 0/11</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/10</t>
+          <t>1 / 0.4 / 0/11</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>2 / 1.3 / 0/9</t>
+          <t>2 / 1.4 / 0/10</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="G68" s="10" t="inlineStr">
+        <is>
+          <t>0 / 0.6 / 0/7</t>
+        </is>
+      </c>
+      <c r="H68" s="10" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="G68" s="10" t="inlineStr">
-        <is>
-          <t>0 / 0.7 / 0/6</t>
-        </is>
-      </c>
-      <c r="H68" s="10" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
       <c r="I68" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
     </row>
@@ -5243,42 +5243,42 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>3 / 3.1 / 1/10</t>
+          <t>3 / 3.1 / 1/11</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/10</t>
+          <t>0 / 0.1 / 0/11</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>1 / 1.8 / 0/10</t>
+          <t>1 / 1.7 / 0/11</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/9</t>
+          <t>1 / 0.7 / 0/10</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
+          <t>1 / 0.1 / 0/10</t>
+        </is>
+      </c>
+      <c r="G69" s="11" t="inlineStr">
+        <is>
+          <t>0 / 0.3 / 0/7</t>
+        </is>
+      </c>
+      <c r="H69" s="11" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
-      <c r="G69" s="11" t="inlineStr">
-        <is>
-          <t>0 / 0.3 / 0/6</t>
-        </is>
-      </c>
-      <c r="H69" s="11" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/5</t>
+          <t>0 / 0.0 / 0/6</t>
         </is>
       </c>
     </row>
@@ -5290,42 +5290,42 @@
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>10 / 2.2 / 2/10</t>
+          <t>10 / 2.9 / 3/11</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/10</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/10</t>
+          <t>2 / 0.5 / 0/11</t>
         </is>
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>4 / 2.6 / 0/9</t>
+          <t>4 / 2.7 / 0/10</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/9</t>
+          <t>0 / 0.4 / 0/10</t>
         </is>
       </c>
       <c r="G70" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/6</t>
+          <t>0 / 0.1 / 0/7</t>
         </is>
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="I70" s="10" t="inlineStr">
         <is>
-          <t>4 / 0.8 / 0/5</t>
+          <t>4 / 1.3 / 0/6</t>
         </is>
       </c>
     </row>
@@ -5338,29 +5338,29 @@
       <c r="B71" s="11" t="inlineStr"/>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/11</t>
+          <t>1 / 1.0 / 0/12</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>11 / 4.0 / 1/11</t>
+          <t>11 / 4.6 / 2/12</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>3 / 3.9 / 2/9</t>
+          <t>4 / 3.9 / 2/10</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr"/>
       <c r="G71" s="11" t="inlineStr">
         <is>
-          <t>3 / 2.7 / 0/6</t>
+          <t>3 / 2.7 / 0/7</t>
         </is>
       </c>
       <c r="H71" s="11" t="inlineStr"/>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>5 / 3.4 / 0/5</t>
+          <t>5 / 3.7 / 0/6</t>
         </is>
       </c>
     </row>
@@ -5373,37 +5373,37 @@
       <c r="B72" s="10" t="inlineStr"/>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/11</t>
+          <t>1 / 1.1 / 0/12</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/11</t>
+          <t>1 / 1.0 / 0/12</t>
         </is>
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>3 / 1.1 / 0/9</t>
+          <t>4 / 1.4 / 0/10</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/9</t>
+          <t>1 / 0.5 / 0/10</t>
         </is>
       </c>
       <c r="G72" s="10" t="inlineStr">
         <is>
-          <t>1 / 1.3 / 0/6</t>
+          <t>1 / 1.3 / 0/7</t>
         </is>
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="I72" s="10" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/5</t>
+          <t>1 / 1.0 / 0/6</t>
         </is>
       </c>
     </row>
@@ -5416,37 +5416,37 @@
       <c r="B73" s="11" t="inlineStr"/>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>6 / 1.3 / 1/11</t>
+          <t>6 / 1.7 / 2/12</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/9</t>
+          <t>1 / 0.6 / 0/10</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>5 / 2.4 / 0/9</t>
+          <t>5 / 2.7 / 0/10</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
         <is>
-          <t>3 / 2.2 / 0/6</t>
+          <t>3 / 2.3 / 0/7</t>
         </is>
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>3 / 3.1 / 0/8</t>
+          <t>3 / 3.1 / 0/9</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>2 / 0.4 / 0/5</t>
+          <t>2 / 0.7 / 0/6</t>
         </is>
       </c>
     </row>
@@ -5460,32 +5460,32 @@
       <c r="C74" s="10" t="inlineStr"/>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>3 / 2.0 / 0/11</t>
+          <t>3 / 2.1 / 0/12</t>
         </is>
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>4 / 3.0 / 0/9</t>
+          <t>4 / 3.1 / 0/10</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t>3 / 1.1 / 0/9</t>
+          <t>2 / 1.2 / 0/10</t>
         </is>
       </c>
       <c r="G74" s="10" t="inlineStr">
         <is>
-          <t>0 / 2.7 / 0/6</t>
+          <t>0 / 2.3 / 0/7</t>
         </is>
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/8</t>
+          <t>0 / 0.6 / 0/9</t>
         </is>
       </c>
       <c r="I74" s="10" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/5</t>
+          <t>2 / 1.2 / 0/6</t>
         </is>
       </c>
     </row>
@@ -5498,37 +5498,37 @@
       <c r="B75" s="11" t="inlineStr"/>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>0 / 1.3 / 0/11</t>
+          <t>0 / 1.2 / 0/12</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>1 / 2.1 / 0/11</t>
+          <t>1 / 2.0 / 0/12</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>2 / 0.4 / 0/9</t>
+          <t>2 / 0.6 / 0/10</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>2 / 1.4 / 0/9</t>
+          <t>2 / 1.5 / 0/10</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.8 / 0/6</t>
+          <t>0 / 0.7 / 0/7</t>
         </is>
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/8</t>
+          <t>0 / 0.2 / 0/9</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/5</t>
+          <t>1 / 0.5 / 0/6</t>
         </is>
       </c>
     </row>
@@ -5541,37 +5541,37 @@
       <c r="B76" s="10" t="inlineStr"/>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/11</t>
+          <t>0 / 0.7 / 0/12</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>0 / 1.2 / 0/11</t>
+          <t>0 / 1.1 / 0/12</t>
         </is>
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>2 / 1.0 / 0/9</t>
+          <t>2 / 1.1 / 0/10</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t>2 / 0.4 / 0/9</t>
+          <t>2 / 0.6 / 0/10</t>
         </is>
       </c>
       <c r="G76" s="10" t="inlineStr">
         <is>
-          <t>2 / 4.0 / 0/6</t>
+          <t>2 / 3.7 / 0/7</t>
         </is>
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/8</t>
+          <t>1 / 1.2 / 0/9</t>
         </is>
       </c>
       <c r="I76" s="10" t="inlineStr">
         <is>
-          <t>4 / 2.8 / 0/5</t>
+          <t>4 / 3.0 / 0/6</t>
         </is>
       </c>
     </row>
@@ -5584,33 +5584,33 @@
       <c r="B77" s="11" t="inlineStr"/>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>1 / 3.5 / 0/11</t>
+          <t>1 / 3.3 / 0/12</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>3 / 0.9 / 0/11</t>
+          <t>3 / 1.1 / 0/12</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/9</t>
+          <t>0 / 0.1 / 0/10</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
-          <t>12 / 2.7 / 1/9</t>
+          <t>12 / 3.6 / 2/10</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr"/>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/8</t>
+          <t>2 / 1.6 / 0/9</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>2 / 1.0 / 0/5</t>
+          <t>1 / 1.0 / 0/6</t>
         </is>
       </c>
     </row>
@@ -5624,32 +5624,32 @@
       <c r="C78" s="10" t="inlineStr"/>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>4 / 2.0 / 0/11</t>
+          <t>4 / 2.2 / 0/12</t>
         </is>
       </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
-          <t>4 / 3.1 / 0/9</t>
+          <t>4 / 3.2 / 0/10</t>
         </is>
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t>6 / 2.0 / 1/9</t>
+          <t>5 / 2.3 / 1/10</t>
         </is>
       </c>
       <c r="G78" s="10" t="inlineStr">
         <is>
-          <t>0 / 2.3 / 2/6</t>
+          <t>0 / 2.0 / 2/7</t>
         </is>
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="I78" s="10" t="inlineStr">
         <is>
-          <t>4 / 1.4 / 0/5</t>
+          <t>3 / 1.7 / 0/6</t>
         </is>
       </c>
     </row>
@@ -5664,19 +5664,19 @@
       <c r="D79" s="11" t="inlineStr"/>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>4 / 4.0 / 0/9</t>
+          <t>5 / 4.1 / 0/10</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>16 / 5.6 / 3/9</t>
+          <t>16 / 6.6 / 4/10</t>
         </is>
       </c>
       <c r="G79" s="11" t="inlineStr"/>
       <c r="H79" s="11" t="inlineStr"/>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>3 / 2.6 / 0/5</t>
+          <t>3 / 2.7 / 0/6</t>
         </is>
       </c>
     </row>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1650</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="3">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1308</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="4">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>342</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1701</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="6">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7">
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8">
@@ -933,10 +933,8 @@
           <t>Bedfordshire</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
+      <c r="B2" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr"/>
@@ -953,7 +951,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="4" t="inlineStr"/>
@@ -974,13 +972,11 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
+      <c r="D4" s="3" t="n">
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
@@ -999,15 +995,13 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
       <c r="D5" s="4" t="inlineStr"/>
       <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
+      <c r="F5" s="5" t="n">
+        <v>12</v>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr"/>
@@ -1020,7 +1014,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr"/>
@@ -1054,7 +1048,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr"/>
@@ -1088,7 +1082,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr"/>
@@ -1152,7 +1146,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr"/>
@@ -1169,7 +1163,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
       <c r="D15" s="4" t="inlineStr"/>
@@ -1207,7 +1201,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
       <c r="D17" s="4" t="inlineStr"/>
@@ -1226,7 +1220,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr"/>
@@ -1251,15 +1245,15 @@
       </c>
       <c r="C19" s="4" t="inlineStr"/>
       <c r="D19" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I19" s="4" t="inlineStr"/>
     </row>
@@ -1319,7 +1313,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C23" s="5" t="n">
         <v>6</v>
@@ -1355,7 +1349,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
       <c r="D25" s="4" t="inlineStr"/>
@@ -1372,7 +1366,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>2</v>
@@ -1466,7 +1460,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="inlineStr"/>
@@ -1500,23 +1494,23 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>42</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>6</v>
@@ -1612,13 +1606,13 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr"/>
@@ -1682,7 +1676,7 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="inlineStr"/>
@@ -1699,7 +1693,7 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C45" s="4" t="inlineStr"/>
       <c r="D45" s="4" t="inlineStr"/>
@@ -1735,7 +1729,7 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C47" s="4" t="inlineStr"/>
       <c r="D47" s="4" t="inlineStr"/>
@@ -1754,10 +1748,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="2" t="inlineStr"/>
@@ -1803,7 +1797,7 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C51" s="4" t="inlineStr"/>
       <c r="D51" s="4" t="inlineStr"/>
@@ -1880,7 +1874,7 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C56" s="2" t="inlineStr"/>
       <c r="D56" s="2" t="inlineStr"/>
@@ -1927,7 +1921,7 @@
         </is>
       </c>
       <c r="B59" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C59" s="4" t="inlineStr"/>
       <c r="D59" s="4" t="inlineStr"/>
@@ -1965,7 +1959,7 @@
         </is>
       </c>
       <c r="B61" s="5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C61" s="4" t="inlineStr"/>
       <c r="D61" s="4" t="inlineStr"/>
@@ -1974,7 +1968,7 @@
       <c r="G61" s="4" t="inlineStr"/>
       <c r="H61" s="4" t="inlineStr"/>
       <c r="I61" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
@@ -1984,7 +1978,7 @@
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C62" s="2" t="inlineStr"/>
       <c r="D62" s="2" t="inlineStr"/>
@@ -2003,20 +1997,20 @@
         </is>
       </c>
       <c r="B63" s="5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D63" s="4" t="inlineStr"/>
       <c r="E63" s="4" t="inlineStr"/>
       <c r="F63" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G63" s="4" t="inlineStr"/>
       <c r="H63" s="4" t="inlineStr"/>
       <c r="I63" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64">
@@ -2026,10 +2020,10 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D64" s="2" t="inlineStr"/>
       <c r="E64" s="2" t="inlineStr"/>
@@ -2135,17 +2129,17 @@
         </is>
       </c>
       <c r="B71" s="5" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C71" s="4" t="inlineStr"/>
       <c r="D71" s="4" t="inlineStr"/>
       <c r="E71" s="4" t="inlineStr"/>
       <c r="F71" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G71" s="4" t="inlineStr"/>
       <c r="H71" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I71" s="4" t="inlineStr"/>
     </row>
@@ -2156,7 +2150,7 @@
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C72" s="2" t="inlineStr"/>
       <c r="D72" s="2" t="inlineStr"/>
@@ -2173,7 +2167,7 @@
         </is>
       </c>
       <c r="B73" s="5" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C73" s="4" t="inlineStr"/>
       <c r="D73" s="4" t="inlineStr"/>
@@ -2193,7 +2187,7 @@
         <v>16</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D74" s="2" t="inlineStr"/>
       <c r="E74" s="2" t="inlineStr"/>
@@ -2209,7 +2203,7 @@
         </is>
       </c>
       <c r="B75" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C75" s="4" t="inlineStr"/>
       <c r="D75" s="4" t="inlineStr"/>
@@ -2243,7 +2237,7 @@
         </is>
       </c>
       <c r="B77" s="5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C77" s="4" t="inlineStr"/>
       <c r="D77" s="4" t="inlineStr"/>
@@ -2264,7 +2258,7 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
@@ -2285,7 +2279,7 @@
         </is>
       </c>
       <c r="B79" s="5" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C79" s="5" t="n">
         <v>1</v>
@@ -2301,7 +2295,7 @@
         </is>
       </c>
       <c r="H79" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I79" s="4" t="inlineStr"/>
     </row>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sitewide'!$A$1:$B$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'JobG8 categories'!$A$1:$C$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'JobG8 categories'!$A$1:$C$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'LIVE'!$A$1:$I$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOT LIVE'!$A$1:$I$79</definedName>
   </definedNames>
@@ -595,7 +595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -627,10 +627,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2619</v>
+        <v>2489</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>210</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3">
@@ -640,10 +640,10 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1618</v>
+        <v>1641</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -653,36 +653,36 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1304</v>
+        <v>1261</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>682</v>
+        <v>686</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Medical</t>
+          <t>Call Centre / CustomerService</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>830</v>
+        <v>855</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>45</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Call Centre / CustomerService</t>
+          <t>Healthcare &amp; Medical</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>685</v>
+        <v>829</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>132</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -692,10 +692,10 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>386</v>
+        <v>373</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>8</v>
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -770,36 +770,36 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Advert / Media / Entertainment</t>
+          <t>Insurance &amp; Superannuation</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Insurance &amp; Superannuation</t>
+          <t>Advert / Media / Entertainment</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>2</v>
@@ -822,40 +822,27 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Published JobG8 ID absent from current feed</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="7" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Total Ontap JobG8 jobs published today</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n">
+      <c r="B18" s="9" t="n">
         <v>10000</v>
       </c>
-      <c r="C19" s="9" t="n">
-        <v>1308</v>
+      <c r="C18" s="9" t="n">
+        <v>1390</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C19"/>
+  <autoFilter ref="A1:C18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -941,7 +941,11 @@
         <v>29</v>
       </c>
       <c r="C3" s="4" t="inlineStr"/>
-      <c r="D3" s="4" t="inlineStr"/>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
       <c r="E3" s="4" t="inlineStr"/>
       <c r="F3" s="5" t="n">
         <v>13</v>
@@ -966,7 +970,11 @@
         <v>8</v>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>CHECK</t>
@@ -1212,7 +1220,11 @@
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
           <t>CHECK</t>
@@ -1339,9 +1351,17 @@
         <v>41</v>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
-      <c r="D25" s="4" t="inlineStr"/>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
       <c r="E25" s="4" t="inlineStr"/>
-      <c r="F25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
       <c r="G25" s="4" t="inlineStr"/>
       <c r="H25" s="4" t="inlineStr"/>
       <c r="I25" s="4" t="inlineStr"/>
@@ -1358,9 +1378,17 @@
       <c r="C26" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
       <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
@@ -1742,7 +1770,11 @@
       </c>
       <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr"/>
@@ -1864,7 +1896,11 @@
         <v>22</v>
       </c>
       <c r="C56" s="2" t="inlineStr"/>
-      <c r="D56" s="2" t="inlineStr"/>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr"/>
@@ -1989,7 +2025,11 @@
       <c r="C63" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D63" s="4" t="inlineStr"/>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
       <c r="E63" s="4" t="inlineStr"/>
       <c r="F63" s="5" t="n">
         <v>10</v>
@@ -2012,7 +2052,11 @@
       <c r="C64" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D64" s="2" t="inlineStr"/>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
       <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr"/>
@@ -2055,7 +2099,11 @@
           <t>Wales South - Cardiff &amp; Vale</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr"/>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
       <c r="C67" s="4" t="inlineStr"/>
       <c r="D67" s="4" t="inlineStr"/>
       <c r="E67" s="4" t="inlineStr"/>
@@ -2414,11 +2462,7 @@
           <t>0 / 3.2 / 3/12</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>8 / 2.2 / 2/12</t>
-        </is>
-      </c>
+      <c r="D3" s="11" t="inlineStr"/>
       <c r="E3" s="11" t="inlineStr">
         <is>
           <t>2 / 0.8 / 0/10</t>
@@ -2455,11 +2499,7 @@
           <t>3 / 2.9 / 1/10</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>8 / 3.2 / 2/10</t>
-        </is>
-      </c>
+      <c r="F4" s="10" t="inlineStr"/>
       <c r="G4" s="10" t="inlineStr"/>
       <c r="H4" s="10" t="inlineStr">
         <is>
@@ -3049,11 +3089,7 @@
           <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>7 / 3.3 / 2/10</t>
-        </is>
-      </c>
+      <c r="F18" s="10" t="inlineStr"/>
       <c r="G18" s="10" t="inlineStr"/>
       <c r="H18" s="10" t="inlineStr">
         <is>
@@ -3324,21 +3360,13 @@
           <t>3 / 2.3 / 0/12</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>9 / 4.4 / 2/12</t>
-        </is>
-      </c>
+      <c r="D25" s="11" t="inlineStr"/>
       <c r="E25" s="11" t="inlineStr">
         <is>
           <t>2 / 1.6 / 0/10</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
-        <is>
-          <t>9 / 2.8 / 2/10</t>
-        </is>
-      </c>
+      <c r="F25" s="11" t="inlineStr"/>
       <c r="G25" s="11" t="inlineStr">
         <is>
           <t>1 / 1.0 / 0/7</t>
@@ -3363,21 +3391,13 @@
       </c>
       <c r="B26" s="10" t="inlineStr"/>
       <c r="C26" s="10" t="inlineStr"/>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>9 / 4.9 / 2/12</t>
-        </is>
-      </c>
+      <c r="D26" s="10" t="inlineStr"/>
       <c r="E26" s="10" t="inlineStr">
         <is>
           <t>3 / 4.2 / 2/10</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
-        <is>
-          <t>7 / 3.2 / 2/10</t>
-        </is>
-      </c>
+      <c r="F26" s="10" t="inlineStr"/>
       <c r="G26" s="10" t="inlineStr">
         <is>
           <t>0 / 2.6 / 1/7</t>
@@ -4315,11 +4335,7 @@
           <t>2 / 1.7 / 0/10</t>
         </is>
       </c>
-      <c r="F48" s="10" t="inlineStr">
-        <is>
-          <t>9 / 5.0 / 3/10</t>
-        </is>
-      </c>
+      <c r="F48" s="10" t="inlineStr"/>
       <c r="G48" s="10" t="inlineStr">
         <is>
           <t>1 / 2.6 / 0/7</t>
@@ -4673,11 +4689,7 @@
           <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
-      <c r="D56" s="10" t="inlineStr">
-        <is>
-          <t>7 / 3.6 / 2/11</t>
-        </is>
-      </c>
+      <c r="D56" s="10" t="inlineStr"/>
       <c r="E56" s="10" t="inlineStr">
         <is>
           <t>0 / 0.2 / 0/10</t>
@@ -4966,11 +4978,7 @@
       </c>
       <c r="B63" s="11" t="inlineStr"/>
       <c r="C63" s="11" t="inlineStr"/>
-      <c r="D63" s="11" t="inlineStr">
-        <is>
-          <t>6 / 4.6 / 5/12</t>
-        </is>
-      </c>
+      <c r="D63" s="11" t="inlineStr"/>
       <c r="E63" s="11" t="inlineStr">
         <is>
           <t>5 / 4.1 / 0/10</t>
@@ -4997,11 +5005,7 @@
       </c>
       <c r="B64" s="10" t="inlineStr"/>
       <c r="C64" s="10" t="inlineStr"/>
-      <c r="D64" s="10" t="inlineStr">
-        <is>
-          <t>7 / 3.9 / 2/12</t>
-        </is>
-      </c>
+      <c r="D64" s="10" t="inlineStr"/>
       <c r="E64" s="10" t="inlineStr">
         <is>
           <t>4 / 2.2 / 0/10</t>
@@ -5128,11 +5132,7 @@
           <t>Wales South - Cardiff &amp; Vale</t>
         </is>
       </c>
-      <c r="B67" s="11" t="inlineStr">
-        <is>
-          <t>9 / 4.8 / 3/11</t>
-        </is>
-      </c>
+      <c r="B67" s="11" t="inlineStr"/>
       <c r="C67" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/11</t>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1752</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="3">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1801</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="6">
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr"/>
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>2</v>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1749</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="3">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1798</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="6">
@@ -627,10 +627,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2489</v>
+        <v>2362</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>225</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3">
@@ -643,7 +643,7 @@
         <v>1641</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -653,10 +653,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1261</v>
+        <v>1272</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="5">
@@ -666,10 +666,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>855</v>
+        <v>954</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>237</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6">
@@ -679,10 +679,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>829</v>
+        <v>848</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7">
@@ -695,33 +695,33 @@
         <v>414</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>HR / Recruitment</t>
+          <t>Banking &amp; Financial Services</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Banking &amp; Financial Services</t>
+          <t>HR / Recruitment</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>8</v>
@@ -783,36 +783,36 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Advert / Media / Entertainment</t>
+          <t>Executive Positions</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Executive Positions</t>
+          <t>Advert / Media / Entertainment</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>1</v>
@@ -838,7 +838,7 @@
         <v>10000</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1390</v>
+        <v>1496</v>
       </c>
     </row>
   </sheetData>
@@ -1965,7 +1965,7 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C60" s="2" t="inlineStr"/>
       <c r="D60" s="2" t="inlineStr"/>
@@ -2471,7 +2471,7 @@
       <c r="F3" s="11" t="inlineStr"/>
       <c r="G3" s="11" t="inlineStr">
         <is>
-          <t>2 / 0.7 / 0/7</t>
+          <t>1 / 0.6 / 0/7</t>
         </is>
       </c>
       <c r="H3" s="11" t="inlineStr"/>
@@ -2496,7 +2496,7 @@
       <c r="D4" s="10" t="inlineStr"/>
       <c r="E4" s="10" t="inlineStr">
         <is>
-          <t>3 / 2.9 / 1/10</t>
+          <t>4 / 3.0 / 1/10</t>
         </is>
       </c>
       <c r="F4" s="10" t="inlineStr"/>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="I4" s="10" t="inlineStr">
         <is>
-          <t>4 / 2.3 / 0/6</t>
+          <t>5 / 2.5 / 0/6</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>5 / 2.8 / 1/6</t>
+          <t>6 / 3.0 / 2/6</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>5 / 2.3 / 1/12</t>
+          <t>1 / 2.0 / 1/12</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="I10" s="10" t="inlineStr">
         <is>
-          <t>31 / 6.0 / 1/6</t>
+          <t>1 / 1.0 / 0/6</t>
         </is>
       </c>
     </row>
@@ -2927,7 +2927,7 @@
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>3 / 1.1 / 0/10</t>
+          <t>2 / 1.0 / 0/10</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>3 / 2.2 / 0/10</t>
+          <t>2 / 2.1 / 0/10</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>4 / 3.9 / 2/12</t>
+          <t>3 / 3.8 / 2/12</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>3 / 1.6 / 0/10</t>
+          <t>2 / 1.5 / 0/10</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
@@ -3048,7 +3048,7 @@
       <c r="E17" s="11" t="inlineStr"/>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>5 / 3.0 / 1/10</t>
+          <t>6 / 3.1 / 2/10</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/12</t>
+          <t>0 / 0.7 / 0/12</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>3 / 2.5 / 0/12</t>
+          <t>4 / 2.6 / 0/12</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/12</t>
+          <t>1 / 0.8 / 0/12</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/12</t>
+          <t>1 / 0.1 / 0/12</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
@@ -3958,7 +3958,7 @@
       <c r="E39" s="11" t="inlineStr"/>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>2 / 1.6 / 0/10</t>
+          <t>1 / 1.5 / 0/10</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>78 / 19.3 / 2/6</t>
+          <t>9 / 7.8 / 2/6</t>
         </is>
       </c>
     </row>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>3 / 2.2 / 0/10</t>
+          <t>4 / 2.3 / 0/10</t>
         </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
@@ -4201,7 +4201,7 @@
       <c r="B45" s="11" t="inlineStr"/>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>1 / 1.7 / 0/11</t>
+          <t>0 / 1.6 / 0/11</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/6</t>
+          <t>0 / 0.8 / 0/6</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>4 / 4.1 / 0/11</t>
+          <t>2 / 3.9 / 0/11</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -4287,7 +4287,7 @@
       <c r="B47" s="11" t="inlineStr"/>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/12</t>
+          <t>3 / 0.7 / 0/12</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>3 / 1.5 / 0/11</t>
+          <t>2 / 1.4 / 0/11</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/7</t>
+          <t>0 / 0.1 / 0/7</t>
         </is>
       </c>
       <c r="H50" s="10" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>3 / 2.3 / 0/11</t>
+          <t>4 / 2.4 / 0/11</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
@@ -4692,14 +4692,14 @@
       <c r="D56" s="10" t="inlineStr"/>
       <c r="E56" s="10" t="inlineStr">
         <is>
+          <t>1 / 0.3 / 0/10</t>
+        </is>
+      </c>
+      <c r="F56" s="10" t="inlineStr">
+        <is>
           <t>0 / 0.2 / 0/10</t>
         </is>
       </c>
-      <c r="F56" s="10" t="inlineStr">
-        <is>
-          <t>0 / 0.2 / 0/10</t>
-        </is>
-      </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
           <t>0 / 0.3 / 0/7</t>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="I56" s="10" t="inlineStr">
         <is>
-          <t>10 / 4.2 / 2/6</t>
+          <t>5 / 3.3 / 1/6</t>
         </is>
       </c>
     </row>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>0 / 1.0 / 0/12</t>
+          <t>1 / 1.1 / 0/12</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/10</t>
+          <t>0 / 0.3 / 0/10</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr"/>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>3 / 1.4 / 0/12</t>
+          <t>4 / 1.5 / 0/12</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
@@ -4901,7 +4901,7 @@
       <c r="B61" s="11" t="inlineStr"/>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/12</t>
+          <t>0 / 0.2 / 0/12</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
@@ -4940,7 +4940,7 @@
       <c r="B62" s="10" t="inlineStr"/>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/12</t>
+          <t>0 / 0.8 / 0/12</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
@@ -4981,7 +4981,7 @@
       <c r="D63" s="11" t="inlineStr"/>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>5 / 4.1 / 0/10</t>
+          <t>4 / 4.0 / 0/10</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr"/>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t>4 / 4.1 / 0/7</t>
+          <t>3 / 4.0 / 0/7</t>
         </is>
       </c>
       <c r="H64" s="10" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>2 / 0.5 / 0/6</t>
+          <t>1 / 0.3 / 0/6</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/11</t>
+          <t>0 / 0.3 / 0/11</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>3 / 3.1 / 1/11</t>
+          <t>5 / 3.3 / 1/11</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>10 / 2.9 / 3/11</t>
+          <t>12 / 3.1 / 3/11</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="I70" s="10" t="inlineStr">
         <is>
-          <t>4 / 1.3 / 0/6</t>
+          <t>2 / 1.0 / 0/6</t>
         </is>
       </c>
     </row>
@@ -5324,12 +5324,12 @@
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>11 / 4.6 / 2/12</t>
+          <t>10 / 4.5 / 2/12</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>4 / 3.9 / 2/10</t>
+          <t>5 / 4.0 / 2/10</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr"/>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>5 / 2.7 / 0/10</t>
+          <t>4 / 2.6 / 0/10</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>2 / 0.7 / 0/6</t>
+          <t>1 / 0.5 / 0/6</t>
         </is>
       </c>
     </row>
@@ -5451,12 +5451,12 @@
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t>2 / 1.2 / 0/10</t>
+          <t>1 / 1.1 / 0/10</t>
         </is>
       </c>
       <c r="G74" s="10" t="inlineStr">
         <is>
-          <t>0 / 2.3 / 0/7</t>
+          <t>1 / 2.4 / 0/7</t>
         </is>
       </c>
       <c r="H74" s="10" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="I76" s="10" t="inlineStr">
         <is>
-          <t>4 / 3.0 / 0/6</t>
+          <t>5 / 3.2 / 0/6</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
-          <t>4 / 3.2 / 0/10</t>
+          <t>3 / 3.1 / 0/10</t>
         </is>
       </c>
       <c r="F78" s="10" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="I78" s="10" t="inlineStr">
         <is>
-          <t>3 / 1.7 / 0/6</t>
+          <t>1 / 1.3 / 0/6</t>
         </is>
       </c>
     </row>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1728</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="3">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1390</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="4">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1777</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="6">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8">
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr"/>
@@ -939,21 +939,19 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" s="4" t="inlineStr"/>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
+      <c r="D3" s="5" t="n">
+        <v>8</v>
       </c>
       <c r="E3" s="4" t="inlineStr"/>
       <c r="F3" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
       <c r="H3" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" s="4" t="inlineStr"/>
     </row>
@@ -964,17 +962,15 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
+      <c r="F4" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -991,7 +987,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
       <c r="D5" s="4" t="inlineStr"/>
@@ -1010,7 +1006,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr"/>
@@ -1061,7 +1057,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr"/>
@@ -1078,7 +1074,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr"/>
@@ -1159,7 +1155,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
       <c r="D15" s="4" t="inlineStr"/>
@@ -1180,7 +1176,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr"/>
@@ -1221,10 +1217,8 @@
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
+      <c r="F18" s="3" t="n">
+        <v>7</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
@@ -1245,15 +1239,15 @@
       </c>
       <c r="C19" s="4" t="inlineStr"/>
       <c r="D19" s="5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="5" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I19" s="4" t="inlineStr"/>
     </row>
@@ -1296,7 +1290,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="2" t="inlineStr"/>
@@ -1313,10 +1307,10 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D23" s="4" t="inlineStr"/>
       <c r="E23" s="4" t="inlineStr"/>
@@ -1324,7 +1318,7 @@
       <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="4" t="inlineStr"/>
       <c r="I23" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -1349,19 +1343,15 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
+      <c r="D25" s="5" t="n">
+        <v>9</v>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
+      <c r="F25" s="5" t="n">
+        <v>11</v>
       </c>
       <c r="G25" s="4" t="inlineStr"/>
       <c r="H25" s="4" t="inlineStr"/>
@@ -1374,21 +1364,17 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
+      <c r="D26" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
+      <c r="F26" s="3" t="n">
+        <v>7</v>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr"/>
@@ -1476,7 +1462,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="inlineStr"/>
@@ -1493,7 +1479,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C33" s="4" t="inlineStr"/>
       <c r="D33" s="4" t="inlineStr"/>
@@ -1510,26 +1496,26 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -1539,7 +1525,7 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
       <c r="D35" s="4" t="inlineStr"/>
@@ -1622,13 +1608,13 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr"/>
@@ -1692,7 +1678,7 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="inlineStr"/>
@@ -1709,7 +1695,7 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C45" s="4" t="inlineStr"/>
       <c r="D45" s="4" t="inlineStr"/>
@@ -1745,7 +1731,7 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C47" s="4" t="inlineStr"/>
       <c r="D47" s="4" t="inlineStr"/>
@@ -1764,17 +1750,15 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
+      <c r="F48" s="3" t="n">
+        <v>7</v>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr"/>
@@ -1894,13 +1878,11 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C56" s="2" t="inlineStr"/>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
+      <c r="D56" s="3" t="n">
+        <v>7</v>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr"/>
@@ -1945,7 +1927,7 @@
         </is>
       </c>
       <c r="B59" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C59" s="4" t="inlineStr"/>
       <c r="D59" s="4" t="inlineStr"/>
@@ -1966,7 +1948,7 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C60" s="2" t="inlineStr"/>
       <c r="D60" s="2" t="inlineStr"/>
@@ -1983,7 +1965,7 @@
         </is>
       </c>
       <c r="B61" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C61" s="4" t="inlineStr"/>
       <c r="D61" s="4" t="inlineStr"/>
@@ -2002,7 +1984,7 @@
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C62" s="2" t="inlineStr"/>
       <c r="D62" s="2" t="inlineStr"/>
@@ -2026,10 +2008,8 @@
       <c r="C63" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
+      <c r="D63" s="5" t="n">
+        <v>5</v>
       </c>
       <c r="E63" s="4" t="inlineStr"/>
       <c r="F63" s="5" t="n">
@@ -2038,7 +2018,7 @@
       <c r="G63" s="4" t="inlineStr"/>
       <c r="H63" s="4" t="inlineStr"/>
       <c r="I63" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="64">
@@ -2048,15 +2028,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C64" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
+      <c r="D64" s="3" t="n">
+        <v>7</v>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr"/>
@@ -2100,10 +2078,8 @@
           <t>Wales South - Cardiff &amp; Vale</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
+      <c r="B67" s="5" t="n">
+        <v>10</v>
       </c>
       <c r="C67" s="4" t="inlineStr"/>
       <c r="D67" s="4" t="inlineStr"/>
@@ -2165,7 +2141,7 @@
         </is>
       </c>
       <c r="B71" s="5" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C71" s="4" t="inlineStr"/>
       <c r="D71" s="4" t="inlineStr"/>
@@ -2175,7 +2151,7 @@
       </c>
       <c r="G71" s="4" t="inlineStr"/>
       <c r="H71" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I71" s="4" t="inlineStr"/>
     </row>
@@ -2220,7 +2196,7 @@
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C74" s="3" t="n">
         <v>3</v>
@@ -2239,7 +2215,7 @@
         </is>
       </c>
       <c r="B75" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C75" s="4" t="inlineStr"/>
       <c r="D75" s="4" t="inlineStr"/>
@@ -2256,7 +2232,7 @@
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C76" s="2" t="inlineStr"/>
       <c r="D76" s="2" t="inlineStr"/>
@@ -2273,7 +2249,7 @@
         </is>
       </c>
       <c r="B77" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C77" s="4" t="inlineStr"/>
       <c r="D77" s="4" t="inlineStr"/>
@@ -2294,7 +2270,7 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
@@ -2315,13 +2291,13 @@
         </is>
       </c>
       <c r="B79" s="5" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C79" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E79" s="4" t="inlineStr"/>
       <c r="F79" s="4" t="inlineStr"/>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1805</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="3">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1463</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="4">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>342</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1867</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="6">
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr"/>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="5" t="n">
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="3" t="n">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
       <c r="D5" s="4" t="inlineStr"/>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr"/>
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr"/>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
       <c r="D15" s="4" t="inlineStr"/>
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr"/>
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
       <c r="D19" s="5" t="n">
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C21" s="4" t="inlineStr"/>
       <c r="D21" s="4" t="inlineStr"/>
@@ -1310,7 +1310,7 @@
         <v>73</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D23" s="4" t="inlineStr"/>
       <c r="E23" s="4" t="inlineStr"/>
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
       <c r="D25" s="5" t="n">
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>2</v>
@@ -1462,7 +1462,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="inlineStr"/>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>14</v>
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C45" s="4" t="inlineStr"/>
       <c r="D45" s="4" t="inlineStr"/>
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C47" s="4" t="inlineStr"/>
       <c r="D47" s="4" t="inlineStr"/>
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>2</v>
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C56" s="2" t="inlineStr"/>
       <c r="D56" s="3" t="n">
@@ -1965,7 +1965,7 @@
         </is>
       </c>
       <c r="B61" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C61" s="4" t="inlineStr"/>
       <c r="D61" s="4" t="inlineStr"/>
@@ -2006,7 +2006,7 @@
         <v>60</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D63" s="5" t="n">
         <v>5</v>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="B67" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C67" s="4" t="inlineStr"/>
       <c r="D67" s="4" t="inlineStr"/>
@@ -2141,7 +2141,7 @@
         </is>
       </c>
       <c r="B71" s="5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C71" s="4" t="inlineStr"/>
       <c r="D71" s="4" t="inlineStr"/>
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="B73" s="5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C73" s="4" t="inlineStr"/>
       <c r="D73" s="4" t="inlineStr"/>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C76" s="2" t="inlineStr"/>
       <c r="D76" s="2" t="inlineStr"/>
@@ -2249,7 +2249,7 @@
         </is>
       </c>
       <c r="B77" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C77" s="4" t="inlineStr"/>
       <c r="D77" s="4" t="inlineStr"/>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="B79" s="5" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C79" s="5" t="n">
         <v>2</v>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -633,7 +633,7 @@
         <v>2380</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>273</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3">
@@ -659,7 +659,7 @@
         <v>1329</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>701</v>
+        <v>726</v>
       </c>
     </row>
     <row r="5">
@@ -672,7 +672,7 @@
         <v>878</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6">
@@ -698,7 +698,7 @@
         <v>429</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
@@ -737,7 +737,7 @@
         <v>340</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11">
@@ -763,7 +763,7 @@
         <v>229</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -839,7 +839,7 @@
         <v>10000</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>1463</v>
+        <v>1504</v>
       </c>
     </row>
   </sheetData>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1854</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="3">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1916</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="6">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
       <c r="D17" s="4" t="inlineStr"/>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>1</v>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="B79" s="5" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C79" s="5" t="n">
         <v>2</v>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -997,7 +997,11 @@
       </c>
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1011,7 +1015,11 @@
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr"/>
@@ -1046,7 +1054,11 @@
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr"/>
     </row>
@@ -1062,7 +1074,11 @@
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr"/>
       <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
       <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="4" t="inlineStr"/>
       <c r="I9" s="4" t="inlineStr"/>
@@ -1200,7 +1216,11 @@
       <c r="E17" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
       <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="4" t="inlineStr"/>
       <c r="I17" s="4" t="inlineStr"/>
@@ -1510,7 +1530,11 @@
       <c r="F34" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
       <c r="H34" s="3" t="n">
         <v>14</v>
       </c>
@@ -1530,7 +1554,11 @@
       <c r="C35" s="4" t="inlineStr"/>
       <c r="D35" s="4" t="inlineStr"/>
       <c r="E35" s="4" t="inlineStr"/>
-      <c r="F35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
       <c r="G35" s="4" t="inlineStr"/>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr"/>
@@ -1617,14 +1645,22 @@
         <v>12</v>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
           <t>CHECK</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -1632,7 +1668,11 @@
           <t>North Scotland</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr"/>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
       <c r="C41" s="4" t="inlineStr"/>
       <c r="D41" s="4" t="inlineStr"/>
       <c r="E41" s="4" t="inlineStr"/>
@@ -1847,7 +1887,11 @@
           <t>Scotland Central - Tayside</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
       <c r="C54" s="2" t="inlineStr"/>
       <c r="D54" s="2" t="inlineStr"/>
       <c r="E54" s="2" t="inlineStr"/>
@@ -2039,7 +2083,11 @@
       <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
       <c r="I64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
@@ -2125,7 +2173,11 @@
           <t>Wales South - Valleys</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
       <c r="C70" s="2" t="inlineStr"/>
       <c r="D70" s="2" t="inlineStr"/>
       <c r="E70" s="2" t="inlineStr"/>
@@ -2522,11 +2574,7 @@
           <t>1 / 0.8 / 0/10</t>
         </is>
       </c>
-      <c r="I5" s="12" t="inlineStr">
-        <is>
-          <t>6 / 3.4 / 3/7</t>
-        </is>
-      </c>
+      <c r="I5" s="12" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
@@ -2550,11 +2598,7 @@
           <t>1 / 1.2 / 0/11</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t>6 / 3.2 / 3/11</t>
-        </is>
-      </c>
+      <c r="F6" s="11" t="inlineStr"/>
       <c r="G6" s="11" t="inlineStr">
         <is>
           <t>3 / 4.1 / 2/8</t>
@@ -2641,11 +2685,7 @@
           <t>1 / 0.5 / 0/11</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
-        <is>
-          <t>7 / 5.2 / 4/8</t>
-        </is>
-      </c>
+      <c r="G8" s="11" t="inlineStr"/>
       <c r="H8" s="11" t="inlineStr">
         <is>
           <t>0 / 0.1 / 0/10</t>
@@ -2679,11 +2719,7 @@
           <t>2 / 1.2 / 0/11</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>6 / 2.9 / 3/11</t>
-        </is>
-      </c>
+      <c r="F9" s="12" t="inlineStr"/>
       <c r="G9" s="12" t="inlineStr">
         <is>
           <t>1 / 1.9 / 0/8</t>
@@ -3023,11 +3059,7 @@
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr"/>
-      <c r="F17" s="12" t="inlineStr">
-        <is>
-          <t>7 / 3.5 / 3/11</t>
-        </is>
-      </c>
+      <c r="F17" s="12" t="inlineStr"/>
       <c r="G17" s="12" t="inlineStr">
         <is>
           <t>5 / 5.6 / 2/8</t>
@@ -3723,11 +3755,7 @@
       <c r="D34" s="11" t="inlineStr"/>
       <c r="E34" s="11" t="inlineStr"/>
       <c r="F34" s="11" t="inlineStr"/>
-      <c r="G34" s="11" t="inlineStr">
-        <is>
-          <t>7 / 5.6 / 4/8</t>
-        </is>
-      </c>
+      <c r="G34" s="11" t="inlineStr"/>
       <c r="H34" s="11" t="inlineStr"/>
       <c r="I34" s="11" t="inlineStr"/>
     </row>
@@ -3753,11 +3781,7 @@
           <t>2 / 0.6 / 0/11</t>
         </is>
       </c>
-      <c r="F35" s="12" t="inlineStr">
-        <is>
-          <t>7 / 2.7 / 2/11</t>
-        </is>
-      </c>
+      <c r="F35" s="12" t="inlineStr"/>
       <c r="G35" s="12" t="inlineStr">
         <is>
           <t>1 / 0.6 / 0/8</t>
@@ -3968,22 +3992,14 @@
           <t>1 / 1.0 / 0/11</t>
         </is>
       </c>
-      <c r="F40" s="11" t="inlineStr">
-        <is>
-          <t>6 / 4.5 / 3/11</t>
-        </is>
-      </c>
+      <c r="F40" s="11" t="inlineStr"/>
       <c r="G40" s="11" t="inlineStr"/>
       <c r="H40" s="11" t="inlineStr">
         <is>
           <t>1 / 1.1 / 0/10</t>
         </is>
       </c>
-      <c r="I40" s="11" t="inlineStr">
-        <is>
-          <t>8 / 7.9 / 3/7</t>
-        </is>
-      </c>
+      <c r="I40" s="11" t="inlineStr"/>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="12" t="inlineStr">
@@ -3991,11 +4007,7 @@
           <t>North Scotland</t>
         </is>
       </c>
-      <c r="B41" s="12" t="inlineStr">
-        <is>
-          <t>5 / 5.5 / 4/12</t>
-        </is>
-      </c>
+      <c r="B41" s="12" t="inlineStr"/>
       <c r="C41" s="12" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/12</t>
@@ -4566,11 +4578,7 @@
           <t>Scotland Central - Tayside</t>
         </is>
       </c>
-      <c r="B54" s="11" t="inlineStr">
-        <is>
-          <t>5 / 4.0 / 0/12</t>
-        </is>
-      </c>
+      <c r="B54" s="11" t="inlineStr"/>
       <c r="C54" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/12</t>
@@ -4998,11 +5006,7 @@
           <t>3 / 3.9 / 0/8</t>
         </is>
       </c>
-      <c r="H64" s="11" t="inlineStr">
-        <is>
-          <t>5 / 5.6 / 6/10</t>
-        </is>
-      </c>
+      <c r="H64" s="11" t="inlineStr"/>
       <c r="I64" s="11" t="inlineStr">
         <is>
           <t>5 / 3.3 / 0/7</t>
@@ -5246,11 +5250,7 @@
           <t>Wales South - Valleys</t>
         </is>
       </c>
-      <c r="B70" s="11" t="inlineStr">
-        <is>
-          <t>7 / 3.4 / 4/12</t>
-        </is>
-      </c>
+      <c r="B70" s="11" t="inlineStr"/>
       <c r="C70" s="11" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/12</t>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sitewide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JobG8 categories" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PAGES" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LIVE" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NOT LIVE" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Sitewide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="JobG8 categories" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="PAGES" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="LIVE" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="NOT LIVE" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sitewide'!$A$1:$B$9</definedName>
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -132,14 +132,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7609,63 +7603,69 @@
       <c r="B2" s="13" t="inlineStr"/>
       <c r="C2" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.2 / 0/13</t>
         </is>
       </c>
       <c r="D2" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 2.1 / 0/13</t>
         </is>
       </c>
       <c r="E2" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4 / 3.8 / 0/11</t>
         </is>
       </c>
       <c r="F2" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.1 / 0/11</t>
         </is>
       </c>
       <c r="G2" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.8 / 0/8</t>
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I2" s="14" t="n">
-        <v>2</v>
+          <t>1 / 1.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I2" s="13" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Berkshire</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr"/>
-      <c r="C3" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" s="15" t="inlineStr"/>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F3" s="15" t="inlineStr"/>
-      <c r="G3" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H3" s="15" t="inlineStr"/>
-      <c r="I3" s="16" t="n">
-        <v>7</v>
+      <c r="B3" s="14" t="inlineStr"/>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>0 / 3.0 / 3/13</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr"/>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>2 / 0.9 / 0/11</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr"/>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.6 / 0/8</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="inlineStr"/>
+      <c r="I3" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.4 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -7675,58 +7675,64 @@
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr"/>
-      <c r="C4" s="14" t="n">
-        <v>3</v>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.8 / 0/13</t>
+        </is>
       </c>
       <c r="D4" s="13" t="inlineStr"/>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 3.0 / 1/11</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr"/>
       <c r="G4" s="13" t="inlineStr"/>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I4" s="14" t="n">
-        <v>1</v>
+          <t>2 / 1.8 / 0/10</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>5 / 2.9 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Buckinghamshire</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr"/>
-      <c r="C5" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E5" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="15" t="inlineStr"/>
-      <c r="G5" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I5" s="15" t="inlineStr"/>
+      <c r="B5" s="14" t="inlineStr"/>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.6 / 0/13</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.7 / 0/13</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr"/>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>2 / 2.1 / 0/8</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.8 / 0/10</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
@@ -7735,71 +7741,79 @@
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr"/>
-      <c r="C6" s="14" t="n">
-        <v>2</v>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>1 / 0.2 / 0/13</t>
+        </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 2.6 / 0/13</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.2 / 0/11</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr"/>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 4.1 / 2/8</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I6" s="14" t="n">
-        <v>2</v>
+          <t>0 / 0.1 / 0/10</t>
+        </is>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Cheshire - East</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr"/>
-      <c r="C7" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I7" s="16" t="n">
-        <v>2</v>
+      <c r="B7" s="14" t="inlineStr"/>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.5 / 0/13</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>3 / 1.8 / 0/13</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/11</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.1 / 0/11</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>3 / 2.1 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -7811,67 +7825,73 @@
       <c r="B8" s="13" t="inlineStr"/>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.3 / 0/13</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.9 / 1/13</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 1.5 / 0/11</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.5 / 0/11</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr"/>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I8" s="14" t="n">
-        <v>1</v>
+          <t>0 / 0.1 / 0/10</t>
+        </is>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Cheshire - West</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr"/>
-      <c r="C9" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F9" s="15" t="inlineStr"/>
-      <c r="G9" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I9" s="16" t="n">
-        <v>1</v>
+      <c r="B9" s="14" t="inlineStr"/>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>0 / 1.2 / 0/13</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.8 / 0/13</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>2 / 1.2 / 0/11</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr"/>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.9 / 0/8</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.4 / 0/10</t>
+        </is>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.4 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -7881,78 +7901,86 @@
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr"/>
-      <c r="C10" s="14" t="n">
-        <v>2</v>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>0 / 1.2 / 0/13</t>
+        </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.8 / 0/13</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.2 / 0/11</t>
         </is>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.2 / 0/8</t>
         </is>
       </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I10" s="14" t="n">
-        <v>55</v>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.9 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Cumbria - North</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.5 / 0/13</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>0 / 2.4 / 3/13</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/8</t>
+        </is>
+      </c>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
     </row>
@@ -7962,82 +7990,88 @@
           <t>Cumbria - South</t>
         </is>
       </c>
-      <c r="B12" s="14" t="n">
-        <v>1</v>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>1 / 1.1 / 0/13</t>
+        </is>
       </c>
       <c r="C12" s="13" t="inlineStr"/>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.8 / 0/13</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 0.8 / 0/11</t>
         </is>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.5 / 0/8</t>
         </is>
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.3 / 0/10</t>
         </is>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Cumbria - West</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E13" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I13" s="16" t="n">
-        <v>1</v>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>0 / 1.5 / 0/13</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.6 / 0/13</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.4 / 0/8</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -8047,72 +8081,78 @@
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr"/>
-      <c r="C14" s="14" t="n">
-        <v>1</v>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.3 / 0/13</t>
+        </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 2.5 / 0/13</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 0.8 / 0/11</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 1.2 / 0/11</t>
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 2.9 / 0/8</t>
         </is>
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I14" s="14" t="n">
-        <v>1</v>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>3 / 1.9 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>Devon</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr"/>
-      <c r="C15" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E15" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F15" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G15" s="15" t="inlineStr"/>
-      <c r="H15" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I15" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B15" s="14" t="inlineStr"/>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>3 / 0.6 / 0/13</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>5 / 3.5 / 0/13</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>2 / 2.1 / 0/11</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>5 / 2.0 / 2/11</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr"/>
+      <c r="H15" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.1 / 0/10</t>
+        </is>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>2 / 1.3 / 0/7</t>
         </is>
       </c>
     </row>
@@ -8123,69 +8163,75 @@
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr"/>
-      <c r="C16" s="14" t="n">
-        <v>2</v>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/13</t>
+        </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 3.8 / 2/13</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.2 / 0/11</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 1.6 / 0/11</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 2.6 / 0/8</t>
         </is>
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I16" s="14" t="n">
-        <v>3</v>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>3 / 0.7 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Essex</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr"/>
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D17" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E17" s="15" t="inlineStr"/>
-      <c r="F17" s="15" t="inlineStr"/>
-      <c r="G17" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H17" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I17" s="16" t="n">
-        <v>3</v>
+      <c r="B17" s="14" t="inlineStr"/>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.6 / 0/13</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>6 / 2.6 / 1/13</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr"/>
+      <c r="F17" s="14" t="inlineStr"/>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>5 / 5.6 / 2/8</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.1 / 0/10</t>
+        </is>
+      </c>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>4 / 2.6 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -8195,57 +8241,63 @@
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr"/>
-      <c r="C18" s="14" t="n">
-        <v>4</v>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>1 / 0.4 / 0/13</t>
+        </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4 / 1.8 / 0/13</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr"/>
       <c r="G18" s="13" t="inlineStr"/>
       <c r="H18" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.2 / 0/10</t>
         </is>
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 1.9 / 0/7</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr"/>
-      <c r="C19" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" s="15" t="inlineStr"/>
-      <c r="E19" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F19" s="15" t="inlineStr"/>
-      <c r="G19" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H19" s="15" t="inlineStr"/>
-      <c r="I19" s="16" t="n">
-        <v>8</v>
+      <c r="B19" s="14" t="inlineStr"/>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>3 / 1.3 / 0/13</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr"/>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>4 / 3.9 / 2/11</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="inlineStr"/>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>4 / 3.8 / 0/8</t>
+        </is>
+      </c>
+      <c r="H19" s="14" t="inlineStr"/>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>3 / 2.4 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -8254,80 +8306,88 @@
           <t>Greater Manchester - North</t>
         </is>
       </c>
-      <c r="B20" s="14" t="n">
-        <v>5</v>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>3 / 3.1 / 1/13</t>
+        </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.2 / 0/13</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
       <c r="H20" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I20" s="14" t="n">
-        <v>4</v>
+          <t>0 / 0.1 / 0/10</t>
+        </is>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>1 / 0.4 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Greater Manchester - South</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr"/>
-      <c r="C21" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F21" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G21" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H21" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I21" s="16" t="n">
-        <v>5</v>
+      <c r="B21" s="14" t="inlineStr"/>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.7 / 0/13</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.6 / 0/13</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.5 / 0/11</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="inlineStr">
+        <is>
+          <t>2 / 0.5 / 0/11</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="H21" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>3 / 1.3 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -8337,72 +8397,76 @@
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr"/>
-      <c r="C22" s="14" t="n">
-        <v>0</v>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
       </c>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.8 / 0/13</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.5 / 0/11</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.2 / 0/8</t>
         </is>
       </c>
       <c r="H22" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I22" s="14" t="n">
-        <v>2</v>
+          <t>1 / 1.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>Hampshire</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr"/>
-      <c r="C23" s="15" t="inlineStr"/>
-      <c r="D23" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E23" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H23" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I23" s="15" t="inlineStr"/>
+      <c r="B23" s="14" t="inlineStr"/>
+      <c r="C23" s="14" t="inlineStr"/>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>13 / 8.3 / 9/13</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>0 / 1.4 / 0/11</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>10 / 5.9 / 4/11</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>1 / 2.4 / 0/8</t>
+        </is>
+      </c>
+      <c r="H23" s="14" t="inlineStr">
+        <is>
+          <t>4 / 3.6 / 0/10</t>
+        </is>
+      </c>
+      <c r="I23" s="14" t="inlineStr"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="13" t="inlineStr">
@@ -8410,74 +8474,80 @@
           <t>Herefordshire</t>
         </is>
       </c>
-      <c r="B24" s="14" t="n">
-        <v>1</v>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>0 / 1.2 / 0/13</t>
+        </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.4 / 0/13</t>
         </is>
       </c>
       <c r="D24" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.9 / 0/8</t>
         </is>
       </c>
       <c r="H24" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
       <c r="I24" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>Hertfordshire</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr"/>
-      <c r="C25" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="15" t="inlineStr"/>
-      <c r="E25" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F25" s="15" t="inlineStr"/>
-      <c r="G25" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H25" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I25" s="16" t="n">
-        <v>5</v>
+      <c r="B25" s="14" t="inlineStr"/>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>3 / 2.4 / 0/13</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr"/>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.5 / 0/11</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr"/>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="H25" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.4 / 0/10</t>
+        </is>
+      </c>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>3 / 2.0 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -8491,66 +8561,70 @@
       <c r="D26" s="13" t="inlineStr"/>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5 / 4.3 / 2/11</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr"/>
       <c r="G26" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 2.2 / 1/8</t>
         </is>
       </c>
       <c r="H26" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I26" s="14" t="n">
-        <v>4</v>
+          <t>2 / 1.7 / 0/10</t>
+        </is>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>3 / 1.4 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>Lancashire - Blackpool &amp; Fylde</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D27" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E27" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F27" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G27" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H27" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I27" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.7 / 0/13</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>2 / 1.1 / 0/11</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/8</t>
+        </is>
+      </c>
+      <c r="H27" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
     </row>
@@ -8560,81 +8634,91 @@
           <t>Lancashire - Central</t>
         </is>
       </c>
-      <c r="B28" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" s="14" t="n">
-        <v>1</v>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>3 / 2.8 / 0/13</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/13</t>
+        </is>
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.4 / 0/13</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.6 / 0/8</t>
         </is>
       </c>
       <c r="H28" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I28" s="14" t="n">
-        <v>1</v>
+          <t>0 / 0.2 / 0/10</t>
+        </is>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>Lancashire - East</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="D29" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E29" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F29" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G29" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H29" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I29" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>4 / 2.7 / 0/13</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.8 / 0/13</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/13</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/11</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>3 / 1.5 / 0/11</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.1 / 0/8</t>
+        </is>
+      </c>
+      <c r="H29" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
     </row>
@@ -8646,87 +8730,89 @@
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C30" s="14" t="n">
-        <v>3</v>
+          <t>2 / 1.2 / 0/13</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>0 / 1.0 / 0/13</t>
+        </is>
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.2 / 0/13</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
       <c r="H30" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.3 / 0/10</t>
         </is>
       </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>Lancashire - West</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C31" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D31" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E31" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F31" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G31" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H31" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I31" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>0 / 1.1 / 0/12</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/12</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.2 / 0/12</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
     </row>
@@ -8737,75 +8823,83 @@
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr"/>
-      <c r="C32" s="14" t="n">
-        <v>1</v>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/13</t>
+        </is>
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 1.6 / 0/13</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 1.5 / 0/11</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 1.2 / 0/11</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 2.8 / 1/8</t>
         </is>
       </c>
       <c r="H32" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I32" s="14" t="n">
-        <v>5</v>
+          <t>1 / 0.8 / 0/10</t>
+        </is>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>2 / 2.6 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t>Lincolnshire</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr"/>
-      <c r="C33" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D33" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E33" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F33" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G33" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H33" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I33" s="16" t="n">
-        <v>2</v>
+      <c r="B33" s="14" t="inlineStr"/>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>0 / 1.5 / 0/13</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>5 / 1.8 / 0/13</t>
+        </is>
+      </c>
+      <c r="E33" s="14" t="inlineStr">
+        <is>
+          <t>2 / 1.5 / 0/11</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="inlineStr">
+        <is>
+          <t>2 / 2.6 / 0/11</t>
+        </is>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>1 / 2.4 / 0/8</t>
+        </is>
+      </c>
+      <c r="H33" s="14" t="inlineStr">
+        <is>
+          <t>2 / 1.5 / 0/10</t>
+        </is>
+      </c>
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -8824,38 +8918,42 @@
       <c r="I34" s="13" t="inlineStr"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>Merseyside - Liverpool</t>
         </is>
       </c>
-      <c r="B35" s="15" t="inlineStr"/>
-      <c r="C35" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D35" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E35" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F35" s="15" t="inlineStr"/>
-      <c r="G35" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H35" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I35" s="16" t="n">
-        <v>0</v>
+      <c r="B35" s="14" t="inlineStr"/>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.3 / 0/13</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/13</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>2 / 0.6 / 0/11</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr"/>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.6 / 0/8</t>
+        </is>
+      </c>
+      <c r="H35" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/10</t>
+        </is>
+      </c>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
@@ -8866,87 +8964,89 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C36" s="14" t="n">
-        <v>1</v>
+          <t>0 / 0.1 / 0/12</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="F36" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="G36" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
       <c r="H36" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
       <c r="I36" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="14" t="inlineStr">
         <is>
           <t>Merseyside - St Helens &amp; Knowsley</t>
         </is>
       </c>
-      <c r="B37" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C37" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D37" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E37" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F37" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G37" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H37" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I37" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.8 / 0/12</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.8 / 0/12</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="F37" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.5 / 0/8</t>
+        </is>
+      </c>
+      <c r="H37" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I37" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
     </row>
@@ -8956,74 +9056,84 @@
           <t>Merseyside - Wirral</t>
         </is>
       </c>
-      <c r="B38" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" s="14" t="n">
-        <v>0</v>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>1 / 1.5 / 0/13</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.4 / 0/13</t>
+        </is>
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.0 / 0/13</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.5 / 0/11</t>
         </is>
       </c>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 0.7 / 0/11</t>
         </is>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.4 / 0/8</t>
         </is>
       </c>
       <c r="H38" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I38" s="14" t="n">
-        <v>2</v>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="14" t="inlineStr">
         <is>
           <t>Norfolk</t>
         </is>
       </c>
-      <c r="B39" s="15" t="inlineStr"/>
-      <c r="C39" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D39" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E39" s="15" t="inlineStr"/>
-      <c r="F39" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G39" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H39" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I39" s="16" t="n">
-        <v>3</v>
+      <c r="B39" s="14" t="inlineStr"/>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.9 / 0/13</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.7 / 0/13</t>
+        </is>
+      </c>
+      <c r="E39" s="14" t="inlineStr"/>
+      <c r="F39" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.5 / 0/11</t>
+        </is>
+      </c>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>2 / 3.6 / 2/8</t>
+        </is>
+      </c>
+      <c r="H39" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/10</t>
+        </is>
+      </c>
+      <c r="I39" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.9 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
@@ -9037,56 +9147,58 @@
       <c r="D40" s="13" t="inlineStr"/>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.0 / 0/11</t>
         </is>
       </c>
       <c r="F40" s="13" t="inlineStr"/>
       <c r="G40" s="13" t="inlineStr"/>
       <c r="H40" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.1 / 0/10</t>
         </is>
       </c>
       <c r="I40" s="13" t="inlineStr"/>
     </row>
     <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="A41" s="14" t="inlineStr">
         <is>
           <t>North Scotland</t>
         </is>
       </c>
-      <c r="B41" s="15" t="inlineStr"/>
-      <c r="C41" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E41" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F41" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G41" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H41" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I41" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B41" s="14" t="inlineStr"/>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>6 / 3.5 / 3/12</t>
+        </is>
+      </c>
+      <c r="E41" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/11</t>
+        </is>
+      </c>
+      <c r="F41" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.5 / 0/8</t>
+        </is>
+      </c>
+      <c r="H41" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I41" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
     </row>
@@ -9096,82 +9208,92 @@
           <t>North Wales - East</t>
         </is>
       </c>
-      <c r="B42" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="C42" s="14" t="n">
-        <v>0</v>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>4 / 4.5 / 1/12</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/12</t>
+        </is>
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 1.5 / 0/12</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="F42" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.5 / 0/11</t>
         </is>
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.4 / 0/8</t>
         </is>
       </c>
       <c r="H42" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I42" s="14" t="n">
-        <v>2</v>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="A43" s="14" t="inlineStr">
         <is>
           <t>North Wales - West</t>
         </is>
       </c>
-      <c r="B43" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C43" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E43" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F43" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G43" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H43" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I43" s="16" t="n">
-        <v>0</v>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>3 / 2.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="H43" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.4 / 0/10</t>
+        </is>
+      </c>
+      <c r="I43" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.6 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
@@ -9181,72 +9303,78 @@
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr"/>
-      <c r="C44" s="14" t="n">
-        <v>1</v>
+      <c r="C44" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10 / 4.5 / 3/13</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.3 / 0/11</t>
         </is>
       </c>
       <c r="F44" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4 / 2.5 / 0/11</t>
         </is>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 2.9 / 2/8</t>
         </is>
       </c>
       <c r="H44" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I44" s="14" t="n">
-        <v>4</v>
+          <t>3 / 2.6 / 1/10</t>
+        </is>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>1 / 0.4 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="15" t="inlineStr">
+      <c r="A45" s="14" t="inlineStr">
         <is>
           <t>Northern Ireland - East</t>
         </is>
       </c>
-      <c r="B45" s="15" t="inlineStr"/>
-      <c r="C45" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E45" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F45" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G45" s="15" t="inlineStr"/>
-      <c r="H45" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I45" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B45" s="14" t="inlineStr"/>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.6 / 0/12</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="E45" s="14" t="inlineStr">
+        <is>
+          <t>2 / 1.3 / 0/11</t>
+        </is>
+      </c>
+      <c r="F45" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.1 / 0/11</t>
+        </is>
+      </c>
+      <c r="G45" s="14" t="inlineStr"/>
+      <c r="H45" s="14" t="inlineStr">
+        <is>
+          <t>3 / 0.4 / 0/10</t>
+        </is>
+      </c>
+      <c r="I45" s="14" t="inlineStr">
+        <is>
+          <t>2 / 1.0 / 0/7</t>
         </is>
       </c>
     </row>
@@ -9256,76 +9384,84 @@
           <t>Northern Ireland - West</t>
         </is>
       </c>
-      <c r="B46" s="14" t="n">
-        <v>2</v>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>20 / 5.2 / 1/12</t>
+        </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 1.3 / 0/12</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="F46" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.1 / 0/8</t>
         </is>
       </c>
       <c r="H46" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I46" s="14" t="n">
-        <v>1</v>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="A47" s="14" t="inlineStr">
         <is>
           <t>Nottinghamshire</t>
         </is>
       </c>
-      <c r="B47" s="15" t="inlineStr"/>
-      <c r="C47" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E47" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F47" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G47" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H47" s="15" t="inlineStr"/>
-      <c r="I47" s="16" t="n">
-        <v>3</v>
+      <c r="B47" s="14" t="inlineStr"/>
+      <c r="C47" s="14" t="inlineStr">
+        <is>
+          <t>2 / 0.8 / 0/13</t>
+        </is>
+      </c>
+      <c r="D47" s="14" t="inlineStr">
+        <is>
+          <t>4 / 2.2 / 0/13</t>
+        </is>
+      </c>
+      <c r="E47" s="14" t="inlineStr">
+        <is>
+          <t>2 / 2.1 / 0/11</t>
+        </is>
+      </c>
+      <c r="F47" s="14" t="inlineStr">
+        <is>
+          <t>4 / 2.4 / 0/11</t>
+        </is>
+      </c>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>1 / 3.0 / 2/8</t>
+        </is>
+      </c>
+      <c r="H47" s="14" t="inlineStr"/>
+      <c r="I47" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
@@ -9338,73 +9474,75 @@
       <c r="C48" s="13" t="inlineStr"/>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4 / 3.2 / 0/13</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 1.7 / 0/11</t>
         </is>
       </c>
       <c r="F48" s="13" t="inlineStr"/>
       <c r="G48" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 2.4 / 0/8</t>
         </is>
       </c>
       <c r="H48" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I48" s="14" t="n">
-        <v>1</v>
+          <t>1 / 0.4 / 0/10</t>
+        </is>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>3 / 1.4 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="15" t="inlineStr">
+      <c r="A49" s="14" t="inlineStr">
         <is>
           <t>Rutland</t>
         </is>
       </c>
-      <c r="B49" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C49" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D49" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E49" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F49" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G49" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H49" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I49" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="H49" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I49" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
     </row>
@@ -9416,82 +9554,86 @@
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 1.4 / 0/12</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="F50" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.1 / 0/8</t>
         </is>
       </c>
       <c r="H50" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.1 / 0/7</t>
         </is>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="15" t="inlineStr">
+      <c r="A51" s="14" t="inlineStr">
         <is>
           <t>Scotland Central - Edinburgh &amp; Lothians</t>
         </is>
       </c>
-      <c r="B51" s="15" t="inlineStr"/>
-      <c r="C51" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D51" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E51" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F51" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G51" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H51" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I51" s="16" t="n">
-        <v>2</v>
+      <c r="B51" s="14" t="inlineStr"/>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/12</t>
+        </is>
+      </c>
+      <c r="D51" s="14" t="inlineStr">
+        <is>
+          <t>3 / 2.4 / 0/12</t>
+        </is>
+      </c>
+      <c r="E51" s="14" t="inlineStr">
+        <is>
+          <t>3 / 2.5 / 0/11</t>
+        </is>
+      </c>
+      <c r="F51" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.3 / 0/11</t>
+        </is>
+      </c>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.1 / 0/8</t>
+        </is>
+      </c>
+      <c r="H51" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.5 / 0/10</t>
+        </is>
+      </c>
+      <c r="I51" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.4 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
@@ -9500,83 +9642,91 @@
           <t>Scotland Central - Falkirk &amp; Stirling</t>
         </is>
       </c>
-      <c r="B52" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C52" s="14" t="n">
-        <v>1</v>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>1 / 2.4 / 0/12</t>
+        </is>
+      </c>
+      <c r="C52" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="F52" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="G52" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 1.0 / 0/8</t>
         </is>
       </c>
       <c r="H52" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I52" s="14" t="n">
-        <v>0</v>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I52" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="15" t="inlineStr">
+      <c r="A53" s="14" t="inlineStr">
         <is>
           <t>Scotland Central - Fife</t>
         </is>
       </c>
-      <c r="B53" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C53" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E53" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F53" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G53" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H53" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I53" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>2 / 1.6 / 0/12</t>
+        </is>
+      </c>
+      <c r="C53" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="D53" s="14" t="inlineStr">
+        <is>
+          <t>2 / 1.2 / 0/12</t>
+        </is>
+      </c>
+      <c r="E53" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="F53" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.5 / 0/8</t>
+        </is>
+      </c>
+      <c r="H53" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I53" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
     </row>
@@ -9589,83 +9739,85 @@
       <c r="B54" s="13" t="inlineStr"/>
       <c r="C54" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.2 / 0/12</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.2 / 0/11</t>
         </is>
       </c>
       <c r="F54" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.2 / 0/11</t>
         </is>
       </c>
       <c r="G54" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.5 / 0/8</t>
         </is>
       </c>
       <c r="H54" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
       <c r="I54" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.4 / 0/7</t>
         </is>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="15" t="inlineStr">
+      <c r="A55" s="14" t="inlineStr">
         <is>
           <t>Scotland West - Ayrshire</t>
         </is>
       </c>
-      <c r="B55" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C55" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D55" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E55" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F55" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G55" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H55" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I55" s="16" t="n">
-        <v>0</v>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.6 / 0/12</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="D55" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="E55" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.5 / 0/11</t>
+        </is>
+      </c>
+      <c r="F55" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="H55" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I55" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.7 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
@@ -9675,75 +9827,83 @@
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr"/>
-      <c r="C56" s="14" t="n">
-        <v>0</v>
+      <c r="C56" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
       </c>
       <c r="D56" s="13" t="inlineStr"/>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.4 / 0/11</t>
         </is>
       </c>
       <c r="F56" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.3 / 0/11</t>
         </is>
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.2 / 0/8</t>
         </is>
       </c>
       <c r="H56" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I56" s="14" t="n">
-        <v>0</v>
+          <t>0 / 0.5 / 0/10</t>
+        </is>
+      </c>
+      <c r="I56" s="13" t="inlineStr">
+        <is>
+          <t>4 / 3.4 / 1/7</t>
+        </is>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="15" t="inlineStr">
+      <c r="A57" s="14" t="inlineStr">
         <is>
           <t>Scotland West - Lanarkshire</t>
         </is>
       </c>
-      <c r="B57" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C57" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D57" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E57" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F57" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G57" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H57" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I57" s="16" t="n">
-        <v>0</v>
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.4 / 0/12</t>
+        </is>
+      </c>
+      <c r="C57" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/12</t>
+        </is>
+      </c>
+      <c r="D57" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.3 / 0/12</t>
+        </is>
+      </c>
+      <c r="E57" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="F57" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.1 / 0/8</t>
+        </is>
+      </c>
+      <c r="H57" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I57" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
@@ -9754,75 +9914,81 @@
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C58" s="14" t="n">
-        <v>0</v>
+          <t>1 / 1.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="C58" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
       </c>
       <c r="D58" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.5 / 0/12</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="F58" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="G58" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.5 / 0/8</t>
         </is>
       </c>
       <c r="H58" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I58" s="14" t="n">
-        <v>0</v>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I58" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="15" t="inlineStr">
+      <c r="A59" s="14" t="inlineStr">
         <is>
           <t>Shropshire</t>
         </is>
       </c>
-      <c r="B59" s="15" t="inlineStr"/>
-      <c r="C59" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="D59" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E59" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F59" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G59" s="15" t="inlineStr"/>
-      <c r="H59" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I59" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B59" s="14" t="inlineStr"/>
+      <c r="C59" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.6 / 0/13</t>
+        </is>
+      </c>
+      <c r="D59" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.1 / 0/13</t>
+        </is>
+      </c>
+      <c r="E59" s="14" t="inlineStr">
+        <is>
+          <t>3 / 1.9 / 0/11</t>
+        </is>
+      </c>
+      <c r="F59" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.4 / 0/11</t>
+        </is>
+      </c>
+      <c r="G59" s="14" t="inlineStr"/>
+      <c r="H59" s="14" t="inlineStr">
+        <is>
+          <t>2 / 1.9 / 0/10</t>
+        </is>
+      </c>
+      <c r="I59" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
     </row>
@@ -9833,74 +9999,80 @@
         </is>
       </c>
       <c r="B60" s="13" t="inlineStr"/>
-      <c r="C60" s="14" t="n">
-        <v>4</v>
+      <c r="C60" s="13" t="inlineStr">
+        <is>
+          <t>2 / 3.4 / 3/13</t>
+        </is>
       </c>
       <c r="D60" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4 / 1.7 / 0/13</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.5 / 0/11</t>
         </is>
       </c>
       <c r="F60" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4 / 1.2 / 0/11</t>
         </is>
       </c>
       <c r="G60" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 2.6 / 1/8</t>
         </is>
       </c>
       <c r="H60" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I60" s="14" t="n">
-        <v>0</v>
+          <t>1 / 0.2 / 0/10</t>
+        </is>
+      </c>
+      <c r="I60" s="13" t="inlineStr">
+        <is>
+          <t>2 / 0.9 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="15" t="inlineStr">
+      <c r="A61" s="14" t="inlineStr">
         <is>
           <t>Staffordshire</t>
         </is>
       </c>
-      <c r="B61" s="15" t="inlineStr"/>
-      <c r="C61" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="D61" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E61" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F61" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G61" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H61" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I61" s="15" t="inlineStr"/>
+      <c r="B61" s="14" t="inlineStr"/>
+      <c r="C61" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/13</t>
+        </is>
+      </c>
+      <c r="D61" s="14" t="inlineStr">
+        <is>
+          <t>2 / 1.5 / 0/13</t>
+        </is>
+      </c>
+      <c r="E61" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="F61" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.3 / 0/11</t>
+        </is>
+      </c>
+      <c r="G61" s="14" t="inlineStr">
+        <is>
+          <t>3 / 2.6 / 0/8</t>
+        </is>
+      </c>
+      <c r="H61" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/10</t>
+        </is>
+      </c>
+      <c r="I61" s="14" t="inlineStr"/>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="13" t="inlineStr">
@@ -9909,62 +10081,64 @@
         </is>
       </c>
       <c r="B62" s="13" t="inlineStr"/>
-      <c r="C62" s="14" t="n">
-        <v>0</v>
+      <c r="C62" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.8 / 0/13</t>
+        </is>
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 1.8 / 0/13</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr"/>
       <c r="F62" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.5 / 0/11</t>
         </is>
       </c>
       <c r="G62" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.6 / 0/8</t>
         </is>
       </c>
       <c r="H62" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.0 / 0/10</t>
         </is>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.6 / 0/7</t>
         </is>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="15" t="inlineStr">
+      <c r="A63" s="14" t="inlineStr">
         <is>
           <t>Surrey</t>
         </is>
       </c>
-      <c r="B63" s="15" t="inlineStr"/>
-      <c r="C63" s="15" t="inlineStr"/>
-      <c r="D63" s="15" t="inlineStr"/>
-      <c r="E63" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F63" s="15" t="inlineStr"/>
-      <c r="G63" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H63" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I63" s="15" t="inlineStr"/>
+      <c r="B63" s="14" t="inlineStr"/>
+      <c r="C63" s="14" t="inlineStr"/>
+      <c r="D63" s="14" t="inlineStr"/>
+      <c r="E63" s="14" t="inlineStr">
+        <is>
+          <t>6 / 4.2 / 1/11</t>
+        </is>
+      </c>
+      <c r="F63" s="14" t="inlineStr"/>
+      <c r="G63" s="14" t="inlineStr">
+        <is>
+          <t>3 / 4.6 / 2/8</t>
+        </is>
+      </c>
+      <c r="H63" s="14" t="inlineStr">
+        <is>
+          <t>3 / 2.2 / 0/10</t>
+        </is>
+      </c>
+      <c r="I63" s="14" t="inlineStr"/>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="13" t="inlineStr">
@@ -9977,67 +10151,71 @@
       <c r="D64" s="13" t="inlineStr"/>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4 / 2.4 / 0/11</t>
         </is>
       </c>
       <c r="F64" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5 / 2.9 / 0/11</t>
         </is>
       </c>
       <c r="G64" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 3.9 / 0/8</t>
         </is>
       </c>
       <c r="H64" s="13" t="inlineStr"/>
-      <c r="I64" s="14" t="n">
-        <v>4</v>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>5 / 3.3 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="15" t="inlineStr">
+      <c r="A65" s="14" t="inlineStr">
         <is>
           <t>Wales - Mid</t>
         </is>
       </c>
-      <c r="B65" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C65" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D65" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E65" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F65" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G65" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H65" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I65" s="16" t="n">
-        <v>1</v>
+      <c r="B65" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/12</t>
+        </is>
+      </c>
+      <c r="C65" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="E65" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="F65" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="G65" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="H65" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I65" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -10046,81 +10224,87 @@
           <t>Wales - West</t>
         </is>
       </c>
-      <c r="B66" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C66" s="14" t="n">
-        <v>1</v>
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>4 / 2.2 / 0/12</t>
+        </is>
+      </c>
+      <c r="C66" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
       </c>
       <c r="D66" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="F66" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="G66" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.5 / 0/8</t>
         </is>
       </c>
       <c r="H66" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.3 / 0/10</t>
         </is>
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="15" t="inlineStr">
+      <c r="A67" s="14" t="inlineStr">
         <is>
           <t>Wales South - Cardiff &amp; Vale</t>
         </is>
       </c>
-      <c r="B67" s="15" t="inlineStr"/>
-      <c r="C67" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D67" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E67" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F67" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G67" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H67" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I67" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B67" s="14" t="inlineStr"/>
+      <c r="C67" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="D67" s="14" t="inlineStr">
+        <is>
+          <t>3 / 1.9 / 0/12</t>
+        </is>
+      </c>
+      <c r="E67" s="14" t="inlineStr">
+        <is>
+          <t>2 / 1.5 / 0/11</t>
+        </is>
+      </c>
+      <c r="F67" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="G67" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.9 / 0/8</t>
+        </is>
+      </c>
+      <c r="H67" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I67" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.4 / 0/7</t>
         </is>
       </c>
     </row>
@@ -10132,84 +10316,90 @@
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 2.4 / 0/12</t>
         </is>
       </c>
       <c r="C68" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.1 / 0/12</t>
         </is>
       </c>
       <c r="D68" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.2 / 0/12</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 1.5 / 0/11</t>
         </is>
       </c>
       <c r="F68" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="G68" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.5 / 0/8</t>
         </is>
       </c>
       <c r="H68" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
       <c r="I68" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="15" t="inlineStr">
+      <c r="A69" s="14" t="inlineStr">
         <is>
           <t>Wales South - Swansea Bay</t>
         </is>
       </c>
-      <c r="B69" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C69" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D69" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E69" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F69" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G69" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H69" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I69" s="16" t="n">
-        <v>10</v>
+      <c r="B69" s="14" t="inlineStr">
+        <is>
+          <t>4 / 3.3 / 1/12</t>
+        </is>
+      </c>
+      <c r="C69" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/12</t>
+        </is>
+      </c>
+      <c r="D69" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.7 / 0/12</t>
+        </is>
+      </c>
+      <c r="E69" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.6 / 0/11</t>
+        </is>
+      </c>
+      <c r="F69" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/11</t>
+        </is>
+      </c>
+      <c r="G69" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/8</t>
+        </is>
+      </c>
+      <c r="H69" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I69" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
@@ -10219,69 +10409,75 @@
         </is>
       </c>
       <c r="B70" s="13" t="inlineStr"/>
-      <c r="C70" s="14" t="n">
-        <v>0</v>
+      <c r="C70" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 0.7 / 0/12</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4 / 2.8 / 0/11</t>
         </is>
       </c>
       <c r="F70" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.4 / 0/11</t>
         </is>
       </c>
       <c r="G70" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.1 / 0/8</t>
         </is>
       </c>
       <c r="H70" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I70" s="14" t="n">
-        <v>19</v>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>2 / 1.1 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="15" t="inlineStr">
+      <c r="A71" s="14" t="inlineStr">
         <is>
           <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
-      <c r="B71" s="15" t="inlineStr"/>
-      <c r="C71" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D71" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="15" t="inlineStr"/>
-      <c r="G71" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="15" t="inlineStr"/>
-      <c r="I71" s="16" t="n">
-        <v>1</v>
+      <c r="B71" s="14" t="inlineStr"/>
+      <c r="C71" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="D71" s="14" t="inlineStr">
+        <is>
+          <t>10 / 4.9 / 3/13</t>
+        </is>
+      </c>
+      <c r="E71" s="14" t="inlineStr">
+        <is>
+          <t>4 / 4.0 / 2/11</t>
+        </is>
+      </c>
+      <c r="F71" s="14" t="inlineStr"/>
+      <c r="G71" s="14" t="inlineStr">
+        <is>
+          <t>3 / 2.8 / 0/8</t>
+        </is>
+      </c>
+      <c r="H71" s="14" t="inlineStr"/>
+      <c r="I71" s="14" t="inlineStr">
+        <is>
+          <t>5 / 3.9 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
@@ -10291,77 +10487,83 @@
         </is>
       </c>
       <c r="B72" s="13" t="inlineStr"/>
-      <c r="C72" s="14" t="n">
-        <v>1</v>
+      <c r="C72" s="13" t="inlineStr">
+        <is>
+          <t>1 / 1.1 / 0/13</t>
+        </is>
       </c>
       <c r="D72" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.0 / 0/13</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 1.5 / 0/11</t>
         </is>
       </c>
       <c r="F72" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.5 / 0/11</t>
         </is>
       </c>
       <c r="G72" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.2 / 0/8</t>
         </is>
       </c>
       <c r="H72" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.0 / 0/7</t>
         </is>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="15" t="inlineStr">
+      <c r="A73" s="14" t="inlineStr">
         <is>
           <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
-      <c r="B73" s="15" t="inlineStr"/>
-      <c r="C73" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="D73" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I73" s="16" t="n">
-        <v>1</v>
+      <c r="B73" s="14" t="inlineStr"/>
+      <c r="C73" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="D73" s="14" t="inlineStr">
+        <is>
+          <t>6 / 2.0 / 3/13</t>
+        </is>
+      </c>
+      <c r="E73" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.6 / 0/11</t>
+        </is>
+      </c>
+      <c r="F73" s="14" t="inlineStr">
+        <is>
+          <t>3 / 2.6 / 0/11</t>
+        </is>
+      </c>
+      <c r="G73" s="14" t="inlineStr">
+        <is>
+          <t>2 / 2.2 / 0/8</t>
+        </is>
+      </c>
+      <c r="H73" s="14" t="inlineStr">
+        <is>
+          <t>3 / 3.1 / 0/10</t>
+        </is>
+      </c>
+      <c r="I73" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.6 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -10374,70 +10576,76 @@
       <c r="C74" s="13" t="inlineStr"/>
       <c r="D74" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 2.2 / 0/13</t>
         </is>
       </c>
       <c r="E74" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4 / 3.2 / 0/11</t>
         </is>
       </c>
       <c r="F74" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.1 / 0/11</t>
         </is>
       </c>
       <c r="G74" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 2.1 / 0/8</t>
         </is>
       </c>
       <c r="H74" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="14" t="n">
-        <v>4</v>
+          <t>0 / 0.5 / 0/10</t>
+        </is>
+      </c>
+      <c r="I74" s="13" t="inlineStr">
+        <is>
+          <t>2 / 1.3 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="15" t="inlineStr">
+      <c r="A75" s="14" t="inlineStr">
         <is>
           <t>Worcestershire</t>
         </is>
       </c>
-      <c r="B75" s="15" t="inlineStr"/>
-      <c r="C75" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D75" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E75" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F75" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G75" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H75" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I75" s="16" t="n">
-        <v>1</v>
+      <c r="B75" s="14" t="inlineStr"/>
+      <c r="C75" s="14" t="inlineStr">
+        <is>
+          <t>0 / 1.1 / 0/13</t>
+        </is>
+      </c>
+      <c r="D75" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.9 / 0/13</t>
+        </is>
+      </c>
+      <c r="E75" s="14" t="inlineStr">
+        <is>
+          <t>2 / 0.7 / 0/11</t>
+        </is>
+      </c>
+      <c r="F75" s="14" t="inlineStr">
+        <is>
+          <t>3 / 1.6 / 0/11</t>
+        </is>
+      </c>
+      <c r="G75" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.6 / 0/8</t>
+        </is>
+      </c>
+      <c r="H75" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/10</t>
+        </is>
+      </c>
+      <c r="I75" s="14" t="inlineStr">
+        <is>
+          <t>2 / 0.7 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -10447,71 +10655,79 @@
         </is>
       </c>
       <c r="B76" s="13" t="inlineStr"/>
-      <c r="C76" s="14" t="n">
-        <v>3</v>
+      <c r="C76" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.6 / 0/13</t>
+        </is>
       </c>
       <c r="D76" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 1.0 / 0/13</t>
         </is>
       </c>
       <c r="E76" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 1.2 / 0/11</t>
         </is>
       </c>
       <c r="F76" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 0.7 / 0/11</t>
         </is>
       </c>
       <c r="G76" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 3.5 / 0/8</t>
         </is>
       </c>
       <c r="H76" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I76" s="14" t="n">
-        <v>5</v>
+          <t>1 / 1.2 / 0/10</t>
+        </is>
+      </c>
+      <c r="I76" s="13" t="inlineStr">
+        <is>
+          <t>5 / 3.4 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="15" t="inlineStr">
+      <c r="A77" s="14" t="inlineStr">
         <is>
           <t>Yorkshire - North</t>
         </is>
       </c>
-      <c r="B77" s="15" t="inlineStr"/>
-      <c r="C77" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="D77" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E77" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F77" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G77" s="15" t="inlineStr"/>
-      <c r="H77" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I77" s="16" t="n">
-        <v>2</v>
+      <c r="B77" s="14" t="inlineStr"/>
+      <c r="C77" s="14" t="inlineStr">
+        <is>
+          <t>1 / 3.2 / 0/13</t>
+        </is>
+      </c>
+      <c r="D77" s="14" t="inlineStr">
+        <is>
+          <t>3 / 1.2 / 0/13</t>
+        </is>
+      </c>
+      <c r="E77" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/11</t>
+        </is>
+      </c>
+      <c r="F77" s="14" t="inlineStr">
+        <is>
+          <t>12 / 4.4 / 3/11</t>
+        </is>
+      </c>
+      <c r="G77" s="14" t="inlineStr"/>
+      <c r="H77" s="14" t="inlineStr">
+        <is>
+          <t>2 / 1.6 / 0/10</t>
+        </is>
+      </c>
+      <c r="I77" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
@@ -10524,56 +10740,60 @@
       <c r="C78" s="13" t="inlineStr"/>
       <c r="D78" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4 / 2.3 / 0/13</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 3.1 / 0/11</t>
         </is>
       </c>
       <c r="F78" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5 / 2.5 / 1/11</t>
         </is>
       </c>
       <c r="G78" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 1.8 / 2/8</t>
         </is>
       </c>
       <c r="H78" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I78" s="14" t="n">
-        <v>11</v>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I78" s="13" t="inlineStr">
+        <is>
+          <t>2 / 1.4 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="15" t="inlineStr">
+      <c r="A79" s="14" t="inlineStr">
         <is>
           <t>Yorkshire - West</t>
         </is>
       </c>
-      <c r="B79" s="15" t="inlineStr"/>
-      <c r="C79" s="15" t="inlineStr"/>
-      <c r="D79" s="15" t="inlineStr"/>
-      <c r="E79" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="15" t="inlineStr"/>
-      <c r="H79" s="15" t="inlineStr"/>
-      <c r="I79" s="16" t="n">
-        <v>5</v>
+      <c r="B79" s="14" t="inlineStr"/>
+      <c r="C79" s="14" t="inlineStr"/>
+      <c r="D79" s="14" t="inlineStr"/>
+      <c r="E79" s="14" t="inlineStr">
+        <is>
+          <t>5 / 4.2 / 0/11</t>
+        </is>
+      </c>
+      <c r="F79" s="14" t="inlineStr">
+        <is>
+          <t>16 / 7.5 / 5/11</t>
+        </is>
+      </c>
+      <c r="G79" s="14" t="inlineStr"/>
+      <c r="H79" s="14" t="inlineStr"/>
+      <c r="I79" s="14" t="inlineStr">
+        <is>
+          <t>3 / 2.7 / 0/7</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -643,10 +643,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2380</v>
+        <v>2342</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>280</v>
+        <v>296</v>
       </c>
     </row>
     <row r="3">
@@ -656,10 +656,10 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1675</v>
+        <v>1670</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
@@ -669,10 +669,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1329</v>
+        <v>1332</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>726</v>
+        <v>723</v>
       </c>
     </row>
     <row r="5">
@@ -682,10 +682,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>878</v>
+        <v>901</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>834</v>
+        <v>815</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="7">
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8">
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>35</v>
@@ -743,27 +743,27 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>HR / Recruitment</t>
+          <t>Retail &amp; Consumer Products</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Retail &amp; Consumer Products</t>
+          <t>HR / Recruitment</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12">
@@ -773,10 +773,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -786,10 +786,10 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -799,10 +799,10 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="C15" s="8" t="inlineStr"/>
     </row>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -836,11 +836,9 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>109</v>
-      </c>
-      <c r="C17" s="7" t="n">
-        <v>1</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="C17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
@@ -852,7 +850,7 @@
         <v>10000</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>1504</v>
+        <v>1533</v>
       </c>
     </row>
   </sheetData>
@@ -7683,14 +7681,14 @@
       <c r="D4" s="13" t="inlineStr"/>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>3 / 3.0 / 1/11</t>
+          <t>2 / 2.9 / 1/11</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr"/>
       <c r="G4" s="13" t="inlineStr"/>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.8 / 0/10</t>
+          <t>3 / 1.9 / 0/10</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
@@ -7759,7 +7757,7 @@
       <c r="F6" s="13" t="inlineStr"/>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>3 / 4.1 / 2/8</t>
+          <t>2 / 4.0 / 2/8</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
@@ -7769,7 +7767,7 @@
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/7</t>
+          <t>0 / 0.9 / 0/7</t>
         </is>
       </c>
     </row>
@@ -7812,7 +7810,7 @@
       </c>
       <c r="I7" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.1 / 0/7</t>
+          <t>2 / 2.0 / 0/7</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7838,7 @@
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/11</t>
+          <t>0 / 0.4 / 0/11</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr"/>
@@ -7869,7 +7867,7 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.8 / 0/13</t>
+          <t>2 / 1.8 / 0/13</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -7903,12 +7901,12 @@
       <c r="B10" s="13" t="inlineStr"/>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.2 / 0/13</t>
+          <t>1 / 1.3 / 0/13</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/13</t>
+          <t>2 / 0.8 / 0/13</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
@@ -8098,7 +8096,7 @@
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.2 / 0/11</t>
+          <t>2 / 1.1 / 0/11</t>
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr">
@@ -8131,7 +8129,7 @@
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>5 / 3.5 / 0/13</t>
+          <t>6 / 3.5 / 1/13</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
@@ -8170,7 +8168,7 @@
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>3 / 3.8 / 2/13</t>
+          <t>4 / 3.8 / 2/13</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
@@ -8180,7 +8178,7 @@
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.6 / 0/11</t>
+          <t>2 / 1.5 / 0/11</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
@@ -8213,7 +8211,7 @@
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>6 / 2.6 / 1/13</t>
+          <t>5 / 2.5 / 0/13</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr"/>
@@ -8230,7 +8228,7 @@
       </c>
       <c r="I17" s="14" t="inlineStr">
         <is>
-          <t>4 / 2.6 / 0/7</t>
+          <t>5 / 2.7 / 0/7</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8246,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>4 / 1.8 / 0/13</t>
+          <t>3 / 1.7 / 0/13</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
@@ -8260,12 +8258,12 @@
       <c r="G18" s="13" t="inlineStr"/>
       <c r="H18" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/10</t>
+          <t>0 / 1.1 / 0/10</t>
         </is>
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.9 / 0/7</t>
+          <t>3 / 2.0 / 0/7</t>
         </is>
       </c>
     </row>
@@ -8308,7 +8306,7 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>3 / 3.1 / 1/13</t>
+          <t>2 / 3.0 / 1/13</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
@@ -8546,7 +8544,7 @@
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.0 / 0/7</t>
+          <t>4 / 2.1 / 0/7</t>
         </is>
       </c>
     </row>
@@ -8683,7 +8681,7 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>4 / 2.7 / 0/13</t>
+          <t>3 / 2.6 / 0/13</t>
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr">
@@ -8830,7 +8828,7 @@
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.6 / 0/13</t>
+          <t>1 / 1.5 / 0/13</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
@@ -8840,7 +8838,7 @@
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.2 / 0/11</t>
+          <t>0 / 1.0 / 0/11</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr">
@@ -8878,7 +8876,7 @@
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/11</t>
+          <t>3 / 1.6 / 0/11</t>
         </is>
       </c>
       <c r="F33" s="14" t="inlineStr">
@@ -8942,7 +8940,7 @@
       <c r="F35" s="14" t="inlineStr"/>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/8</t>
+          <t>2 / 0.8 / 0/8</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
@@ -9178,7 +9176,7 @@
       </c>
       <c r="E41" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/11</t>
+          <t>1 / 0.3 / 0/11</t>
         </is>
       </c>
       <c r="F41" s="14" t="inlineStr">
@@ -9272,7 +9270,7 @@
       </c>
       <c r="E43" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>1 / 0.1 / 0/11</t>
         </is>
       </c>
       <c r="F43" s="14" t="inlineStr">
@@ -9310,7 +9308,7 @@
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>10 / 4.5 / 3/13</t>
+          <t>9 / 4.5 / 3/13</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -9320,7 +9318,7 @@
       </c>
       <c r="F44" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.5 / 0/11</t>
+          <t>3 / 2.4 / 0/11</t>
         </is>
       </c>
       <c r="G44" s="13" t="inlineStr">
@@ -9330,7 +9328,7 @@
       </c>
       <c r="H44" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.6 / 1/10</t>
+          <t>2 / 2.5 / 1/10</t>
         </is>
       </c>
       <c r="I44" s="13" t="inlineStr">
@@ -9348,7 +9346,7 @@
       <c r="B45" s="14" t="inlineStr"/>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.6 / 0/12</t>
+          <t>2 / 1.7 / 0/12</t>
         </is>
       </c>
       <c r="D45" s="14" t="inlineStr">
@@ -9358,7 +9356,7 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.3 / 0/11</t>
+          <t>4 / 1.5 / 0/11</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr">
@@ -9369,7 +9367,7 @@
       <c r="G45" s="14" t="inlineStr"/>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>3 / 0.4 / 0/10</t>
+          <t>2 / 0.3 / 0/10</t>
         </is>
       </c>
       <c r="I45" s="14" t="inlineStr">
@@ -9411,7 +9409,7 @@
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/8</t>
+          <t>1 / 0.2 / 0/8</t>
         </is>
       </c>
       <c r="H46" s="13" t="inlineStr">
@@ -9449,7 +9447,7 @@
       </c>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>4 / 2.4 / 0/11</t>
+          <t>3 / 2.3 / 0/11</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
@@ -9840,7 +9838,7 @@
       </c>
       <c r="F56" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/11</t>
+          <t>0 / 0.2 / 0/11</t>
         </is>
       </c>
       <c r="G56" s="13" t="inlineStr">
@@ -9850,12 +9848,12 @@
       </c>
       <c r="H56" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/10</t>
+          <t>1 / 0.6 / 0/10</t>
         </is>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.4 / 1/7</t>
+          <t>2 / 3.1 / 1/7</t>
         </is>
       </c>
     </row>
@@ -9972,7 +9970,7 @@
       </c>
       <c r="E59" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.9 / 0/11</t>
+          <t>2 / 1.8 / 0/11</t>
         </is>
       </c>
       <c r="F59" s="14" t="inlineStr">
@@ -10006,7 +10004,7 @@
       </c>
       <c r="D60" s="13" t="inlineStr">
         <is>
-          <t>4 / 1.7 / 0/13</t>
+          <t>3 / 1.6 / 0/13</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
@@ -10049,7 +10047,7 @@
       </c>
       <c r="D61" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/13</t>
+          <t>1 / 1.4 / 0/13</t>
         </is>
       </c>
       <c r="E61" s="14" t="inlineStr">
@@ -10059,7 +10057,7 @@
       </c>
       <c r="F61" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.3 / 0/11</t>
+          <t>2 / 1.4 / 0/11</t>
         </is>
       </c>
       <c r="G61" s="14" t="inlineStr">
@@ -10104,7 +10102,7 @@
       </c>
       <c r="H62" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/10</t>
+          <t>0 / 0.9 / 0/10</t>
         </is>
       </c>
       <c r="I62" s="13" t="inlineStr">
@@ -10124,7 +10122,7 @@
       <c r="D63" s="14" t="inlineStr"/>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>6 / 4.2 / 1/11</t>
+          <t>5 / 4.1 / 0/11</t>
         </is>
       </c>
       <c r="F63" s="14" t="inlineStr"/>
@@ -10161,13 +10159,13 @@
       </c>
       <c r="G64" s="13" t="inlineStr">
         <is>
-          <t>3 / 3.9 / 0/8</t>
+          <t>2 / 3.8 / 0/8</t>
         </is>
       </c>
       <c r="H64" s="13" t="inlineStr"/>
       <c r="I64" s="13" t="inlineStr">
         <is>
-          <t>5 / 3.3 / 0/7</t>
+          <t>4 / 3.1 / 0/7</t>
         </is>
       </c>
     </row>
@@ -10226,7 +10224,7 @@
       </c>
       <c r="B66" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.2 / 0/12</t>
+          <t>3 / 2.2 / 0/12</t>
         </is>
       </c>
       <c r="C66" s="13" t="inlineStr">
@@ -10316,7 +10314,7 @@
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.4 / 0/12</t>
+          <t>2 / 2.5 / 0/12</t>
         </is>
       </c>
       <c r="C68" s="13" t="inlineStr">
@@ -10378,7 +10376,7 @@
       </c>
       <c r="E69" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/11</t>
+          <t>1 / 0.7 / 0/11</t>
         </is>
       </c>
       <c r="F69" s="14" t="inlineStr">
@@ -10454,7 +10452,7 @@
       <c r="B71" s="14" t="inlineStr"/>
       <c r="C71" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/13</t>
+          <t>2 / 1.1 / 0/13</t>
         </is>
       </c>
       <c r="D71" s="14" t="inlineStr">
@@ -10499,7 +10497,7 @@
       </c>
       <c r="E72" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.5 / 0/11</t>
+          <t>4 / 1.6 / 0/11</t>
         </is>
       </c>
       <c r="F72" s="13" t="inlineStr">
@@ -10532,7 +10530,7 @@
       <c r="B73" s="14" t="inlineStr"/>
       <c r="C73" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/13</t>
+          <t>1 / 0.1 / 0/13</t>
         </is>
       </c>
       <c r="D73" s="14" t="inlineStr">
@@ -10547,7 +10545,7 @@
       </c>
       <c r="F73" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.6 / 0/11</t>
+          <t>4 / 2.7 / 0/11</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
@@ -10562,7 +10560,7 @@
       </c>
       <c r="I73" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/7</t>
+          <t>0 / 0.4 / 0/7</t>
         </is>
       </c>
     </row>
@@ -10586,7 +10584,7 @@
       </c>
       <c r="F74" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/11</t>
+          <t>2 / 1.2 / 0/11</t>
         </is>
       </c>
       <c r="G74" s="13" t="inlineStr">
@@ -10629,12 +10627,12 @@
       </c>
       <c r="F75" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.6 / 0/11</t>
+          <t>2 / 1.5 / 0/11</t>
         </is>
       </c>
       <c r="G75" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/8</t>
+          <t>1 / 0.8 / 0/8</t>
         </is>
       </c>
       <c r="H75" s="14" t="inlineStr">
@@ -10687,7 +10685,7 @@
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
-          <t>5 / 3.4 / 0/7</t>
+          <t>4 / 3.3 / 0/7</t>
         </is>
       </c>
     </row>
@@ -10715,7 +10713,7 @@
       </c>
       <c r="F77" s="14" t="inlineStr">
         <is>
-          <t>12 / 4.4 / 3/11</t>
+          <t>11 / 4.3 / 3/11</t>
         </is>
       </c>
       <c r="G77" s="14" t="inlineStr"/>
@@ -10726,7 +10724,7 @@
       </c>
       <c r="I77" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/7</t>
+          <t>2 / 1.1 / 0/7</t>
         </is>
       </c>
     </row>
@@ -10765,7 +10763,7 @@
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.4 / 0/7</t>
+          <t>1 / 1.3 / 0/7</t>
         </is>
       </c>
     </row>
@@ -10785,7 +10783,7 @@
       </c>
       <c r="F79" s="14" t="inlineStr">
         <is>
-          <t>16 / 7.5 / 5/11</t>
+          <t>17 / 7.5 / 5/11</t>
         </is>
       </c>
       <c r="G79" s="14" t="inlineStr"/>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sitewide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JobG8 categories" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PAGES" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CITY OPPORTUNITIES" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LIVE" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NOT LIVE" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Sitewide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="JobG8 categories" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="PAGES" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="CITY OPPORTUNITIES" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="LIVE" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="NOT LIVE" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sitewide'!$A$1:$B$9</definedName>
@@ -93,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -134,14 +134,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -14548,63 +14542,69 @@
       <c r="B2" s="13" t="inlineStr"/>
       <c r="C2" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.2 / 0/13</t>
         </is>
       </c>
       <c r="D2" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 2.1 / 0/13</t>
         </is>
       </c>
       <c r="E2" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4 / 3.8 / 0/11</t>
         </is>
       </c>
       <c r="F2" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.1 / 0/11</t>
         </is>
       </c>
       <c r="G2" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.8 / 0/8</t>
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I2" s="14" t="n">
-        <v>2</v>
+          <t>1 / 1.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I2" s="13" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Berkshire</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr"/>
-      <c r="C3" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" s="15" t="inlineStr"/>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F3" s="15" t="inlineStr"/>
-      <c r="G3" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H3" s="15" t="inlineStr"/>
-      <c r="I3" s="16" t="n">
-        <v>7</v>
+      <c r="B3" s="14" t="inlineStr"/>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>0 / 3.0 / 3/13</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr"/>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>2 / 0.9 / 0/11</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr"/>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.6 / 0/8</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="inlineStr"/>
+      <c r="I3" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.4 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -14614,58 +14614,64 @@
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr"/>
-      <c r="C4" s="14" t="n">
-        <v>3</v>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.8 / 0/13</t>
+        </is>
       </c>
       <c r="D4" s="13" t="inlineStr"/>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 2.9 / 1/11</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr"/>
       <c r="G4" s="13" t="inlineStr"/>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I4" s="14" t="n">
-        <v>1</v>
+          <t>3 / 1.9 / 0/10</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>5 / 2.9 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Buckinghamshire</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr"/>
-      <c r="C5" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E5" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="15" t="inlineStr"/>
-      <c r="G5" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I5" s="15" t="inlineStr"/>
+      <c r="B5" s="14" t="inlineStr"/>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.6 / 0/13</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.7 / 0/13</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr"/>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>2 / 2.1 / 0/8</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.8 / 0/10</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
@@ -14674,71 +14680,79 @@
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr"/>
-      <c r="C6" s="14" t="n">
-        <v>2</v>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>1 / 0.2 / 0/13</t>
+        </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 2.6 / 0/13</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.2 / 0/11</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr"/>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 4.0 / 2/8</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I6" s="14" t="n">
-        <v>2</v>
+          <t>0 / 0.1 / 0/10</t>
+        </is>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.9 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Cheshire - East</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr"/>
-      <c r="C7" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I7" s="16" t="n">
-        <v>2</v>
+      <c r="B7" s="14" t="inlineStr"/>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.5 / 0/13</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>3 / 1.8 / 0/13</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/11</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.1 / 0/11</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>2 / 2.0 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -14750,67 +14764,73 @@
       <c r="B8" s="13" t="inlineStr"/>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.3 / 0/13</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.9 / 1/13</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 1.5 / 0/11</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.4 / 0/11</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr"/>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I8" s="14" t="n">
-        <v>1</v>
+          <t>0 / 0.1 / 0/10</t>
+        </is>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Cheshire - West</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr"/>
-      <c r="C9" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F9" s="15" t="inlineStr"/>
-      <c r="G9" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I9" s="16" t="n">
-        <v>1</v>
+      <c r="B9" s="14" t="inlineStr"/>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>0 / 1.2 / 0/13</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>2 / 1.8 / 0/13</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>2 / 1.2 / 0/11</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr"/>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.9 / 0/8</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.4 / 0/10</t>
+        </is>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.4 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -14820,78 +14840,86 @@
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr"/>
-      <c r="C10" s="14" t="n">
-        <v>2</v>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>1 / 1.3 / 0/13</t>
+        </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 0.8 / 0/13</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.2 / 0/11</t>
         </is>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.2 / 0/8</t>
         </is>
       </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I10" s="14" t="n">
-        <v>55</v>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.9 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Cumbria - North</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.5 / 0/13</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>0 / 2.4 / 3/13</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/8</t>
+        </is>
+      </c>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
     </row>
@@ -14901,82 +14929,88 @@
           <t>Cumbria - South</t>
         </is>
       </c>
-      <c r="B12" s="14" t="n">
-        <v>1</v>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>1 / 1.1 / 0/13</t>
+        </is>
       </c>
       <c r="C12" s="13" t="inlineStr"/>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.8 / 0/13</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 0.8 / 0/11</t>
         </is>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.5 / 0/8</t>
         </is>
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.3 / 0/10</t>
         </is>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Cumbria - West</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E13" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I13" s="16" t="n">
-        <v>1</v>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>0 / 1.5 / 0/13</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.6 / 0/13</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.4 / 0/8</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -14986,72 +15020,78 @@
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr"/>
-      <c r="C14" s="14" t="n">
-        <v>1</v>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.3 / 0/13</t>
+        </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 2.5 / 0/13</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 0.8 / 0/11</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 1.1 / 0/11</t>
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 2.9 / 0/8</t>
         </is>
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I14" s="14" t="n">
-        <v>1</v>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>3 / 1.9 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>Devon</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr"/>
-      <c r="C15" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E15" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F15" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G15" s="15" t="inlineStr"/>
-      <c r="H15" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I15" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B15" s="14" t="inlineStr"/>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>3 / 0.6 / 0/13</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>6 / 3.5 / 1/13</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>2 / 2.1 / 0/11</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>5 / 2.0 / 2/11</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr"/>
+      <c r="H15" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.1 / 0/10</t>
+        </is>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>2 / 1.3 / 0/7</t>
         </is>
       </c>
     </row>
@@ -15062,69 +15102,75 @@
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr"/>
-      <c r="C16" s="14" t="n">
-        <v>2</v>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/13</t>
+        </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4 / 3.8 / 2/13</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.2 / 0/11</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 1.5 / 0/11</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 2.6 / 0/8</t>
         </is>
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I16" s="14" t="n">
-        <v>3</v>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>3 / 0.7 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Essex</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr"/>
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D17" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E17" s="15" t="inlineStr"/>
-      <c r="F17" s="15" t="inlineStr"/>
-      <c r="G17" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H17" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I17" s="16" t="n">
-        <v>3</v>
+      <c r="B17" s="14" t="inlineStr"/>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.6 / 0/13</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>5 / 2.5 / 0/13</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr"/>
+      <c r="F17" s="14" t="inlineStr"/>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>5 / 5.6 / 2/8</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.1 / 0/10</t>
+        </is>
+      </c>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>5 / 2.7 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -15134,57 +15180,63 @@
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr"/>
-      <c r="C18" s="14" t="n">
-        <v>4</v>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>1 / 0.4 / 0/13</t>
+        </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 1.7 / 0/13</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr"/>
       <c r="G18" s="13" t="inlineStr"/>
       <c r="H18" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 1.1 / 0/10</t>
         </is>
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 2.0 / 0/7</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr"/>
-      <c r="C19" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" s="15" t="inlineStr"/>
-      <c r="E19" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F19" s="15" t="inlineStr"/>
-      <c r="G19" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H19" s="15" t="inlineStr"/>
-      <c r="I19" s="16" t="n">
-        <v>8</v>
+      <c r="B19" s="14" t="inlineStr"/>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>3 / 1.3 / 0/13</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr"/>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>4 / 3.9 / 2/11</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="inlineStr"/>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>4 / 3.8 / 0/8</t>
+        </is>
+      </c>
+      <c r="H19" s="14" t="inlineStr"/>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>3 / 2.4 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -15193,80 +15245,88 @@
           <t>Greater Manchester - North</t>
         </is>
       </c>
-      <c r="B20" s="14" t="n">
-        <v>5</v>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>2 / 3.0 / 1/13</t>
+        </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.2 / 0/13</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
       <c r="H20" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I20" s="14" t="n">
-        <v>4</v>
+          <t>0 / 0.1 / 0/10</t>
+        </is>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>1 / 0.4 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Greater Manchester - South</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr"/>
-      <c r="C21" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F21" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G21" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H21" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I21" s="16" t="n">
-        <v>5</v>
+      <c r="B21" s="14" t="inlineStr"/>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.7 / 0/13</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.6 / 0/13</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.5 / 0/11</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="inlineStr">
+        <is>
+          <t>2 / 0.5 / 0/11</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="H21" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>3 / 1.3 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -15276,72 +15336,76 @@
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr"/>
-      <c r="C22" s="14" t="n">
-        <v>0</v>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
       </c>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.8 / 0/13</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.5 / 0/11</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.2 / 0/8</t>
         </is>
       </c>
       <c r="H22" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I22" s="14" t="n">
-        <v>2</v>
+          <t>1 / 1.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>Hampshire</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr"/>
-      <c r="C23" s="15" t="inlineStr"/>
-      <c r="D23" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E23" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H23" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I23" s="15" t="inlineStr"/>
+      <c r="B23" s="14" t="inlineStr"/>
+      <c r="C23" s="14" t="inlineStr"/>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>13 / 8.3 / 9/13</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>0 / 1.4 / 0/11</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>10 / 5.9 / 4/11</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>1 / 2.4 / 0/8</t>
+        </is>
+      </c>
+      <c r="H23" s="14" t="inlineStr">
+        <is>
+          <t>4 / 3.6 / 0/10</t>
+        </is>
+      </c>
+      <c r="I23" s="14" t="inlineStr"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="13" t="inlineStr">
@@ -15349,74 +15413,80 @@
           <t>Herefordshire</t>
         </is>
       </c>
-      <c r="B24" s="14" t="n">
-        <v>1</v>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>0 / 1.2 / 0/13</t>
+        </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.4 / 0/13</t>
         </is>
       </c>
       <c r="D24" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.9 / 0/8</t>
         </is>
       </c>
       <c r="H24" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
       <c r="I24" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>Hertfordshire</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr"/>
-      <c r="C25" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="15" t="inlineStr"/>
-      <c r="E25" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F25" s="15" t="inlineStr"/>
-      <c r="G25" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H25" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I25" s="16" t="n">
-        <v>5</v>
+      <c r="B25" s="14" t="inlineStr"/>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>3 / 2.4 / 0/13</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr"/>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.5 / 0/11</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr"/>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="H25" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.4 / 0/10</t>
+        </is>
+      </c>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>4 / 2.1 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -15430,66 +15500,70 @@
       <c r="D26" s="13" t="inlineStr"/>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5 / 4.3 / 2/11</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr"/>
       <c r="G26" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 2.2 / 1/8</t>
         </is>
       </c>
       <c r="H26" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I26" s="14" t="n">
-        <v>4</v>
+          <t>2 / 1.7 / 0/10</t>
+        </is>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>3 / 1.4 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>Lancashire - Blackpool &amp; Fylde</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D27" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E27" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F27" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G27" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H27" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I27" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.7 / 0/13</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>2 / 1.1 / 0/11</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/8</t>
+        </is>
+      </c>
+      <c r="H27" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
     </row>
@@ -15499,81 +15573,91 @@
           <t>Lancashire - Central</t>
         </is>
       </c>
-      <c r="B28" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" s="14" t="n">
-        <v>1</v>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>3 / 2.8 / 0/13</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/13</t>
+        </is>
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.4 / 0/13</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.6 / 0/8</t>
         </is>
       </c>
       <c r="H28" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I28" s="14" t="n">
-        <v>1</v>
+          <t>0 / 0.2 / 0/10</t>
+        </is>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>Lancashire - East</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="D29" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E29" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F29" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G29" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H29" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I29" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>3 / 2.6 / 0/13</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.8 / 0/13</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/13</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/11</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>3 / 1.5 / 0/11</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.1 / 0/8</t>
+        </is>
+      </c>
+      <c r="H29" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
     </row>
@@ -15585,87 +15669,89 @@
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C30" s="14" t="n">
-        <v>3</v>
+          <t>2 / 1.2 / 0/13</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>0 / 1.0 / 0/13</t>
+        </is>
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.2 / 0/13</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
       <c r="H30" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.3 / 0/10</t>
         </is>
       </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>Lancashire - West</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C31" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D31" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E31" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F31" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G31" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H31" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I31" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>0 / 1.1 / 0/12</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/12</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.2 / 0/12</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
     </row>
@@ -15676,75 +15762,83 @@
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr"/>
-      <c r="C32" s="14" t="n">
-        <v>1</v>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/13</t>
+        </is>
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.5 / 0/13</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 1.5 / 0/11</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 1.0 / 0/11</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 2.8 / 1/8</t>
         </is>
       </c>
       <c r="H32" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I32" s="14" t="n">
-        <v>5</v>
+          <t>1 / 0.8 / 0/10</t>
+        </is>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>2 / 2.6 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t>Lincolnshire</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr"/>
-      <c r="C33" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D33" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E33" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F33" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G33" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H33" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I33" s="16" t="n">
-        <v>2</v>
+      <c r="B33" s="14" t="inlineStr"/>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>0 / 1.5 / 0/13</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>5 / 1.8 / 0/13</t>
+        </is>
+      </c>
+      <c r="E33" s="14" t="inlineStr">
+        <is>
+          <t>3 / 1.6 / 0/11</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="inlineStr">
+        <is>
+          <t>2 / 2.6 / 0/11</t>
+        </is>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>1 / 2.4 / 0/8</t>
+        </is>
+      </c>
+      <c r="H33" s="14" t="inlineStr">
+        <is>
+          <t>2 / 1.5 / 0/10</t>
+        </is>
+      </c>
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -15763,38 +15857,42 @@
       <c r="I34" s="13" t="inlineStr"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>Merseyside - Liverpool</t>
         </is>
       </c>
-      <c r="B35" s="15" t="inlineStr"/>
-      <c r="C35" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D35" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E35" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F35" s="15" t="inlineStr"/>
-      <c r="G35" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H35" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I35" s="16" t="n">
-        <v>0</v>
+      <c r="B35" s="14" t="inlineStr"/>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.3 / 0/13</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/13</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>2 / 0.6 / 0/11</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr"/>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>2 / 0.8 / 0/8</t>
+        </is>
+      </c>
+      <c r="H35" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/10</t>
+        </is>
+      </c>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
@@ -15805,87 +15903,89 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C36" s="14" t="n">
-        <v>1</v>
+          <t>0 / 0.1 / 0/12</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="F36" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="G36" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
       <c r="H36" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
       <c r="I36" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="14" t="inlineStr">
         <is>
           <t>Merseyside - St Helens &amp; Knowsley</t>
         </is>
       </c>
-      <c r="B37" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C37" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D37" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E37" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F37" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G37" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H37" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I37" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.8 / 0/12</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.8 / 0/12</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="F37" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.5 / 0/8</t>
+        </is>
+      </c>
+      <c r="H37" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I37" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
     </row>
@@ -15895,74 +15995,84 @@
           <t>Merseyside - Wirral</t>
         </is>
       </c>
-      <c r="B38" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" s="14" t="n">
-        <v>0</v>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>1 / 1.5 / 0/13</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.4 / 0/13</t>
+        </is>
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.0 / 0/13</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.5 / 0/11</t>
         </is>
       </c>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 0.7 / 0/11</t>
         </is>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.4 / 0/8</t>
         </is>
       </c>
       <c r="H38" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I38" s="14" t="n">
-        <v>2</v>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="14" t="inlineStr">
         <is>
           <t>Norfolk</t>
         </is>
       </c>
-      <c r="B39" s="15" t="inlineStr"/>
-      <c r="C39" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D39" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E39" s="15" t="inlineStr"/>
-      <c r="F39" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G39" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H39" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I39" s="16" t="n">
-        <v>3</v>
+      <c r="B39" s="14" t="inlineStr"/>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.9 / 0/13</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.7 / 0/13</t>
+        </is>
+      </c>
+      <c r="E39" s="14" t="inlineStr"/>
+      <c r="F39" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.5 / 0/11</t>
+        </is>
+      </c>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>2 / 3.6 / 2/8</t>
+        </is>
+      </c>
+      <c r="H39" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/10</t>
+        </is>
+      </c>
+      <c r="I39" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.9 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
@@ -15976,56 +16086,58 @@
       <c r="D40" s="13" t="inlineStr"/>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.0 / 0/11</t>
         </is>
       </c>
       <c r="F40" s="13" t="inlineStr"/>
       <c r="G40" s="13" t="inlineStr"/>
       <c r="H40" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.1 / 0/10</t>
         </is>
       </c>
       <c r="I40" s="13" t="inlineStr"/>
     </row>
     <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="A41" s="14" t="inlineStr">
         <is>
           <t>North Scotland</t>
         </is>
       </c>
-      <c r="B41" s="15" t="inlineStr"/>
-      <c r="C41" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E41" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F41" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G41" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H41" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I41" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B41" s="14" t="inlineStr"/>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>6 / 3.5 / 3/12</t>
+        </is>
+      </c>
+      <c r="E41" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.3 / 0/11</t>
+        </is>
+      </c>
+      <c r="F41" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.5 / 0/8</t>
+        </is>
+      </c>
+      <c r="H41" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I41" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
     </row>
@@ -16035,82 +16147,92 @@
           <t>North Wales - East</t>
         </is>
       </c>
-      <c r="B42" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="C42" s="14" t="n">
-        <v>0</v>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>4 / 4.5 / 1/12</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/12</t>
+        </is>
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 1.5 / 0/12</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="F42" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.5 / 0/11</t>
         </is>
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.4 / 0/8</t>
         </is>
       </c>
       <c r="H42" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I42" s="14" t="n">
-        <v>2</v>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="A43" s="14" t="inlineStr">
         <is>
           <t>North Wales - West</t>
         </is>
       </c>
-      <c r="B43" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C43" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E43" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F43" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G43" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H43" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I43" s="16" t="n">
-        <v>0</v>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>3 / 2.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.1 / 0/11</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="H43" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.4 / 0/10</t>
+        </is>
+      </c>
+      <c r="I43" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.6 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
@@ -16120,72 +16242,78 @@
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr"/>
-      <c r="C44" s="14" t="n">
-        <v>1</v>
+      <c r="C44" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9 / 4.5 / 3/13</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.3 / 0/11</t>
         </is>
       </c>
       <c r="F44" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 2.4 / 0/11</t>
         </is>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 2.9 / 2/8</t>
         </is>
       </c>
       <c r="H44" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I44" s="14" t="n">
-        <v>4</v>
+          <t>2 / 2.5 / 1/10</t>
+        </is>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>1 / 0.4 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="15" t="inlineStr">
+      <c r="A45" s="14" t="inlineStr">
         <is>
           <t>Northern Ireland - East</t>
         </is>
       </c>
-      <c r="B45" s="15" t="inlineStr"/>
-      <c r="C45" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E45" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F45" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G45" s="15" t="inlineStr"/>
-      <c r="H45" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I45" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B45" s="14" t="inlineStr"/>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>2 / 1.7 / 0/12</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="E45" s="14" t="inlineStr">
+        <is>
+          <t>4 / 1.5 / 0/11</t>
+        </is>
+      </c>
+      <c r="F45" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.1 / 0/11</t>
+        </is>
+      </c>
+      <c r="G45" s="14" t="inlineStr"/>
+      <c r="H45" s="14" t="inlineStr">
+        <is>
+          <t>2 / 0.3 / 0/10</t>
+        </is>
+      </c>
+      <c r="I45" s="14" t="inlineStr">
+        <is>
+          <t>2 / 1.0 / 0/7</t>
         </is>
       </c>
     </row>
@@ -16195,76 +16323,84 @@
           <t>Northern Ireland - West</t>
         </is>
       </c>
-      <c r="B46" s="14" t="n">
-        <v>2</v>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>20 / 5.2 / 1/12</t>
+        </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 1.3 / 0/12</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="F46" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.2 / 0/8</t>
         </is>
       </c>
       <c r="H46" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I46" s="14" t="n">
-        <v>1</v>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="A47" s="14" t="inlineStr">
         <is>
           <t>Nottinghamshire</t>
         </is>
       </c>
-      <c r="B47" s="15" t="inlineStr"/>
-      <c r="C47" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E47" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F47" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G47" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H47" s="15" t="inlineStr"/>
-      <c r="I47" s="16" t="n">
-        <v>3</v>
+      <c r="B47" s="14" t="inlineStr"/>
+      <c r="C47" s="14" t="inlineStr">
+        <is>
+          <t>2 / 0.8 / 0/13</t>
+        </is>
+      </c>
+      <c r="D47" s="14" t="inlineStr">
+        <is>
+          <t>4 / 2.2 / 0/13</t>
+        </is>
+      </c>
+      <c r="E47" s="14" t="inlineStr">
+        <is>
+          <t>2 / 2.1 / 0/11</t>
+        </is>
+      </c>
+      <c r="F47" s="14" t="inlineStr">
+        <is>
+          <t>3 / 2.3 / 0/11</t>
+        </is>
+      </c>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>1 / 3.0 / 2/8</t>
+        </is>
+      </c>
+      <c r="H47" s="14" t="inlineStr"/>
+      <c r="I47" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
@@ -16277,73 +16413,75 @@
       <c r="C48" s="13" t="inlineStr"/>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4 / 3.2 / 0/13</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 1.7 / 0/11</t>
         </is>
       </c>
       <c r="F48" s="13" t="inlineStr"/>
       <c r="G48" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 2.4 / 0/8</t>
         </is>
       </c>
       <c r="H48" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I48" s="14" t="n">
-        <v>1</v>
+          <t>1 / 0.4 / 0/10</t>
+        </is>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>3 / 1.4 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="15" t="inlineStr">
+      <c r="A49" s="14" t="inlineStr">
         <is>
           <t>Rutland</t>
         </is>
       </c>
-      <c r="B49" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C49" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D49" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E49" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F49" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G49" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H49" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I49" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="H49" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I49" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
     </row>
@@ -16355,82 +16493,86 @@
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 1.4 / 0/12</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="F50" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.1 / 0/8</t>
         </is>
       </c>
       <c r="H50" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.1 / 0/7</t>
         </is>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="15" t="inlineStr">
+      <c r="A51" s="14" t="inlineStr">
         <is>
           <t>Scotland Central - Edinburgh &amp; Lothians</t>
         </is>
       </c>
-      <c r="B51" s="15" t="inlineStr"/>
-      <c r="C51" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D51" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E51" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F51" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G51" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H51" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I51" s="16" t="n">
-        <v>2</v>
+      <c r="B51" s="14" t="inlineStr"/>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/12</t>
+        </is>
+      </c>
+      <c r="D51" s="14" t="inlineStr">
+        <is>
+          <t>3 / 2.4 / 0/12</t>
+        </is>
+      </c>
+      <c r="E51" s="14" t="inlineStr">
+        <is>
+          <t>3 / 2.5 / 0/11</t>
+        </is>
+      </c>
+      <c r="F51" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.3 / 0/11</t>
+        </is>
+      </c>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.1 / 0/8</t>
+        </is>
+      </c>
+      <c r="H51" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.5 / 0/10</t>
+        </is>
+      </c>
+      <c r="I51" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.4 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
@@ -16439,83 +16581,91 @@
           <t>Scotland Central - Falkirk &amp; Stirling</t>
         </is>
       </c>
-      <c r="B52" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C52" s="14" t="n">
-        <v>1</v>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>1 / 2.4 / 0/12</t>
+        </is>
+      </c>
+      <c r="C52" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="F52" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="G52" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 1.0 / 0/8</t>
         </is>
       </c>
       <c r="H52" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I52" s="14" t="n">
-        <v>0</v>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I52" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="15" t="inlineStr">
+      <c r="A53" s="14" t="inlineStr">
         <is>
           <t>Scotland Central - Fife</t>
         </is>
       </c>
-      <c r="B53" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C53" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E53" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F53" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G53" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H53" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I53" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>2 / 1.6 / 0/12</t>
+        </is>
+      </c>
+      <c r="C53" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="D53" s="14" t="inlineStr">
+        <is>
+          <t>2 / 1.2 / 0/12</t>
+        </is>
+      </c>
+      <c r="E53" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="F53" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.5 / 0/8</t>
+        </is>
+      </c>
+      <c r="H53" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I53" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
     </row>
@@ -16528,83 +16678,85 @@
       <c r="B54" s="13" t="inlineStr"/>
       <c r="C54" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.2 / 0/12</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.2 / 0/11</t>
         </is>
       </c>
       <c r="F54" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.2 / 0/11</t>
         </is>
       </c>
       <c r="G54" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.5 / 0/8</t>
         </is>
       </c>
       <c r="H54" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
       <c r="I54" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.4 / 0/7</t>
         </is>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="15" t="inlineStr">
+      <c r="A55" s="14" t="inlineStr">
         <is>
           <t>Scotland West - Ayrshire</t>
         </is>
       </c>
-      <c r="B55" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C55" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D55" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E55" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F55" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G55" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H55" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I55" s="16" t="n">
-        <v>0</v>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.6 / 0/12</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="D55" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="E55" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.5 / 0/11</t>
+        </is>
+      </c>
+      <c r="F55" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="H55" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I55" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.7 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
@@ -16614,75 +16766,83 @@
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr"/>
-      <c r="C56" s="14" t="n">
-        <v>0</v>
+      <c r="C56" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
       </c>
       <c r="D56" s="13" t="inlineStr"/>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.4 / 0/11</t>
         </is>
       </c>
       <c r="F56" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.2 / 0/11</t>
         </is>
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.2 / 0/8</t>
         </is>
       </c>
       <c r="H56" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I56" s="14" t="n">
-        <v>0</v>
+          <t>1 / 0.6 / 0/10</t>
+        </is>
+      </c>
+      <c r="I56" s="13" t="inlineStr">
+        <is>
+          <t>2 / 3.1 / 1/7</t>
+        </is>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="15" t="inlineStr">
+      <c r="A57" s="14" t="inlineStr">
         <is>
           <t>Scotland West - Lanarkshire</t>
         </is>
       </c>
-      <c r="B57" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C57" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D57" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E57" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F57" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G57" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H57" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I57" s="16" t="n">
-        <v>0</v>
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.4 / 0/12</t>
+        </is>
+      </c>
+      <c r="C57" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/12</t>
+        </is>
+      </c>
+      <c r="D57" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.3 / 0/12</t>
+        </is>
+      </c>
+      <c r="E57" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="F57" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.1 / 0/8</t>
+        </is>
+      </c>
+      <c r="H57" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I57" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
@@ -16693,75 +16853,81 @@
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C58" s="14" t="n">
-        <v>0</v>
+          <t>1 / 1.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="C58" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
       </c>
       <c r="D58" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.5 / 0/12</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="F58" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="G58" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.5 / 0/8</t>
         </is>
       </c>
       <c r="H58" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I58" s="14" t="n">
-        <v>0</v>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I58" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="15" t="inlineStr">
+      <c r="A59" s="14" t="inlineStr">
         <is>
           <t>Shropshire</t>
         </is>
       </c>
-      <c r="B59" s="15" t="inlineStr"/>
-      <c r="C59" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="D59" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E59" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F59" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G59" s="15" t="inlineStr"/>
-      <c r="H59" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I59" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B59" s="14" t="inlineStr"/>
+      <c r="C59" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.6 / 0/13</t>
+        </is>
+      </c>
+      <c r="D59" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.1 / 0/13</t>
+        </is>
+      </c>
+      <c r="E59" s="14" t="inlineStr">
+        <is>
+          <t>2 / 1.8 / 0/11</t>
+        </is>
+      </c>
+      <c r="F59" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.4 / 0/11</t>
+        </is>
+      </c>
+      <c r="G59" s="14" t="inlineStr"/>
+      <c r="H59" s="14" t="inlineStr">
+        <is>
+          <t>2 / 1.9 / 0/10</t>
+        </is>
+      </c>
+      <c r="I59" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
     </row>
@@ -16772,74 +16938,80 @@
         </is>
       </c>
       <c r="B60" s="13" t="inlineStr"/>
-      <c r="C60" s="14" t="n">
-        <v>4</v>
+      <c r="C60" s="13" t="inlineStr">
+        <is>
+          <t>2 / 3.4 / 3/13</t>
+        </is>
       </c>
       <c r="D60" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 1.6 / 0/13</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.5 / 0/11</t>
         </is>
       </c>
       <c r="F60" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4 / 1.2 / 0/11</t>
         </is>
       </c>
       <c r="G60" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 2.6 / 1/8</t>
         </is>
       </c>
       <c r="H60" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I60" s="14" t="n">
-        <v>0</v>
+          <t>1 / 0.2 / 0/10</t>
+        </is>
+      </c>
+      <c r="I60" s="13" t="inlineStr">
+        <is>
+          <t>2 / 0.9 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="15" t="inlineStr">
+      <c r="A61" s="14" t="inlineStr">
         <is>
           <t>Staffordshire</t>
         </is>
       </c>
-      <c r="B61" s="15" t="inlineStr"/>
-      <c r="C61" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="D61" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E61" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F61" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G61" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H61" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I61" s="15" t="inlineStr"/>
+      <c r="B61" s="14" t="inlineStr"/>
+      <c r="C61" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/13</t>
+        </is>
+      </c>
+      <c r="D61" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.4 / 0/13</t>
+        </is>
+      </c>
+      <c r="E61" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="F61" s="14" t="inlineStr">
+        <is>
+          <t>2 / 1.4 / 0/11</t>
+        </is>
+      </c>
+      <c r="G61" s="14" t="inlineStr">
+        <is>
+          <t>3 / 2.6 / 0/8</t>
+        </is>
+      </c>
+      <c r="H61" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/10</t>
+        </is>
+      </c>
+      <c r="I61" s="14" t="inlineStr"/>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="13" t="inlineStr">
@@ -16848,62 +17020,64 @@
         </is>
       </c>
       <c r="B62" s="13" t="inlineStr"/>
-      <c r="C62" s="14" t="n">
-        <v>0</v>
+      <c r="C62" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.8 / 0/13</t>
+        </is>
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 1.8 / 0/13</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr"/>
       <c r="F62" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.5 / 0/11</t>
         </is>
       </c>
       <c r="G62" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.6 / 0/8</t>
         </is>
       </c>
       <c r="H62" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.9 / 0/10</t>
         </is>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.6 / 0/7</t>
         </is>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="15" t="inlineStr">
+      <c r="A63" s="14" t="inlineStr">
         <is>
           <t>Surrey</t>
         </is>
       </c>
-      <c r="B63" s="15" t="inlineStr"/>
-      <c r="C63" s="15" t="inlineStr"/>
-      <c r="D63" s="15" t="inlineStr"/>
-      <c r="E63" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F63" s="15" t="inlineStr"/>
-      <c r="G63" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H63" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I63" s="15" t="inlineStr"/>
+      <c r="B63" s="14" t="inlineStr"/>
+      <c r="C63" s="14" t="inlineStr"/>
+      <c r="D63" s="14" t="inlineStr"/>
+      <c r="E63" s="14" t="inlineStr">
+        <is>
+          <t>5 / 4.1 / 0/11</t>
+        </is>
+      </c>
+      <c r="F63" s="14" t="inlineStr"/>
+      <c r="G63" s="14" t="inlineStr">
+        <is>
+          <t>3 / 4.6 / 2/8</t>
+        </is>
+      </c>
+      <c r="H63" s="14" t="inlineStr">
+        <is>
+          <t>3 / 2.2 / 0/10</t>
+        </is>
+      </c>
+      <c r="I63" s="14" t="inlineStr"/>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="13" t="inlineStr">
@@ -16916,67 +17090,71 @@
       <c r="D64" s="13" t="inlineStr"/>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4 / 2.4 / 0/11</t>
         </is>
       </c>
       <c r="F64" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5 / 2.9 / 0/11</t>
         </is>
       </c>
       <c r="G64" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 3.8 / 0/8</t>
         </is>
       </c>
       <c r="H64" s="13" t="inlineStr"/>
-      <c r="I64" s="14" t="n">
-        <v>4</v>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>4 / 3.1 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="15" t="inlineStr">
+      <c r="A65" s="14" t="inlineStr">
         <is>
           <t>Wales - Mid</t>
         </is>
       </c>
-      <c r="B65" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C65" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D65" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E65" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F65" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G65" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H65" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I65" s="16" t="n">
-        <v>1</v>
+      <c r="B65" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/12</t>
+        </is>
+      </c>
+      <c r="C65" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="E65" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="F65" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="G65" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/8</t>
+        </is>
+      </c>
+      <c r="H65" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I65" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -16985,81 +17163,87 @@
           <t>Wales - West</t>
         </is>
       </c>
-      <c r="B66" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C66" s="14" t="n">
-        <v>1</v>
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>3 / 2.2 / 0/12</t>
+        </is>
+      </c>
+      <c r="C66" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
       </c>
       <c r="D66" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="F66" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="G66" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.5 / 0/8</t>
         </is>
       </c>
       <c r="H66" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.3 / 0/10</t>
         </is>
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="15" t="inlineStr">
+      <c r="A67" s="14" t="inlineStr">
         <is>
           <t>Wales South - Cardiff &amp; Vale</t>
         </is>
       </c>
-      <c r="B67" s="15" t="inlineStr"/>
-      <c r="C67" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D67" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E67" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F67" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G67" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H67" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I67" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B67" s="14" t="inlineStr"/>
+      <c r="C67" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="D67" s="14" t="inlineStr">
+        <is>
+          <t>3 / 1.9 / 0/12</t>
+        </is>
+      </c>
+      <c r="E67" s="14" t="inlineStr">
+        <is>
+          <t>2 / 1.5 / 0/11</t>
+        </is>
+      </c>
+      <c r="F67" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="G67" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.9 / 0/8</t>
+        </is>
+      </c>
+      <c r="H67" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I67" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.4 / 0/7</t>
         </is>
       </c>
     </row>
@@ -17071,84 +17255,90 @@
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 2.5 / 0/12</t>
         </is>
       </c>
       <c r="C68" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.1 / 0/12</t>
         </is>
       </c>
       <c r="D68" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.2 / 0/12</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 1.5 / 0/11</t>
         </is>
       </c>
       <c r="F68" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="G68" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.5 / 0/8</t>
         </is>
       </c>
       <c r="H68" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
       <c r="I68" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="15" t="inlineStr">
+      <c r="A69" s="14" t="inlineStr">
         <is>
           <t>Wales South - Swansea Bay</t>
         </is>
       </c>
-      <c r="B69" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C69" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D69" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E69" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F69" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G69" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H69" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I69" s="16" t="n">
-        <v>10</v>
+      <c r="B69" s="14" t="inlineStr">
+        <is>
+          <t>4 / 3.3 / 1/12</t>
+        </is>
+      </c>
+      <c r="C69" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/12</t>
+        </is>
+      </c>
+      <c r="D69" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.7 / 0/12</t>
+        </is>
+      </c>
+      <c r="E69" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.7 / 0/11</t>
+        </is>
+      </c>
+      <c r="F69" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/11</t>
+        </is>
+      </c>
+      <c r="G69" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/8</t>
+        </is>
+      </c>
+      <c r="H69" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I69" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
@@ -17158,69 +17348,75 @@
         </is>
       </c>
       <c r="B70" s="13" t="inlineStr"/>
-      <c r="C70" s="14" t="n">
-        <v>0</v>
+      <c r="C70" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 0.7 / 0/12</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4 / 2.8 / 0/11</t>
         </is>
       </c>
       <c r="F70" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.4 / 0/11</t>
         </is>
       </c>
       <c r="G70" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.1 / 0/8</t>
         </is>
       </c>
       <c r="H70" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I70" s="14" t="n">
-        <v>19</v>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>2 / 1.1 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="15" t="inlineStr">
+      <c r="A71" s="14" t="inlineStr">
         <is>
           <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
-      <c r="B71" s="15" t="inlineStr"/>
-      <c r="C71" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D71" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="15" t="inlineStr"/>
-      <c r="G71" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="15" t="inlineStr"/>
-      <c r="I71" s="16" t="n">
-        <v>1</v>
+      <c r="B71" s="14" t="inlineStr"/>
+      <c r="C71" s="14" t="inlineStr">
+        <is>
+          <t>2 / 1.1 / 0/13</t>
+        </is>
+      </c>
+      <c r="D71" s="14" t="inlineStr">
+        <is>
+          <t>10 / 4.9 / 3/13</t>
+        </is>
+      </c>
+      <c r="E71" s="14" t="inlineStr">
+        <is>
+          <t>4 / 4.0 / 2/11</t>
+        </is>
+      </c>
+      <c r="F71" s="14" t="inlineStr"/>
+      <c r="G71" s="14" t="inlineStr">
+        <is>
+          <t>3 / 2.8 / 0/8</t>
+        </is>
+      </c>
+      <c r="H71" s="14" t="inlineStr"/>
+      <c r="I71" s="14" t="inlineStr">
+        <is>
+          <t>5 / 3.9 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
@@ -17230,77 +17426,83 @@
         </is>
       </c>
       <c r="B72" s="13" t="inlineStr"/>
-      <c r="C72" s="14" t="n">
-        <v>1</v>
+      <c r="C72" s="13" t="inlineStr">
+        <is>
+          <t>1 / 1.1 / 0/13</t>
+        </is>
       </c>
       <c r="D72" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.0 / 0/13</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4 / 1.6 / 0/11</t>
         </is>
       </c>
       <c r="F72" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 0.5 / 0/11</t>
         </is>
       </c>
       <c r="G72" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.2 / 0/8</t>
         </is>
       </c>
       <c r="H72" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 / 1.0 / 0/7</t>
         </is>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="15" t="inlineStr">
+      <c r="A73" s="14" t="inlineStr">
         <is>
           <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
-      <c r="B73" s="15" t="inlineStr"/>
-      <c r="C73" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="D73" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I73" s="16" t="n">
-        <v>1</v>
+      <c r="B73" s="14" t="inlineStr"/>
+      <c r="C73" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.1 / 0/13</t>
+        </is>
+      </c>
+      <c r="D73" s="14" t="inlineStr">
+        <is>
+          <t>6 / 2.0 / 3/13</t>
+        </is>
+      </c>
+      <c r="E73" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.6 / 0/11</t>
+        </is>
+      </c>
+      <c r="F73" s="14" t="inlineStr">
+        <is>
+          <t>4 / 2.7 / 0/11</t>
+        </is>
+      </c>
+      <c r="G73" s="14" t="inlineStr">
+        <is>
+          <t>2 / 2.2 / 0/8</t>
+        </is>
+      </c>
+      <c r="H73" s="14" t="inlineStr">
+        <is>
+          <t>3 / 3.1 / 0/10</t>
+        </is>
+      </c>
+      <c r="I73" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.4 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -17313,70 +17515,76 @@
       <c r="C74" s="13" t="inlineStr"/>
       <c r="D74" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 2.2 / 0/13</t>
         </is>
       </c>
       <c r="E74" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4 / 3.2 / 0/11</t>
         </is>
       </c>
       <c r="F74" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 1.2 / 0/11</t>
         </is>
       </c>
       <c r="G74" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 2.1 / 0/8</t>
         </is>
       </c>
       <c r="H74" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="14" t="n">
-        <v>4</v>
+          <t>0 / 0.5 / 0/10</t>
+        </is>
+      </c>
+      <c r="I74" s="13" t="inlineStr">
+        <is>
+          <t>2 / 1.3 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="15" t="inlineStr">
+      <c r="A75" s="14" t="inlineStr">
         <is>
           <t>Worcestershire</t>
         </is>
       </c>
-      <c r="B75" s="15" t="inlineStr"/>
-      <c r="C75" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D75" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E75" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F75" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G75" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H75" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I75" s="16" t="n">
-        <v>1</v>
+      <c r="B75" s="14" t="inlineStr"/>
+      <c r="C75" s="14" t="inlineStr">
+        <is>
+          <t>0 / 1.1 / 0/13</t>
+        </is>
+      </c>
+      <c r="D75" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.9 / 0/13</t>
+        </is>
+      </c>
+      <c r="E75" s="14" t="inlineStr">
+        <is>
+          <t>2 / 0.7 / 0/11</t>
+        </is>
+      </c>
+      <c r="F75" s="14" t="inlineStr">
+        <is>
+          <t>2 / 1.5 / 0/11</t>
+        </is>
+      </c>
+      <c r="G75" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.8 / 0/8</t>
+        </is>
+      </c>
+      <c r="H75" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/10</t>
+        </is>
+      </c>
+      <c r="I75" s="14" t="inlineStr">
+        <is>
+          <t>2 / 0.7 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -17386,71 +17594,79 @@
         </is>
       </c>
       <c r="B76" s="13" t="inlineStr"/>
-      <c r="C76" s="14" t="n">
-        <v>3</v>
+      <c r="C76" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.6 / 0/13</t>
+        </is>
       </c>
       <c r="D76" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 1.0 / 0/13</t>
         </is>
       </c>
       <c r="E76" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 1.2 / 0/11</t>
         </is>
       </c>
       <c r="F76" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 0.7 / 0/11</t>
         </is>
       </c>
       <c r="G76" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 / 3.5 / 0/8</t>
         </is>
       </c>
       <c r="H76" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I76" s="14" t="n">
-        <v>5</v>
+          <t>1 / 1.2 / 0/10</t>
+        </is>
+      </c>
+      <c r="I76" s="13" t="inlineStr">
+        <is>
+          <t>4 / 3.3 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="15" t="inlineStr">
+      <c r="A77" s="14" t="inlineStr">
         <is>
           <t>Yorkshire - North</t>
         </is>
       </c>
-      <c r="B77" s="15" t="inlineStr"/>
-      <c r="C77" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="D77" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E77" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F77" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G77" s="15" t="inlineStr"/>
-      <c r="H77" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I77" s="16" t="n">
-        <v>2</v>
+      <c r="B77" s="14" t="inlineStr"/>
+      <c r="C77" s="14" t="inlineStr">
+        <is>
+          <t>1 / 3.2 / 0/13</t>
+        </is>
+      </c>
+      <c r="D77" s="14" t="inlineStr">
+        <is>
+          <t>3 / 1.2 / 0/13</t>
+        </is>
+      </c>
+      <c r="E77" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/11</t>
+        </is>
+      </c>
+      <c r="F77" s="14" t="inlineStr">
+        <is>
+          <t>11 / 4.3 / 3/11</t>
+        </is>
+      </c>
+      <c r="G77" s="14" t="inlineStr"/>
+      <c r="H77" s="14" t="inlineStr">
+        <is>
+          <t>2 / 1.6 / 0/10</t>
+        </is>
+      </c>
+      <c r="I77" s="14" t="inlineStr">
+        <is>
+          <t>2 / 1.1 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
@@ -17463,56 +17679,60 @@
       <c r="C78" s="13" t="inlineStr"/>
       <c r="D78" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4 / 2.3 / 0/13</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 / 3.1 / 0/11</t>
         </is>
       </c>
       <c r="F78" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5 / 2.5 / 1/11</t>
         </is>
       </c>
       <c r="G78" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 / 1.8 / 2/8</t>
         </is>
       </c>
       <c r="H78" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I78" s="14" t="n">
-        <v>11</v>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="I78" s="13" t="inlineStr">
+        <is>
+          <t>1 / 1.3 / 0/7</t>
+        </is>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="15" t="inlineStr">
+      <c r="A79" s="14" t="inlineStr">
         <is>
           <t>Yorkshire - West</t>
         </is>
       </c>
-      <c r="B79" s="15" t="inlineStr"/>
-      <c r="C79" s="15" t="inlineStr"/>
-      <c r="D79" s="15" t="inlineStr"/>
-      <c r="E79" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="15" t="inlineStr"/>
-      <c r="H79" s="15" t="inlineStr"/>
-      <c r="I79" s="16" t="n">
-        <v>5</v>
+      <c r="B79" s="14" t="inlineStr"/>
+      <c r="C79" s="14" t="inlineStr"/>
+      <c r="D79" s="14" t="inlineStr"/>
+      <c r="E79" s="14" t="inlineStr">
+        <is>
+          <t>5 / 4.2 / 0/11</t>
+        </is>
+      </c>
+      <c r="F79" s="14" t="inlineStr">
+        <is>
+          <t>17 / 7.5 / 5/11</t>
+        </is>
+      </c>
+      <c r="G79" s="14" t="inlineStr"/>
+      <c r="H79" s="14" t="inlineStr"/>
+      <c r="I79" s="14" t="inlineStr">
+        <is>
+          <t>3 / 2.7 / 0/7</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sitewide'!$A$1:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'JobG8 categories'!$A$1:$C$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'PAGES'!$A$1:$H$137</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$F$284</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$F$281</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'LIVE'!$A$1:$I$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'NOT LIVE'!$A$1:$I$79</definedName>
   </definedNames>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1851</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="3">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>347</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1913</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="6">
@@ -645,10 +645,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2342</v>
+        <v>2540</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>296</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3">
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1670</v>
+        <v>1692</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
@@ -671,10 +671,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1332</v>
+        <v>1297</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>723</v>
+        <v>699</v>
       </c>
     </row>
     <row r="5">
@@ -684,10 +684,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>901</v>
+        <v>837</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6">
@@ -697,10 +697,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>815</v>
+        <v>614</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>247</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>437</v>
+        <v>467</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>33</v>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>12</v>
@@ -732,27 +732,27 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Retail &amp; Consumer Products</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Retail &amp; Consumer Products</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>349</v>
+        <v>366</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
@@ -762,10 +762,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>11</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>8</v>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>22</v>
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="C15" s="8" t="inlineStr"/>
     </row>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>8</v>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C17" s="8" t="inlineStr"/>
     </row>
@@ -852,7 +852,7 @@
         <v>10000</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>1533</v>
+        <v>1470</v>
       </c>
     </row>
   </sheetData>
@@ -6012,7 +6012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F284"/>
+  <dimension ref="A1:F281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7292,7 +7292,7 @@
         </is>
       </c>
       <c r="D49" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E49" s="5" t="n">
         <v>0</v>
@@ -7787,7 +7787,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Hayes</t>
+          <t>Hornchurch</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Hornchurch</t>
+          <t>Ilford</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -7835,7 +7835,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Ilford</t>
+          <t>Islington</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Islington</t>
+          <t>Lambeth</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Lambeth</t>
+          <t>Loughton</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Loughton</t>
+          <t>Northwood</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -7931,7 +7931,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Northwood</t>
+          <t>Rainham</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Rainham</t>
+          <t>Sidcup</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -7979,7 +7979,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Romford</t>
+          <t>South Croydon</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Sidcup</t>
+          <t>Sutton-in-ashfield</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -8022,21 +8022,21 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>MONITOR</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>South Croydon</t>
+          <t>Aylesbury</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E80" s="3" t="n">
         <v>0</v>
@@ -8046,21 +8046,21 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>MONITOR</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Sutton-in-ashfield</t>
+          <t>Chelmsford</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D81" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E81" s="5" t="n">
         <v>0</v>
@@ -8075,12 +8075,12 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Aylesbury</t>
+          <t>Cramlington</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D82" s="3" t="n">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Chelmsford</t>
+          <t>Crewe</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D83" s="5" t="n">
@@ -8123,12 +8123,12 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Cramlington</t>
+          <t>Eastbourne</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D84" s="3" t="n">
@@ -8147,12 +8147,12 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Crewe</t>
+          <t>Eastleigh</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D85" s="5" t="n">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Dorking</t>
+          <t>Epsom</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Eastbourne</t>
+          <t>Exeter</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D87" s="5" t="n">
@@ -8219,12 +8219,12 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Eastleigh</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D88" s="3" t="n">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Epsom</t>
+          <t>Gloucester</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D89" s="5" t="n">
@@ -8267,12 +8267,12 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Exeter</t>
+          <t>Harrogate</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D90" s="3" t="n">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Hastings</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D91" s="5" t="n">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Gloucester</t>
+          <t>High Wycombe</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D92" s="3" t="n">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Harrogate</t>
+          <t>Macclesfield</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D93" s="5" t="n">
@@ -8363,12 +8363,12 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Hastings</t>
+          <t>Redhill</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D94" s="3" t="n">
@@ -8387,12 +8387,12 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>High Wycombe</t>
+          <t>Rotherham</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D95" s="5" t="n">
@@ -8411,12 +8411,12 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Macclesfield</t>
+          <t>Solihull</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D96" s="3" t="n">
@@ -8435,16 +8435,16 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Milton Keynes</t>
+          <t>Alresford</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D97" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E97" s="5" t="n">
         <v>0</v>
@@ -8459,16 +8459,16 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Redhill</t>
+          <t>Barrow-in-furness</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Cumbria - South</t>
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E98" s="3" t="n">
         <v>0</v>
@@ -8483,16 +8483,16 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Rotherham</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D99" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E99" s="5" t="n">
         <v>0</v>
@@ -8507,16 +8507,16 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Solihull</t>
+          <t>Berwick-upon-tweed</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E100" s="3" t="n">
         <v>0</v>
@@ -8531,12 +8531,12 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Alresford</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D101" s="5" t="n">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Barrow-in-furness</t>
+          <t>Crawley</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Cumbria - South</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D102" s="3" t="n">
@@ -8579,12 +8579,12 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Dorking</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D103" s="5" t="n">
@@ -8603,12 +8603,12 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Berwick-upon-tweed</t>
+          <t>Driffield</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Yorkshire - East</t>
         </is>
       </c>
       <c r="D104" s="3" t="n">
@@ -8627,12 +8627,12 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Ellesmere Port</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D105" s="5" t="n">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Crawley</t>
+          <t>Fareham</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D106" s="3" t="n">
@@ -8675,12 +8675,12 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Driffield</t>
+          <t>Gravesend</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - East</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D107" s="5" t="n">
@@ -8699,12 +8699,12 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Ellesmere Port</t>
+          <t>Hessle</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Yorkshire - East</t>
         </is>
       </c>
       <c r="D108" s="3" t="n">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Fareham</t>
+          <t>Kettering</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D109" s="5" t="n">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Gravesend</t>
+          <t>Knaresborough</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D110" s="3" t="n">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Hessle</t>
+          <t>Knutsford</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - East</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D111" s="5" t="n">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Kettering</t>
+          <t>Lichfield</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D112" s="3" t="n">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Knaresborough</t>
+          <t>Lingfield</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D113" s="5" t="n">
@@ -8843,12 +8843,12 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Knutsford</t>
+          <t>Lowestoft</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D114" s="3" t="n">
@@ -8867,12 +8867,12 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Lichfield</t>
+          <t>Milton Keynes</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D115" s="5" t="n">
@@ -8891,12 +8891,12 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Lingfield</t>
+          <t>Newry</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D116" s="3" t="n">
@@ -8915,12 +8915,12 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Lowestoft</t>
+          <t>Nuneaton</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D117" s="5" t="n">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Newry</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D118" s="3" t="n">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Nuneaton</t>
+          <t>Pudsey</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D119" s="5" t="n">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Romsey</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9011,12 +9011,12 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Pudsey</t>
+          <t>Slough</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D121" s="5" t="n">
@@ -9035,12 +9035,12 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Romsey</t>
+          <t>Stafford</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D122" s="3" t="n">
@@ -9059,12 +9059,12 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Slough</t>
+          <t>Staines</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D123" s="5" t="n">
@@ -9083,12 +9083,12 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Stafford</t>
+          <t>Stockport</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D124" s="3" t="n">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Staines</t>
+          <t>Stoke-on-trent</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D125" s="5" t="n">
@@ -9131,12 +9131,12 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Stockport</t>
+          <t>Tipton</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D126" s="3" t="n">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Stoke-on-trent</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D127" s="5" t="n">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Tipton</t>
+          <t>Weston-super-mare</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D128" s="3" t="n">
@@ -9203,12 +9203,12 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Worcester</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Worcestershire</t>
         </is>
       </c>
       <c r="D129" s="5" t="n">
@@ -9227,16 +9227,16 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Weston-super-mare</t>
+          <t>Abingdon</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D130" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E130" s="3" t="n">
         <v>0</v>
@@ -9251,16 +9251,16 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Worcester</t>
+          <t>Aldershot</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Worcestershire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D131" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E131" s="5" t="n">
         <v>0</v>
@@ -9275,12 +9275,12 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Abingdon</t>
+          <t>Alton</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D132" s="3" t="n">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Aldershot</t>
+          <t>Ashford</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D133" s="5" t="n">
@@ -9323,12 +9323,12 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Alton</t>
+          <t>Ballymena</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D134" s="3" t="n">
@@ -9347,12 +9347,12 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Ashford</t>
+          <t>Banbury</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D135" s="5" t="n">
@@ -9371,12 +9371,12 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Ballymena</t>
+          <t>Banstead</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D136" s="3" t="n">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Banbury</t>
+          <t>Barry</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Wales South - Cardiff &amp; Vale</t>
         </is>
       </c>
       <c r="D137" s="5" t="n">
@@ -9419,12 +9419,12 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Banstead</t>
+          <t>Basingstoke</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D138" s="3" t="n">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Barry</t>
+          <t>Batley</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Wales South - Cardiff &amp; Vale</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D139" s="5" t="n">
@@ -9467,12 +9467,12 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Basingstoke</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D140" s="3" t="n">
@@ -9491,12 +9491,12 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Batley</t>
+          <t>Berkhamsted</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D141" s="5" t="n">
@@ -9515,12 +9515,12 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Bicester</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D142" s="3" t="n">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Berkhamsted</t>
+          <t>Bingley</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D143" s="5" t="n">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Bicester</t>
+          <t>Bishop Auckland</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D144" s="3" t="n">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Bingley</t>
+          <t>Bishop's Stortford</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D145" s="5" t="n">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Bishop Auckland</t>
+          <t>Bognor Regis</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D146" s="3" t="n">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Bishop's Stortford</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D147" s="5" t="n">
@@ -9659,12 +9659,12 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Bognor Regis</t>
+          <t>Brentwood</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D148" s="3" t="n">
@@ -9683,12 +9683,12 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Bridport</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D149" s="5" t="n">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Brentwood</t>
+          <t>Brinsworth</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D150" s="3" t="n">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Bridport</t>
+          <t>Bury St Edmunds</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D151" s="5" t="n">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Brinsworth</t>
+          <t>Cannock</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D152" s="3" t="n">
@@ -9779,12 +9779,12 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Bury St Edmunds</t>
+          <t>Canterbury</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D153" s="5" t="n">
@@ -9803,12 +9803,12 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Cannock</t>
+          <t>Cheadle</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D154" s="3" t="n">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Canterbury</t>
+          <t>Chelmsley Wood</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D155" s="5" t="n">
@@ -9851,12 +9851,12 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Cheadle</t>
+          <t>Chertsey</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D156" s="3" t="n">
@@ -9875,12 +9875,12 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>Chelmsley Wood</t>
+          <t>Chesham</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D157" s="5" t="n">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Chertsey</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Derbyshire</t>
         </is>
       </c>
       <c r="D158" s="3" t="n">
@@ -9923,12 +9923,12 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>Chesham</t>
+          <t>Chichester</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D159" s="5" t="n">
@@ -9947,12 +9947,12 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Cirencester</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Derbyshire</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D160" s="3" t="n">
@@ -9971,12 +9971,12 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Chichester</t>
+          <t>Cleethorpes</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D161" s="5" t="n">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Cirencester</t>
+          <t>Cobham</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D162" s="3" t="n">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>Cleethorpes</t>
+          <t>Congleton</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D163" s="5" t="n">
@@ -10043,12 +10043,12 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Cobham</t>
+          <t>Congresbury</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D164" s="3" t="n">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Congleton</t>
+          <t>Corby</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D165" s="5" t="n">
@@ -10091,12 +10091,12 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Congresbury</t>
+          <t>Cottingham</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Yorkshire - East</t>
         </is>
       </c>
       <c r="D166" s="3" t="n">
@@ -10115,12 +10115,12 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Corby</t>
+          <t>Cranbrook</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D167" s="5" t="n">
@@ -10139,12 +10139,12 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Cottingham</t>
+          <t>Darlington</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - East</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D168" s="3" t="n">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Cranbrook</t>
+          <t>Dartford</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
@@ -10187,12 +10187,12 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Darlington</t>
+          <t>Dewsbury</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D170" s="3" t="n">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Dartford</t>
+          <t>Dorchester</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D171" s="5" t="n">
@@ -10235,12 +10235,12 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Dewsbury</t>
+          <t>Droitwich</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Worcestershire</t>
         </is>
       </c>
       <c r="D172" s="3" t="n">
@@ -10259,12 +10259,12 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Diss</t>
+          <t>Dudley</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D173" s="5" t="n">
@@ -10283,12 +10283,12 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Dorchester</t>
+          <t>Fakenham</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D174" s="3" t="n">
@@ -10307,12 +10307,12 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Droitwich</t>
+          <t>Falmouth</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Worcestershire</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D175" s="5" t="n">
@@ -10331,12 +10331,12 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Dudley</t>
+          <t>Farnham</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D176" s="3" t="n">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Fakenham</t>
+          <t>Faygate</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D177" s="5" t="n">
@@ -10379,12 +10379,12 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Falmouth</t>
+          <t>Felixstowe</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D178" s="3" t="n">
@@ -10403,7 +10403,7 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Farnham</t>
+          <t>Fetcham</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
@@ -10427,12 +10427,12 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Faygate</t>
+          <t>Freshwater</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D180" s="3" t="n">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Felixstowe</t>
+          <t>Frodsham</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D181" s="5" t="n">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Fetcham</t>
+          <t>Frome</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D182" s="3" t="n">
@@ -10499,12 +10499,12 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Freshwater</t>
+          <t>Godalming</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D183" s="5" t="n">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Frodsham</t>
+          <t>Gosport</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D184" s="3" t="n">
@@ -10547,12 +10547,12 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Frome</t>
+          <t>Grantham</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D185" s="5" t="n">
@@ -10571,12 +10571,12 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Godalming</t>
+          <t>Great Yarmouth</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D186" s="3" t="n">
@@ -10595,12 +10595,12 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Gosport</t>
+          <t>Guildford</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D187" s="5" t="n">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Grantham</t>
+          <t>Hailsham</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D188" s="3" t="n">
@@ -10643,12 +10643,12 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Great Yarmouth</t>
+          <t>Harlow</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D189" s="5" t="n">
@@ -10667,12 +10667,12 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Guildford</t>
+          <t>Hartlepool</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D190" s="3" t="n">
@@ -10691,12 +10691,12 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Hailsham</t>
+          <t>Havant</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D191" s="5" t="n">
@@ -10715,12 +10715,12 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Harlow</t>
+          <t>Horley</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D192" s="3" t="n">
@@ -10739,12 +10739,12 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Hartlepool</t>
+          <t>Horsham</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D193" s="5" t="n">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Havant</t>
+          <t>Hove</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D194" s="3" t="n">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Horley</t>
+          <t>Keighley</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D195" s="5" t="n">
@@ -10811,12 +10811,12 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Horsham</t>
+          <t>Kenilworth</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D196" s="3" t="n">
@@ -10835,12 +10835,12 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Hove</t>
+          <t>Kings Langley</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D197" s="5" t="n">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Keighley</t>
+          <t>Knaphill</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D198" s="3" t="n">
@@ -10883,12 +10883,12 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Kenilworth</t>
+          <t>Knowle</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D199" s="5" t="n">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Kings Langley</t>
+          <t>Leamington Spa</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D200" s="3" t="n">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Knaphill</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D201" s="5" t="n">
@@ -10955,12 +10955,12 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Knowle</t>
+          <t>Lisburn</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D202" s="3" t="n">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Leamington Spa</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Scotland Central - Edinburgh &amp; Lothians</t>
         </is>
       </c>
       <c r="D203" s="5" t="n">
@@ -11003,12 +11003,12 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Loughborough</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D204" s="3" t="n">
@@ -11027,12 +11027,12 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Lisburn</t>
+          <t>Luton</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D205" s="5" t="n">
@@ -11051,12 +11051,12 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Maidenhead</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Scotland Central - Edinburgh &amp; Lothians</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D206" s="3" t="n">
@@ -11075,12 +11075,12 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Loughborough</t>
+          <t>Mansfield</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D207" s="5" t="n">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Luton</t>
+          <t>Marlborough</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D208" s="3" t="n">
@@ -11123,12 +11123,12 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Maidenhead</t>
+          <t>Marlow</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D209" s="5" t="n">
@@ -11147,12 +11147,12 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Mansfield</t>
+          <t>Nantwich</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Nottinghamshire</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D210" s="3" t="n">
@@ -11171,12 +11171,12 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Marlborough</t>
+          <t>Newbury</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D211" s="5" t="n">
@@ -11195,12 +11195,12 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Marlow</t>
+          <t>Newtownabbey</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D212" s="3" t="n">
@@ -11219,12 +11219,12 @@
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>Nantwich</t>
+          <t>Normanton</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D213" s="5" t="n">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Newbury</t>
+          <t>North Shields</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D214" s="3" t="n">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>Newtownabbey</t>
+          <t>Northampton</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D215" s="5" t="n">
@@ -11291,12 +11291,12 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Normanton</t>
+          <t>Northwich</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D216" s="3" t="n">
@@ -11315,12 +11315,12 @@
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>North Shields</t>
+          <t>Okehampton</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D217" s="5" t="n">
@@ -11339,12 +11339,12 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Northampton</t>
+          <t>Otley</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D218" s="3" t="n">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>Northwich</t>
+          <t>Oxted</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D219" s="5" t="n">
@@ -11387,12 +11387,12 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Okehampton</t>
+          <t>Peterlee</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D220" s="3" t="n">
@@ -11411,12 +11411,12 @@
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Otley</t>
+          <t>Pickering</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D221" s="5" t="n">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Oxted</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D222" s="3" t="n">
@@ -11459,12 +11459,12 @@
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>Peterlee</t>
+          <t>Poole</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D223" s="5" t="n">
@@ -11483,12 +11483,12 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>Pickering</t>
+          <t>Portishead</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D224" s="3" t="n">
@@ -11507,12 +11507,12 @@
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Potters Bar</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D225" s="5" t="n">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>Poole</t>
+          <t>Prudhoe</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D226" s="3" t="n">
@@ -11555,12 +11555,12 @@
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>Portishead</t>
+          <t>Ramsgate</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D227" s="5" t="n">
@@ -11579,12 +11579,12 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>Potters Bar</t>
+          <t>Redruth</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D228" s="3" t="n">
@@ -11603,12 +11603,12 @@
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>Prudhoe</t>
+          <t>Ripon</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D229" s="5" t="n">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>Ramsgate</t>
+          <t>Rochester</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
@@ -11651,12 +11651,12 @@
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>Redruth</t>
+          <t>Royston</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D231" s="5" t="n">
@@ -11675,12 +11675,12 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Ripon</t>
+          <t>Rugby</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D232" s="3" t="n">
@@ -11699,12 +11699,12 @@
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>Rochester</t>
+          <t>Runcorn</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Cheshire - Warrington &amp; Halton</t>
         </is>
       </c>
       <c r="D233" s="5" t="n">
@@ -11723,12 +11723,12 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Royston</t>
+          <t>Rushden</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D234" s="3" t="n">
@@ -11747,12 +11747,12 @@
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>Rugby</t>
+          <t>Ryton</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D235" s="5" t="n">
@@ -11771,12 +11771,12 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Runcorn</t>
+          <t>Sale</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - Warrington &amp; Halton</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D236" s="3" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>Rushden</t>
+          <t>Salisbury</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D237" s="5" t="n">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>Ryton</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D238" s="3" t="n">
@@ -11843,12 +11843,12 @@
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>Sale</t>
+          <t>Scunthorpe</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D239" s="5" t="n">
@@ -11867,12 +11867,12 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Salisbury</t>
+          <t>Sevenoaks</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D240" s="3" t="n">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>Sandy</t>
+          <t>Shepperton</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D241" s="5" t="n">
@@ -11915,12 +11915,12 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>Scunthorpe</t>
+          <t>Shirley</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D242" s="3" t="n">
@@ -11939,12 +11939,12 @@
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>Sevenoaks</t>
+          <t>Shrewsbury</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Shropshire</t>
         </is>
       </c>
       <c r="D243" s="5" t="n">
@@ -11963,12 +11963,12 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>Shepperton</t>
+          <t>Snodland</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D244" s="3" t="n">
@@ -11987,12 +11987,12 @@
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>Shirley</t>
+          <t>Southam</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D245" s="5" t="n">
@@ -12011,12 +12011,12 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>Shrewsbury</t>
+          <t>Southend-on-sea</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Shropshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D246" s="3" t="n">
@@ -12035,12 +12035,12 @@
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>Snodland</t>
+          <t>Spalding</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D247" s="5" t="n">
@@ -12059,12 +12059,12 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>Southam</t>
+          <t>St. Ives</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D248" s="3" t="n">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>Southend-on-sea</t>
+          <t>St. Neots</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D249" s="5" t="n">
@@ -12107,12 +12107,12 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>Spalding</t>
+          <t>Stanley</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D250" s="3" t="n">
@@ -12131,12 +12131,12 @@
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>St. Ives</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D251" s="5" t="n">
@@ -12155,12 +12155,12 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>St. Neots</t>
+          <t>Stone</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D252" s="3" t="n">
@@ -12179,12 +12179,12 @@
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>Stanley</t>
+          <t>Stratford-upon-avon</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D253" s="5" t="n">
@@ -12203,12 +12203,12 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Stretford</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D254" s="3" t="n">
@@ -12227,12 +12227,12 @@
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>Stone</t>
+          <t>Stroud</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D255" s="5" t="n">
@@ -12251,12 +12251,12 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>Stratford-upon-avon</t>
+          <t>Sunbury-on-thames</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D256" s="3" t="n">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>Stretford</t>
+          <t>Tadworth</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D257" s="5" t="n">
@@ -12299,12 +12299,12 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>Stroud</t>
+          <t>Tamworth</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D258" s="3" t="n">
@@ -12323,12 +12323,12 @@
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>Sunbury-on-thames</t>
+          <t>Taunton</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D259" s="5" t="n">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>Tadworth</t>
+          <t>Telford</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Shropshire</t>
         </is>
       </c>
       <c r="D260" s="3" t="n">
@@ -12371,12 +12371,12 @@
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>Tamworth</t>
+          <t>Thame</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D261" s="5" t="n">
@@ -12395,12 +12395,12 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>Taunton</t>
+          <t>Thatcham</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D262" s="3" t="n">
@@ -12419,12 +12419,12 @@
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>Telford</t>
+          <t>Thetford</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>Shropshire</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D263" s="5" t="n">
@@ -12443,12 +12443,12 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>Thame</t>
+          <t>Torquay</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D264" s="3" t="n">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>Thatcham</t>
+          <t>Trowbridge</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D265" s="5" t="n">
@@ -12491,12 +12491,12 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>Thetford</t>
+          <t>Truro</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D266" s="3" t="n">
@@ -12515,12 +12515,12 @@
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>Torquay</t>
+          <t>Tunbridge Wells</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D267" s="5" t="n">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>Trowbridge</t>
+          <t>Uttoxeter</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D268" s="3" t="n">
@@ -12563,12 +12563,12 @@
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>Truro</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D269" s="5" t="n">
@@ -12587,12 +12587,12 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>Tunbridge Wells</t>
+          <t>Walton-on-thames</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D270" s="3" t="n">
@@ -12611,12 +12611,12 @@
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>Uttoxeter</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D271" s="5" t="n">
@@ -12635,12 +12635,12 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Wellington</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Shropshire</t>
         </is>
       </c>
       <c r="D272" s="3" t="n">
@@ -12659,12 +12659,12 @@
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>Walton-on-thames</t>
+          <t>Welwyn Garden City</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D273" s="5" t="n">
@@ -12683,12 +12683,12 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>West Malling</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D274" s="3" t="n">
@@ -12707,12 +12707,12 @@
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>Wellington</t>
+          <t>Whitby</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>Shropshire</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D275" s="5" t="n">
@@ -12731,12 +12731,12 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>Welwyn Garden City</t>
+          <t>Whitstable</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D276" s="3" t="n">
@@ -12755,12 +12755,12 @@
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>West Malling</t>
+          <t>Wilmslow</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D277" s="5" t="n">
@@ -12779,12 +12779,12 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>Whitby</t>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D278" s="3" t="n">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>Whitstable</t>
+          <t>Winsford</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D279" s="5" t="n">
@@ -12827,12 +12827,12 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>Wilmslow</t>
+          <t>Wokingham</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D280" s="3" t="n">
@@ -12851,12 +12851,12 @@
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Yeovil</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D281" s="5" t="n">
@@ -12867,80 +12867,8 @@
       </c>
       <c r="F281" s="4" t="inlineStr"/>
     </row>
-    <row r="282">
-      <c r="A282" s="2" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B282" s="2" t="inlineStr">
-        <is>
-          <t>Winsford</t>
-        </is>
-      </c>
-      <c r="C282" s="2" t="inlineStr">
-        <is>
-          <t>Cheshire - West</t>
-        </is>
-      </c>
-      <c r="D282" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E282" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F282" s="2" t="inlineStr"/>
-    </row>
-    <row r="283">
-      <c r="A283" s="4" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B283" s="4" t="inlineStr">
-        <is>
-          <t>Wokingham</t>
-        </is>
-      </c>
-      <c r="C283" s="4" t="inlineStr">
-        <is>
-          <t>Berkshire</t>
-        </is>
-      </c>
-      <c r="D283" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E283" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F283" s="4" t="inlineStr"/>
-    </row>
-    <row r="284">
-      <c r="A284" s="2" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B284" s="2" t="inlineStr">
-        <is>
-          <t>Yeovil</t>
-        </is>
-      </c>
-      <c r="C284" s="2" t="inlineStr">
-        <is>
-          <t>Somerset</t>
-        </is>
-      </c>
-      <c r="D284" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E284" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F284" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F284"/>
+  <autoFilter ref="A1:F281"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13084,7 +13012,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
       <c r="D5" s="4" t="inlineStr"/>
@@ -13460,7 +13388,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
       <c r="D25" s="5" t="n">
@@ -13613,7 +13541,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>14</v>
@@ -13712,7 +13640,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C39" s="4" t="inlineStr"/>
       <c r="D39" s="4" t="inlineStr"/>
@@ -13733,7 +13661,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>1</v>
@@ -14144,7 +14072,7 @@
         </is>
       </c>
       <c r="B63" s="5" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C63" s="5" t="n">
         <v>4</v>
@@ -14542,37 +14470,37 @@
       <c r="B2" s="13" t="inlineStr"/>
       <c r="C2" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/13</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="D2" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.1 / 0/13</t>
+          <t>1 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="E2" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.8 / 0/11</t>
+          <t>3 / 3.8 / 0/12</t>
         </is>
       </c>
       <c r="F2" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/11</t>
+          <t>1 / 1.1 / 0/12</t>
         </is>
       </c>
       <c r="G2" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/8</t>
+          <t>1 / 0.8 / 0/9</t>
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/10</t>
+          <t>1 / 1.0 / 0/11</t>
         </is>
       </c>
       <c r="I2" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/7</t>
+          <t>1 / 1.0 / 0/8</t>
         </is>
       </c>
     </row>
@@ -14585,25 +14513,25 @@
       <c r="B3" s="14" t="inlineStr"/>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>0 / 3.0 / 3/13</t>
+          <t>3 / 3.0 / 3/14</t>
         </is>
       </c>
       <c r="D3" s="14" t="inlineStr"/>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.9 / 0/11</t>
+          <t>2 / 1.0 / 0/12</t>
         </is>
       </c>
       <c r="F3" s="14" t="inlineStr"/>
       <c r="G3" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/8</t>
+          <t>1 / 0.7 / 0/9</t>
         </is>
       </c>
       <c r="H3" s="14" t="inlineStr"/>
       <c r="I3" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/7</t>
+          <t>1 / 0.5 / 0/8</t>
         </is>
       </c>
     </row>
@@ -14616,25 +14544,25 @@
       <c r="B4" s="13" t="inlineStr"/>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.8 / 0/13</t>
+          <t>0 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr"/>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.9 / 1/11</t>
+          <t>2 / 2.8 / 1/12</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr"/>
       <c r="G4" s="13" t="inlineStr"/>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.9 / 0/10</t>
+          <t>3 / 2.0 / 0/11</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
-          <t>5 / 2.9 / 0/7</t>
+          <t>5 / 3.1 / 0/8</t>
         </is>
       </c>
     </row>
@@ -14647,28 +14575,28 @@
       <c r="B5" s="14" t="inlineStr"/>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/13</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/13</t>
+          <t>2 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/11</t>
+          <t>1 / 1.0 / 0/12</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr"/>
       <c r="G5" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.1 / 0/8</t>
+          <t>2 / 2.1 / 0/9</t>
         </is>
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/10</t>
+          <t>1 / 0.8 / 0/11</t>
         </is>
       </c>
       <c r="I5" s="14" t="inlineStr"/>
@@ -14682,33 +14610,33 @@
       <c r="B6" s="13" t="inlineStr"/>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/13</t>
+          <t>1 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.6 / 0/13</t>
+          <t>3 / 2.6 / 0/14</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/11</t>
+          <t>1 / 1.2 / 0/12</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr"/>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>2 / 4.0 / 2/8</t>
+          <t>2 / 3.8 / 2/9</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/10</t>
+          <t>0 / 0.1 / 0/11</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/7</t>
+          <t>0 / 0.8 / 0/8</t>
         </is>
       </c>
     </row>
@@ -14721,37 +14649,37 @@
       <c r="B7" s="14" t="inlineStr"/>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/13</t>
+          <t>0 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.8 / 0/13</t>
+          <t>3 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/11</t>
+          <t>0 / 0.2 / 0/12</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/11</t>
+          <t>2 / 1.2 / 0/12</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/10</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="I7" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.0 / 0/7</t>
+          <t>2 / 2.0 / 0/8</t>
         </is>
       </c>
     </row>
@@ -14764,33 +14692,33 @@
       <c r="B8" s="13" t="inlineStr"/>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.3 / 0/13</t>
+          <t>1 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.9 / 1/13</t>
+          <t>1 / 1.9 / 1/14</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/11</t>
+          <t>2 / 1.5 / 0/12</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/11</t>
+          <t>0 / 0.3 / 0/12</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr"/>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/10</t>
+          <t>0 / 0.1 / 0/11</t>
         </is>
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/7</t>
+          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
     </row>
@@ -14803,33 +14731,33 @@
       <c r="B9" s="14" t="inlineStr"/>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.2 / 0/13</t>
+          <t>0 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.8 / 0/13</t>
+          <t>1 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.2 / 0/11</t>
+          <t>2 / 1.2 / 0/12</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr"/>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.9 / 0/8</t>
+          <t>1 / 1.8 / 0/9</t>
         </is>
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/10</t>
+          <t>1 / 0.5 / 0/11</t>
         </is>
       </c>
       <c r="I9" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/7</t>
+          <t>1 / 0.5 / 0/8</t>
         </is>
       </c>
     </row>
@@ -14842,37 +14770,37 @@
       <c r="B10" s="13" t="inlineStr"/>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.3 / 0/13</t>
+          <t>1 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.8 / 0/13</t>
+          <t>2 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/12</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/9</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.2 / 0/11</t>
-        </is>
-      </c>
-      <c r="G10" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.2 / 0/8</t>
-        </is>
-      </c>
-      <c r="H10" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/10</t>
-        </is>
-      </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/7</t>
+          <t>0 / 0.8 / 0/8</t>
         </is>
       </c>
     </row>
@@ -14884,42 +14812,42 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 0/13</t>
+          <t>1 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>0 / 2.4 / 3/13</t>
+          <t>0 / 2.2 / 3/14</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/13</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/9</t>
+        </is>
+      </c>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
-      <c r="G11" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.1 / 0/8</t>
-        </is>
-      </c>
-      <c r="H11" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/10</t>
-        </is>
-      </c>
       <c r="I11" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/7</t>
+          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
     </row>
@@ -14931,38 +14859,38 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/13</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr"/>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/13</t>
+          <t>1 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.8 / 0/11</t>
+          <t>2 / 0.9 / 0/12</t>
         </is>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/8</t>
+          <t>0 / 0.4 / 0/9</t>
         </is>
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/10</t>
+          <t>1 / 0.4 / 0/11</t>
         </is>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/7</t>
+          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
     </row>
@@ -14974,42 +14902,42 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.5 / 0/13</t>
+          <t>0 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/13</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/13</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.3 / 0/9</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
-      <c r="G13" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.4 / 0/8</t>
-        </is>
-      </c>
-      <c r="H13" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/10</t>
-        </is>
-      </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/7</t>
+          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
     </row>
@@ -15022,37 +14950,37 @@
       <c r="B14" s="13" t="inlineStr"/>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/13</t>
+          <t>0 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.5 / 0/13</t>
+          <t>3 / 2.6 / 0/14</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.8 / 0/11</t>
+          <t>2 / 0.9 / 0/12</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/11</t>
+          <t>2 / 1.2 / 0/12</t>
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.9 / 0/8</t>
+          <t>2 / 2.8 / 0/9</t>
         </is>
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/10</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.9 / 0/7</t>
+          <t>2 / 1.9 / 0/8</t>
         </is>
       </c>
     </row>
@@ -15065,33 +14993,33 @@
       <c r="B15" s="14" t="inlineStr"/>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>3 / 0.6 / 0/13</t>
+          <t>3 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>6 / 3.5 / 1/13</t>
+          <t>6 / 3.7 / 2/14</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.1 / 0/11</t>
+          <t>2 / 2.1 / 0/12</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>5 / 2.0 / 2/11</t>
+          <t>6 / 2.3 / 3/12</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr"/>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/10</t>
+          <t>1 / 1.1 / 0/11</t>
         </is>
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.3 / 0/7</t>
+          <t>2 / 1.4 / 0/8</t>
         </is>
       </c>
     </row>
@@ -15104,37 +15032,37 @@
       <c r="B16" s="13" t="inlineStr"/>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/13</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.8 / 2/13</t>
+          <t>4 / 3.9 / 2/14</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/11</t>
+          <t>0 / 0.2 / 0/12</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/11</t>
+          <t>2 / 1.6 / 0/12</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.6 / 0/8</t>
+          <t>0 / 2.3 / 0/9</t>
         </is>
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/10</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="I16" s="13" t="inlineStr">
         <is>
-          <t>3 / 0.7 / 0/7</t>
+          <t>4 / 1.1 / 0/8</t>
         </is>
       </c>
     </row>
@@ -15147,29 +15075,29 @@
       <c r="B17" s="14" t="inlineStr"/>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/13</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>5 / 2.5 / 0/13</t>
+          <t>6 / 2.8 / 1/14</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr"/>
       <c r="F17" s="14" t="inlineStr"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>5 / 5.6 / 2/8</t>
+          <t>5 / 5.6 / 2/9</t>
         </is>
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/10</t>
+          <t>1 / 1.1 / 0/11</t>
         </is>
       </c>
       <c r="I17" s="14" t="inlineStr">
         <is>
-          <t>5 / 2.7 / 0/7</t>
+          <t>5 / 3.0 / 0/8</t>
         </is>
       </c>
     </row>
@@ -15182,29 +15110,29 @@
       <c r="B18" s="13" t="inlineStr"/>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/13</t>
+          <t>1 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.7 / 0/13</t>
+          <t>4 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr"/>
       <c r="G18" s="13" t="inlineStr"/>
       <c r="H18" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.1 / 0/10</t>
+          <t>0 / 1.0 / 0/11</t>
         </is>
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.0 / 0/7</t>
+          <t>4 / 2.2 / 0/8</t>
         </is>
       </c>
     </row>
@@ -15217,25 +15145,25 @@
       <c r="B19" s="14" t="inlineStr"/>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.3 / 0/13</t>
+          <t>2 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr"/>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>4 / 3.9 / 2/11</t>
+          <t>5 / 4.0 / 2/12</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr"/>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>4 / 3.8 / 0/8</t>
+          <t>5 / 3.9 / 0/9</t>
         </is>
       </c>
       <c r="H19" s="14" t="inlineStr"/>
       <c r="I19" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.4 / 0/7</t>
+          <t>3 / 2.5 / 0/8</t>
         </is>
       </c>
     </row>
@@ -15247,42 +15175,42 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.0 / 1/13</t>
+          <t>2 / 2.9 / 1/14</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/13</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/13</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="H20" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/10</t>
+          <t>0 / 0.1 / 0/11</t>
         </is>
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/7</t>
+          <t>1 / 0.5 / 0/8</t>
         </is>
       </c>
     </row>
@@ -15295,37 +15223,37 @@
       <c r="B21" s="14" t="inlineStr"/>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/13</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/13</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/11</t>
+          <t>1 / 0.6 / 0/12</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.5 / 0/11</t>
+          <t>2 / 0.7 / 0/12</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/10</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="I21" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.3 / 0/7</t>
+          <t>3 / 1.5 / 0/8</t>
         </is>
       </c>
     </row>
@@ -15338,37 +15266,37 @@
       <c r="B22" s="13" t="inlineStr"/>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/13</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/13</t>
+          <t>1 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/11</t>
+          <t>1 / 0.5 / 0/12</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/8</t>
+          <t>0 / 0.2 / 0/9</t>
         </is>
       </c>
       <c r="H22" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/10</t>
+          <t>1 / 1.0 / 0/11</t>
         </is>
       </c>
       <c r="I22" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/7</t>
+          <t>1 / 1.0 / 0/8</t>
         </is>
       </c>
     </row>
@@ -15382,27 +15310,27 @@
       <c r="C23" s="14" t="inlineStr"/>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>13 / 8.3 / 9/13</t>
+          <t>13 / 8.6 / 10/14</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.4 / 0/11</t>
+          <t>0 / 1.2 / 0/12</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>10 / 5.9 / 4/11</t>
+          <t>12 / 6.4 / 5/12</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.4 / 0/8</t>
+          <t>2 / 2.3 / 0/9</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>4 / 3.6 / 0/10</t>
+          <t>4 / 3.6 / 0/11</t>
         </is>
       </c>
       <c r="I23" s="14" t="inlineStr"/>
@@ -15415,42 +15343,42 @@
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.2 / 0/13</t>
+          <t>0 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/13</t>
+          <t>1 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="D24" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/13</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.8 / 0/9</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
-      <c r="F24" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
-      <c r="G24" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.9 / 0/8</t>
-        </is>
-      </c>
-      <c r="H24" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/10</t>
-        </is>
-      </c>
       <c r="I24" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/7</t>
+          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
     </row>
@@ -15463,29 +15391,29 @@
       <c r="B25" s="14" t="inlineStr"/>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.4 / 0/13</t>
+          <t>2 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr"/>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 0/11</t>
+          <t>0 / 1.4 / 0/12</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/8</t>
+          <t>1 / 1.0 / 0/9</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/10</t>
+          <t>1 / 0.5 / 0/11</t>
         </is>
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
-          <t>4 / 2.1 / 0/7</t>
+          <t>3 / 2.2 / 0/8</t>
         </is>
       </c>
     </row>
@@ -15500,23 +15428,23 @@
       <c r="D26" s="13" t="inlineStr"/>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>5 / 4.3 / 2/11</t>
+          <t>5 / 4.3 / 2/12</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr"/>
       <c r="G26" s="13" t="inlineStr">
         <is>
-          <t>0 / 2.2 / 1/8</t>
+          <t>0 / 2.0 / 1/9</t>
         </is>
       </c>
       <c r="H26" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.7 / 0/10</t>
+          <t>1 / 1.6 / 0/11</t>
         </is>
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.4 / 0/7</t>
+          <t>4 / 1.8 / 0/8</t>
         </is>
       </c>
     </row>
@@ -15528,42 +15456,42 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/13</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/13</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/13</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>2 / 1.2 / 0/12</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/9</t>
+        </is>
+      </c>
+      <c r="H27" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>2 / 1.1 / 0/11</t>
-        </is>
-      </c>
-      <c r="G27" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.2 / 0/8</t>
-        </is>
-      </c>
-      <c r="H27" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/10</t>
-        </is>
-      </c>
       <c r="I27" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/7</t>
+          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
     </row>
@@ -15575,42 +15503,42 @@
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.8 / 0/13</t>
+          <t>2 / 2.8 / 0/14</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/13</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/13</t>
+          <t>1 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/8</t>
+          <t>1 / 0.7 / 0/9</t>
         </is>
       </c>
       <c r="H28" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/10</t>
+          <t>0 / 0.2 / 0/11</t>
         </is>
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/7</t>
+          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
     </row>
@@ -15622,42 +15550,42 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.6 / 0/13</t>
+          <t>3 / 2.6 / 0/14</t>
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/13</t>
+          <t>1 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/13</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/11</t>
+          <t>0 / 0.2 / 0/12</t>
         </is>
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.5 / 0/11</t>
+          <t>3 / 1.6 / 0/12</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/8</t>
+          <t>0 / 1.0 / 0/9</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/10</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="I29" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/7</t>
+          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
     </row>
@@ -15669,42 +15597,42 @@
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.2 / 0/13</t>
+          <t>2 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.0 / 0/13</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/13</t>
+          <t>1 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/9</t>
+        </is>
+      </c>
+      <c r="H30" s="13" t="inlineStr">
+        <is>
+          <t>1 / 0.4 / 0/11</t>
+        </is>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
-      <c r="H30" s="13" t="inlineStr">
-        <is>
-          <t>1 / 0.3 / 0/10</t>
-        </is>
-      </c>
-      <c r="I30" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
     </row>
@@ -15716,42 +15644,42 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.1 / 0/12</t>
+          <t>0 / 1.0 / 0/13</t>
         </is>
       </c>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/12</t>
+          <t>0 / 0.1 / 0/13</t>
         </is>
       </c>
       <c r="D31" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/12</t>
+          <t>1 / 1.2 / 0/13</t>
         </is>
       </c>
       <c r="E31" s="14" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/9</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
-      <c r="F31" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
-      <c r="G31" s="14" t="inlineStr">
+      <c r="I31" s="14" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
-      <c r="H31" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/10</t>
-        </is>
-      </c>
-      <c r="I31" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
     </row>
@@ -15764,37 +15692,37 @@
       <c r="B32" s="13" t="inlineStr"/>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/13</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 0/13</t>
+          <t>2 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/11</t>
+          <t>1 / 1.4 / 0/12</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.0 / 0/11</t>
+          <t>1 / 1.0 / 0/12</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.8 / 1/8</t>
+          <t>2 / 2.7 / 1/9</t>
         </is>
       </c>
       <c r="H32" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/10</t>
+          <t>1 / 0.8 / 0/11</t>
         </is>
       </c>
       <c r="I32" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.6 / 0/7</t>
+          <t>2 / 2.5 / 0/8</t>
         </is>
       </c>
     </row>
@@ -15807,37 +15735,37 @@
       <c r="B33" s="14" t="inlineStr"/>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.5 / 0/13</t>
+          <t>0 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
-          <t>5 / 1.8 / 0/13</t>
+          <t>4 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.6 / 0/11</t>
+          <t>2 / 1.7 / 0/12</t>
         </is>
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.6 / 0/11</t>
+          <t>2 / 2.6 / 0/12</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.4 / 0/8</t>
+          <t>1 / 2.2 / 0/9</t>
         </is>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/10</t>
+          <t>2 / 1.5 / 0/11</t>
         </is>
       </c>
       <c r="I33" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/7</t>
+          <t>1 / 1.0 / 0/8</t>
         </is>
       </c>
     </row>
@@ -15865,33 +15793,33 @@
       <c r="B35" s="14" t="inlineStr"/>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/13</t>
+          <t>0 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/13</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.6 / 0/11</t>
+          <t>1 / 0.7 / 0/12</t>
         </is>
       </c>
       <c r="F35" s="14" t="inlineStr"/>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.8 / 0/8</t>
+          <t>3 / 1.0 / 0/9</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/10</t>
+          <t>0 / 0.1 / 0/11</t>
         </is>
       </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/7</t>
+          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
     </row>
@@ -15903,42 +15831,42 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/12</t>
+          <t>0 / 0.1 / 0/13</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
-      <c r="D36" s="13" t="inlineStr">
+      <c r="F36" s="13" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
-      <c r="E36" s="13" t="inlineStr">
+      <c r="G36" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/9</t>
+        </is>
+      </c>
+      <c r="H36" s="13" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
-      <c r="F36" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
-      <c r="G36" s="13" t="inlineStr">
+      <c r="I36" s="13" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
-      <c r="H36" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/10</t>
-        </is>
-      </c>
-      <c r="I36" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
     </row>
@@ -15950,42 +15878,42 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.8 / 0/12</t>
+          <t>1 / 1.8 / 0/13</t>
         </is>
       </c>
       <c r="C37" s="14" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.8 / 0/13</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
-      <c r="D37" s="14" t="inlineStr">
-        <is>
-          <t>1 / 0.8 / 0/12</t>
-        </is>
-      </c>
-      <c r="E37" s="14" t="inlineStr">
+      <c r="F37" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.4 / 0/9</t>
+        </is>
+      </c>
+      <c r="H37" s="14" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
-      <c r="F37" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
-      <c r="G37" s="14" t="inlineStr">
-        <is>
-          <t>1 / 1.5 / 0/8</t>
-        </is>
-      </c>
-      <c r="H37" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/10</t>
-        </is>
-      </c>
       <c r="I37" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/7</t>
+          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
     </row>
@@ -15997,42 +15925,42 @@
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 0/13</t>
+          <t>1 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/13</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/13</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/11</t>
+          <t>1 / 0.5 / 0/12</t>
         </is>
       </c>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.7 / 0/11</t>
+          <t>2 / 0.8 / 0/12</t>
         </is>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/8</t>
+          <t>1 / 0.4 / 0/9</t>
         </is>
       </c>
       <c r="H38" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/10</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/7</t>
+          <t>1 / 1.0 / 0/8</t>
         </is>
       </c>
     </row>
@@ -16045,33 +15973,33 @@
       <c r="B39" s="14" t="inlineStr"/>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/13</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="D39" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/13</t>
+          <t>1 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="E39" s="14" t="inlineStr"/>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 0/11</t>
+          <t>0 / 1.3 / 0/12</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>2 / 3.6 / 2/8</t>
+          <t>2 / 3.4 / 2/9</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/10</t>
+          <t>0 / 0.2 / 0/11</t>
         </is>
       </c>
       <c r="I39" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/7</t>
+          <t>1 / 0.9 / 0/8</t>
         </is>
       </c>
     </row>
@@ -16086,14 +16014,14 @@
       <c r="D40" s="13" t="inlineStr"/>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/11</t>
+          <t>1 / 1.0 / 0/12</t>
         </is>
       </c>
       <c r="F40" s="13" t="inlineStr"/>
       <c r="G40" s="13" t="inlineStr"/>
       <c r="H40" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/10</t>
+          <t>1 / 1.1 / 0/11</t>
         </is>
       </c>
       <c r="I40" s="13" t="inlineStr"/>
@@ -16107,37 +16035,37 @@
       <c r="B41" s="14" t="inlineStr"/>
       <c r="C41" s="14" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>6 / 3.7 / 4/13</t>
+        </is>
+      </c>
+      <c r="E41" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.3 / 0/12</t>
+        </is>
+      </c>
+      <c r="F41" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
-      <c r="D41" s="14" t="inlineStr">
-        <is>
-          <t>6 / 3.5 / 3/12</t>
-        </is>
-      </c>
-      <c r="E41" s="14" t="inlineStr">
-        <is>
-          <t>1 / 0.3 / 0/11</t>
-        </is>
-      </c>
-      <c r="F41" s="14" t="inlineStr">
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.4 / 0/9</t>
+        </is>
+      </c>
+      <c r="H41" s="14" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
-      <c r="G41" s="14" t="inlineStr">
-        <is>
-          <t>1 / 1.5 / 0/8</t>
-        </is>
-      </c>
-      <c r="H41" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/10</t>
-        </is>
-      </c>
       <c r="I41" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/7</t>
+          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
     </row>
@@ -16149,42 +16077,42 @@
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>4 / 4.5 / 1/12</t>
+          <t>3 / 4.4 / 1/13</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/12</t>
+          <t>0 / 0.2 / 0/13</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/12</t>
+          <t>2 / 1.5 / 0/13</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="F42" s="13" t="inlineStr">
+        <is>
+          <t>1 / 0.6 / 0/12</t>
+        </is>
+      </c>
+      <c r="G42" s="13" t="inlineStr">
+        <is>
+          <t>1 / 1.3 / 0/9</t>
+        </is>
+      </c>
+      <c r="H42" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
-      <c r="F42" s="13" t="inlineStr">
-        <is>
-          <t>1 / 0.5 / 0/11</t>
-        </is>
-      </c>
-      <c r="G42" s="13" t="inlineStr">
-        <is>
-          <t>1 / 1.4 / 0/8</t>
-        </is>
-      </c>
-      <c r="H42" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/10</t>
-        </is>
-      </c>
       <c r="I42" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/7</t>
+          <t>1 / 1.0 / 0/8</t>
         </is>
       </c>
     </row>
@@ -16196,42 +16124,42 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.0 / 0/12</t>
+          <t>3 / 2.1 / 0/13</t>
         </is>
       </c>
       <c r="C43" s="14" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.2 / 0/12</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
-      <c r="D43" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
-      <c r="E43" s="14" t="inlineStr">
-        <is>
-          <t>1 / 0.1 / 0/11</t>
-        </is>
-      </c>
-      <c r="F43" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/10</t>
+          <t>1 / 0.5 / 0/11</t>
         </is>
       </c>
       <c r="I43" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/7</t>
+          <t>1 / 0.6 / 0/8</t>
         </is>
       </c>
     </row>
@@ -16244,37 +16172,37 @@
       <c r="B44" s="13" t="inlineStr"/>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/13</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>9 / 4.5 / 3/13</t>
+          <t>10 / 4.9 / 4/14</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.3 / 0/11</t>
+          <t>1 / 1.2 / 0/12</t>
         </is>
       </c>
       <c r="F44" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.4 / 0/11</t>
+          <t>3 / 2.4 / 0/12</t>
         </is>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.9 / 2/8</t>
+          <t>1 / 2.7 / 2/9</t>
         </is>
       </c>
       <c r="H44" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.5 / 1/10</t>
+          <t>2 / 2.5 / 1/11</t>
         </is>
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/7</t>
+          <t>1 / 0.5 / 0/8</t>
         </is>
       </c>
     </row>
@@ -16287,33 +16215,33 @@
       <c r="B45" s="14" t="inlineStr"/>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.7 / 0/12</t>
+          <t>2 / 1.7 / 0/13</t>
         </is>
       </c>
       <c r="D45" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/12</t>
+          <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>4 / 1.5 / 0/11</t>
+          <t>9 / 2.1 / 1/12</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/11</t>
+          <t>1 / 0.2 / 0/12</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr"/>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.3 / 0/10</t>
+          <t>3 / 0.5 / 0/11</t>
         </is>
       </c>
       <c r="I45" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.0 / 0/7</t>
+          <t>3 / 1.2 / 0/8</t>
         </is>
       </c>
     </row>
@@ -16325,42 +16253,42 @@
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>20 / 5.2 / 1/12</t>
+          <t>22 / 6.5 / 2/13</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="D46" s="13" t="inlineStr">
+        <is>
+          <t>3 / 1.5 / 0/13</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
-      <c r="D46" s="13" t="inlineStr">
-        <is>
-          <t>3 / 1.3 / 0/12</t>
-        </is>
-      </c>
-      <c r="E46" s="13" t="inlineStr">
+      <c r="F46" s="13" t="inlineStr">
+        <is>
+          <t>1 / 0.1 / 0/12</t>
+        </is>
+      </c>
+      <c r="G46" s="13" t="inlineStr">
+        <is>
+          <t>1 / 0.3 / 0/9</t>
+        </is>
+      </c>
+      <c r="H46" s="13" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
-      <c r="F46" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
-      <c r="G46" s="13" t="inlineStr">
-        <is>
-          <t>1 / 0.2 / 0/8</t>
-        </is>
-      </c>
-      <c r="H46" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/10</t>
-        </is>
-      </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/7</t>
+          <t>2 / 0.2 / 0/8</t>
         </is>
       </c>
     </row>
@@ -16373,33 +16301,33 @@
       <c r="B47" s="14" t="inlineStr"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.8 / 0/13</t>
+          <t>2 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="D47" s="14" t="inlineStr">
         <is>
-          <t>4 / 2.2 / 0/13</t>
+          <t>3 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.1 / 0/11</t>
+          <t>2 / 2.1 / 0/12</t>
         </is>
       </c>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.3 / 0/11</t>
+          <t>3 / 2.3 / 0/12</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>1 / 3.0 / 2/8</t>
+          <t>1 / 2.8 / 2/9</t>
         </is>
       </c>
       <c r="H47" s="14" t="inlineStr"/>
       <c r="I47" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/7</t>
+          <t>1 / 1.0 / 0/8</t>
         </is>
       </c>
     </row>
@@ -16413,28 +16341,28 @@
       <c r="C48" s="13" t="inlineStr"/>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.2 / 0/13</t>
+          <t>4 / 3.2 / 0/14</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.7 / 0/11</t>
+          <t>2 / 1.8 / 0/12</t>
         </is>
       </c>
       <c r="F48" s="13" t="inlineStr"/>
       <c r="G48" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.4 / 0/8</t>
+          <t>1 / 2.2 / 0/9</t>
         </is>
       </c>
       <c r="H48" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/10</t>
+          <t>2 / 0.5 / 0/11</t>
         </is>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.4 / 0/7</t>
+          <t>3 / 1.6 / 0/8</t>
         </is>
       </c>
     </row>
@@ -16446,42 +16374,42 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/13</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/13</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="D49" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/13</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="E49" s="14" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/9</t>
+        </is>
+      </c>
+      <c r="H49" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
-      <c r="F49" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
-      <c r="G49" s="14" t="inlineStr">
+      <c r="I49" s="14" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
-      <c r="H49" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/10</t>
-        </is>
-      </c>
-      <c r="I49" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
     </row>
@@ -16493,42 +16421,42 @@
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.4 / 0/12</t>
+          <t>2 / 1.5 / 0/13</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="D50" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
-      <c r="D50" s="13" t="inlineStr">
+      <c r="F50" s="13" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
-      <c r="E50" s="13" t="inlineStr">
+      <c r="G50" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/9</t>
+        </is>
+      </c>
+      <c r="H50" s="13" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
-      <c r="F50" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
-      <c r="G50" s="13" t="inlineStr">
+      <c r="I50" s="13" t="inlineStr">
         <is>
           <t>0 / 0.1 / 0/8</t>
-        </is>
-      </c>
-      <c r="H50" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/10</t>
-        </is>
-      </c>
-      <c r="I50" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.1 / 0/7</t>
         </is>
       </c>
     </row>
@@ -16541,37 +16469,37 @@
       <c r="B51" s="14" t="inlineStr"/>
       <c r="C51" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/12</t>
+          <t>0 / 0.1 / 0/13</t>
         </is>
       </c>
       <c r="D51" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.4 / 0/12</t>
+          <t>3 / 2.5 / 0/13</t>
         </is>
       </c>
       <c r="E51" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.5 / 0/11</t>
+          <t>3 / 2.6 / 0/12</t>
         </is>
       </c>
       <c r="F51" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/11</t>
+          <t>0 / 0.2 / 0/12</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/8</t>
+          <t>1 / 1.1 / 0/9</t>
         </is>
       </c>
       <c r="H51" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/10</t>
+          <t>1 / 0.5 / 0/11</t>
         </is>
       </c>
       <c r="I51" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/7</t>
+          <t>1 / 0.5 / 0/8</t>
         </is>
       </c>
     </row>
@@ -16583,42 +16511,42 @@
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.4 / 0/12</t>
+          <t>1 / 2.3 / 0/13</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="D52" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
-      <c r="D52" s="13" t="inlineStr">
+      <c r="F52" s="13" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
-      <c r="E52" s="13" t="inlineStr">
+      <c r="G52" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.9 / 0/9</t>
+        </is>
+      </c>
+      <c r="H52" s="13" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
-      <c r="F52" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
-      <c r="G52" s="13" t="inlineStr">
-        <is>
-          <t>0 / 1.0 / 0/8</t>
-        </is>
-      </c>
-      <c r="H52" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/10</t>
-        </is>
-      </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/7</t>
+          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
     </row>
@@ -16630,42 +16558,42 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.6 / 0/12</t>
+          <t>2 / 1.6 / 0/13</t>
         </is>
       </c>
       <c r="C53" s="14" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="D53" s="14" t="inlineStr">
+        <is>
+          <t>2 / 1.2 / 0/13</t>
+        </is>
+      </c>
+      <c r="E53" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
-      <c r="D53" s="14" t="inlineStr">
-        <is>
-          <t>2 / 1.2 / 0/12</t>
-        </is>
-      </c>
-      <c r="E53" s="14" t="inlineStr">
+      <c r="F53" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.4 / 0/9</t>
+        </is>
+      </c>
+      <c r="H53" s="14" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
-      <c r="F53" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
-      <c r="G53" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.5 / 0/8</t>
-        </is>
-      </c>
-      <c r="H53" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/10</t>
-        </is>
-      </c>
       <c r="I53" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/7</t>
+          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
     </row>
@@ -16678,37 +16606,37 @@
       <c r="B54" s="13" t="inlineStr"/>
       <c r="C54" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/12</t>
+          <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.2 / 0/13</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>1 / 1.2 / 0/12</t>
+        </is>
+      </c>
+      <c r="F54" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.2 / 0/12</t>
         </is>
       </c>
-      <c r="E54" s="13" t="inlineStr">
-        <is>
-          <t>1 / 1.2 / 0/11</t>
-        </is>
-      </c>
-      <c r="F54" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.2 / 0/11</t>
-        </is>
-      </c>
       <c r="G54" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/8</t>
+          <t>0 / 0.4 / 0/9</t>
         </is>
       </c>
       <c r="H54" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/10</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="I54" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/7</t>
+          <t>1 / 0.5 / 0/8</t>
         </is>
       </c>
     </row>
@@ -16720,42 +16648,42 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
+          <t>1 / 0.6 / 0/13</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="D55" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="E55" s="14" t="inlineStr">
+        <is>
           <t>1 / 0.6 / 0/12</t>
         </is>
       </c>
-      <c r="C55" s="14" t="inlineStr">
+      <c r="F55" s="14" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
-      <c r="D55" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
-      <c r="E55" s="14" t="inlineStr">
-        <is>
-          <t>1 / 0.5 / 0/11</t>
-        </is>
-      </c>
-      <c r="F55" s="14" t="inlineStr">
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/9</t>
+        </is>
+      </c>
+      <c r="H55" s="14" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
-      <c r="G55" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
-      <c r="H55" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/10</t>
-        </is>
-      </c>
       <c r="I55" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/7</t>
+          <t>1 / 0.8 / 0/8</t>
         </is>
       </c>
     </row>
@@ -16768,33 +16696,33 @@
       <c r="B56" s="13" t="inlineStr"/>
       <c r="C56" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/12</t>
+          <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
       <c r="D56" s="13" t="inlineStr"/>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/11</t>
+          <t>1 / 0.4 / 0/12</t>
         </is>
       </c>
       <c r="F56" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/11</t>
+          <t>0 / 0.2 / 0/12</t>
         </is>
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/8</t>
+          <t>0 / 0.2 / 0/9</t>
         </is>
       </c>
       <c r="H56" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/10</t>
+          <t>1 / 0.6 / 0/11</t>
         </is>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.1 / 1/7</t>
+          <t>1 / 2.9 / 1/8</t>
         </is>
       </c>
     </row>
@@ -16806,42 +16734,42 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/12</t>
+          <t>0 / 0.4 / 0/13</t>
         </is>
       </c>
       <c r="C57" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/12</t>
+          <t>0 / 0.1 / 0/13</t>
         </is>
       </c>
       <c r="D57" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/12</t>
+          <t>0 / 0.3 / 0/13</t>
         </is>
       </c>
       <c r="E57" s="14" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="F57" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.2 / 0/9</t>
+        </is>
+      </c>
+      <c r="H57" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
-      <c r="F57" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
-      <c r="G57" s="14" t="inlineStr">
-        <is>
-          <t>1 / 0.1 / 0/8</t>
-        </is>
-      </c>
-      <c r="H57" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/10</t>
-        </is>
-      </c>
       <c r="I57" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/7</t>
+          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
     </row>
@@ -16853,42 +16781,42 @@
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/12</t>
+          <t>1 / 1.0 / 0/13</t>
         </is>
       </c>
       <c r="C58" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="D58" s="13" t="inlineStr">
+        <is>
+          <t>1 / 0.5 / 0/13</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
-      <c r="D58" s="13" t="inlineStr">
-        <is>
-          <t>1 / 0.5 / 0/12</t>
-        </is>
-      </c>
-      <c r="E58" s="13" t="inlineStr">
+      <c r="F58" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="G58" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.4 / 0/9</t>
+        </is>
+      </c>
+      <c r="H58" s="13" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
-      <c r="F58" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
-      <c r="G58" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.5 / 0/8</t>
-        </is>
-      </c>
-      <c r="H58" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/10</t>
-        </is>
-      </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/7</t>
+          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
     </row>
@@ -16901,33 +16829,33 @@
       <c r="B59" s="14" t="inlineStr"/>
       <c r="C59" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.6 / 0/13</t>
+          <t>0 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="D59" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/13</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="E59" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.8 / 0/11</t>
+          <t>1 / 1.8 / 0/12</t>
         </is>
       </c>
       <c r="F59" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/11</t>
+          <t>1 / 0.4 / 0/12</t>
         </is>
       </c>
       <c r="G59" s="14" t="inlineStr"/>
       <c r="H59" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.9 / 0/10</t>
+          <t>2 / 1.9 / 0/11</t>
         </is>
       </c>
       <c r="I59" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/7</t>
+          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
     </row>
@@ -16940,37 +16868,37 @@
       <c r="B60" s="13" t="inlineStr"/>
       <c r="C60" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.4 / 3/13</t>
+          <t>2 / 3.3 / 3/14</t>
         </is>
       </c>
       <c r="D60" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.6 / 0/13</t>
+          <t>3 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/11</t>
+          <t>1 / 0.5 / 0/12</t>
         </is>
       </c>
       <c r="F60" s="13" t="inlineStr">
         <is>
-          <t>4 / 1.2 / 0/11</t>
+          <t>4 / 1.4 / 0/12</t>
         </is>
       </c>
       <c r="G60" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.6 / 1/8</t>
+          <t>1 / 2.4 / 1/9</t>
         </is>
       </c>
       <c r="H60" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/10</t>
+          <t>1 / 0.3 / 0/11</t>
         </is>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.9 / 0/7</t>
+          <t>2 / 1.0 / 0/8</t>
         </is>
       </c>
     </row>
@@ -16983,32 +16911,32 @@
       <c r="B61" s="14" t="inlineStr"/>
       <c r="C61" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/13</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="D61" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.4 / 0/13</t>
+          <t>2 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="E61" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="F61" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.4 / 0/11</t>
+          <t>2 / 1.4 / 0/12</t>
         </is>
       </c>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.6 / 0/8</t>
+          <t>3 / 2.7 / 0/9</t>
         </is>
       </c>
       <c r="H61" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/10</t>
+          <t>0 / 0.1 / 0/11</t>
         </is>
       </c>
       <c r="I61" s="14" t="inlineStr"/>
@@ -17022,33 +16950,33 @@
       <c r="B62" s="13" t="inlineStr"/>
       <c r="C62" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.8 / 0/13</t>
+          <t>0 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.8 / 0/13</t>
+          <t>3 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr"/>
       <c r="F62" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/11</t>
+          <t>1 / 0.6 / 0/12</t>
         </is>
       </c>
       <c r="G62" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.6 / 0/8</t>
+          <t>1 / 1.6 / 0/9</t>
         </is>
       </c>
       <c r="H62" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/10</t>
+          <t>0 / 0.8 / 0/11</t>
         </is>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/7</t>
+          <t>1 / 0.6 / 0/8</t>
         </is>
       </c>
     </row>
@@ -17063,18 +16991,18 @@
       <c r="D63" s="14" t="inlineStr"/>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>5 / 4.1 / 0/11</t>
+          <t>5 / 4.2 / 0/12</t>
         </is>
       </c>
       <c r="F63" s="14" t="inlineStr"/>
       <c r="G63" s="14" t="inlineStr">
         <is>
-          <t>3 / 4.6 / 2/8</t>
+          <t>3 / 4.4 / 2/9</t>
         </is>
       </c>
       <c r="H63" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.2 / 0/10</t>
+          <t>3 / 2.3 / 0/11</t>
         </is>
       </c>
       <c r="I63" s="14" t="inlineStr"/>
@@ -17090,23 +17018,23 @@
       <c r="D64" s="13" t="inlineStr"/>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.4 / 0/11</t>
+          <t>4 / 2.5 / 0/12</t>
         </is>
       </c>
       <c r="F64" s="13" t="inlineStr">
         <is>
-          <t>5 / 2.9 / 0/11</t>
+          <t>5 / 3.1 / 0/12</t>
         </is>
       </c>
       <c r="G64" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.8 / 0/8</t>
+          <t>2 / 3.6 / 0/9</t>
         </is>
       </c>
       <c r="H64" s="13" t="inlineStr"/>
       <c r="I64" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.1 / 0/7</t>
+          <t>4 / 3.2 / 0/8</t>
         </is>
       </c>
     </row>
@@ -17118,42 +17046,42 @@
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/12</t>
+          <t>0 / 0.1 / 0/13</t>
         </is>
       </c>
       <c r="C65" s="14" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="E65" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
-      <c r="D65" s="14" t="inlineStr">
+      <c r="F65" s="14" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
-      <c r="E65" s="14" t="inlineStr">
+      <c r="G65" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/9</t>
+        </is>
+      </c>
+      <c r="H65" s="14" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
-      <c r="F65" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
-      <c r="G65" s="14" t="inlineStr">
+      <c r="I65" s="14" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/8</t>
-        </is>
-      </c>
-      <c r="H65" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/10</t>
-        </is>
-      </c>
-      <c r="I65" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/7</t>
         </is>
       </c>
     </row>
@@ -17165,42 +17093,42 @@
       </c>
       <c r="B66" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.2 / 0/12</t>
+          <t>3 / 2.2 / 0/13</t>
         </is>
       </c>
       <c r="C66" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="D66" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="E66" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
-      <c r="D66" s="13" t="inlineStr">
+      <c r="F66" s="13" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
-      <c r="E66" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
-      <c r="F66" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
       <c r="G66" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/8</t>
+          <t>0 / 0.4 / 0/9</t>
         </is>
       </c>
       <c r="H66" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/10</t>
+          <t>1 / 0.4 / 0/11</t>
         </is>
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/7</t>
+          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
     </row>
@@ -17213,37 +17141,37 @@
       <c r="B67" s="14" t="inlineStr"/>
       <c r="C67" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/12</t>
+          <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
       <c r="D67" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.9 / 0/12</t>
+          <t>3 / 2.0 / 0/13</t>
         </is>
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/11</t>
+          <t>2 / 1.5 / 0/12</t>
         </is>
       </c>
       <c r="F67" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/11</t>
+          <t>1 / 1.0 / 0/12</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/8</t>
+          <t>0 / 0.8 / 0/9</t>
         </is>
       </c>
       <c r="H67" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/10</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="I67" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/7</t>
+          <t>0 / 0.4 / 0/8</t>
         </is>
       </c>
     </row>
@@ -17255,42 +17183,42 @@
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.5 / 0/12</t>
+          <t>2 / 2.5 / 0/13</t>
         </is>
       </c>
       <c r="C68" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/12</t>
+          <t>0 / 0.1 / 0/13</t>
         </is>
       </c>
       <c r="D68" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/12</t>
+          <t>0 / 0.2 / 0/13</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/11</t>
+          <t>2 / 1.5 / 0/12</t>
         </is>
       </c>
       <c r="F68" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/12</t>
+        </is>
+      </c>
+      <c r="G68" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.4 / 0/9</t>
+        </is>
+      </c>
+      <c r="H68" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
-      <c r="G68" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.5 / 0/8</t>
-        </is>
-      </c>
-      <c r="H68" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/10</t>
-        </is>
-      </c>
       <c r="I68" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/7</t>
+          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
     </row>
@@ -17302,42 +17230,42 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>4 / 3.3 / 1/12</t>
+          <t>2 / 3.2 / 1/13</t>
         </is>
       </c>
       <c r="C69" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/12</t>
+          <t>0 / 0.1 / 0/13</t>
         </is>
       </c>
       <c r="D69" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.7 / 0/12</t>
+          <t>1 / 1.6 / 0/13</t>
         </is>
       </c>
       <c r="E69" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/11</t>
+          <t>1 / 0.8 / 0/12</t>
         </is>
       </c>
       <c r="F69" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/11</t>
+          <t>1 / 0.2 / 0/12</t>
         </is>
       </c>
       <c r="G69" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/8</t>
+          <t>0 / 0.2 / 0/9</t>
         </is>
       </c>
       <c r="H69" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/10</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="I69" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/7</t>
+          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
     </row>
@@ -17350,37 +17278,37 @@
       <c r="B70" s="13" t="inlineStr"/>
       <c r="C70" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/12</t>
+          <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.7 / 0/12</t>
+          <t>1 / 0.7 / 0/13</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.8 / 0/11</t>
+          <t>4 / 2.9 / 0/12</t>
         </is>
       </c>
       <c r="F70" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/11</t>
+          <t>0 / 0.3 / 0/12</t>
         </is>
       </c>
       <c r="G70" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/8</t>
+          <t>0 / 0.1 / 0/9</t>
         </is>
       </c>
       <c r="H70" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/10</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="I70" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/7</t>
+          <t>1 / 1.1 / 0/8</t>
         </is>
       </c>
     </row>
@@ -17393,29 +17321,29 @@
       <c r="B71" s="14" t="inlineStr"/>
       <c r="C71" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/13</t>
+          <t>2 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="D71" s="14" t="inlineStr">
         <is>
-          <t>10 / 4.9 / 3/13</t>
+          <t>11 / 5.4 / 4/14</t>
         </is>
       </c>
       <c r="E71" s="14" t="inlineStr">
         <is>
-          <t>4 / 4.0 / 2/11</t>
+          <t>4 / 4.0 / 2/12</t>
         </is>
       </c>
       <c r="F71" s="14" t="inlineStr"/>
       <c r="G71" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.8 / 0/8</t>
+          <t>3 / 2.8 / 0/9</t>
         </is>
       </c>
       <c r="H71" s="14" t="inlineStr"/>
       <c r="I71" s="14" t="inlineStr">
         <is>
-          <t>5 / 3.9 / 0/7</t>
+          <t>4 / 3.9 / 0/8</t>
         </is>
       </c>
     </row>
@@ -17428,37 +17356,37 @@
       <c r="B72" s="13" t="inlineStr"/>
       <c r="C72" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/13</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="D72" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/13</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
         <is>
-          <t>4 / 1.6 / 0/11</t>
+          <t>4 / 1.8 / 0/12</t>
         </is>
       </c>
       <c r="F72" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/11</t>
+          <t>1 / 0.6 / 0/12</t>
         </is>
       </c>
       <c r="G72" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/8</t>
+          <t>1 / 1.2 / 0/9</t>
         </is>
       </c>
       <c r="H72" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/10</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/7</t>
+          <t>1 / 1.0 / 0/8</t>
         </is>
       </c>
     </row>
@@ -17471,37 +17399,37 @@
       <c r="B73" s="14" t="inlineStr"/>
       <c r="C73" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/13</t>
+          <t>1 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="D73" s="14" t="inlineStr">
         <is>
-          <t>6 / 2.0 / 3/13</t>
+          <t>6 / 2.3 / 4/14</t>
         </is>
       </c>
       <c r="E73" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/11</t>
+          <t>1 / 0.7 / 0/12</t>
         </is>
       </c>
       <c r="F73" s="14" t="inlineStr">
         <is>
-          <t>4 / 2.7 / 0/11</t>
+          <t>4 / 2.8 / 0/12</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.2 / 0/8</t>
+          <t>3 / 2.3 / 0/9</t>
         </is>
       </c>
       <c r="H73" s="14" t="inlineStr">
         <is>
-          <t>3 / 3.1 / 0/10</t>
+          <t>3 / 3.1 / 0/11</t>
         </is>
       </c>
       <c r="I73" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/7</t>
+          <t>0 / 0.4 / 0/8</t>
         </is>
       </c>
     </row>
@@ -17515,32 +17443,32 @@
       <c r="C74" s="13" t="inlineStr"/>
       <c r="D74" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.2 / 0/13</t>
+          <t>3 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="E74" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.2 / 0/11</t>
+          <t>4 / 3.2 / 0/12</t>
         </is>
       </c>
       <c r="F74" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.2 / 0/11</t>
+          <t>2 / 1.2 / 0/12</t>
         </is>
       </c>
       <c r="G74" s="13" t="inlineStr">
         <is>
-          <t>0 / 2.1 / 0/8</t>
+          <t>0 / 1.9 / 0/9</t>
         </is>
       </c>
       <c r="H74" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/10</t>
+          <t>1 / 0.5 / 0/11</t>
         </is>
       </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.3 / 0/7</t>
+          <t>2 / 1.4 / 0/8</t>
         </is>
       </c>
     </row>
@@ -17553,37 +17481,37 @@
       <c r="B75" s="14" t="inlineStr"/>
       <c r="C75" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.1 / 0/13</t>
+          <t>0 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="D75" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.9 / 0/13</t>
+          <t>2 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="E75" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.7 / 0/11</t>
+          <t>2 / 0.8 / 0/12</t>
         </is>
       </c>
       <c r="F75" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/11</t>
+          <t>1 / 1.5 / 0/12</t>
         </is>
       </c>
       <c r="G75" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/8</t>
+          <t>1 / 0.8 / 0/9</t>
         </is>
       </c>
       <c r="H75" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/10</t>
+          <t>0 / 0.2 / 0/11</t>
         </is>
       </c>
       <c r="I75" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.7 / 0/7</t>
+          <t>2 / 0.9 / 0/8</t>
         </is>
       </c>
     </row>
@@ -17596,37 +17524,37 @@
       <c r="B76" s="13" t="inlineStr"/>
       <c r="C76" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/13</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="D76" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.0 / 0/13</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="E76" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.2 / 0/11</t>
+          <t>2 / 1.2 / 0/12</t>
         </is>
       </c>
       <c r="F76" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.7 / 0/11</t>
+          <t>2 / 0.8 / 0/12</t>
         </is>
       </c>
       <c r="G76" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.5 / 0/8</t>
+          <t>2 / 3.3 / 0/9</t>
         </is>
       </c>
       <c r="H76" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/10</t>
+          <t>1 / 1.2 / 0/11</t>
         </is>
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.3 / 0/7</t>
+          <t>3 / 3.2 / 0/8</t>
         </is>
       </c>
     </row>
@@ -17639,33 +17567,33 @@
       <c r="B77" s="14" t="inlineStr"/>
       <c r="C77" s="14" t="inlineStr">
         <is>
-          <t>1 / 3.2 / 0/13</t>
+          <t>1 / 3.0 / 0/14</t>
         </is>
       </c>
       <c r="D77" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.2 / 0/13</t>
+          <t>4 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="E77" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/11</t>
+          <t>0 / 0.1 / 0/12</t>
         </is>
       </c>
       <c r="F77" s="14" t="inlineStr">
         <is>
-          <t>11 / 4.3 / 3/11</t>
+          <t>9 / 4.7 / 4/12</t>
         </is>
       </c>
       <c r="G77" s="14" t="inlineStr"/>
       <c r="H77" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.6 / 0/10</t>
+          <t>1 / 1.5 / 0/11</t>
         </is>
       </c>
       <c r="I77" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/7</t>
+          <t>2 / 1.2 / 0/8</t>
         </is>
       </c>
     </row>
@@ -17679,32 +17607,32 @@
       <c r="C78" s="13" t="inlineStr"/>
       <c r="D78" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.3 / 0/13</t>
+          <t>3 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
         <is>
-          <t>3 / 3.1 / 0/11</t>
+          <t>3 / 3.1 / 0/12</t>
         </is>
       </c>
       <c r="F78" s="13" t="inlineStr">
         <is>
-          <t>5 / 2.5 / 1/11</t>
+          <t>5 / 2.8 / 1/12</t>
         </is>
       </c>
       <c r="G78" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.8 / 2/8</t>
+          <t>0 / 1.6 / 2/9</t>
         </is>
       </c>
       <c r="H78" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/10</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.3 / 0/7</t>
+          <t>1 / 1.2 / 0/8</t>
         </is>
       </c>
     </row>
@@ -17719,19 +17647,19 @@
       <c r="D79" s="14" t="inlineStr"/>
       <c r="E79" s="14" t="inlineStr">
         <is>
-          <t>5 / 4.2 / 0/11</t>
+          <t>4 / 4.2 / 0/12</t>
         </is>
       </c>
       <c r="F79" s="14" t="inlineStr">
         <is>
-          <t>17 / 7.5 / 5/11</t>
+          <t>18 / 8.4 / 6/12</t>
         </is>
       </c>
       <c r="G79" s="14" t="inlineStr"/>
       <c r="H79" s="14" t="inlineStr"/>
       <c r="I79" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.7 / 0/7</t>
+          <t>3 / 2.8 / 0/8</t>
         </is>
       </c>
     </row>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -17,8 +17,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sitewide'!$A$1:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'JobG8 categories'!$A$1:$C$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'PAGES'!$A$1:$H$137</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$F$281</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'PAGES'!$A$1:$H$150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$F$272</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'LIVE'!$A$1:$I$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'NOT LIVE'!$A$1:$I$79</definedName>
   </definedNames>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1842</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="3">
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1504</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="4">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>338</v>
+        <v>329</v>
       </c>
     </row>
     <row r="5">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1904</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="6">
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>62</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -867,7 +867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H137"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -941,7 +941,7 @@
       <c r="D2" s="11" t="inlineStr"/>
       <c r="E2" s="11" t="inlineStr"/>
       <c r="F2" s="12" t="n">
-        <v>1964</v>
+        <v>1937</v>
       </c>
       <c r="G2" s="11" t="inlineStr"/>
       <c r="H2" s="11" t="inlineStr">
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="F3" s="12" t="n">
-        <v>1833</v>
+        <v>1793</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>1833</v>
+        <v>1793</v>
       </c>
       <c r="H3" s="11" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="F4" s="12" t="n">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="G4" s="11" t="inlineStr"/>
       <c r="H4" s="11" t="inlineStr">
@@ -1442,7 +1442,7 @@
         <v>1</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>1</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>1</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>1</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>1</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>1</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>1</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>1</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>1</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>1</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>1</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>1</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>1</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>1</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>1</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>1</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>1</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>1</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>1</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>1</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>1</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>1</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>1</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>1</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>1</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>1</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
@@ -3277,24 +3277,24 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Finance &amp; Accounts</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>/job-search/oxfordshire/service-administrator-jobs</t>
+          <t>/job-search/london/finance-accounts-jobs</t>
         </is>
       </c>
       <c r="F66" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -3325,14 +3325,14 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>/job-search/bristol-bath/service-administrator-jobs</t>
+          <t>/job-search/oxfordshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F67" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -3363,14 +3363,14 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>/job-search/essex/service-administrator-jobs</t>
+          <t>/job-search/bristol-bath/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F68" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3391,24 +3391,24 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Customer Service &amp; Contact Centre</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>/job-search/hampshire/customer-service-jobs</t>
+          <t>/job-search/essex/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F69" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
@@ -3429,24 +3429,24 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Customer Service &amp; Contact Centre</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>/job-search/cambridgeshire/service-administrator-jobs</t>
+          <t>/job-search/hampshire/customer-service-jobs</t>
         </is>
       </c>
       <c r="F70" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -3477,14 +3477,14 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>/job-search/gloucestershire/service-administrator-jobs</t>
+          <t>/job-search/cambridgeshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F71" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
@@ -3505,24 +3505,24 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Support Worker</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>/job-search/london/support-worker</t>
+          <t>/job-search/gloucestershire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3543,24 +3543,24 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Support Worker</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>/job-search/dorset/service-administrator-jobs</t>
+          <t>/job-search/london/support-worker</t>
         </is>
       </c>
       <c r="F73" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
@@ -3581,24 +3581,24 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Customer Service &amp; Contact Centre</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>/job-search/staffordshire/customer-service-jobs</t>
+          <t>/job-search/dorset/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F74" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -3619,24 +3619,24 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Customer Service &amp; Contact Centre</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>/job-search/devon/service-administrator-jobs</t>
+          <t>/job-search/staffordshire/customer-service-jobs</t>
         </is>
       </c>
       <c r="F75" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
@@ -3657,24 +3657,24 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Customer Service &amp; Contact Centre</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>/job-search/surrey/customer-service-jobs</t>
+          <t>/job-search/devon/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F76" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -3695,24 +3695,24 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Customer Service &amp; Contact Centre</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>/job-search/wiltshire/service-administrator-jobs</t>
+          <t>/job-search/surrey/customer-service-jobs</t>
         </is>
       </c>
       <c r="F77" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -3743,14 +3743,14 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>/job-search/northamptonshire/service-administrator-jobs</t>
+          <t>/job-search/wiltshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F78" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -3781,14 +3781,14 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>/job-search/berkshire/service-administrator-jobs</t>
+          <t>/job-search/northamptonshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F79" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Nottinghamshire</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -3819,14 +3819,14 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>/job-search/nottinghamshire/service-administrator-jobs</t>
+          <t>/job-search/berkshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F80" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -3857,14 +3857,14 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>/job-search/buckinghamshire/service-administrator-jobs</t>
+          <t>/job-search/nottinghamshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F81" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
@@ -3885,24 +3885,24 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Support Worker</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>/job-search/surrey/support-worker</t>
+          <t>/job-search/buckinghamshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F82" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -3923,24 +3923,24 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Support Worker</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>/job-search/hertfordshire/service-administrator-jobs</t>
+          <t>/job-search/surrey/support-worker</t>
         </is>
       </c>
       <c r="F83" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -3971,14 +3971,14 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>/job-search/staffordshire/service-administrator-jobs</t>
+          <t>/job-search/hertfordshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F84" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -4009,14 +4009,14 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>/job-search/norfolk/service-administrator-jobs</t>
+          <t>/job-search/staffordshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F85" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -4047,14 +4047,14 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>/job-search/birmingham-solihull/service-administrator-jobs</t>
+          <t>/job-search/norfolk/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F86" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4075,24 +4075,24 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>HR &amp; Recruitment</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>/job-search/west-yorkshire/hr-recruitment-jobs</t>
+          <t>/job-search/birmingham-solihull/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F87" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
@@ -4113,24 +4113,24 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>HR &amp; Recruitment</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>/job-search/greater-manchester-south/service-administrator-jobs</t>
+          <t>/job-search/west-yorkshire/hr-recruitment-jobs</t>
         </is>
       </c>
       <c r="F88" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4151,24 +4151,24 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Support Worker</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>/job-search/wiltshire/support-worker</t>
+          <t>/job-search/greater-manchester-south/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F89" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
@@ -4189,24 +4189,24 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Support Worker</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>/job-search/somerset/service-administrator-jobs</t>
+          <t>/job-search/wiltshire/support-worker</t>
         </is>
       </c>
       <c r="F90" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4227,24 +4227,24 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>/job-search/london/customer-sales-jobs</t>
+          <t>/job-search/somerset/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F91" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -4275,14 +4275,14 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>/job-search/west-yorkshire/customer-sales-jobs</t>
+          <t>/job-search/london/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F92" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -4313,14 +4313,14 @@
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>/job-search/manchester-salford/customer-sales-jobs</t>
+          <t>/job-search/west-yorkshire/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F93" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
@@ -4341,24 +4341,24 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>/job-search/leicestershire/service-administrator-jobs</t>
+          <t>/job-search/manchester-salford/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F94" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - Warrington &amp; Halton</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -4389,14 +4389,14 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>/job-search/warrington-halton/service-administrator-jobs</t>
+          <t>/job-search/leicestershire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F95" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Cheshire - Warrington &amp; Halton</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>/job-search/cornwall/service-administrator-jobs</t>
+          <t>/job-search/warrington-halton/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F96" s="3" t="n">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -4465,14 +4465,14 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>/job-search/suffolk/service-administrator-jobs</t>
+          <t>/job-search/cornwall/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F97" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Derbyshire</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -4503,14 +4503,14 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>/job-search/derbyshire/service-administrator-jobs</t>
+          <t>/job-search/suffolk/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F98" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Derbyshire</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -4541,14 +4541,14 @@
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>/job-search/cheshire-east/service-administrator-jobs</t>
+          <t>/job-search/derbyshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F99" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -4579,14 +4579,14 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>/job-search/lincolnshire/service-administrator-jobs</t>
+          <t>/job-search/cheshire-east/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F100" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Merseyside - Liverpool</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -4617,14 +4617,14 @@
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>/job-search/merseyside-liverpool/service-administrator-jobs</t>
+          <t>/job-search/lincolnshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F101" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Shropshire</t>
+          <t>Merseyside - Liverpool</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -4655,14 +4655,14 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>/job-search/shropshire/service-administrator-jobs</t>
+          <t>/job-search/merseyside-liverpool/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F102" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - Wigan &amp; Bolton</t>
+          <t>Shropshire</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -4693,14 +4693,14 @@
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>/job-search/wigan-bolton/service-administrator-jobs</t>
+          <t>/job-search/shropshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F103" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Greater Manchester - Wigan &amp; Bolton</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>/job-search/black-country/service-administrator-jobs</t>
+          <t>/job-search/wigan-bolton/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F104" s="3" t="n">
@@ -4759,24 +4759,24 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Legal Assistant &amp; Paralegal</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>/job-search/london/paralegal-jobs</t>
+          <t>/job-search/black-country/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F105" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -4807,14 +4807,14 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>/job-search/suffolk/paralegal-jobs</t>
+          <t>/job-search/london/paralegal-jobs</t>
         </is>
       </c>
       <c r="F106" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -4845,14 +4845,14 @@
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>/job-search/essex/paralegal-jobs</t>
+          <t>/job-search/suffolk/paralegal-jobs</t>
         </is>
       </c>
       <c r="F107" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
@@ -4873,24 +4873,24 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Legal Assistant &amp; Paralegal</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>/job-search/london/marketing-jobs</t>
+          <t>/job-search/essex/paralegal-jobs</t>
         </is>
       </c>
       <c r="F108" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
@@ -4921,14 +4921,14 @@
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>/job-search/surrey/marketing-jobs</t>
+          <t>/job-search/london/marketing-jobs</t>
         </is>
       </c>
       <c r="F109" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -4959,14 +4959,14 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>/job-search/manchester-salford/marketing-jobs</t>
+          <t>/job-search/surrey/marketing-jobs</t>
         </is>
       </c>
       <c r="F110" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
@@ -4997,14 +4997,14 @@
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>/job-search/birmingham-solihull/marketing-jobs</t>
+          <t>/job-search/manchester-salford/marketing-jobs</t>
         </is>
       </c>
       <c r="F111" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
@@ -5025,24 +5025,24 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>HR &amp; Recruitment</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>/job-search/berkshire/hr-recruitment-jobs</t>
+          <t>/job-search/birmingham-solihull/marketing-jobs</t>
         </is>
       </c>
       <c r="F112" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
@@ -5073,14 +5073,14 @@
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>/job-search/manchester-salford/hr-recruitment-jobs</t>
+          <t>/job-search/berkshire/hr-recruitment-jobs</t>
         </is>
       </c>
       <c r="F113" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Nottinghamshire</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -5111,14 +5111,14 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>/job-search/nottinghamshire/hr-recruitment-jobs</t>
+          <t>/job-search/manchester-salford/hr-recruitment-jobs</t>
         </is>
       </c>
       <c r="F114" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
@@ -5149,14 +5149,14 @@
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>/job-search/birmingham-solihull/hr-recruitment-jobs</t>
+          <t>/job-search/nottinghamshire/hr-recruitment-jobs</t>
         </is>
       </c>
       <c r="F115" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
@@ -5177,24 +5177,24 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>HR &amp; Recruitment</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>/job-search/cheshire-west/service-administrator-jobs</t>
+          <t>/job-search/birmingham-solihull/hr-recruitment-jobs</t>
         </is>
       </c>
       <c r="F116" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5215,24 +5215,24 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Scotland Central - Edinburgh &amp; Lothians</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>HR &amp; Recruitment</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>/job-search/edinburgh-lothians/service-administrator-jobs</t>
+          <t>/job-search/sussex/hr-recruitment-jobs</t>
         </is>
       </c>
       <c r="F117" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Worcestershire</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -5263,14 +5263,14 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>/job-search/worcestershire/service-administrator-jobs</t>
+          <t>/job-search/cheshire-west/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F118" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -5291,24 +5291,24 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Scotland Central - Edinburgh &amp; Lothians</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>/job-search/berkshire/marketing-jobs</t>
+          <t>/job-search/edinburgh-lothians/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F119" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
@@ -5329,24 +5329,24 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Worcestershire</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Support Worker</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>/job-search/kent/support-worker</t>
+          <t>/job-search/worcestershire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F120" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -5367,24 +5367,24 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>North East</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>/job-search/north-east/customer-sales-jobs</t>
+          <t>/job-search/berkshire/marketing-jobs</t>
         </is>
       </c>
       <c r="F121" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -5415,14 +5415,14 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>/job-search/oxfordshire/support-worker</t>
+          <t>/job-search/kent/support-worker</t>
         </is>
       </c>
       <c r="F122" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -5443,24 +5443,24 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>North East</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>/job-search/bedfordshire/service-administrator-jobs</t>
+          <t>/job-search/north-east/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F123" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
@@ -5481,24 +5481,24 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Support Worker</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>/job-search/bristol-bath/customer-sales-jobs</t>
+          <t>/job-search/oxfordshire/support-worker</t>
         </is>
       </c>
       <c r="F124" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -5519,24 +5519,24 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>/job-search/buckinghamshire/marketing-jobs</t>
+          <t>/job-search/bedfordshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F125" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
@@ -5557,24 +5557,24 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Wales South - Cardiff &amp; Vale</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>/job-search/cardiff-vale/service-administrator-jobs</t>
+          <t>/job-search/bristol-bath/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F126" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -5595,24 +5595,24 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>/job-search/berkshire/customer-sales-jobs</t>
+          <t>/job-search/buckinghamshire/marketing-jobs</t>
         </is>
       </c>
       <c r="F127" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
@@ -5633,24 +5633,24 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Wales South - Cardiff &amp; Vale</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>/job-search/hertfordshire/customer-sales-jobs</t>
+          <t>/job-search/cardiff-vale/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F128" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
@@ -5681,14 +5681,14 @@
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>/job-search/kent/customer-sales-jobs</t>
+          <t>/job-search/berkshire/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F129" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Scotland West - Glasgow</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -5719,14 +5719,14 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>/job-search/glasgow/customer-sales-jobs</t>
+          <t>/job-search/hertfordshire/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F130" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
@@ -5757,14 +5757,14 @@
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>/job-search/surrey/customer-sales-jobs</t>
+          <t>/job-search/kent/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F131" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Scotland West - Glasgow</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -5795,14 +5795,14 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>/job-search/sussex/customer-sales-jobs</t>
+          <t>/job-search/glasgow/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F132" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -5823,24 +5823,24 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>/job-search/bristol-bath/marketing-jobs</t>
+          <t>/job-search/surrey/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F133" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
@@ -5861,24 +5861,24 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>/job-search/gloucestershire/marketing-jobs</t>
+          <t>/job-search/sussex/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F134" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
@@ -5909,14 +5909,14 @@
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>/job-search/hertfordshire/marketing-jobs</t>
+          <t>/job-search/bristol-bath/marketing-jobs</t>
         </is>
       </c>
       <c r="F135" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -5947,14 +5947,14 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>/job-search/kent/marketing-jobs</t>
+          <t>/job-search/gloucestershire/marketing-jobs</t>
         </is>
       </c>
       <c r="F136" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -5975,33 +5975,527 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
+          <t>Hertfordshire</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>/job-search/hertfordshire/marketing-jobs</t>
+        </is>
+      </c>
+      <c r="F137" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G137" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H137" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Regional/category</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Kent</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>/job-search/kent/marketing-jobs</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G138" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>Regional/category</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
           <t>Oxfordshire</t>
         </is>
       </c>
-      <c r="D137" s="4" t="inlineStr">
+      <c r="D139" s="4" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="E137" s="4" t="inlineStr">
+      <c r="E139" s="4" t="inlineStr">
         <is>
           <t>/job-search/oxfordshire/marketing-jobs</t>
         </is>
       </c>
-      <c r="F137" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G137" s="5" t="n">
+      <c r="F139" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G139" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H139" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Regional/category</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>North Scotland</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Admin &amp; Customer Service</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>/job-search/north-scotland/service-administrator-jobs</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G140" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>Regional/category</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>Scotland Central - Tayside</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>Admin &amp; Customer Service</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>/job-search/tayside/service-administrator-jobs</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G141" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H141" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Regional/category</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Wales South - Valleys</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Admin &amp; Customer Service</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>/job-search/south-wales-valleys/service-administrator-jobs</t>
+        </is>
+      </c>
+      <c r="F142" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G142" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>Regional/category</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>Cambridgeshire</t>
+        </is>
+      </c>
+      <c r="D143" s="4" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>/job-search/cambridgeshire/marketing-jobs</t>
+        </is>
+      </c>
+      <c r="F143" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H143" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Regional/category</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Cheshire - West</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>/job-search/cheshire-west/marketing-jobs</t>
+        </is>
+      </c>
+      <c r="F144" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G144" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="H137" s="4" t="inlineStr">
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>Regional/category</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>Essex</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>/job-search/essex/marketing-jobs</t>
+        </is>
+      </c>
+      <c r="F145" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G145" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H145" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Regional/category</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Merseyside - Liverpool</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>/job-search/merseyside-liverpool/marketing-jobs</t>
+        </is>
+      </c>
+      <c r="F146" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>Regional/category</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>North East</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>/job-search/north-east/marketing-jobs</t>
+        </is>
+      </c>
+      <c r="F147" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H147" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Regional/category</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Cheshire - Warrington &amp; Halton</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Finance &amp; Accounts</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>/job-search/warrington-halton/finance-accounts-jobs</t>
+        </is>
+      </c>
+      <c r="F148" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>Regional/category</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>Buckinghamshire</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t>Customer Service &amp; Contact Centre</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>/job-search/buckinghamshire/customer-service-jobs</t>
+        </is>
+      </c>
+      <c r="F149" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G149" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H149" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Regional/category</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>North East</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Customer Service &amp; Contact Centre</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>/job-search/north-east/customer-service-jobs</t>
+        </is>
+      </c>
+      <c r="F150" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G150" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H137"/>
+  <autoFilter ref="A1:H150"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6012,7 +6506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F281"/>
+  <dimension ref="A1:F272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6072,7 +6566,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>0</v>
@@ -6135,16 +6629,16 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Altrincham</t>
+          <t>Gateshead</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>0</v>
@@ -6159,16 +6653,16 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Chester</t>
+          <t>Norwich</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
@@ -6183,12 +6677,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Durham</t>
+          <t>Chester</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -6207,12 +6701,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Maidstone</t>
+          <t>Durham</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -6231,12 +6725,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Northallerton</t>
+          <t>Maidstone</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -6255,12 +6749,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Norwich</t>
+          <t>Northallerton</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -6303,12 +6797,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Bracknell</t>
+          <t>Altrincham</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -6327,12 +6821,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Brighouse</t>
+          <t>Bracknell</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -6351,12 +6845,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Chester Le Street</t>
+          <t>Brighouse</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -6375,12 +6869,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Gateshead</t>
+          <t>Chester Le Street</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -6399,12 +6893,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Hemel Hempstead</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -6423,12 +6917,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Huntingdon</t>
+          <t>Hemel Hempstead</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -6447,12 +6941,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Leicester</t>
+          <t>High Wycombe</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -6495,12 +6989,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Ringwood</t>
+          <t>Scarborough</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -6519,12 +7013,12 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Scarborough</t>
+          <t>Swindon</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -6543,12 +7037,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Swindon</t>
+          <t>Tonbridge</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -6562,50 +7056,58 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>CREATE</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Tonbridge</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>/manchester/service-administrator-jobs</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>CREATE</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Winchester</t>
+          <t>Newcastle</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>/newcastle/service-administrator-jobs</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -6615,23 +7117,23 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Newcastle</t>
+          <t>Bristol</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>89</v>
+        <v>32</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>/newcastle/service-administrator-jobs</t>
+          <t>/bristol/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -6643,23 +7145,23 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>/manchester/service-administrator-jobs</t>
+          <t>/birmingham/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -6671,23 +7173,23 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Belfast</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E27" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>/birmingham/service-administrator-jobs</t>
+          <t>/belfast/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -6699,23 +7201,23 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Bristol</t>
+          <t>Leeds</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>/bristol/service-administrator-jobs</t>
+          <t>/leeds/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -6727,23 +7229,23 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Belfast</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Merseyside - Liverpool</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>/belfast/service-administrator-jobs</t>
+          <t>/liverpool/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -6755,23 +7257,23 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Hull</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Yorkshire - East</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>/leeds/service-administrator-jobs</t>
+          <t>/hull/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -6792,7 +7294,7 @@
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E31" s="5" t="n">
         <v>1</v>
@@ -6811,23 +7313,23 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Hull</t>
+          <t>Bradford</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - East</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>/hull/service-administrator-jobs</t>
+          <t>/bradford/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -6848,7 +7350,7 @@
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>1</v>
@@ -6867,23 +7369,23 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Cardiff</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Merseyside - Liverpool</t>
+          <t>Wales South - Cardiff &amp; Vale</t>
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>/liverpool/service-administrator-jobs</t>
+          <t>/cardiff/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -6895,23 +7397,23 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Bradford</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Scotland Central - Edinburgh &amp; Lothians</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E35" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>/bradford/service-administrator-jobs</t>
+          <t>/edinburgh/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -6923,23 +7425,23 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Cardiff</t>
+          <t>Oxford</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Wales South - Cardiff &amp; Vale</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>/cardiff/service-administrator-jobs</t>
+          <t>/oxford/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -6951,23 +7453,23 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Scotland Central - Edinburgh &amp; Lothians</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>/edinburgh/service-administrator-jobs</t>
+          <t>/southampton/service-administrator-jobs, /southampton/support-worker</t>
         </is>
       </c>
     </row>
@@ -6979,23 +7481,23 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Cambridge</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>/southampton/service-administrator-jobs, /southampton/support-worker</t>
+          <t>/cambridge/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7518,7 @@
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E39" s="5" t="n">
         <v>1</v>
@@ -7035,7 +7537,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Cambridge</t>
+          <t>Peterborough</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -7044,14 +7546,14 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>/cambridge/service-administrator-jobs</t>
+          <t>/peterborough/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7063,23 +7565,23 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Oxford</t>
+          <t>Brighton &amp; Hove</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E41" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>/oxford/service-administrator-jobs</t>
+          <t>/brighton-hove/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7091,23 +7593,23 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Peterborough</t>
+          <t>York</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>/peterborough/service-administrator-jobs</t>
+          <t>/york/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7119,23 +7621,23 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E43" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>/brighton-hove/service-administrator-jobs</t>
+          <t>/coventry/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7147,23 +7649,23 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Huddersfield</t>
+          <t>Warrington</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Cheshire - Warrington &amp; Halton</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>/huddersfield/service-administrator-jobs</t>
+          <t>/warrington/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7175,23 +7677,23 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>York</t>
+          <t>Huddersfield</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E45" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>/york/service-administrator-jobs</t>
+          <t>/huddersfield/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7203,77 +7705,69 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Coventry</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
-        </is>
-      </c>
+          <t>Barnsley</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E46" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>/coventry/service-administrator-jobs</t>
+          <t>/barnsley/service-administrator-jobs</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>HOLD – LONDON</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Warrington</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - Warrington &amp; Halton</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D47" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>/warrington/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>HOLD – LONDON</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Barnsley</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr"/>
+          <t>Wandsworth</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
       <c r="D48" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>/barnsley/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -7292,7 +7786,7 @@
         </is>
       </c>
       <c r="D49" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E49" s="5" t="n">
         <v>0</v>
@@ -7316,7 +7810,7 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E50" s="3" t="n">
         <v>0</v>
@@ -7331,7 +7825,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Wandsworth</t>
+          <t>Harrow</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -7340,7 +7834,7 @@
         </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E51" s="5" t="n">
         <v>0</v>
@@ -7355,7 +7849,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Isleworth</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -7379,7 +7873,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Isleworth</t>
+          <t>Uxbridge</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -7403,7 +7897,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Uxbridge</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -7412,7 +7906,7 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E54" s="3" t="n">
         <v>0</v>
@@ -7451,7 +7945,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Hammersmith And Fulham</t>
+          <t>Sutton</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -7475,7 +7969,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Harrow</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -7484,7 +7978,7 @@
         </is>
       </c>
       <c r="D57" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E57" s="5" t="n">
         <v>0</v>
@@ -7499,7 +7993,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Morden</t>
+          <t>Beckenham</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -7508,7 +8002,7 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E58" s="3" t="n">
         <v>0</v>
@@ -7523,7 +8017,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Southall</t>
+          <t>Bushey</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -7532,7 +8026,7 @@
         </is>
       </c>
       <c r="D59" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59" s="5" t="n">
         <v>0</v>
@@ -7547,7 +8041,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Sutton</t>
+          <t>Carshalton</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -7556,7 +8050,7 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E60" s="3" t="n">
         <v>0</v>
@@ -7571,7 +8065,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Chessington</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -7595,7 +8089,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Beckenham</t>
+          <t>Enfield</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -7619,7 +8113,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Hornchurch</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -7643,7 +8137,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Broxbourne</t>
+          <t>Ilford</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -7667,7 +8161,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Bushey</t>
+          <t>Islington</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -7691,7 +8185,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Carshalton</t>
+          <t>Kingston Upon Thames</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -7715,7 +8209,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Chessington</t>
+          <t>Lambeth</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -7739,7 +8233,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Edgware</t>
+          <t>Morden</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -7763,7 +8257,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Enfield</t>
+          <t>Rainham</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -7787,7 +8281,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Hornchurch</t>
+          <t>Sidcup</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -7811,7 +8305,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Ilford</t>
+          <t>Southall</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -7835,7 +8329,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Islington</t>
+          <t>Sutton-in-ashfield</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -7854,21 +8348,21 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>MONITOR</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Lambeth</t>
+          <t>Aylesbury</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D73" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E73" s="5" t="n">
         <v>0</v>
@@ -7878,21 +8372,21 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>MONITOR</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Loughton</t>
+          <t>Chelmsford</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E74" s="3" t="n">
         <v>0</v>
@@ -7902,21 +8396,21 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>MONITOR</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Northwood</t>
+          <t>Crewe</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D75" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E75" s="5" t="n">
         <v>0</v>
@@ -7926,21 +8420,21 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>MONITOR</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Rainham</t>
+          <t>Darlington</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E76" s="3" t="n">
         <v>0</v>
@@ -7950,21 +8444,21 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>MONITOR</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Sidcup</t>
+          <t>Eastleigh</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D77" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E77" s="5" t="n">
         <v>0</v>
@@ -7974,21 +8468,21 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>MONITOR</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>South Croydon</t>
+          <t>Epsom</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E78" s="3" t="n">
         <v>0</v>
@@ -7998,21 +8492,21 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>MONITOR</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Sutton-in-ashfield</t>
+          <t>Exeter</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D79" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E79" s="5" t="n">
         <v>0</v>
@@ -8027,12 +8521,12 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Aylesbury</t>
+          <t>Fareham</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D80" s="3" t="n">
@@ -8051,12 +8545,12 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Chelmsford</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D81" s="5" t="n">
@@ -8075,12 +8569,12 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Cramlington</t>
+          <t>Gloucester</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D82" s="3" t="n">
@@ -8099,12 +8593,12 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Crewe</t>
+          <t>Harrogate</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D83" s="5" t="n">
@@ -8123,7 +8617,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Eastbourne</t>
+          <t>Hastings</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -8147,12 +8641,12 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Eastleigh</t>
+          <t>Inverness</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D85" s="5" t="n">
@@ -8171,12 +8665,12 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Epsom</t>
+          <t>Leicester</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D86" s="3" t="n">
@@ -8195,12 +8689,12 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Exeter</t>
+          <t>Macclesfield</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D87" s="5" t="n">
@@ -8219,12 +8713,12 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Milton Keynes</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D88" s="3" t="n">
@@ -8243,12 +8737,12 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Gloucester</t>
+          <t>Newry</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D89" s="5" t="n">
@@ -8267,12 +8761,12 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Harrogate</t>
+          <t>Redhill</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D90" s="3" t="n">
@@ -8291,12 +8785,12 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Hastings</t>
+          <t>Ringwood</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D91" s="5" t="n">
@@ -8315,12 +8809,12 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>High Wycombe</t>
+          <t>Rotherham</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D92" s="3" t="n">
@@ -8339,12 +8833,12 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Macclesfield</t>
+          <t>Solihull</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D93" s="5" t="n">
@@ -8363,12 +8857,12 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Redhill</t>
+          <t>Stoke-on-trent</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D94" s="3" t="n">
@@ -8387,12 +8881,12 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Rotherham</t>
+          <t>Winchester</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D95" s="5" t="n">
@@ -8411,16 +8905,16 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Solihull</t>
+          <t>Alresford</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E96" s="3" t="n">
         <v>0</v>
@@ -8435,12 +8929,12 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Alresford</t>
+          <t>Barrow-in-furness</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Cumbria - South</t>
         </is>
       </c>
       <c r="D97" s="5" t="n">
@@ -8459,12 +8953,12 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Barrow-in-furness</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Cumbria - South</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D98" s="3" t="n">
@@ -8483,12 +8977,12 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D99" s="5" t="n">
@@ -8531,12 +9025,12 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Chelmsley Wood</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D101" s="5" t="n">
@@ -8579,12 +9073,12 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Dorking</t>
+          <t>Dewsbury</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D103" s="5" t="n">
@@ -8603,12 +9097,12 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Driffield</t>
+          <t>Dorking</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - East</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D104" s="3" t="n">
@@ -8627,12 +9121,12 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Ellesmere Port</t>
+          <t>Driffield</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Yorkshire - East</t>
         </is>
       </c>
       <c r="D105" s="5" t="n">
@@ -8651,12 +9145,12 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Fareham</t>
+          <t>Eastbourne</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D106" s="3" t="n">
@@ -8675,12 +9169,12 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Gravesend</t>
+          <t>Ellesmere Port</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D107" s="5" t="n">
@@ -8699,12 +9193,12 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Hessle</t>
+          <t>Forfar</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - East</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D108" s="3" t="n">
@@ -8723,12 +9217,12 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Kettering</t>
+          <t>Gravesend</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D109" s="5" t="n">
@@ -8747,12 +9241,12 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Knaresborough</t>
+          <t>Hebburn</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D110" s="3" t="n">
@@ -8771,12 +9265,12 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Knutsford</t>
+          <t>Hessle</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Yorkshire - East</t>
         </is>
       </c>
       <c r="D111" s="5" t="n">
@@ -8795,12 +9289,12 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Lichfield</t>
+          <t>Huntingdon</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D112" s="3" t="n">
@@ -8819,12 +9313,12 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Lingfield</t>
+          <t>Kettering</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D113" s="5" t="n">
@@ -8843,12 +9337,12 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Lowestoft</t>
+          <t>Knaresborough</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D114" s="3" t="n">
@@ -8867,12 +9361,12 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Milton Keynes</t>
+          <t>Knutsford</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D115" s="5" t="n">
@@ -8891,12 +9385,12 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Newry</t>
+          <t>Lichfield</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D116" s="3" t="n">
@@ -8915,12 +9409,12 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Nuneaton</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D117" s="5" t="n">
@@ -8939,12 +9433,12 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Lingfield</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D118" s="3" t="n">
@@ -8963,12 +9457,12 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Pudsey</t>
+          <t>Newtownabbey</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D119" s="5" t="n">
@@ -8987,12 +9481,12 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Romsey</t>
+          <t>Nuneaton</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D120" s="3" t="n">
@@ -9011,12 +9505,12 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Slough</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D121" s="5" t="n">
@@ -9035,12 +9529,12 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Stafford</t>
+          <t>Romsey</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D122" s="3" t="n">
@@ -9059,12 +9553,12 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Staines</t>
+          <t>Sale</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D123" s="5" t="n">
@@ -9083,12 +9577,12 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Stockport</t>
+          <t>Sevenoaks</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D124" s="3" t="n">
@@ -9107,12 +9601,12 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Stoke-on-trent</t>
+          <t>Slough</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D125" s="5" t="n">
@@ -9131,12 +9625,12 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Tipton</t>
+          <t>Stafford</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D126" s="3" t="n">
@@ -9155,12 +9649,12 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Staines</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D127" s="5" t="n">
@@ -9179,12 +9673,12 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Weston-super-mare</t>
+          <t>Stockport</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D128" s="3" t="n">
@@ -9203,12 +9697,12 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Worcester</t>
+          <t>Tipton</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Worcestershire</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D129" s="5" t="n">
@@ -9227,16 +9721,16 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Abingdon</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D130" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E130" s="3" t="n">
         <v>0</v>
@@ -9251,16 +9745,16 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Aldershot</t>
+          <t>Weston-super-mare</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D131" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E131" s="5" t="n">
         <v>0</v>
@@ -9275,16 +9769,16 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Alton</t>
+          <t>Worcester</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Worcestershire</t>
         </is>
       </c>
       <c r="D132" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E132" s="3" t="n">
         <v>0</v>
@@ -9299,12 +9793,12 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Ashford</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D133" s="5" t="n">
@@ -9323,12 +9817,12 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Ballymena</t>
+          <t>Aldershot</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D134" s="3" t="n">
@@ -9347,12 +9841,12 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Banbury</t>
+          <t>Alton</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D135" s="5" t="n">
@@ -9371,12 +9865,12 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Banstead</t>
+          <t>Amersham</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D136" s="3" t="n">
@@ -9395,12 +9889,12 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Barry</t>
+          <t>Ballyclare</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Wales South - Cardiff &amp; Vale</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D137" s="5" t="n">
@@ -9419,12 +9913,12 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Basingstoke</t>
+          <t>Ballymena</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D138" s="3" t="n">
@@ -9443,12 +9937,12 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Batley</t>
+          <t>Barry</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Wales South - Cardiff &amp; Vale</t>
         </is>
       </c>
       <c r="D139" s="5" t="n">
@@ -9467,12 +9961,12 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Basingstoke</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D140" s="3" t="n">
@@ -9491,12 +9985,12 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Berkhamsted</t>
+          <t>Batley</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D141" s="5" t="n">
@@ -9515,12 +10009,12 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Bicester</t>
+          <t>Berkhamsted</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D142" s="3" t="n">
@@ -9539,12 +10033,12 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Bingley</t>
+          <t>Bicester</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D143" s="5" t="n">
@@ -9563,12 +10057,12 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Bishop Auckland</t>
+          <t>Bingley</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D144" s="3" t="n">
@@ -9587,12 +10081,12 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Bishop's Stortford</t>
+          <t>Bishop Auckland</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D145" s="5" t="n">
@@ -9611,12 +10105,12 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Bognor Regis</t>
+          <t>Bishop's Stortford</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D146" s="3" t="n">
@@ -9635,12 +10129,12 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Bognor Regis</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D147" s="5" t="n">
@@ -9659,12 +10153,12 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Brentwood</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D148" s="3" t="n">
@@ -9683,7 +10177,7 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Bridport</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
@@ -9707,12 +10201,12 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Brinsworth</t>
+          <t>Brentwood</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D150" s="3" t="n">
@@ -9731,12 +10225,12 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Bury St Edmunds</t>
+          <t>Bridport</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D151" s="5" t="n">
@@ -9755,12 +10249,12 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Cannock</t>
+          <t>Brinsworth</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D152" s="3" t="n">
@@ -9779,12 +10273,12 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Canterbury</t>
+          <t>Buckingham</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D153" s="5" t="n">
@@ -9803,12 +10297,12 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Cheadle</t>
+          <t>Bury St Edmunds</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D154" s="3" t="n">
@@ -9827,12 +10321,12 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Chelmsley Wood</t>
+          <t>Cannock</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D155" s="5" t="n">
@@ -9851,12 +10345,12 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Chertsey</t>
+          <t>Canterbury</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D156" s="3" t="n">
@@ -9875,12 +10369,12 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>Chesham</t>
+          <t>Cheadle</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D157" s="5" t="n">
@@ -9899,12 +10393,12 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Chertsey</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Derbyshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D158" s="3" t="n">
@@ -9923,12 +10417,12 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>Chichester</t>
+          <t>Chesham</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D159" s="5" t="n">
@@ -9947,12 +10441,12 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Cirencester</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Derbyshire</t>
         </is>
       </c>
       <c r="D160" s="3" t="n">
@@ -9971,12 +10465,12 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Cleethorpes</t>
+          <t>Chichester</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D161" s="5" t="n">
@@ -9995,12 +10489,12 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Cobham</t>
+          <t>Cirencester</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D162" s="3" t="n">
@@ -10019,12 +10513,12 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>Congleton</t>
+          <t>Cleethorpes</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D163" s="5" t="n">
@@ -10043,12 +10537,12 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Congresbury</t>
+          <t>Colchester</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D164" s="3" t="n">
@@ -10067,12 +10561,12 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Corby</t>
+          <t>Congresbury</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D165" s="5" t="n">
@@ -10091,12 +10585,12 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Cottingham</t>
+          <t>Corby</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - East</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D166" s="3" t="n">
@@ -10115,12 +10609,12 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Cranbrook</t>
+          <t>Cottingham</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Yorkshire - East</t>
         </is>
       </c>
       <c r="D167" s="5" t="n">
@@ -10139,12 +10633,12 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Darlington</t>
+          <t>Cramlington</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D168" s="3" t="n">
@@ -10163,7 +10657,7 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Dartford</t>
+          <t>Cranbrook</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
@@ -10187,12 +10681,12 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Dewsbury</t>
+          <t>Dartford</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D170" s="3" t="n">
@@ -10211,12 +10705,12 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Dorchester</t>
+          <t>Droitwich</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Worcestershire</t>
         </is>
       </c>
       <c r="D171" s="5" t="n">
@@ -10235,12 +10729,12 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Droitwich</t>
+          <t>Dudley</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Worcestershire</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D172" s="3" t="n">
@@ -10259,12 +10753,12 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Dudley</t>
+          <t>Fakenham</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D173" s="5" t="n">
@@ -10283,12 +10777,12 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Fakenham</t>
+          <t>Falmouth</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D174" s="3" t="n">
@@ -10307,12 +10801,12 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Falmouth</t>
+          <t>Farnham</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D175" s="5" t="n">
@@ -10331,12 +10825,12 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Farnham</t>
+          <t>Faversham</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D176" s="3" t="n">
@@ -10427,12 +10921,12 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Freshwater</t>
+          <t>Frome</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D180" s="3" t="n">
@@ -10451,12 +10945,12 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Frodsham</t>
+          <t>Godalming</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D181" s="5" t="n">
@@ -10475,12 +10969,12 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Frome</t>
+          <t>Gosport</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D182" s="3" t="n">
@@ -10499,12 +10993,12 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Godalming</t>
+          <t>Great Yarmouth</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D183" s="5" t="n">
@@ -10523,12 +11017,12 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Gosport</t>
+          <t>Guildford</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D184" s="3" t="n">
@@ -10547,12 +11041,12 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Grantham</t>
+          <t>Hailsham</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D185" s="5" t="n">
@@ -10571,12 +11065,12 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Great Yarmouth</t>
+          <t>Harlow</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D186" s="3" t="n">
@@ -10595,12 +11089,12 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Guildford</t>
+          <t>Hartlepool</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D187" s="5" t="n">
@@ -10619,12 +11113,12 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Hailsham</t>
+          <t>Havant</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D188" s="3" t="n">
@@ -10643,12 +11137,12 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Harlow</t>
+          <t>Henley-on-thames</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D189" s="5" t="n">
@@ -10667,12 +11161,12 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Hartlepool</t>
+          <t>Horley</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D190" s="3" t="n">
@@ -10691,12 +11185,12 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Havant</t>
+          <t>Horsham</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D191" s="5" t="n">
@@ -10715,12 +11209,12 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Horley</t>
+          <t>Hove</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D192" s="3" t="n">
@@ -10739,12 +11233,12 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Horsham</t>
+          <t>Keighley</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D193" s="5" t="n">
@@ -10763,12 +11257,12 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Hove</t>
+          <t>Kenilworth</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D194" s="3" t="n">
@@ -10787,12 +11281,12 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Keighley</t>
+          <t>Kings Langley</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D195" s="5" t="n">
@@ -10811,12 +11305,12 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Kenilworth</t>
+          <t>Knowle</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D196" s="3" t="n">
@@ -10835,12 +11329,12 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Kings Langley</t>
+          <t>Leamington Spa</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D197" s="5" t="n">
@@ -10859,12 +11353,12 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Knaphill</t>
+          <t>Lisburn</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D198" s="3" t="n">
@@ -10883,12 +11377,12 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Knowle</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Scotland Central - Edinburgh &amp; Lothians</t>
         </is>
       </c>
       <c r="D199" s="5" t="n">
@@ -10907,12 +11401,12 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Leamington Spa</t>
+          <t>Loughborough</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D200" s="3" t="n">
@@ -10931,12 +11425,12 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Luton</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D201" s="5" t="n">
@@ -10955,12 +11449,12 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Lisburn</t>
+          <t>Maidenhead</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D202" s="3" t="n">
@@ -10979,12 +11473,12 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Mansfield</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>Scotland Central - Edinburgh &amp; Lothians</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D203" s="5" t="n">
@@ -11003,12 +11497,12 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Loughborough</t>
+          <t>Marlborough</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D204" s="3" t="n">
@@ -11027,12 +11521,12 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Luton</t>
+          <t>Marlow</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D205" s="5" t="n">
@@ -11051,12 +11545,12 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Maidenhead</t>
+          <t>Montrose</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D206" s="3" t="n">
@@ -11075,12 +11569,12 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Mansfield</t>
+          <t>Nantwich</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>Nottinghamshire</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D207" s="5" t="n">
@@ -11099,12 +11593,12 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Marlborough</t>
+          <t>Newbury</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D208" s="3" t="n">
@@ -11123,12 +11617,12 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Marlow</t>
+          <t>Normanton</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D209" s="5" t="n">
@@ -11147,12 +11641,12 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Nantwich</t>
+          <t>Northampton</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D210" s="3" t="n">
@@ -11171,12 +11665,12 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Newbury</t>
+          <t>Northwich</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D211" s="5" t="n">
@@ -11195,12 +11689,12 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Newtownabbey</t>
+          <t>Okehampton</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D212" s="3" t="n">
@@ -11219,7 +11713,7 @@
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>Normanton</t>
+          <t>Otley</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
@@ -11243,12 +11737,12 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>North Shields</t>
+          <t>Oxted</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D214" s="3" t="n">
@@ -11267,12 +11761,12 @@
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>Northampton</t>
+          <t>Peterlee</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D215" s="5" t="n">
@@ -11291,12 +11785,12 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Northwich</t>
+          <t>Pickering</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D216" s="3" t="n">
@@ -11315,7 +11809,7 @@
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>Okehampton</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
@@ -11339,12 +11833,12 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Otley</t>
+          <t>Pontypridd</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Wales South - Valleys</t>
         </is>
       </c>
       <c r="D218" s="3" t="n">
@@ -11363,12 +11857,12 @@
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>Oxted</t>
+          <t>Poole</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D219" s="5" t="n">
@@ -11387,12 +11881,12 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Peterlee</t>
+          <t>Portishead</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D220" s="3" t="n">
@@ -11411,12 +11905,12 @@
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Pickering</t>
+          <t>Potters Bar</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D221" s="5" t="n">
@@ -11435,12 +11929,12 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Pudsey</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D222" s="3" t="n">
@@ -11459,12 +11953,12 @@
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>Poole</t>
+          <t>Ramsgate</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D223" s="5" t="n">
@@ -11483,12 +11977,12 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>Portishead</t>
+          <t>Redruth</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D224" s="3" t="n">
@@ -11507,12 +12001,12 @@
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>Potters Bar</t>
+          <t>Ripon</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D225" s="5" t="n">
@@ -11531,12 +12025,12 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>Prudhoe</t>
+          <t>Rochester</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D226" s="3" t="n">
@@ -11555,12 +12049,12 @@
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>Ramsgate</t>
+          <t>Royston</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D227" s="5" t="n">
@@ -11579,12 +12073,12 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>Redruth</t>
+          <t>Rugby</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D228" s="3" t="n">
@@ -11603,12 +12097,12 @@
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>Ripon</t>
+          <t>Runcorn</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Cheshire - Warrington &amp; Halton</t>
         </is>
       </c>
       <c r="D229" s="5" t="n">
@@ -11627,12 +12121,12 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>Rochester</t>
+          <t>Rushden</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D230" s="3" t="n">
@@ -11651,12 +12145,12 @@
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>Royston</t>
+          <t>Ryton</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D231" s="5" t="n">
@@ -11675,12 +12169,12 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Rugby</t>
+          <t>Salisbury</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D232" s="3" t="n">
@@ -11699,12 +12193,12 @@
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>Runcorn</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - Warrington &amp; Halton</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D233" s="5" t="n">
@@ -11723,12 +12217,12 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Rushden</t>
+          <t>Scunthorpe</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D234" s="3" t="n">
@@ -11747,12 +12241,12 @@
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>Ryton</t>
+          <t>Shepperton</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D235" s="5" t="n">
@@ -11771,12 +12265,12 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Sale</t>
+          <t>Sherborne</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D236" s="3" t="n">
@@ -11795,12 +12289,12 @@
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>Salisbury</t>
+          <t>Shrewsbury</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Shropshire</t>
         </is>
       </c>
       <c r="D237" s="5" t="n">
@@ -11819,12 +12313,12 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>Sandy</t>
+          <t>Snodland</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D238" s="3" t="n">
@@ -11843,12 +12337,12 @@
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>Scunthorpe</t>
+          <t>Southam</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D239" s="5" t="n">
@@ -11867,12 +12361,12 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Sevenoaks</t>
+          <t>Southend-on-sea</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D240" s="3" t="n">
@@ -11891,12 +12385,12 @@
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>Shepperton</t>
+          <t>Spalding</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D241" s="5" t="n">
@@ -11915,12 +12409,12 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>Shirley</t>
+          <t>St. Ives</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D242" s="3" t="n">
@@ -11939,12 +12433,12 @@
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>Shrewsbury</t>
+          <t>St. Neots</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>Shropshire</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D243" s="5" t="n">
@@ -11963,12 +12457,12 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>Snodland</t>
+          <t>Stanley</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D244" s="3" t="n">
@@ -11987,12 +12481,12 @@
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>Southam</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D245" s="5" t="n">
@@ -12011,12 +12505,12 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>Southend-on-sea</t>
+          <t>Stratford-upon-avon</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D246" s="3" t="n">
@@ -12035,12 +12529,12 @@
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>Spalding</t>
+          <t>Stretford</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D247" s="5" t="n">
@@ -12059,12 +12553,12 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>St. Ives</t>
+          <t>Stroud</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D248" s="3" t="n">
@@ -12083,12 +12577,12 @@
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>St. Neots</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D249" s="5" t="n">
@@ -12107,12 +12601,12 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>Stanley</t>
+          <t>Tadworth</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D250" s="3" t="n">
@@ -12131,12 +12625,12 @@
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Tamworth</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D251" s="5" t="n">
@@ -12155,12 +12649,12 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>Stone</t>
+          <t>Taunton</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D252" s="3" t="n">
@@ -12179,12 +12673,12 @@
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>Stratford-upon-avon</t>
+          <t>Telford</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Shropshire</t>
         </is>
       </c>
       <c r="D253" s="5" t="n">
@@ -12203,12 +12697,12 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Stretford</t>
+          <t>Thatcham</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D254" s="3" t="n">
@@ -12227,12 +12721,12 @@
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>Stroud</t>
+          <t>Thetford</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D255" s="5" t="n">
@@ -12251,12 +12745,12 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>Sunbury-on-thames</t>
+          <t>Truro</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D256" s="3" t="n">
@@ -12275,12 +12769,12 @@
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>Tadworth</t>
+          <t>Tunbridge Wells</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D257" s="5" t="n">
@@ -12299,12 +12793,12 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>Tamworth</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D258" s="3" t="n">
@@ -12323,12 +12817,12 @@
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>Taunton</t>
+          <t>Walton-on-thames</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D259" s="5" t="n">
@@ -12347,12 +12841,12 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>Telford</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Shropshire</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D260" s="3" t="n">
@@ -12371,12 +12865,12 @@
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>Thame</t>
+          <t>Wellington</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Shropshire</t>
         </is>
       </c>
       <c r="D261" s="5" t="n">
@@ -12395,12 +12889,12 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>Thatcham</t>
+          <t>Welwyn Garden City</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D262" s="3" t="n">
@@ -12419,12 +12913,12 @@
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>Thetford</t>
+          <t>West Malling</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D263" s="5" t="n">
@@ -12443,12 +12937,12 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>Torquay</t>
+          <t>Whitby</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D264" s="3" t="n">
@@ -12467,12 +12961,12 @@
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>Trowbridge</t>
+          <t>Whitstable</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D265" s="5" t="n">
@@ -12491,12 +12985,12 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>Truro</t>
+          <t>Wilmslow</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D266" s="3" t="n">
@@ -12515,12 +13009,12 @@
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>Tunbridge Wells</t>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D267" s="5" t="n">
@@ -12539,12 +13033,12 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>Uttoxeter</t>
+          <t>Winsford</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D268" s="3" t="n">
@@ -12563,12 +13057,12 @@
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Wokingham</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D269" s="5" t="n">
@@ -12587,12 +13081,12 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>Walton-on-thames</t>
+          <t>Woodbridge</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D270" s="3" t="n">
@@ -12611,12 +13105,12 @@
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Worthing</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D271" s="5" t="n">
@@ -12635,12 +13129,12 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>Wellington</t>
+          <t>Yeovil</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>Shropshire</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D272" s="3" t="n">
@@ -12651,224 +13145,8 @@
       </c>
       <c r="F272" s="2" t="inlineStr"/>
     </row>
-    <row r="273">
-      <c r="A273" s="4" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B273" s="4" t="inlineStr">
-        <is>
-          <t>Welwyn Garden City</t>
-        </is>
-      </c>
-      <c r="C273" s="4" t="inlineStr">
-        <is>
-          <t>Hertfordshire</t>
-        </is>
-      </c>
-      <c r="D273" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E273" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F273" s="4" t="inlineStr"/>
-    </row>
-    <row r="274">
-      <c r="A274" s="2" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B274" s="2" t="inlineStr">
-        <is>
-          <t>West Malling</t>
-        </is>
-      </c>
-      <c r="C274" s="2" t="inlineStr">
-        <is>
-          <t>Kent</t>
-        </is>
-      </c>
-      <c r="D274" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E274" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F274" s="2" t="inlineStr"/>
-    </row>
-    <row r="275">
-      <c r="A275" s="4" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B275" s="4" t="inlineStr">
-        <is>
-          <t>Whitby</t>
-        </is>
-      </c>
-      <c r="C275" s="4" t="inlineStr">
-        <is>
-          <t>Yorkshire - North</t>
-        </is>
-      </c>
-      <c r="D275" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E275" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F275" s="4" t="inlineStr"/>
-    </row>
-    <row r="276">
-      <c r="A276" s="2" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B276" s="2" t="inlineStr">
-        <is>
-          <t>Whitstable</t>
-        </is>
-      </c>
-      <c r="C276" s="2" t="inlineStr">
-        <is>
-          <t>Kent</t>
-        </is>
-      </c>
-      <c r="D276" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E276" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F276" s="2" t="inlineStr"/>
-    </row>
-    <row r="277">
-      <c r="A277" s="4" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B277" s="4" t="inlineStr">
-        <is>
-          <t>Wilmslow</t>
-        </is>
-      </c>
-      <c r="C277" s="4" t="inlineStr">
-        <is>
-          <t>Cheshire - East</t>
-        </is>
-      </c>
-      <c r="D277" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E277" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F277" s="4" t="inlineStr"/>
-    </row>
-    <row r="278">
-      <c r="A278" s="2" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B278" s="2" t="inlineStr">
-        <is>
-          <t>Windsor</t>
-        </is>
-      </c>
-      <c r="C278" s="2" t="inlineStr">
-        <is>
-          <t>Berkshire</t>
-        </is>
-      </c>
-      <c r="D278" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E278" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F278" s="2" t="inlineStr"/>
-    </row>
-    <row r="279">
-      <c r="A279" s="4" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B279" s="4" t="inlineStr">
-        <is>
-          <t>Winsford</t>
-        </is>
-      </c>
-      <c r="C279" s="4" t="inlineStr">
-        <is>
-          <t>Cheshire - West</t>
-        </is>
-      </c>
-      <c r="D279" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E279" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F279" s="4" t="inlineStr"/>
-    </row>
-    <row r="280">
-      <c r="A280" s="2" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B280" s="2" t="inlineStr">
-        <is>
-          <t>Wokingham</t>
-        </is>
-      </c>
-      <c r="C280" s="2" t="inlineStr">
-        <is>
-          <t>Berkshire</t>
-        </is>
-      </c>
-      <c r="D280" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E280" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F280" s="2" t="inlineStr"/>
-    </row>
-    <row r="281">
-      <c r="A281" s="4" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B281" s="4" t="inlineStr">
-        <is>
-          <t>Yeovil</t>
-        </is>
-      </c>
-      <c r="C281" s="4" t="inlineStr">
-        <is>
-          <t>Somerset</t>
-        </is>
-      </c>
-      <c r="D281" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E281" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F281" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F281"/>
+  <autoFilter ref="A1:F272"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12947,7 +13225,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr"/>
@@ -12968,15 +13246,15 @@
       </c>
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" s="4" t="inlineStr"/>
       <c r="F3" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
       <c r="H3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" s="4" t="inlineStr"/>
     </row>
@@ -12987,7 +13265,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="3" t="n">
@@ -13012,7 +13290,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
       <c r="D5" s="4" t="inlineStr"/>
@@ -13022,10 +13300,8 @@
       </c>
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
+      <c r="I5" s="5" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -13035,15 +13311,13 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
+      <c r="F6" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr"/>
@@ -13056,7 +13330,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr"/>
@@ -13079,10 +13353,8 @@
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
+      <c r="G8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr"/>
@@ -13099,10 +13371,8 @@
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr"/>
       <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
+      <c r="F9" s="5" t="n">
+        <v>7</v>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="4" t="inlineStr"/>
@@ -13179,7 +13449,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr"/>
@@ -13196,7 +13466,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
       <c r="D15" s="4" t="inlineStr"/>
@@ -13217,7 +13487,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr"/>
@@ -13234,17 +13504,15 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
       <c r="D17" s="4" t="inlineStr"/>
       <c r="E17" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>7</v>
       </c>
       <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="4" t="inlineStr"/>
@@ -13257,13 +13525,13 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
@@ -13280,19 +13548,19 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
       <c r="D19" s="5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" s="4" t="inlineStr"/>
     </row>
@@ -13355,7 +13623,7 @@
         <v>73</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D23" s="4" t="inlineStr"/>
       <c r="E23" s="4" t="inlineStr"/>
@@ -13363,7 +13631,7 @@
       <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="4" t="inlineStr"/>
       <c r="I23" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -13388,7 +13656,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
       <c r="D25" s="5" t="n">
@@ -13396,7 +13664,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr"/>
       <c r="F25" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G25" s="4" t="inlineStr"/>
       <c r="H25" s="4" t="inlineStr"/>
@@ -13409,13 +13677,13 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="3" t="n">
@@ -13507,7 +13775,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="inlineStr"/>
@@ -13524,7 +13792,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C33" s="4" t="inlineStr"/>
       <c r="D33" s="4" t="inlineStr"/>
@@ -13541,24 +13809,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>14</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>19</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>68</v>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
+        <v>60</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>7</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>14</v>
@@ -13574,15 +13840,13 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
       <c r="D35" s="4" t="inlineStr"/>
       <c r="E35" s="4" t="inlineStr"/>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
+      <c r="F35" s="5" t="n">
+        <v>8</v>
       </c>
       <c r="G35" s="4" t="inlineStr"/>
       <c r="H35" s="4" t="inlineStr"/>
@@ -13640,7 +13904,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C39" s="4" t="inlineStr"/>
       <c r="D39" s="4" t="inlineStr"/>
@@ -13661,30 +13925,26 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>143</v>
+        <v>102</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F40" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>CHECK</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
-      </c>
       <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
+      <c r="I40" s="3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="41">
@@ -13693,10 +13953,8 @@
           <t>North Scotland</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
+      <c r="B41" s="5" t="n">
+        <v>5</v>
       </c>
       <c r="C41" s="4" t="inlineStr"/>
       <c r="D41" s="4" t="inlineStr"/>
@@ -13760,7 +14018,7 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C45" s="4" t="inlineStr"/>
       <c r="D45" s="4" t="inlineStr"/>
@@ -13815,15 +14073,15 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr"/>
@@ -13866,7 +14124,7 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C51" s="4" t="inlineStr"/>
       <c r="D51" s="4" t="inlineStr"/>
@@ -13912,10 +14170,8 @@
           <t>Scotland Central - Tayside</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="C54" s="2" t="inlineStr"/>
       <c r="D54" s="2" t="inlineStr"/>
@@ -13947,11 +14203,11 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C56" s="2" t="inlineStr"/>
       <c r="D56" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr"/>
@@ -13996,7 +14252,7 @@
         </is>
       </c>
       <c r="B59" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C59" s="4" t="inlineStr"/>
       <c r="D59" s="4" t="inlineStr"/>
@@ -14017,7 +14273,7 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C60" s="2" t="inlineStr"/>
       <c r="D60" s="2" t="inlineStr"/>
@@ -14034,7 +14290,7 @@
         </is>
       </c>
       <c r="B61" s="5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C61" s="4" t="inlineStr"/>
       <c r="D61" s="4" t="inlineStr"/>
@@ -14043,7 +14299,7 @@
       <c r="G61" s="4" t="inlineStr"/>
       <c r="H61" s="4" t="inlineStr"/>
       <c r="I61" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -14053,7 +14309,7 @@
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C62" s="2" t="inlineStr"/>
       <c r="D62" s="2" t="inlineStr"/>
@@ -14072,13 +14328,13 @@
         </is>
       </c>
       <c r="B63" s="5" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E63" s="4" t="inlineStr"/>
       <c r="F63" s="5" t="n">
@@ -14087,7 +14343,7 @@
       <c r="G63" s="4" t="inlineStr"/>
       <c r="H63" s="4" t="inlineStr"/>
       <c r="I63" s="5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64">
@@ -14097,21 +14353,19 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C64" s="3" t="n">
         <v>4</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
+      <c r="H64" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
     </row>
@@ -14152,7 +14406,7 @@
         </is>
       </c>
       <c r="B67" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C67" s="4" t="inlineStr"/>
       <c r="D67" s="4" t="inlineStr"/>
@@ -14198,10 +14452,8 @@
           <t>Wales South - Valleys</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="C70" s="2" t="inlineStr"/>
       <c r="D70" s="2" t="inlineStr"/>
@@ -14218,17 +14470,17 @@
         </is>
       </c>
       <c r="B71" s="5" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C71" s="4" t="inlineStr"/>
       <c r="D71" s="4" t="inlineStr"/>
       <c r="E71" s="4" t="inlineStr"/>
       <c r="F71" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G71" s="4" t="inlineStr"/>
       <c r="H71" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I71" s="4" t="inlineStr"/>
     </row>
@@ -14256,7 +14508,7 @@
         </is>
       </c>
       <c r="B73" s="5" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C73" s="4" t="inlineStr"/>
       <c r="D73" s="4" t="inlineStr"/>
@@ -14276,7 +14528,7 @@
         <v>11</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D74" s="2" t="inlineStr"/>
       <c r="E74" s="2" t="inlineStr"/>
@@ -14326,7 +14578,7 @@
         </is>
       </c>
       <c r="B77" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C77" s="4" t="inlineStr"/>
       <c r="D77" s="4" t="inlineStr"/>
@@ -14347,7 +14599,7 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
@@ -14368,7 +14620,7 @@
         </is>
       </c>
       <c r="B79" s="5" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C79" s="5" t="n">
         <v>2</v>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1799</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="3">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="5">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1877</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="6">
@@ -6629,12 +6629,12 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Gateshead</t>
+          <t>Norwich</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -6653,16 +6653,16 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Norwich</t>
+          <t>Chester</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
@@ -6677,12 +6677,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Chester</t>
+          <t>Durham</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Durham</t>
+          <t>Gateshead</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -13925,7 +13925,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>2</v>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -645,10 +645,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2540</v>
+        <v>2551</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="3">
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1692</v>
+        <v>1679</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
@@ -671,10 +671,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1297</v>
+        <v>1324</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>699</v>
+        <v>705</v>
       </c>
     </row>
     <row r="5">
@@ -684,10 +684,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6">
@@ -697,10 +697,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>467</v>
+        <v>447</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
@@ -726,33 +726,33 @@
         <v>423</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Retail &amp; Consumer Products</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Retail &amp; Consumer Products</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
@@ -762,10 +762,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>11</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>8</v>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>22</v>
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C15" s="8" t="inlineStr"/>
     </row>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>8</v>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C17" s="8" t="inlineStr"/>
     </row>
@@ -852,7 +852,7 @@
         <v>10000</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>1470</v>
+        <v>1467</v>
       </c>
     </row>
   </sheetData>
@@ -14765,7 +14765,7 @@
       <c r="B3" s="14" t="inlineStr"/>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>3 / 3.0 / 3/14</t>
+          <t>2 / 2.9 / 3/14</t>
         </is>
       </c>
       <c r="D3" s="14" t="inlineStr"/>
@@ -14848,7 +14848,7 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/11</t>
+          <t>0 / 0.7 / 0/11</t>
         </is>
       </c>
       <c r="I5" s="14" t="inlineStr"/>
@@ -15027,7 +15027,7 @@
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.9 / 0/14</t>
+          <t>1 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.9 / 0/8</t>
+          <t>1 / 1.8 / 0/8</t>
         </is>
       </c>
     </row>
@@ -15245,28 +15245,28 @@
       <c r="B15" s="14" t="inlineStr"/>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>3 / 0.8 / 0/14</t>
+          <t>2 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>6 / 3.7 / 2/14</t>
+          <t>7 / 3.8 / 2/14</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.1 / 0/12</t>
+          <t>1 / 2.0 / 0/12</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>6 / 2.3 / 3/12</t>
+          <t>5 / 2.2 / 2/12</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr"/>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/11</t>
+          <t>0 / 1.0 / 0/11</t>
         </is>
       </c>
       <c r="I15" s="14" t="inlineStr">
@@ -15299,7 +15299,7 @@
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.6 / 0/12</t>
+          <t>1 / 1.5 / 0/12</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
@@ -15349,7 +15349,7 @@
       </c>
       <c r="I17" s="14" t="inlineStr">
         <is>
-          <t>5 / 3.0 / 0/8</t>
+          <t>4 / 2.9 / 0/8</t>
         </is>
       </c>
     </row>
@@ -15362,7 +15362,7 @@
       <c r="B18" s="13" t="inlineStr"/>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
@@ -15403,7 +15403,7 @@
       <c r="D19" s="14" t="inlineStr"/>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>5 / 4.0 / 2/12</t>
+          <t>6 / 4.1 / 3/12</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr"/>
@@ -15427,7 +15427,7 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.9 / 1/14</t>
+          <t>3 / 3.0 / 1/14</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
@@ -15505,7 +15505,7 @@
       </c>
       <c r="I21" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.5 / 0/8</t>
+          <t>2 / 1.4 / 0/8</t>
         </is>
       </c>
     </row>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/12</t>
+          <t>0 / 0.4 / 0/12</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
@@ -15562,22 +15562,22 @@
       <c r="C23" s="14" t="inlineStr"/>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>13 / 8.6 / 10/14</t>
+          <t>14 / 8.7 / 10/14</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.2 / 0/12</t>
+          <t>1 / 1.3 / 0/12</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>12 / 6.4 / 5/12</t>
+          <t>8 / 6.1 / 5/12</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.3 / 0/9</t>
+          <t>1 / 2.2 / 0/9</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
@@ -15600,7 +15600,7 @@
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="D24" s="13" t="inlineStr">
@@ -15649,7 +15649,7 @@
       <c r="D25" s="14" t="inlineStr"/>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.4 / 0/12</t>
+          <t>1 / 1.5 / 0/12</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr"/>
@@ -15775,7 +15775,7 @@
       </c>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/12</t>
+          <t>1 / 0.1 / 0/12</t>
         </is>
       </c>
       <c r="G28" s="13" t="inlineStr">
@@ -15812,7 +15812,7 @@
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>1 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
@@ -15959,12 +15959,12 @@
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/12</t>
+          <t>2 / 1.1 / 0/12</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.7 / 1/9</t>
+          <t>3 / 2.8 / 1/9</t>
         </is>
       </c>
       <c r="H32" s="13" t="inlineStr">
@@ -16197,7 +16197,7 @@
       </c>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.8 / 0/12</t>
+          <t>1 / 0.8 / 0/12</t>
         </is>
       </c>
       <c r="G38" s="13" t="inlineStr">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>2 / 3.4 / 2/9</t>
+          <t>1 / 3.3 / 2/9</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
@@ -16339,7 +16339,7 @@
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/13</t>
+          <t>1 / 1.5 / 0/13</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -16349,12 +16349,12 @@
       </c>
       <c r="F42" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/12</t>
+          <t>2 / 0.7 / 0/12</t>
         </is>
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.3 / 0/9</t>
+          <t>2 / 1.4 / 0/9</t>
         </is>
       </c>
       <c r="H42" s="13" t="inlineStr">
@@ -16376,7 +16376,7 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.1 / 0/13</t>
+          <t>4 / 2.2 / 0/13</t>
         </is>
       </c>
       <c r="C43" s="14" t="inlineStr">
@@ -16424,12 +16424,12 @@
       <c r="B44" s="13" t="inlineStr"/>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/14</t>
+          <t>1 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>10 / 4.9 / 4/14</t>
+          <t>9 / 4.8 / 4/14</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -16467,7 +16467,7 @@
       <c r="B45" s="14" t="inlineStr"/>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.7 / 0/13</t>
+          <t>0 / 1.5 / 0/13</t>
         </is>
       </c>
       <c r="D45" s="14" t="inlineStr">
@@ -16477,23 +16477,23 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>9 / 2.1 / 1/12</t>
+          <t>12 / 2.3 / 1/12</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/12</t>
+          <t>2 / 0.2 / 0/12</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr"/>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>3 / 0.5 / 0/11</t>
+          <t>6 / 0.8 / 1/11</t>
         </is>
       </c>
       <c r="I45" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.2 / 0/8</t>
+          <t>2 / 1.1 / 0/8</t>
         </is>
       </c>
     </row>
@@ -16530,7 +16530,7 @@
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/9</t>
+          <t>0 / 0.2 / 0/9</t>
         </is>
       </c>
       <c r="H46" s="13" t="inlineStr">
@@ -16598,7 +16598,7 @@
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.8 / 0/12</t>
+          <t>1 / 1.7 / 0/12</t>
         </is>
       </c>
       <c r="F48" s="13" t="inlineStr"/>
@@ -16888,7 +16888,7 @@
       </c>
       <c r="I54" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/8</t>
+          <t>0 / 0.4 / 0/8</t>
         </is>
       </c>
     </row>
@@ -17120,12 +17120,12 @@
       <c r="B60" s="13" t="inlineStr"/>
       <c r="C60" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.3 / 3/14</t>
+          <t>0 / 3.1 / 3/14</t>
         </is>
       </c>
       <c r="D60" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.7 / 0/14</t>
+          <t>4 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
@@ -17168,7 +17168,7 @@
       </c>
       <c r="D61" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.4 / 0/14</t>
+          <t>3 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="E61" s="14" t="inlineStr">
@@ -17178,7 +17178,7 @@
       </c>
       <c r="F61" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.4 / 0/12</t>
+          <t>3 / 1.5 / 0/12</t>
         </is>
       </c>
       <c r="G61" s="14" t="inlineStr">
@@ -17207,7 +17207,7 @@
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.9 / 0/14</t>
+          <t>2 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr"/>
@@ -17275,7 +17275,7 @@
       </c>
       <c r="F64" s="13" t="inlineStr">
         <is>
-          <t>5 / 3.1 / 0/12</t>
+          <t>3 / 2.9 / 0/12</t>
         </is>
       </c>
       <c r="G64" s="13" t="inlineStr">
@@ -17398,7 +17398,7 @@
       </c>
       <c r="D67" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.0 / 0/13</t>
+          <t>4 / 2.1 / 0/13</t>
         </is>
       </c>
       <c r="E67" s="14" t="inlineStr">
@@ -17578,7 +17578,7 @@
       </c>
       <c r="D71" s="14" t="inlineStr">
         <is>
-          <t>11 / 5.4 / 4/14</t>
+          <t>10 / 5.3 / 4/14</t>
         </is>
       </c>
       <c r="E71" s="14" t="inlineStr">
@@ -17700,12 +17700,12 @@
       </c>
       <c r="E74" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.2 / 0/12</t>
+          <t>3 / 3.2 / 0/12</t>
         </is>
       </c>
       <c r="F74" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.2 / 0/12</t>
+          <t>1 / 1.2 / 0/12</t>
         </is>
       </c>
       <c r="G74" s="13" t="inlineStr">
@@ -17763,7 +17763,7 @@
       </c>
       <c r="I75" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.9 / 0/8</t>
+          <t>1 / 0.8 / 0/8</t>
         </is>
       </c>
     </row>
@@ -17834,7 +17834,7 @@
       </c>
       <c r="F77" s="14" t="inlineStr">
         <is>
-          <t>9 / 4.7 / 4/12</t>
+          <t>8 / 4.6 / 4/12</t>
         </is>
       </c>
       <c r="G77" s="14" t="inlineStr"/>
@@ -17859,7 +17859,7 @@
       <c r="C78" s="13" t="inlineStr"/>
       <c r="D78" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.4 / 0/14</t>
+          <t>4 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
@@ -17869,7 +17869,7 @@
       </c>
       <c r="F78" s="13" t="inlineStr">
         <is>
-          <t>5 / 2.8 / 1/12</t>
+          <t>6 / 2.8 / 2/12</t>
         </is>
       </c>
       <c r="G78" s="13" t="inlineStr">
@@ -17904,7 +17904,7 @@
       </c>
       <c r="F79" s="14" t="inlineStr">
         <is>
-          <t>18 / 8.4 / 6/12</t>
+          <t>19 / 8.5 / 6/12</t>
         </is>
       </c>
       <c r="G79" s="14" t="inlineStr"/>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sitewide'!$A$1:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'JobG8 categories'!$A$1:$C$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'PAGES'!$A$1:$H$150</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$F$272</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$F$267</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'LIVE'!$A$1:$I$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'NOT LIVE'!$A$1:$I$79</definedName>
   </definedNames>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1798</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="3">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>328</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1876</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="6">
@@ -645,10 +645,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2551</v>
+        <v>2478</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>313</v>
+        <v>308</v>
       </c>
     </row>
     <row r="3">
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1679</v>
+        <v>1694</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -671,10 +671,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1324</v>
+        <v>1356</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>705</v>
+        <v>714</v>
       </c>
     </row>
     <row r="5">
@@ -684,10 +684,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
@@ -697,10 +697,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>447</v>
+        <v>468</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -723,36 +723,36 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Retail &amp; Consumer Products</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Retail &amp; Consumer Products</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11">
@@ -762,10 +762,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>11</v>
@@ -784,27 +784,27 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Consulting &amp; Corporate Strategy</t>
+          <t>Insurance &amp; Superannuation</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Insurance &amp; Superannuation</t>
+          <t>Consulting &amp; Corporate Strategy</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -814,9 +814,11 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>178</v>
-      </c>
-      <c r="C15" s="8" t="inlineStr"/>
+        <v>180</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -825,7 +827,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>8</v>
@@ -838,7 +840,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C17" s="8" t="inlineStr"/>
     </row>
@@ -852,7 +854,7 @@
         <v>10000</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>1467</v>
+        <v>1464</v>
       </c>
     </row>
   </sheetData>
@@ -6506,7 +6508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F272"/>
+  <dimension ref="A1:F267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6614,7 +6616,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
@@ -6629,16 +6631,16 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Norwich</t>
+          <t>Chester</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>0</v>
@@ -6653,12 +6655,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Chester</t>
+          <t>Durham</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -6677,12 +6679,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Durham</t>
+          <t>Gateshead</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -6701,12 +6703,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Gateshead</t>
+          <t>Maidstone</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -6725,12 +6727,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Maidstone</t>
+          <t>Northallerton</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -6749,12 +6751,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Northallerton</t>
+          <t>Norwich</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -6869,12 +6871,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Chester Le Street</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -6893,12 +6895,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Hemel Hempstead</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Scotland Central - Tayside</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -6917,12 +6919,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Hemel Hempstead</t>
+          <t>High Wycombe</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -6941,12 +6943,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>High Wycombe</t>
+          <t>Scarborough</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -6965,12 +6967,12 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Nottingham</t>
+          <t>Swindon</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Nottinghamshire</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -6989,12 +6991,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Scarborough</t>
+          <t>Tonbridge</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -7008,50 +7010,58 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>CREATE</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Swindon</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>/manchester/service-administrator-jobs</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>CREATE</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Tonbridge</t>
+          <t>Newcastle</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>/newcastle/service-administrator-jobs</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -7061,23 +7071,23 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>/manchester/service-administrator-jobs</t>
+          <t>/birmingham/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7089,23 +7099,23 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Newcastle</t>
+          <t>Bristol</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>/newcastle/service-administrator-jobs</t>
+          <t>/bristol/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7117,23 +7127,23 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Bristol</t>
+          <t>Belfast</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>/bristol/service-administrator-jobs</t>
+          <t>/belfast/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7145,23 +7155,23 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Leeds</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>/birmingham/service-administrator-jobs</t>
+          <t>/leeds/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7173,23 +7183,23 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Belfast</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Merseyside - Liverpool</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E27" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>/belfast/service-administrator-jobs</t>
+          <t>/liverpool/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7201,23 +7211,23 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Hull</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Yorkshire - East</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>/leeds/service-administrator-jobs</t>
+          <t>/hull/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7229,23 +7239,23 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Glasgow</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Merseyside - Liverpool</t>
+          <t>Scotland West - Glasgow</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>/liverpool/service-administrator-jobs</t>
+          <t>/glasgow/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7257,23 +7267,23 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Hull</t>
+          <t>Bradford</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - East</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>/hull/service-administrator-jobs</t>
+          <t>/bradford/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7285,23 +7295,23 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Glasgow</t>
+          <t>Sheffield</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Scotland West - Glasgow</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E31" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>/glasgow/service-administrator-jobs</t>
+          <t>/sheffield/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7313,23 +7323,23 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Bradford</t>
+          <t>Cardiff</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Wales South - Cardiff &amp; Vale</t>
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>/bradford/service-administrator-jobs</t>
+          <t>/cardiff/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7341,23 +7351,23 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Sheffield</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>Scotland Central - Edinburgh &amp; Lothians</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>/sheffield/service-administrator-jobs</t>
+          <t>/edinburgh/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7369,23 +7379,23 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Cardiff</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Wales South - Cardiff &amp; Vale</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D34" s="3" t="n">
         <v>9</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>/cardiff/service-administrator-jobs</t>
+          <t>/southampton/service-administrator-jobs, /southampton/support-worker</t>
         </is>
       </c>
     </row>
@@ -7397,23 +7407,23 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Oxford</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Scotland Central - Edinburgh &amp; Lothians</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E35" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>/edinburgh/service-administrator-jobs</t>
+          <t>/oxford/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7425,23 +7435,23 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Oxford</t>
+          <t>Cambridge</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>/oxford/service-administrator-jobs</t>
+          <t>/cambridge/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7453,23 +7463,23 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Doncaster</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>/southampton/service-administrator-jobs, /southampton/support-worker</t>
+          <t>/doncaster/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7481,7 +7491,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Cambridge</t>
+          <t>Peterborough</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -7497,7 +7507,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>/cambridge/service-administrator-jobs</t>
+          <t>/peterborough/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7509,23 +7519,23 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Doncaster</t>
+          <t>York</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E39" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>/doncaster/service-administrator-jobs</t>
+          <t>/york/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7537,23 +7547,23 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Peterborough</t>
+          <t>Brighton &amp; Hove</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>/peterborough/service-administrator-jobs</t>
+          <t>/brighton-hove/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7565,23 +7575,23 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove</t>
+          <t>Warrington</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Cheshire - Warrington &amp; Halton</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E41" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>/brighton-hove/service-administrator-jobs</t>
+          <t>/warrington/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7593,23 +7603,23 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>York</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>/york/service-administrator-jobs</t>
+          <t>/coventry/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7621,23 +7631,23 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>Huddersfield</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E43" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>/coventry/service-administrator-jobs</t>
+          <t>/huddersfield/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7649,77 +7659,69 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Warrington</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Cheshire - Warrington &amp; Halton</t>
-        </is>
-      </c>
+          <t>Barnsley</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>/warrington/service-administrator-jobs</t>
+          <t>/barnsley/service-administrator-jobs</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>HOLD – LONDON</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Huddersfield</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>/huddersfield/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>HOLD – LONDON</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Barnsley</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr"/>
+          <t>Wandsworth</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
       <c r="D46" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>/barnsley/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -7729,7 +7731,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Borehamwood</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -7738,7 +7740,7 @@
         </is>
       </c>
       <c r="D47" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E47" s="5" t="n">
         <v>0</v>
@@ -7753,7 +7755,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Wandsworth</t>
+          <t>Croydon</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -7762,7 +7764,7 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
@@ -7777,7 +7779,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Borehamwood</t>
+          <t>Harrow</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -7801,7 +7803,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Croydon</t>
+          <t>Isleworth</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -7825,7 +7827,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Harrow</t>
+          <t>Uxbridge</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -7849,7 +7851,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Isleworth</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -7858,7 +7860,7 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E52" s="3" t="n">
         <v>0</v>
@@ -7873,7 +7875,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Uxbridge</t>
+          <t>Sutton</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -7882,7 +7884,7 @@
         </is>
       </c>
       <c r="D53" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53" s="5" t="n">
         <v>0</v>
@@ -7897,7 +7899,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -7906,7 +7908,7 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E54" s="3" t="n">
         <v>0</v>
@@ -7921,7 +7923,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Dagenham</t>
+          <t>Beckenham</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -7930,7 +7932,7 @@
         </is>
       </c>
       <c r="D55" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55" s="5" t="n">
         <v>0</v>
@@ -7945,7 +7947,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Sutton</t>
+          <t>Bushey</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -7954,7 +7956,7 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56" s="3" t="n">
         <v>0</v>
@@ -7969,7 +7971,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Carshalton</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -7993,7 +7995,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Beckenham</t>
+          <t>Chessington</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -8017,7 +8019,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Bushey</t>
+          <t>Dagenham</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -8041,7 +8043,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Carshalton</t>
+          <t>Enfield</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -8065,7 +8067,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Chessington</t>
+          <t>Hornchurch</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -8089,7 +8091,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Enfield</t>
+          <t>Ilford</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -8113,7 +8115,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Hornchurch</t>
+          <t>Islington</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -8137,7 +8139,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Ilford</t>
+          <t>Kingston Upon Thames</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -8161,7 +8163,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Islington</t>
+          <t>Lambeth</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -8185,7 +8187,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Kingston Upon Thames</t>
+          <t>Morden</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -8209,7 +8211,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Lambeth</t>
+          <t>Rainham</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -8233,7 +8235,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Morden</t>
+          <t>Sidcup</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -8257,7 +8259,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Rainham</t>
+          <t>Southall</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -8281,7 +8283,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Sidcup</t>
+          <t>Sutton-in-ashfield</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -8300,21 +8302,21 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>MONITOR</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Southall</t>
+          <t>Aylesbury</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D71" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E71" s="5" t="n">
         <v>0</v>
@@ -8324,21 +8326,21 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>MONITOR</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Sutton-in-ashfield</t>
+          <t>Chelmsford</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E72" s="3" t="n">
         <v>0</v>
@@ -8353,12 +8355,12 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Aylesbury</t>
+          <t>Chester Le Street</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D73" s="5" t="n">
@@ -8377,12 +8379,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Chelmsford</t>
+          <t>Crewe</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D74" s="3" t="n">
@@ -8401,12 +8403,12 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Crewe</t>
+          <t>Darlington</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D75" s="5" t="n">
@@ -8425,12 +8427,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Darlington</t>
+          <t>Eastleigh</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D76" s="3" t="n">
@@ -8449,12 +8451,12 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Eastleigh</t>
+          <t>Epsom</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D77" s="5" t="n">
@@ -8473,12 +8475,12 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Epsom</t>
+          <t>Fareham</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D78" s="3" t="n">
@@ -8497,12 +8499,12 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Exeter</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D79" s="5" t="n">
@@ -8521,12 +8523,12 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Fareham</t>
+          <t>Gloucester</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D80" s="3" t="n">
@@ -8545,12 +8547,12 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Harrogate</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D81" s="5" t="n">
@@ -8569,12 +8571,12 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Gloucester</t>
+          <t>Hastings</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D82" s="3" t="n">
@@ -8593,12 +8595,12 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Harrogate</t>
+          <t>Inverness</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D83" s="5" t="n">
@@ -8617,12 +8619,12 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Hastings</t>
+          <t>Leicester</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D84" s="3" t="n">
@@ -8641,12 +8643,12 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Inverness</t>
+          <t>Macclesfield</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D85" s="5" t="n">
@@ -8665,12 +8667,12 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Leicester</t>
+          <t>Milton Keynes</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D86" s="3" t="n">
@@ -8689,12 +8691,12 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Macclesfield</t>
+          <t>Newry</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D87" s="5" t="n">
@@ -8713,12 +8715,12 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Milton Keynes</t>
+          <t>Nottingham</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D88" s="3" t="n">
@@ -8737,12 +8739,12 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Newry</t>
+          <t>Redhill</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D89" s="5" t="n">
@@ -8761,12 +8763,12 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Redhill</t>
+          <t>Ringwood</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D90" s="3" t="n">
@@ -8785,12 +8787,12 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Ringwood</t>
+          <t>Rotherham</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D91" s="5" t="n">
@@ -8809,12 +8811,12 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Rotherham</t>
+          <t>Solihull</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D92" s="3" t="n">
@@ -8833,12 +8835,12 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Solihull</t>
+          <t>Stoke-on-trent</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D93" s="5" t="n">
@@ -8857,12 +8859,12 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Stoke-on-trent</t>
+          <t>Winchester</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D94" s="3" t="n">
@@ -8881,7 +8883,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Winchester</t>
+          <t>Alresford</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -8890,7 +8892,7 @@
         </is>
       </c>
       <c r="D95" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E95" s="5" t="n">
         <v>0</v>
@@ -8905,12 +8907,12 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Alresford</t>
+          <t>Barrow-in-furness</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Cumbria - South</t>
         </is>
       </c>
       <c r="D96" s="3" t="n">
@@ -8929,12 +8931,12 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Barrow-in-furness</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Cumbria - South</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D97" s="5" t="n">
@@ -8953,12 +8955,12 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D98" s="3" t="n">
@@ -8977,12 +8979,12 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Berwick-upon-tweed</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D99" s="5" t="n">
@@ -9001,12 +9003,12 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Berwick-upon-tweed</t>
+          <t>Chelmsley Wood</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D100" s="3" t="n">
@@ -9025,12 +9027,12 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Chelmsley Wood</t>
+          <t>Crawley</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D101" s="5" t="n">
@@ -9049,12 +9051,12 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Crawley</t>
+          <t>Dewsbury</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D102" s="3" t="n">
@@ -9073,12 +9075,12 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Dewsbury</t>
+          <t>Dorking</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D103" s="5" t="n">
@@ -9097,12 +9099,12 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Dorking</t>
+          <t>Driffield</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Yorkshire - East</t>
         </is>
       </c>
       <c r="D104" s="3" t="n">
@@ -9121,12 +9123,12 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Driffield</t>
+          <t>Eastbourne</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - East</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D105" s="5" t="n">
@@ -9145,12 +9147,12 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Eastbourne</t>
+          <t>Ellesmere Port</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D106" s="3" t="n">
@@ -9169,12 +9171,12 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Ellesmere Port</t>
+          <t>Exeter</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D107" s="5" t="n">
@@ -9217,12 +9219,12 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Gravesend</t>
+          <t>Hebburn</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D109" s="5" t="n">
@@ -9241,12 +9243,12 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Hebburn</t>
+          <t>Hessle</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Yorkshire - East</t>
         </is>
       </c>
       <c r="D110" s="3" t="n">
@@ -9265,12 +9267,12 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Hessle</t>
+          <t>Huntingdon</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - East</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D111" s="5" t="n">
@@ -9289,12 +9291,12 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Huntingdon</t>
+          <t>Kettering</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D112" s="3" t="n">
@@ -9313,12 +9315,12 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Kettering</t>
+          <t>Knaresborough</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D113" s="5" t="n">
@@ -9337,12 +9339,12 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Knaresborough</t>
+          <t>Knutsford</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D114" s="3" t="n">
@@ -9361,12 +9363,12 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Knutsford</t>
+          <t>Lichfield</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D115" s="5" t="n">
@@ -9385,12 +9387,12 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Lichfield</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D116" s="3" t="n">
@@ -9409,12 +9411,12 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Lingfield</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D117" s="5" t="n">
@@ -9433,12 +9435,12 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Lingfield</t>
+          <t>Newtownabbey</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D118" s="3" t="n">
@@ -9457,12 +9459,12 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Newtownabbey</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D119" s="5" t="n">
@@ -9481,12 +9483,12 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Nuneaton</t>
+          <t>Romsey</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D120" s="3" t="n">
@@ -9505,12 +9507,12 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Sale</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D121" s="5" t="n">
@@ -9529,12 +9531,12 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Romsey</t>
+          <t>Slough</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D122" s="3" t="n">
@@ -9553,12 +9555,12 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Sale</t>
+          <t>Stafford</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D123" s="5" t="n">
@@ -9577,12 +9579,12 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Sevenoaks</t>
+          <t>Staines</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D124" s="3" t="n">
@@ -9601,12 +9603,12 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Slough</t>
+          <t>Stockport</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D125" s="5" t="n">
@@ -9625,12 +9627,12 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Stafford</t>
+          <t>Tipton</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D126" s="3" t="n">
@@ -9649,12 +9651,12 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Staines</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D127" s="5" t="n">
@@ -9673,12 +9675,12 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Stockport</t>
+          <t>Weston-super-mare</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D128" s="3" t="n">
@@ -9697,12 +9699,12 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Tipton</t>
+          <t>Worcester</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Worcestershire</t>
         </is>
       </c>
       <c r="D129" s="5" t="n">
@@ -9721,16 +9723,16 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D130" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E130" s="3" t="n">
         <v>0</v>
@@ -9745,16 +9747,16 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Weston-super-mare</t>
+          <t>Aldershot</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D131" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E131" s="5" t="n">
         <v>0</v>
@@ -9769,16 +9771,16 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Worcester</t>
+          <t>Alton</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Worcestershire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D132" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E132" s="3" t="n">
         <v>0</v>
@@ -9793,12 +9795,12 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Amersham</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D133" s="5" t="n">
@@ -9817,12 +9819,12 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Aldershot</t>
+          <t>Ballyclare</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D134" s="3" t="n">
@@ -9841,12 +9843,12 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Alton</t>
+          <t>Ballymena</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D135" s="5" t="n">
@@ -9865,12 +9867,12 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Amersham</t>
+          <t>Barry</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Wales South - Cardiff &amp; Vale</t>
         </is>
       </c>
       <c r="D136" s="3" t="n">
@@ -9889,12 +9891,12 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Ballyclare</t>
+          <t>Basingstoke</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D137" s="5" t="n">
@@ -9913,12 +9915,12 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Ballymena</t>
+          <t>Batley</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D138" s="3" t="n">
@@ -9937,12 +9939,12 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Barry</t>
+          <t>Berkhamsted</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Wales South - Cardiff &amp; Vale</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D139" s="5" t="n">
@@ -9961,12 +9963,12 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Basingstoke</t>
+          <t>Bicester</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D140" s="3" t="n">
@@ -9985,7 +9987,7 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Batley</t>
+          <t>Bingley</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -10009,12 +10011,12 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Berkhamsted</t>
+          <t>Bishop Auckland</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D142" s="3" t="n">
@@ -10033,12 +10035,12 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Bicester</t>
+          <t>Bishop's Stortford</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D143" s="5" t="n">
@@ -10057,12 +10059,12 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Bingley</t>
+          <t>Bognor Regis</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D144" s="3" t="n">
@@ -10081,12 +10083,12 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Bishop Auckland</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D145" s="5" t="n">
@@ -10105,12 +10107,12 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Bishop's Stortford</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D146" s="3" t="n">
@@ -10129,12 +10131,12 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Bognor Regis</t>
+          <t>Brentwood</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D147" s="5" t="n">
@@ -10153,12 +10155,12 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Bridport</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D148" s="3" t="n">
@@ -10177,12 +10179,12 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Brinsworth</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D149" s="5" t="n">
@@ -10201,12 +10203,12 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Brentwood</t>
+          <t>Buckingham</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D150" s="3" t="n">
@@ -10225,12 +10227,12 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Bridport</t>
+          <t>Bury St Edmunds</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D151" s="5" t="n">
@@ -10249,12 +10251,12 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Brinsworth</t>
+          <t>Cannock</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D152" s="3" t="n">
@@ -10273,12 +10275,12 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Buckingham</t>
+          <t>Canterbury</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D153" s="5" t="n">
@@ -10297,12 +10299,12 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Bury St Edmunds</t>
+          <t>Cheadle</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D154" s="3" t="n">
@@ -10321,12 +10323,12 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Cannock</t>
+          <t>Chertsey</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D155" s="5" t="n">
@@ -10345,12 +10347,12 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Canterbury</t>
+          <t>Chesham</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D156" s="3" t="n">
@@ -10369,12 +10371,12 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>Cheadle</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Derbyshire</t>
         </is>
       </c>
       <c r="D157" s="5" t="n">
@@ -10393,12 +10395,12 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Chertsey</t>
+          <t>Chichester</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D158" s="3" t="n">
@@ -10417,12 +10419,12 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>Chesham</t>
+          <t>Cirencester</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D159" s="5" t="n">
@@ -10441,12 +10443,12 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Colchester</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Derbyshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D160" s="3" t="n">
@@ -10465,12 +10467,12 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Chichester</t>
+          <t>Cottingham</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Yorkshire - East</t>
         </is>
       </c>
       <c r="D161" s="5" t="n">
@@ -10489,12 +10491,12 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Cirencester</t>
+          <t>Cramlington</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D162" s="3" t="n">
@@ -10513,12 +10515,12 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>Cleethorpes</t>
+          <t>Cranbrook</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D163" s="5" t="n">
@@ -10537,12 +10539,12 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Colchester</t>
+          <t>Dartford</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D164" s="3" t="n">
@@ -10561,12 +10563,12 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Congresbury</t>
+          <t>Droitwich</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Worcestershire</t>
         </is>
       </c>
       <c r="D165" s="5" t="n">
@@ -10585,12 +10587,12 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Corby</t>
+          <t>Dudley</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D166" s="3" t="n">
@@ -10609,12 +10611,12 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Cottingham</t>
+          <t>Fakenham</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - East</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D167" s="5" t="n">
@@ -10633,12 +10635,12 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Cramlington</t>
+          <t>Falmouth</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D168" s="3" t="n">
@@ -10657,12 +10659,12 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Cranbrook</t>
+          <t>Farnham</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D169" s="5" t="n">
@@ -10681,7 +10683,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Dartford</t>
+          <t>Faversham</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -10705,12 +10707,12 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Droitwich</t>
+          <t>Faygate</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Worcestershire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D171" s="5" t="n">
@@ -10729,12 +10731,12 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Dudley</t>
+          <t>Felixstowe</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D172" s="3" t="n">
@@ -10753,12 +10755,12 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Fakenham</t>
+          <t>Fetcham</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D173" s="5" t="n">
@@ -10777,12 +10779,12 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Falmouth</t>
+          <t>Frome</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D174" s="3" t="n">
@@ -10801,7 +10803,7 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Farnham</t>
+          <t>Godalming</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
@@ -10825,12 +10827,12 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Faversham</t>
+          <t>Gosport</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D176" s="3" t="n">
@@ -10849,12 +10851,12 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Faygate</t>
+          <t>Great Yarmouth</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D177" s="5" t="n">
@@ -10873,12 +10875,12 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Felixstowe</t>
+          <t>Guildford</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D178" s="3" t="n">
@@ -10897,12 +10899,12 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Fetcham</t>
+          <t>Hailsham</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D179" s="5" t="n">
@@ -10921,12 +10923,12 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Frome</t>
+          <t>Harlow</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D180" s="3" t="n">
@@ -10945,12 +10947,12 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Godalming</t>
+          <t>Hartlepool</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D181" s="5" t="n">
@@ -10969,7 +10971,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Gosport</t>
+          <t>Havant</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -10993,12 +10995,12 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Great Yarmouth</t>
+          <t>Henley-on-thames</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D183" s="5" t="n">
@@ -11017,7 +11019,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Guildford</t>
+          <t>Horley</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
@@ -11041,7 +11043,7 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Hailsham</t>
+          <t>Horsham</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
@@ -11065,12 +11067,12 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Harlow</t>
+          <t>Hove</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D186" s="3" t="n">
@@ -11089,12 +11091,12 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Hartlepool</t>
+          <t>Keighley</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D187" s="5" t="n">
@@ -11113,12 +11115,12 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Havant</t>
+          <t>Kenilworth</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D188" s="3" t="n">
@@ -11137,12 +11139,12 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Henley-on-thames</t>
+          <t>Kings Langley</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D189" s="5" t="n">
@@ -11161,12 +11163,12 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Horley</t>
+          <t>Knowle</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D190" s="3" t="n">
@@ -11185,12 +11187,12 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Horsham</t>
+          <t>Leamington Spa</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D191" s="5" t="n">
@@ -11209,12 +11211,12 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Hove</t>
+          <t>Lisburn</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D192" s="3" t="n">
@@ -11233,12 +11235,12 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Keighley</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Scotland Central - Edinburgh &amp; Lothians</t>
         </is>
       </c>
       <c r="D193" s="5" t="n">
@@ -11257,12 +11259,12 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Kenilworth</t>
+          <t>Loughborough</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D194" s="3" t="n">
@@ -11281,12 +11283,12 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Kings Langley</t>
+          <t>Luton</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D195" s="5" t="n">
@@ -11305,12 +11307,12 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Knowle</t>
+          <t>Maidenhead</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D196" s="3" t="n">
@@ -11329,12 +11331,12 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Leamington Spa</t>
+          <t>Mansfield</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D197" s="5" t="n">
@@ -11353,12 +11355,12 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Lisburn</t>
+          <t>Marlborough</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D198" s="3" t="n">
@@ -11377,12 +11379,12 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Marlow</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>Scotland Central - Edinburgh &amp; Lothians</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D199" s="5" t="n">
@@ -11401,12 +11403,12 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Loughborough</t>
+          <t>Montrose</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D200" s="3" t="n">
@@ -11425,12 +11427,12 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Luton</t>
+          <t>Nantwich</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D201" s="5" t="n">
@@ -11449,7 +11451,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Maidenhead</t>
+          <t>Newbury</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
@@ -11473,12 +11475,12 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Mansfield</t>
+          <t>Normanton</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>Nottinghamshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D203" s="5" t="n">
@@ -11497,12 +11499,12 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Marlborough</t>
+          <t>Northampton</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D204" s="3" t="n">
@@ -11521,12 +11523,12 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Marlow</t>
+          <t>Northwich</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D205" s="5" t="n">
@@ -11545,12 +11547,12 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Montrose</t>
+          <t>Nuneaton</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D206" s="3" t="n">
@@ -11569,12 +11571,12 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Nantwich</t>
+          <t>Okehampton</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D207" s="5" t="n">
@@ -11593,12 +11595,12 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Newbury</t>
+          <t>Otley</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D208" s="3" t="n">
@@ -11617,12 +11619,12 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Normanton</t>
+          <t>Oxted</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D209" s="5" t="n">
@@ -11641,12 +11643,12 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Northampton</t>
+          <t>Peterlee</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D210" s="3" t="n">
@@ -11665,12 +11667,12 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Northwich</t>
+          <t>Pickering</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D211" s="5" t="n">
@@ -11689,7 +11691,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Okehampton</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
@@ -11713,12 +11715,12 @@
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>Otley</t>
+          <t>Pontypridd</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Wales South - Valleys</t>
         </is>
       </c>
       <c r="D213" s="5" t="n">
@@ -11737,12 +11739,12 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Oxted</t>
+          <t>Poole</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D214" s="3" t="n">
@@ -11761,12 +11763,12 @@
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>Peterlee</t>
+          <t>Portishead</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D215" s="5" t="n">
@@ -11785,12 +11787,12 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Pickering</t>
+          <t>Potters Bar</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D216" s="3" t="n">
@@ -11809,12 +11811,12 @@
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Pudsey</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D217" s="5" t="n">
@@ -11833,12 +11835,12 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Pontypridd</t>
+          <t>Ramsgate</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Wales South - Valleys</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D218" s="3" t="n">
@@ -11857,12 +11859,12 @@
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>Poole</t>
+          <t>Redruth</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D219" s="5" t="n">
@@ -11881,12 +11883,12 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Portishead</t>
+          <t>Ripon</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D220" s="3" t="n">
@@ -11905,12 +11907,12 @@
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Potters Bar</t>
+          <t>Rochester</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D221" s="5" t="n">
@@ -11929,12 +11931,12 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Pudsey</t>
+          <t>Royston</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D222" s="3" t="n">
@@ -11953,12 +11955,12 @@
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>Ramsgate</t>
+          <t>Runcorn</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Cheshire - Warrington &amp; Halton</t>
         </is>
       </c>
       <c r="D223" s="5" t="n">
@@ -11977,12 +11979,12 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>Redruth</t>
+          <t>Rushden</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D224" s="3" t="n">
@@ -12001,12 +12003,12 @@
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>Ripon</t>
+          <t>Ryton</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D225" s="5" t="n">
@@ -12025,12 +12027,12 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>Rochester</t>
+          <t>Salisbury</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D226" s="3" t="n">
@@ -12049,12 +12051,12 @@
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>Royston</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D227" s="5" t="n">
@@ -12073,12 +12075,12 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>Rugby</t>
+          <t>Scunthorpe</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D228" s="3" t="n">
@@ -12097,12 +12099,12 @@
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>Runcorn</t>
+          <t>Sevenoaks</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - Warrington &amp; Halton</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D229" s="5" t="n">
@@ -12121,12 +12123,12 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>Rushden</t>
+          <t>Shepperton</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D230" s="3" t="n">
@@ -12145,12 +12147,12 @@
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>Ryton</t>
+          <t>Sherborne</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D231" s="5" t="n">
@@ -12169,12 +12171,12 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Salisbury</t>
+          <t>Shrewsbury</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Shropshire</t>
         </is>
       </c>
       <c r="D232" s="3" t="n">
@@ -12193,12 +12195,12 @@
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>Sandy</t>
+          <t>Snodland</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D233" s="5" t="n">
@@ -12217,12 +12219,12 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Scunthorpe</t>
+          <t>Southam</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D234" s="3" t="n">
@@ -12241,12 +12243,12 @@
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>Shepperton</t>
+          <t>Southend-on-sea</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D235" s="5" t="n">
@@ -12265,12 +12267,12 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Sherborne</t>
+          <t>Spalding</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D236" s="3" t="n">
@@ -12289,12 +12291,12 @@
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>Shrewsbury</t>
+          <t>St. Ives</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>Shropshire</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D237" s="5" t="n">
@@ -12313,12 +12315,12 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>Snodland</t>
+          <t>St. Neots</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D238" s="3" t="n">
@@ -12337,12 +12339,12 @@
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>Southam</t>
+          <t>Stanley</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D239" s="5" t="n">
@@ -12361,12 +12363,12 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Southend-on-sea</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D240" s="3" t="n">
@@ -12385,12 +12387,12 @@
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>Spalding</t>
+          <t>Stratford-upon-avon</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D241" s="5" t="n">
@@ -12409,12 +12411,12 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>St. Ives</t>
+          <t>Stretford</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D242" s="3" t="n">
@@ -12433,12 +12435,12 @@
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>St. Neots</t>
+          <t>Stroud</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D243" s="5" t="n">
@@ -12457,12 +12459,12 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>Stanley</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D244" s="3" t="n">
@@ -12481,12 +12483,12 @@
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Tadworth</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D245" s="5" t="n">
@@ -12505,12 +12507,12 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>Stratford-upon-avon</t>
+          <t>Tamworth</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D246" s="3" t="n">
@@ -12529,12 +12531,12 @@
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>Stretford</t>
+          <t>Taunton</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D247" s="5" t="n">
@@ -12553,12 +12555,12 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>Stroud</t>
+          <t>Telford</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Shropshire</t>
         </is>
       </c>
       <c r="D248" s="3" t="n">
@@ -12577,12 +12579,12 @@
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Thatcham</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D249" s="5" t="n">
@@ -12601,12 +12603,12 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>Tadworth</t>
+          <t>Thetford</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D250" s="3" t="n">
@@ -12625,12 +12627,12 @@
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>Tamworth</t>
+          <t>Truro</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D251" s="5" t="n">
@@ -12649,12 +12651,12 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>Taunton</t>
+          <t>Tunbridge Wells</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D252" s="3" t="n">
@@ -12673,12 +12675,12 @@
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>Telford</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>Shropshire</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D253" s="5" t="n">
@@ -12697,12 +12699,12 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Thatcham</t>
+          <t>Walton-on-thames</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D254" s="3" t="n">
@@ -12721,12 +12723,12 @@
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>Thetford</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D255" s="5" t="n">
@@ -12745,12 +12747,12 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>Truro</t>
+          <t>Wellington</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Shropshire</t>
         </is>
       </c>
       <c r="D256" s="3" t="n">
@@ -12769,12 +12771,12 @@
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>Tunbridge Wells</t>
+          <t>Welwyn Garden City</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D257" s="5" t="n">
@@ -12793,12 +12795,12 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>West Malling</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D258" s="3" t="n">
@@ -12817,12 +12819,12 @@
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>Walton-on-thames</t>
+          <t>Whitby</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D259" s="5" t="n">
@@ -12841,12 +12843,12 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Whitstable</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D260" s="3" t="n">
@@ -12865,12 +12867,12 @@
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>Wellington</t>
+          <t>Wilmslow</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>Shropshire</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D261" s="5" t="n">
@@ -12889,12 +12891,12 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>Welwyn Garden City</t>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D262" s="3" t="n">
@@ -12913,12 +12915,12 @@
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>West Malling</t>
+          <t>Winsford</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D263" s="5" t="n">
@@ -12937,12 +12939,12 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>Whitby</t>
+          <t>Wokingham</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D264" s="3" t="n">
@@ -12961,12 +12963,12 @@
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>Whitstable</t>
+          <t>Woodbridge</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D265" s="5" t="n">
@@ -12985,12 +12987,12 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>Wilmslow</t>
+          <t>Worthing</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D266" s="3" t="n">
@@ -13009,12 +13011,12 @@
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Yeovil</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D267" s="5" t="n">
@@ -13025,128 +13027,8 @@
       </c>
       <c r="F267" s="4" t="inlineStr"/>
     </row>
-    <row r="268">
-      <c r="A268" s="2" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B268" s="2" t="inlineStr">
-        <is>
-          <t>Winsford</t>
-        </is>
-      </c>
-      <c r="C268" s="2" t="inlineStr">
-        <is>
-          <t>Cheshire - West</t>
-        </is>
-      </c>
-      <c r="D268" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E268" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F268" s="2" t="inlineStr"/>
-    </row>
-    <row r="269">
-      <c r="A269" s="4" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B269" s="4" t="inlineStr">
-        <is>
-          <t>Wokingham</t>
-        </is>
-      </c>
-      <c r="C269" s="4" t="inlineStr">
-        <is>
-          <t>Berkshire</t>
-        </is>
-      </c>
-      <c r="D269" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E269" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F269" s="4" t="inlineStr"/>
-    </row>
-    <row r="270">
-      <c r="A270" s="2" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B270" s="2" t="inlineStr">
-        <is>
-          <t>Woodbridge</t>
-        </is>
-      </c>
-      <c r="C270" s="2" t="inlineStr">
-        <is>
-          <t>Suffolk</t>
-        </is>
-      </c>
-      <c r="D270" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E270" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F270" s="2" t="inlineStr"/>
-    </row>
-    <row r="271">
-      <c r="A271" s="4" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B271" s="4" t="inlineStr">
-        <is>
-          <t>Worthing</t>
-        </is>
-      </c>
-      <c r="C271" s="4" t="inlineStr">
-        <is>
-          <t>Sussex</t>
-        </is>
-      </c>
-      <c r="D271" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E271" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F271" s="4" t="inlineStr"/>
-    </row>
-    <row r="272">
-      <c r="A272" s="2" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B272" s="2" t="inlineStr">
-        <is>
-          <t>Yeovil</t>
-        </is>
-      </c>
-      <c r="C272" s="2" t="inlineStr">
-        <is>
-          <t>Somerset</t>
-        </is>
-      </c>
-      <c r="D272" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E272" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F272" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F272"/>
+  <autoFilter ref="A1:F267"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13242,7 +13124,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="5" t="n">
@@ -13265,7 +13147,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="3" t="n">
@@ -13466,7 +13348,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
       <c r="D15" s="4" t="inlineStr"/>
@@ -13677,7 +13559,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>4</v>
@@ -13792,7 +13674,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C33" s="4" t="inlineStr"/>
       <c r="D33" s="4" t="inlineStr"/>
@@ -13809,7 +13691,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>14</v>
@@ -13904,7 +13786,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C39" s="4" t="inlineStr"/>
       <c r="D39" s="4" t="inlineStr"/>
@@ -13925,7 +13807,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>2</v>
@@ -14001,7 +13883,7 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="inlineStr"/>
@@ -14054,7 +13936,7 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C47" s="4" t="inlineStr"/>
       <c r="D47" s="4" t="inlineStr"/>
@@ -14073,7 +13955,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>3</v>
@@ -14353,7 +14235,7 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C64" s="3" t="n">
         <v>4</v>
@@ -14508,7 +14390,7 @@
         </is>
       </c>
       <c r="B73" s="5" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C73" s="4" t="inlineStr"/>
       <c r="D73" s="4" t="inlineStr"/>
@@ -14727,32 +14609,32 @@
       </c>
       <c r="D2" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.0 / 0/14</t>
+          <t>0 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="E2" s="13" t="inlineStr">
         <is>
-          <t>3 / 3.8 / 0/12</t>
+          <t>3 / 3.7 / 0/13</t>
         </is>
       </c>
       <c r="F2" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/12</t>
+          <t>1 / 1.1 / 0/13</t>
         </is>
       </c>
       <c r="G2" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/9</t>
+          <t>1 / 0.8 / 0/10</t>
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/11</t>
+          <t>2 / 1.1 / 0/12</t>
         </is>
       </c>
       <c r="I2" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/8</t>
+          <t>1 / 1.0 / 0/9</t>
         </is>
       </c>
     </row>
@@ -14765,25 +14647,25 @@
       <c r="B3" s="14" t="inlineStr"/>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.9 / 3/14</t>
+          <t>4 / 3.1 / 3/14</t>
         </is>
       </c>
       <c r="D3" s="14" t="inlineStr"/>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.0 / 0/12</t>
+          <t>2 / 1.1 / 0/13</t>
         </is>
       </c>
       <c r="F3" s="14" t="inlineStr"/>
       <c r="G3" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/9</t>
+          <t>1 / 0.7 / 0/10</t>
         </is>
       </c>
       <c r="H3" s="14" t="inlineStr"/>
       <c r="I3" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/8</t>
+          <t>1 / 0.6 / 0/9</t>
         </is>
       </c>
     </row>
@@ -14796,25 +14678,25 @@
       <c r="B4" s="13" t="inlineStr"/>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.8 / 0/14</t>
+          <t>0 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr"/>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.8 / 1/12</t>
+          <t>3 / 2.8 / 1/13</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr"/>
       <c r="G4" s="13" t="inlineStr"/>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.0 / 0/11</t>
+          <t>2 / 2.0 / 0/12</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
-          <t>5 / 3.1 / 0/8</t>
+          <t>5 / 3.3 / 0/9</t>
         </is>
       </c>
     </row>
@@ -14827,7 +14709,7 @@
       <c r="B5" s="14" t="inlineStr"/>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
@@ -14837,18 +14719,18 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/12</t>
+          <t>1 / 1.0 / 0/13</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr"/>
       <c r="G5" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.1 / 0/9</t>
+          <t>2 / 2.1 / 0/10</t>
         </is>
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/11</t>
+          <t>0 / 0.7 / 0/12</t>
         </is>
       </c>
       <c r="I5" s="14" t="inlineStr"/>
@@ -14862,33 +14744,33 @@
       <c r="B6" s="13" t="inlineStr"/>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/14</t>
+          <t>1 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.6 / 0/14</t>
+          <t>3 / 2.5 / 0/14</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/12</t>
+          <t>1 / 1.2 / 0/13</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr"/>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.8 / 2/9</t>
+          <t>2 / 3.6 / 2/10</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/11</t>
+          <t>0 / 0.1 / 0/12</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.8 / 0/8</t>
+          <t>0 / 0.7 / 0/9</t>
         </is>
       </c>
     </row>
@@ -14901,7 +14783,7 @@
       <c r="B7" s="14" t="inlineStr"/>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
@@ -14911,27 +14793,27 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/12</t>
+          <t>0 / 0.2 / 0/13</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.2 / 0/12</t>
+          <t>2 / 1.2 / 0/13</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="I7" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.0 / 0/8</t>
+          <t>2 / 2.0 / 0/9</t>
         </is>
       </c>
     </row>
@@ -14949,28 +14831,28 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.9 / 1/14</t>
+          <t>1 / 1.7 / 1/14</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/12</t>
+          <t>2 / 1.5 / 0/13</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/12</t>
+          <t>0 / 0.3 / 0/13</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr"/>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/11</t>
+          <t>0 / 0.1 / 0/12</t>
         </is>
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
     </row>
@@ -14988,28 +14870,28 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.8 / 0/14</t>
+          <t>1 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.2 / 0/12</t>
+          <t>2 / 1.3 / 0/13</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr"/>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.8 / 0/9</t>
+          <t>1 / 1.7 / 0/10</t>
         </is>
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/11</t>
+          <t>1 / 0.5 / 0/12</t>
         </is>
       </c>
       <c r="I9" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/8</t>
+          <t>1 / 0.6 / 0/9</t>
         </is>
       </c>
     </row>
@@ -15022,37 +14904,37 @@
       <c r="B10" s="13" t="inlineStr"/>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.3 / 0/14</t>
+          <t>1 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>1 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/13</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/10</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.2 / 0/12</t>
-        </is>
-      </c>
-      <c r="G10" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.2 / 0/9</t>
-        </is>
-      </c>
-      <c r="H10" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.8 / 0/8</t>
+          <t>0 / 0.7 / 0/9</t>
         </is>
       </c>
     </row>
@@ -15064,12 +14946,12 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 0/14</t>
+          <t>2 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>0 / 2.2 / 3/14</t>
+          <t>0 / 1.8 / 2/14</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
@@ -15079,27 +14961,27 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/10</t>
+        </is>
+      </c>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
-      <c r="G11" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.1 / 0/9</t>
-        </is>
-      </c>
-      <c r="H11" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
       <c r="I11" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
     </row>
@@ -15111,7 +14993,7 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr"/>
@@ -15122,27 +15004,27 @@
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/12</t>
+          <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.9 / 0/12</t>
+          <t>2 / 1.0 / 0/13</t>
         </is>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/9</t>
+          <t>0 / 0.4 / 0/10</t>
         </is>
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/11</t>
+          <t>1 / 0.4 / 0/12</t>
         </is>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
     </row>
@@ -15154,12 +15036,12 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.4 / 0/14</t>
+          <t>0 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
@@ -15169,27 +15051,27 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.3 / 0/10</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
-      <c r="G13" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.3 / 0/9</t>
-        </is>
-      </c>
-      <c r="H13" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
     </row>
@@ -15207,32 +15089,32 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.6 / 0/14</t>
+          <t>3 / 2.5 / 0/14</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.9 / 0/12</t>
+          <t>2 / 1.0 / 0/13</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.2 / 0/12</t>
+          <t>2 / 1.2 / 0/13</t>
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.8 / 0/9</t>
+          <t>2 / 2.7 / 0/10</t>
         </is>
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.8 / 0/8</t>
+          <t>1 / 1.7 / 0/9</t>
         </is>
       </c>
     </row>
@@ -15245,33 +15127,33 @@
       <c r="B15" s="14" t="inlineStr"/>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.7 / 0/14</t>
+          <t>1 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>7 / 3.8 / 2/14</t>
+          <t>7 / 4.1 / 3/14</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.0 / 0/12</t>
+          <t>1 / 1.9 / 0/13</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>5 / 2.2 / 2/12</t>
+          <t>5 / 2.5 / 2/13</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr"/>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.0 / 0/11</t>
+          <t>0 / 0.9 / 0/12</t>
         </is>
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.4 / 0/8</t>
+          <t>2 / 1.4 / 0/9</t>
         </is>
       </c>
     </row>
@@ -15294,27 +15176,27 @@
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/12</t>
+          <t>0 / 0.2 / 0/13</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 0/12</t>
+          <t>1 / 1.5 / 0/13</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>0 / 2.3 / 0/9</t>
+          <t>0 / 2.1 / 0/10</t>
         </is>
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="I16" s="13" t="inlineStr">
         <is>
-          <t>4 / 1.1 / 0/8</t>
+          <t>4 / 1.4 / 0/9</t>
         </is>
       </c>
     </row>
@@ -15327,29 +15209,29 @@
       <c r="B17" s="14" t="inlineStr"/>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/14</t>
+          <t>0 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>6 / 2.8 / 1/14</t>
+          <t>5 / 2.9 / 1/14</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr"/>
       <c r="F17" s="14" t="inlineStr"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>5 / 5.6 / 2/9</t>
+          <t>5 / 5.5 / 2/10</t>
         </is>
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/11</t>
+          <t>1 / 1.1 / 0/12</t>
         </is>
       </c>
       <c r="I17" s="14" t="inlineStr">
         <is>
-          <t>4 / 2.9 / 0/8</t>
+          <t>4 / 3.0 / 0/9</t>
         </is>
       </c>
     </row>
@@ -15362,29 +15244,29 @@
       <c r="B18" s="13" t="inlineStr"/>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>0 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>4 / 1.9 / 0/14</t>
+          <t>5 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/12</t>
+          <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr"/>
       <c r="G18" s="13" t="inlineStr"/>
       <c r="H18" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.0 / 0/11</t>
+          <t>0 / 0.9 / 0/12</t>
         </is>
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.2 / 0/8</t>
+          <t>4 / 2.4 / 0/9</t>
         </is>
       </c>
     </row>
@@ -15397,25 +15279,25 @@
       <c r="B19" s="14" t="inlineStr"/>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.4 / 0/14</t>
+          <t>2 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr"/>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>6 / 4.1 / 3/12</t>
+          <t>5 / 4.2 / 3/13</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr"/>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>5 / 3.9 / 0/9</t>
+          <t>5 / 4.0 / 0/10</t>
         </is>
       </c>
       <c r="H19" s="14" t="inlineStr"/>
       <c r="I19" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.5 / 0/8</t>
+          <t>3 / 2.6 / 0/9</t>
         </is>
       </c>
     </row>
@@ -15427,7 +15309,7 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>3 / 3.0 / 1/14</t>
+          <t>3 / 2.9 / 1/14</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
@@ -15442,27 +15324,27 @@
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/12</t>
+          <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/12</t>
+          <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
       <c r="H20" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/11</t>
+          <t>0 / 0.1 / 0/12</t>
         </is>
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/8</t>
+          <t>1 / 0.6 / 0/9</t>
         </is>
       </c>
     </row>
@@ -15480,32 +15362,32 @@
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/14</t>
+          <t>0 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/12</t>
+          <t>1 / 0.6 / 0/13</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.7 / 0/12</t>
+          <t>2 / 0.8 / 0/13</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="I21" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.4 / 0/8</t>
+          <t>2 / 1.4 / 0/9</t>
         </is>
       </c>
     </row>
@@ -15523,32 +15405,32 @@
       </c>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/14</t>
+          <t>1 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/12</t>
+          <t>0 / 0.4 / 0/13</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/12</t>
+          <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/9</t>
+          <t>0 / 0.2 / 0/10</t>
         </is>
       </c>
       <c r="H22" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/11</t>
+          <t>1 / 1.0 / 0/12</t>
         </is>
       </c>
       <c r="I22" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/8</t>
+          <t>1 / 1.0 / 0/9</t>
         </is>
       </c>
     </row>
@@ -15562,27 +15444,27 @@
       <c r="C23" s="14" t="inlineStr"/>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>14 / 8.7 / 10/14</t>
+          <t>12 / 9.3 / 11/14</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.3 / 0/12</t>
+          <t>1 / 1.3 / 0/13</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>8 / 6.1 / 5/12</t>
+          <t>7 / 6.2 / 6/13</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.2 / 0/9</t>
+          <t>1 / 2.1 / 0/10</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>4 / 3.6 / 0/11</t>
+          <t>5 / 3.8 / 0/12</t>
         </is>
       </c>
       <c r="I23" s="14" t="inlineStr"/>
@@ -15595,7 +15477,7 @@
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.1 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
@@ -15610,27 +15492,27 @@
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.7 / 0/10</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
-      <c r="F24" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
-      <c r="G24" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.8 / 0/9</t>
-        </is>
-      </c>
-      <c r="H24" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
       <c r="I24" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
     </row>
@@ -15643,29 +15525,29 @@
       <c r="B25" s="14" t="inlineStr"/>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.4 / 0/14</t>
+          <t>1 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr"/>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 0/12</t>
+          <t>1 / 1.5 / 0/13</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/9</t>
+          <t>1 / 1.0 / 0/10</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/11</t>
+          <t>1 / 0.5 / 0/12</t>
         </is>
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.2 / 0/8</t>
+          <t>4 / 2.4 / 0/9</t>
         </is>
       </c>
     </row>
@@ -15680,23 +15562,23 @@
       <c r="D26" s="13" t="inlineStr"/>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>5 / 4.3 / 2/12</t>
+          <t>5 / 4.4 / 2/13</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr"/>
       <c r="G26" s="13" t="inlineStr">
         <is>
-          <t>0 / 2.0 / 1/9</t>
+          <t>0 / 1.8 / 1/10</t>
         </is>
       </c>
       <c r="H26" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.6 / 0/11</t>
+          <t>1 / 1.6 / 0/12</t>
         </is>
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
-          <t>4 / 1.8 / 0/8</t>
+          <t>3 / 1.9 / 0/9</t>
         </is>
       </c>
     </row>
@@ -15723,27 +15605,27 @@
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>2 / 1.2 / 0/13</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/10</t>
+        </is>
+      </c>
+      <c r="H27" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>2 / 1.2 / 0/12</t>
-        </is>
-      </c>
-      <c r="G27" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.2 / 0/9</t>
-        </is>
-      </c>
-      <c r="H27" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
       <c r="I27" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
     </row>
@@ -15755,7 +15637,7 @@
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.8 / 0/14</t>
+          <t>2 / 2.7 / 0/14</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
@@ -15765,32 +15647,32 @@
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/14</t>
+          <t>1 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/12</t>
+          <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/12</t>
+          <t>1 / 0.2 / 0/13</t>
         </is>
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/9</t>
+          <t>0 / 0.6 / 0/10</t>
         </is>
       </c>
       <c r="H28" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/11</t>
+          <t>0 / 0.2 / 0/12</t>
         </is>
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
     </row>
@@ -15802,42 +15684,42 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.6 / 0/14</t>
+          <t>3 / 2.5 / 0/14</t>
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/14</t>
+          <t>2 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/14</t>
+          <t>1 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/12</t>
+          <t>0 / 0.2 / 0/13</t>
         </is>
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.6 / 0/12</t>
+          <t>3 / 1.7 / 0/13</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.0 / 0/9</t>
+          <t>0 / 0.9 / 0/10</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="I29" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
     </row>
@@ -15849,7 +15731,7 @@
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.3 / 0/14</t>
+          <t>2 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
@@ -15859,32 +15741,32 @@
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/14</t>
+          <t>1 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/12</t>
+          <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/12</t>
+          <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="H30" s="13" t="inlineStr">
+        <is>
+          <t>1 / 0.4 / 0/12</t>
+        </is>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/9</t>
-        </is>
-      </c>
-      <c r="H30" s="13" t="inlineStr">
-        <is>
-          <t>1 / 0.4 / 0/11</t>
-        </is>
-      </c>
-      <c r="I30" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
     </row>
@@ -15896,42 +15778,42 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.0 / 0/13</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/13</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="D31" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/13</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="E31" s="14" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
-      <c r="F31" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
-      <c r="G31" s="14" t="inlineStr">
+      <c r="I31" s="14" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
-        </is>
-      </c>
-      <c r="H31" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
-      <c r="I31" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
     </row>
@@ -15949,32 +15831,32 @@
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.6 / 0/14</t>
+          <t>1 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.4 / 0/12</t>
+          <t>1 / 1.4 / 0/13</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/12</t>
+          <t>2 / 1.2 / 0/13</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.8 / 1/9</t>
+          <t>3 / 2.8 / 1/10</t>
         </is>
       </c>
       <c r="H32" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/11</t>
+          <t>0 / 0.8 / 0/12</t>
         </is>
       </c>
       <c r="I32" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.5 / 0/8</t>
+          <t>1 / 2.3 / 0/9</t>
         </is>
       </c>
     </row>
@@ -15987,37 +15869,37 @@
       <c r="B33" s="14" t="inlineStr"/>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.4 / 0/14</t>
+          <t>0 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
-          <t>4 / 1.9 / 0/14</t>
+          <t>4 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.7 / 0/12</t>
+          <t>2 / 1.7 / 0/13</t>
         </is>
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.6 / 0/12</t>
+          <t>2 / 2.5 / 0/13</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.2 / 0/9</t>
+          <t>1 / 2.1 / 0/10</t>
         </is>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/11</t>
+          <t>2 / 1.6 / 0/12</t>
         </is>
       </c>
       <c r="I33" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/8</t>
+          <t>1 / 1.0 / 0/9</t>
         </is>
       </c>
     </row>
@@ -16045,33 +15927,33 @@
       <c r="B35" s="14" t="inlineStr"/>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/12</t>
+          <t>2 / 0.8 / 0/13</t>
         </is>
       </c>
       <c r="F35" s="14" t="inlineStr"/>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.0 / 0/9</t>
+          <t>3 / 1.2 / 0/10</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/11</t>
+          <t>0 / 0.1 / 0/12</t>
         </is>
       </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
     </row>
@@ -16083,42 +15965,42 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/13</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
-      <c r="D36" s="13" t="inlineStr">
+      <c r="F36" s="13" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
-      <c r="E36" s="13" t="inlineStr">
+      <c r="G36" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="H36" s="13" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
-      <c r="F36" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
-      <c r="G36" s="13" t="inlineStr">
+      <c r="I36" s="13" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
-        </is>
-      </c>
-      <c r="H36" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
-      <c r="I36" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
     </row>
@@ -16130,42 +16012,42 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.8 / 0/13</t>
+          <t>1 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="C37" s="14" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.9 / 0/14</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
-      <c r="D37" s="14" t="inlineStr">
-        <is>
-          <t>1 / 0.8 / 0/13</t>
-        </is>
-      </c>
-      <c r="E37" s="14" t="inlineStr">
+      <c r="F37" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>0 / 1.3 / 0/10</t>
+        </is>
+      </c>
+      <c r="H37" s="14" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
-      <c r="F37" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
-      <c r="G37" s="14" t="inlineStr">
-        <is>
-          <t>1 / 1.4 / 0/9</t>
-        </is>
-      </c>
-      <c r="H37" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
       <c r="I37" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
     </row>
@@ -16192,27 +16074,27 @@
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/12</t>
+          <t>1 / 0.5 / 0/13</t>
         </is>
       </c>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/12</t>
+          <t>3 / 0.9 / 0/13</t>
         </is>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/9</t>
+          <t>1 / 0.5 / 0/10</t>
         </is>
       </c>
       <c r="H38" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/8</t>
+          <t>1 / 1.0 / 0/9</t>
         </is>
       </c>
     </row>
@@ -16230,28 +16112,28 @@
       </c>
       <c r="D39" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/14</t>
+          <t>1 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="E39" s="14" t="inlineStr"/>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.3 / 0/12</t>
+          <t>1 / 1.3 / 0/13</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>1 / 3.3 / 2/9</t>
+          <t>1 / 3.1 / 2/10</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/11</t>
+          <t>0 / 0.2 / 0/12</t>
         </is>
       </c>
       <c r="I39" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/8</t>
+          <t>1 / 0.9 / 0/9</t>
         </is>
       </c>
     </row>
@@ -16266,14 +16148,14 @@
       <c r="D40" s="13" t="inlineStr"/>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/12</t>
+          <t>1 / 1.0 / 0/13</t>
         </is>
       </c>
       <c r="F40" s="13" t="inlineStr"/>
       <c r="G40" s="13" t="inlineStr"/>
       <c r="H40" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/11</t>
+          <t>1 / 1.1 / 0/12</t>
         </is>
       </c>
       <c r="I40" s="13" t="inlineStr"/>
@@ -16287,37 +16169,37 @@
       <c r="B41" s="14" t="inlineStr"/>
       <c r="C41" s="14" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>6 / 3.9 / 5/14</t>
+        </is>
+      </c>
+      <c r="E41" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.4 / 0/13</t>
+        </is>
+      </c>
+      <c r="F41" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
-      <c r="D41" s="14" t="inlineStr">
-        <is>
-          <t>6 / 3.7 / 4/13</t>
-        </is>
-      </c>
-      <c r="E41" s="14" t="inlineStr">
-        <is>
-          <t>1 / 0.3 / 0/12</t>
-        </is>
-      </c>
-      <c r="F41" s="14" t="inlineStr">
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.4 / 0/10</t>
+        </is>
+      </c>
+      <c r="H41" s="14" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
-      <c r="G41" s="14" t="inlineStr">
-        <is>
-          <t>1 / 1.4 / 0/9</t>
-        </is>
-      </c>
-      <c r="H41" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
       <c r="I41" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
     </row>
@@ -16329,42 +16211,42 @@
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>3 / 4.4 / 1/13</t>
+          <t>3 / 4.3 / 1/14</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/13</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 0/13</t>
+          <t>1 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="F42" s="13" t="inlineStr">
+        <is>
+          <t>2 / 0.8 / 0/13</t>
+        </is>
+      </c>
+      <c r="G42" s="13" t="inlineStr">
+        <is>
+          <t>2 / 1.5 / 0/10</t>
+        </is>
+      </c>
+      <c r="H42" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
-      <c r="F42" s="13" t="inlineStr">
-        <is>
-          <t>2 / 0.7 / 0/12</t>
-        </is>
-      </c>
-      <c r="G42" s="13" t="inlineStr">
-        <is>
-          <t>2 / 1.4 / 0/9</t>
-        </is>
-      </c>
-      <c r="H42" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
       <c r="I42" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/8</t>
+          <t>1 / 1.0 / 0/9</t>
         </is>
       </c>
     </row>
@@ -16376,42 +16258,42 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>4 / 2.2 / 0/13</t>
+          <t>4 / 2.3 / 0/14</t>
         </is>
       </c>
       <c r="C43" s="14" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.2 / 0/13</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
-      <c r="D43" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/13</t>
-        </is>
-      </c>
-      <c r="E43" s="14" t="inlineStr">
-        <is>
-          <t>1 / 0.2 / 0/12</t>
-        </is>
-      </c>
-      <c r="F43" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/11</t>
+          <t>1 / 0.5 / 0/12</t>
         </is>
       </c>
       <c r="I43" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/8</t>
+          <t>1 / 0.7 / 0/9</t>
         </is>
       </c>
     </row>
@@ -16429,32 +16311,32 @@
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>9 / 4.8 / 4/14</t>
+          <t>9 / 5.1 / 5/14</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/12</t>
+          <t>1 / 1.2 / 0/13</t>
         </is>
       </c>
       <c r="F44" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.4 / 0/12</t>
+          <t>3 / 2.5 / 0/13</t>
         </is>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.7 / 2/9</t>
+          <t>2 / 2.6 / 2/10</t>
         </is>
       </c>
       <c r="H44" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.5 / 1/11</t>
+          <t>2 / 2.4 / 1/12</t>
         </is>
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/8</t>
+          <t>1 / 0.6 / 0/9</t>
         </is>
       </c>
     </row>
@@ -16467,33 +16349,33 @@
       <c r="B45" s="14" t="inlineStr"/>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.5 / 0/13</t>
+          <t>0 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="D45" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/13</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>12 / 2.3 / 1/12</t>
+          <t>14 / 3.2 / 2/13</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.2 / 0/12</t>
+          <t>2 / 0.4 / 0/13</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr"/>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>6 / 0.8 / 1/11</t>
+          <t>6 / 1.2 / 2/12</t>
         </is>
       </c>
       <c r="I45" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/8</t>
+          <t>2 / 1.2 / 0/9</t>
         </is>
       </c>
     </row>
@@ -16505,42 +16387,42 @@
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>22 / 6.5 / 2/13</t>
+          <t>24 / 7.8 / 3/14</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="D46" s="13" t="inlineStr">
+        <is>
+          <t>3 / 1.6 / 0/14</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
-      <c r="D46" s="13" t="inlineStr">
-        <is>
-          <t>3 / 1.5 / 0/13</t>
-        </is>
-      </c>
-      <c r="E46" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
       <c r="F46" s="13" t="inlineStr">
         <is>
+          <t>1 / 0.2 / 0/13</t>
+        </is>
+      </c>
+      <c r="G46" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/10</t>
+        </is>
+      </c>
+      <c r="H46" s="13" t="inlineStr">
+        <is>
           <t>1 / 0.1 / 0/12</t>
         </is>
       </c>
-      <c r="G46" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.2 / 0/9</t>
-        </is>
-      </c>
-      <c r="H46" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.2 / 0/8</t>
+          <t>2 / 0.4 / 0/9</t>
         </is>
       </c>
     </row>
@@ -16558,28 +16440,28 @@
       </c>
       <c r="D47" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.2 / 0/14</t>
+          <t>2 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.1 / 0/12</t>
+          <t>3 / 2.2 / 0/13</t>
         </is>
       </c>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.3 / 0/12</t>
+          <t>4 / 2.5 / 0/13</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.8 / 2/9</t>
+          <t>1 / 2.6 / 2/10</t>
         </is>
       </c>
       <c r="H47" s="14" t="inlineStr"/>
       <c r="I47" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/8</t>
+          <t>1 / 1.0 / 0/9</t>
         </is>
       </c>
     </row>
@@ -16593,28 +16475,28 @@
       <c r="C48" s="13" t="inlineStr"/>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.2 / 0/14</t>
+          <t>4 / 3.4 / 0/14</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.7 / 0/12</t>
+          <t>1 / 1.6 / 0/13</t>
         </is>
       </c>
       <c r="F48" s="13" t="inlineStr"/>
       <c r="G48" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.2 / 0/9</t>
+          <t>1 / 2.1 / 0/10</t>
         </is>
       </c>
       <c r="H48" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.5 / 0/11</t>
+          <t>1 / 0.6 / 0/12</t>
         </is>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.6 / 0/8</t>
+          <t>3 / 1.8 / 0/9</t>
         </is>
       </c>
     </row>
@@ -16641,27 +16523,27 @@
       </c>
       <c r="E49" s="14" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="H49" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
-      <c r="F49" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
-      <c r="G49" s="14" t="inlineStr">
+      <c r="I49" s="14" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
-        </is>
-      </c>
-      <c r="H49" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
-      <c r="I49" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
     </row>
@@ -16673,42 +16555,42 @@
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/13</t>
+          <t>3 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="D50" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
-      <c r="D50" s="13" t="inlineStr">
+      <c r="F50" s="13" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
-      <c r="E50" s="13" t="inlineStr">
+      <c r="G50" s="13" t="inlineStr">
+        <is>
+          <t>1 / 0.2 / 0/10</t>
+        </is>
+      </c>
+      <c r="H50" s="13" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
-      <c r="F50" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
-      <c r="G50" s="13" t="inlineStr">
+      <c r="I50" s="13" t="inlineStr">
         <is>
           <t>0 / 0.1 / 0/9</t>
-        </is>
-      </c>
-      <c r="H50" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
-      <c r="I50" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.1 / 0/8</t>
         </is>
       </c>
     </row>
@@ -16721,37 +16603,37 @@
       <c r="B51" s="14" t="inlineStr"/>
       <c r="C51" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/13</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="D51" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.5 / 0/13</t>
+          <t>3 / 2.5 / 0/14</t>
         </is>
       </c>
       <c r="E51" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.6 / 0/12</t>
+          <t>3 / 2.6 / 0/13</t>
         </is>
       </c>
       <c r="F51" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/12</t>
+          <t>0 / 0.2 / 0/13</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/9</t>
+          <t>1 / 1.1 / 0/10</t>
         </is>
       </c>
       <c r="H51" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/11</t>
+          <t>1 / 0.6 / 0/12</t>
         </is>
       </c>
       <c r="I51" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/8</t>
+          <t>1 / 0.6 / 0/9</t>
         </is>
       </c>
     </row>
@@ -16763,42 +16645,42 @@
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.3 / 0/13</t>
+          <t>1 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="D52" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
-      <c r="D52" s="13" t="inlineStr">
+      <c r="F52" s="13" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
-      <c r="E52" s="13" t="inlineStr">
+      <c r="G52" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.8 / 0/10</t>
+        </is>
+      </c>
+      <c r="H52" s="13" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
-      <c r="F52" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
-      <c r="G52" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.9 / 0/9</t>
-        </is>
-      </c>
-      <c r="H52" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
     </row>
@@ -16810,42 +16692,42 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.6 / 0/13</t>
+          <t>2 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="C53" s="14" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="D53" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.2 / 0/14</t>
+        </is>
+      </c>
+      <c r="E53" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
-      <c r="D53" s="14" t="inlineStr">
-        <is>
-          <t>2 / 1.2 / 0/13</t>
-        </is>
-      </c>
-      <c r="E53" s="14" t="inlineStr">
+      <c r="F53" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.4 / 0/10</t>
+        </is>
+      </c>
+      <c r="H53" s="14" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
-      <c r="F53" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
-      <c r="G53" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.4 / 0/9</t>
-        </is>
-      </c>
-      <c r="H53" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
       <c r="I53" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
     </row>
@@ -16858,37 +16740,37 @@
       <c r="B54" s="13" t="inlineStr"/>
       <c r="C54" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/13</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.1 / 0/14</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>1 / 1.2 / 0/13</t>
+        </is>
+      </c>
+      <c r="F54" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.2 / 0/13</t>
         </is>
       </c>
-      <c r="E54" s="13" t="inlineStr">
-        <is>
-          <t>1 / 1.2 / 0/12</t>
-        </is>
-      </c>
-      <c r="F54" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.2 / 0/12</t>
-        </is>
-      </c>
       <c r="G54" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/9</t>
+          <t>0 / 0.4 / 0/10</t>
         </is>
       </c>
       <c r="H54" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="I54" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/8</t>
+          <t>0 / 0.3 / 0/9</t>
         </is>
       </c>
     </row>
@@ -16900,42 +16782,42 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
+          <t>1 / 0.6 / 0/14</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="D55" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="E55" s="14" t="inlineStr">
+        <is>
           <t>1 / 0.6 / 0/13</t>
         </is>
       </c>
-      <c r="C55" s="14" t="inlineStr">
+      <c r="F55" s="14" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
-      <c r="D55" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/13</t>
-        </is>
-      </c>
-      <c r="E55" s="14" t="inlineStr">
-        <is>
-          <t>1 / 0.6 / 0/12</t>
-        </is>
-      </c>
-      <c r="F55" s="14" t="inlineStr">
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="H55" s="14" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
-      <c r="G55" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/9</t>
-        </is>
-      </c>
-      <c r="H55" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
       <c r="I55" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/8</t>
+          <t>1 / 0.8 / 0/9</t>
         </is>
       </c>
     </row>
@@ -16948,33 +16830,33 @@
       <c r="B56" s="13" t="inlineStr"/>
       <c r="C56" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/13</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="D56" s="13" t="inlineStr"/>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/12</t>
+          <t>1 / 0.5 / 0/13</t>
         </is>
       </c>
       <c r="F56" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/12</t>
+          <t>0 / 0.2 / 0/13</t>
         </is>
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/9</t>
+          <t>0 / 0.2 / 0/10</t>
         </is>
       </c>
       <c r="H56" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/11</t>
+          <t>1 / 0.7 / 0/12</t>
         </is>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.9 / 1/8</t>
+          <t>1 / 2.7 / 1/9</t>
         </is>
       </c>
     </row>
@@ -16986,42 +16868,42 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/13</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="C57" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/13</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="D57" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/13</t>
+          <t>0 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="E57" s="14" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="F57" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.3 / 0/10</t>
+        </is>
+      </c>
+      <c r="H57" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
-      <c r="F57" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
-      <c r="G57" s="14" t="inlineStr">
-        <is>
-          <t>1 / 0.2 / 0/9</t>
-        </is>
-      </c>
-      <c r="H57" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
       <c r="I57" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
     </row>
@@ -17033,42 +16915,42 @@
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/13</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="C58" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="D58" s="13" t="inlineStr">
+        <is>
+          <t>1 / 0.6 / 0/14</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
-      <c r="D58" s="13" t="inlineStr">
-        <is>
-          <t>1 / 0.5 / 0/13</t>
-        </is>
-      </c>
-      <c r="E58" s="13" t="inlineStr">
+      <c r="F58" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="G58" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.4 / 0/10</t>
+        </is>
+      </c>
+      <c r="H58" s="13" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
-      <c r="F58" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
-      <c r="G58" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.4 / 0/9</t>
-        </is>
-      </c>
-      <c r="H58" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
     </row>
@@ -17081,33 +16963,33 @@
       <c r="B59" s="14" t="inlineStr"/>
       <c r="C59" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.5 / 0/14</t>
+          <t>0 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="D59" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="E59" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.8 / 0/12</t>
+          <t>1 / 1.7 / 0/13</t>
         </is>
       </c>
       <c r="F59" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/12</t>
+          <t>1 / 0.5 / 0/13</t>
         </is>
       </c>
       <c r="G59" s="14" t="inlineStr"/>
       <c r="H59" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.9 / 0/11</t>
+          <t>2 / 1.9 / 0/12</t>
         </is>
       </c>
       <c r="I59" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
     </row>
@@ -17120,37 +17002,37 @@
       <c r="B60" s="13" t="inlineStr"/>
       <c r="C60" s="13" t="inlineStr">
         <is>
-          <t>0 / 3.1 / 3/14</t>
+          <t>0 / 2.9 / 3/14</t>
         </is>
       </c>
       <c r="D60" s="13" t="inlineStr">
         <is>
-          <t>4 / 1.8 / 0/14</t>
+          <t>4 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/12</t>
+          <t>1 / 0.5 / 0/13</t>
         </is>
       </c>
       <c r="F60" s="13" t="inlineStr">
         <is>
-          <t>4 / 1.4 / 0/12</t>
+          <t>3 / 1.5 / 0/13</t>
         </is>
       </c>
       <c r="G60" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.4 / 1/9</t>
+          <t>0 / 2.2 / 1/10</t>
         </is>
       </c>
       <c r="H60" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/11</t>
+          <t>1 / 0.3 / 0/12</t>
         </is>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.0 / 0/8</t>
+          <t>2 / 1.1 / 0/9</t>
         </is>
       </c>
     </row>
@@ -17168,27 +17050,27 @@
       </c>
       <c r="D61" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.5 / 0/14</t>
+          <t>2 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="E61" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/12</t>
+          <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
       <c r="F61" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.5 / 0/12</t>
+          <t>2 / 1.5 / 0/13</t>
         </is>
       </c>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.7 / 0/9</t>
+          <t>3 / 2.7 / 0/10</t>
         </is>
       </c>
       <c r="H61" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/11</t>
+          <t>0 / 0.1 / 0/12</t>
         </is>
       </c>
       <c r="I61" s="14" t="inlineStr"/>
@@ -17202,33 +17084,33 @@
       <c r="B62" s="13" t="inlineStr"/>
       <c r="C62" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.9 / 0/14</t>
+          <t>2 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr"/>
       <c r="F62" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/12</t>
+          <t>1 / 0.6 / 0/13</t>
         </is>
       </c>
       <c r="G62" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.6 / 0/9</t>
+          <t>1 / 1.5 / 0/10</t>
         </is>
       </c>
       <c r="H62" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.8 / 0/11</t>
+          <t>0 / 0.8 / 0/12</t>
         </is>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/8</t>
+          <t>1 / 0.7 / 0/9</t>
         </is>
       </c>
     </row>
@@ -17243,18 +17125,18 @@
       <c r="D63" s="14" t="inlineStr"/>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>5 / 4.2 / 0/12</t>
+          <t>5 / 4.2 / 0/13</t>
         </is>
       </c>
       <c r="F63" s="14" t="inlineStr"/>
       <c r="G63" s="14" t="inlineStr">
         <is>
-          <t>3 / 4.4 / 2/9</t>
+          <t>3 / 4.3 / 2/10</t>
         </is>
       </c>
       <c r="H63" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.3 / 0/11</t>
+          <t>3 / 2.3 / 0/12</t>
         </is>
       </c>
       <c r="I63" s="14" t="inlineStr"/>
@@ -17270,23 +17152,23 @@
       <c r="D64" s="13" t="inlineStr"/>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.5 / 0/12</t>
+          <t>4 / 2.6 / 0/13</t>
         </is>
       </c>
       <c r="F64" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.9 / 0/12</t>
+          <t>3 / 2.9 / 0/13</t>
         </is>
       </c>
       <c r="G64" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.6 / 0/9</t>
+          <t>2 / 3.4 / 0/10</t>
         </is>
       </c>
       <c r="H64" s="13" t="inlineStr"/>
       <c r="I64" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.2 / 0/8</t>
+          <t>4 / 3.3 / 0/9</t>
         </is>
       </c>
     </row>
@@ -17298,42 +17180,42 @@
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/13</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="C65" s="14" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="E65" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
-      <c r="D65" s="14" t="inlineStr">
+      <c r="F65" s="14" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
-      <c r="E65" s="14" t="inlineStr">
+      <c r="G65" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/10</t>
+        </is>
+      </c>
+      <c r="H65" s="14" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
-      <c r="F65" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
-      <c r="G65" s="14" t="inlineStr">
+      <c r="I65" s="14" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/9</t>
-        </is>
-      </c>
-      <c r="H65" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
-      <c r="I65" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/8</t>
         </is>
       </c>
     </row>
@@ -17345,42 +17227,42 @@
       </c>
       <c r="B66" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.2 / 0/13</t>
+          <t>3 / 2.3 / 0/14</t>
         </is>
       </c>
       <c r="C66" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="D66" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="E66" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
-      <c r="D66" s="13" t="inlineStr">
+      <c r="F66" s="13" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
-      <c r="E66" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
-      <c r="F66" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
       <c r="G66" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/9</t>
+          <t>0 / 0.4 / 0/10</t>
         </is>
       </c>
       <c r="H66" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/11</t>
+          <t>1 / 0.4 / 0/12</t>
         </is>
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
     </row>
@@ -17393,37 +17275,37 @@
       <c r="B67" s="14" t="inlineStr"/>
       <c r="C67" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/13</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="D67" s="14" t="inlineStr">
         <is>
-          <t>4 / 2.1 / 0/13</t>
+          <t>4 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/12</t>
+          <t>2 / 1.5 / 0/13</t>
         </is>
       </c>
       <c r="F67" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/12</t>
+          <t>1 / 1.0 / 0/13</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.8 / 0/9</t>
+          <t>0 / 0.7 / 0/10</t>
         </is>
       </c>
       <c r="H67" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="I67" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/8</t>
+          <t>0 / 0.3 / 0/9</t>
         </is>
       </c>
     </row>
@@ -17435,42 +17317,42 @@
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.5 / 0/13</t>
+          <t>2 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="C68" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/13</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="D68" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/13</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/12</t>
+          <t>2 / 1.5 / 0/13</t>
         </is>
       </c>
       <c r="F68" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/13</t>
+        </is>
+      </c>
+      <c r="G68" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.4 / 0/10</t>
+        </is>
+      </c>
+      <c r="H68" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
-      <c r="G68" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.4 / 0/9</t>
-        </is>
-      </c>
-      <c r="H68" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/11</t>
-        </is>
-      </c>
       <c r="I68" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
     </row>
@@ -17482,42 +17364,42 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>2 / 3.2 / 1/13</t>
+          <t>2 / 3.1 / 1/14</t>
         </is>
       </c>
       <c r="C69" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/13</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="D69" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.6 / 0/13</t>
+          <t>1 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="E69" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/12</t>
+          <t>1 / 0.8 / 0/13</t>
         </is>
       </c>
       <c r="F69" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/12</t>
+          <t>1 / 0.2 / 0/13</t>
         </is>
       </c>
       <c r="G69" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/9</t>
+          <t>0 / 0.2 / 0/10</t>
         </is>
       </c>
       <c r="H69" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="I69" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/8</t>
+          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
     </row>
@@ -17530,37 +17412,37 @@
       <c r="B70" s="13" t="inlineStr"/>
       <c r="C70" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/13</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/13</t>
+          <t>1 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.9 / 0/12</t>
+          <t>4 / 3.0 / 0/13</t>
         </is>
       </c>
       <c r="F70" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/12</t>
+          <t>0 / 0.3 / 0/13</t>
         </is>
       </c>
       <c r="G70" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/9</t>
+          <t>0 / 0.1 / 0/10</t>
         </is>
       </c>
       <c r="H70" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="I70" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/8</t>
+          <t>1 / 1.1 / 0/9</t>
         </is>
       </c>
     </row>
@@ -17573,29 +17455,29 @@
       <c r="B71" s="14" t="inlineStr"/>
       <c r="C71" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/14</t>
+          <t>2 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="D71" s="14" t="inlineStr">
         <is>
-          <t>10 / 5.3 / 4/14</t>
+          <t>9 / 5.6 / 5/14</t>
         </is>
       </c>
       <c r="E71" s="14" t="inlineStr">
         <is>
-          <t>4 / 4.0 / 2/12</t>
+          <t>4 / 4.0 / 2/13</t>
         </is>
       </c>
       <c r="F71" s="14" t="inlineStr"/>
       <c r="G71" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.8 / 0/9</t>
+          <t>3 / 2.8 / 0/10</t>
         </is>
       </c>
       <c r="H71" s="14" t="inlineStr"/>
       <c r="I71" s="14" t="inlineStr">
         <is>
-          <t>4 / 3.9 / 0/8</t>
+          <t>3 / 3.8 / 0/9</t>
         </is>
       </c>
     </row>
@@ -17608,7 +17490,7 @@
       <c r="B72" s="13" t="inlineStr"/>
       <c r="C72" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>2 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="D72" s="13" t="inlineStr">
@@ -17618,27 +17500,27 @@
       </c>
       <c r="E72" s="13" t="inlineStr">
         <is>
-          <t>4 / 1.8 / 0/12</t>
+          <t>4 / 2.0 / 0/13</t>
         </is>
       </c>
       <c r="F72" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/12</t>
+          <t>1 / 0.6 / 0/13</t>
         </is>
       </c>
       <c r="G72" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/9</t>
+          <t>1 / 1.2 / 0/10</t>
         </is>
       </c>
       <c r="H72" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/8</t>
+          <t>1 / 1.0 / 0/9</t>
         </is>
       </c>
     </row>
@@ -17651,37 +17533,37 @@
       <c r="B73" s="14" t="inlineStr"/>
       <c r="C73" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>1 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="D73" s="14" t="inlineStr">
         <is>
-          <t>6 / 2.3 / 4/14</t>
+          <t>7 / 2.7 / 5/14</t>
         </is>
       </c>
       <c r="E73" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/12</t>
+          <t>1 / 0.7 / 0/13</t>
         </is>
       </c>
       <c r="F73" s="14" t="inlineStr">
         <is>
-          <t>4 / 2.8 / 0/12</t>
+          <t>5 / 3.0 / 0/13</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.3 / 0/9</t>
+          <t>3 / 2.4 / 0/10</t>
         </is>
       </c>
       <c r="H73" s="14" t="inlineStr">
         <is>
-          <t>3 / 3.1 / 0/11</t>
+          <t>3 / 3.1 / 0/12</t>
         </is>
       </c>
       <c r="I73" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/8</t>
+          <t>0 / 0.3 / 0/9</t>
         </is>
       </c>
     </row>
@@ -17695,32 +17577,32 @@
       <c r="C74" s="13" t="inlineStr"/>
       <c r="D74" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.2 / 0/14</t>
+          <t>2 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="E74" s="13" t="inlineStr">
         <is>
-          <t>3 / 3.2 / 0/12</t>
+          <t>4 / 3.2 / 0/13</t>
         </is>
       </c>
       <c r="F74" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/12</t>
+          <t>1 / 1.2 / 0/13</t>
         </is>
       </c>
       <c r="G74" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.9 / 0/9</t>
+          <t>0 / 1.7 / 0/10</t>
         </is>
       </c>
       <c r="H74" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/11</t>
+          <t>1 / 0.6 / 0/12</t>
         </is>
       </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.4 / 0/8</t>
+          <t>2 / 1.4 / 0/9</t>
         </is>
       </c>
     </row>
@@ -17733,7 +17615,7 @@
       <c r="B75" s="14" t="inlineStr"/>
       <c r="C75" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.0 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="D75" s="14" t="inlineStr">
@@ -17743,27 +17625,27 @@
       </c>
       <c r="E75" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.8 / 0/12</t>
+          <t>2 / 0.9 / 0/13</t>
         </is>
       </c>
       <c r="F75" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 0/12</t>
+          <t>2 / 1.5 / 0/13</t>
         </is>
       </c>
       <c r="G75" s="14" t="inlineStr">
         <is>
+          <t>1 / 0.8 / 0/10</t>
+        </is>
+      </c>
+      <c r="H75" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/12</t>
+        </is>
+      </c>
+      <c r="I75" s="14" t="inlineStr">
+        <is>
           <t>1 / 0.8 / 0/9</t>
-        </is>
-      </c>
-      <c r="H75" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.2 / 0/11</t>
-        </is>
-      </c>
-      <c r="I75" s="14" t="inlineStr">
-        <is>
-          <t>1 / 0.8 / 0/8</t>
         </is>
       </c>
     </row>
@@ -17776,37 +17658,37 @@
       <c r="B76" s="13" t="inlineStr"/>
       <c r="C76" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/14</t>
+          <t>0 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="D76" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="E76" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.2 / 0/12</t>
+          <t>2 / 1.3 / 0/13</t>
         </is>
       </c>
       <c r="F76" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.8 / 0/12</t>
+          <t>2 / 0.9 / 0/13</t>
         </is>
       </c>
       <c r="G76" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.3 / 0/9</t>
+          <t>2 / 3.2 / 0/10</t>
         </is>
       </c>
       <c r="H76" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/11</t>
+          <t>1 / 1.2 / 0/12</t>
         </is>
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
-          <t>3 / 3.2 / 0/8</t>
+          <t>3 / 3.2 / 0/9</t>
         </is>
       </c>
     </row>
@@ -17819,33 +17701,33 @@
       <c r="B77" s="14" t="inlineStr"/>
       <c r="C77" s="14" t="inlineStr">
         <is>
-          <t>1 / 3.0 / 0/14</t>
+          <t>1 / 2.7 / 0/14</t>
         </is>
       </c>
       <c r="D77" s="14" t="inlineStr">
         <is>
-          <t>4 / 1.4 / 0/14</t>
+          <t>3 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="E77" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/12</t>
+          <t>0 / 0.1 / 0/13</t>
         </is>
       </c>
       <c r="F77" s="14" t="inlineStr">
         <is>
-          <t>8 / 4.6 / 4/12</t>
+          <t>7 / 4.8 / 5/13</t>
         </is>
       </c>
       <c r="G77" s="14" t="inlineStr"/>
       <c r="H77" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 0/11</t>
+          <t>1 / 1.5 / 0/12</t>
         </is>
       </c>
       <c r="I77" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.2 / 0/8</t>
+          <t>2 / 1.3 / 0/9</t>
         </is>
       </c>
     </row>
@@ -17864,27 +17746,27 @@
       </c>
       <c r="E78" s="13" t="inlineStr">
         <is>
-          <t>3 / 3.1 / 0/12</t>
+          <t>3 / 3.1 / 0/13</t>
         </is>
       </c>
       <c r="F78" s="13" t="inlineStr">
         <is>
-          <t>6 / 2.8 / 2/12</t>
+          <t>6 / 3.1 / 3/13</t>
         </is>
       </c>
       <c r="G78" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.6 / 2/9</t>
+          <t>0 / 1.4 / 2/10</t>
         </is>
       </c>
       <c r="H78" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/11</t>
+          <t>0 / 0.0 / 0/12</t>
         </is>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/8</t>
+          <t>1 / 1.2 / 0/9</t>
         </is>
       </c>
     </row>
@@ -17899,19 +17781,19 @@
       <c r="D79" s="14" t="inlineStr"/>
       <c r="E79" s="14" t="inlineStr">
         <is>
-          <t>4 / 4.2 / 0/12</t>
+          <t>4 / 4.2 / 0/13</t>
         </is>
       </c>
       <c r="F79" s="14" t="inlineStr">
         <is>
-          <t>19 / 8.5 / 6/12</t>
+          <t>19 / 9.3 / 7/13</t>
         </is>
       </c>
       <c r="G79" s="14" t="inlineStr"/>
       <c r="H79" s="14" t="inlineStr"/>
       <c r="I79" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.8 / 0/8</t>
+          <t>3 / 2.8 / 0/9</t>
         </is>
       </c>
     </row>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -17,8 +17,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sitewide'!$A$1:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'JobG8 categories'!$A$1:$C$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'PAGES'!$A$1:$H$150</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$F$267</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'PAGES'!$A$1:$H$149</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$F$300</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'LIVE'!$A$1:$I$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'NOT LIVE'!$A$1:$I$79</definedName>
   </definedNames>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1778</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="3">
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1470</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="4">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>308</v>
+        <v>415</v>
       </c>
     </row>
     <row r="5">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1856</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="6">
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8">
@@ -648,7 +648,7 @@
         <v>2478</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="3">
@@ -674,7 +674,7 @@
         <v>1356</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>714</v>
+        <v>738</v>
       </c>
     </row>
     <row r="5">
@@ -687,7 +687,7 @@
         <v>840</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6">
@@ -700,7 +700,7 @@
         <v>609</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7">
@@ -713,7 +713,7 @@
         <v>468</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -804,7 +804,7 @@
         <v>186</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -854,7 +854,7 @@
         <v>10000</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>1464</v>
+        <v>1501</v>
       </c>
     </row>
   </sheetData>
@@ -869,7 +869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H150"/>
+  <dimension ref="A1:H149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -943,7 +943,7 @@
       <c r="D2" s="11" t="inlineStr"/>
       <c r="E2" s="11" t="inlineStr"/>
       <c r="F2" s="12" t="n">
-        <v>1937</v>
+        <v>2043</v>
       </c>
       <c r="G2" s="11" t="inlineStr"/>
       <c r="H2" s="11" t="inlineStr">
@@ -975,10 +975,10 @@
         </is>
       </c>
       <c r="F3" s="12" t="n">
-        <v>1793</v>
+        <v>1900</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>1793</v>
+        <v>1900</v>
       </c>
       <c r="H3" s="11" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="F4" s="12" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G4" s="11" t="inlineStr"/>
       <c r="H4" s="11" t="inlineStr">
@@ -1520,7 +1520,7 @@
         <v>1</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>1</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>1</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>1</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>1</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>1</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>1</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>1</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>1</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>1</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>1</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>1</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>1</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>1</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>1</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>1</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>1</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>1</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>1</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>1</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>1</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>1</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>1</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>1</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>1</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>1</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>1</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>1</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>1</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>1</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>1</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>1</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>1</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>1</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>1</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>1</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>1</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>1</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>1</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>1</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>1</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>1</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>1</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>1</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>1</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>1</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>1</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>1</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>1</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>1</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>1</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>1</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>1</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>1</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>1</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>1</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>1</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>1</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>1</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>1</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>1</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>1</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>1</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>1</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>1</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>1</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>1</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>1</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>1</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>1</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>1</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         <v>1</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>1</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>1</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>1</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>1</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>1</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>1</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>1</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>1</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>1</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>1</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>1</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>1</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -6395,24 +6395,24 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - Warrington &amp; Halton</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Finance &amp; Accounts</t>
+          <t>Customer Service &amp; Contact Centre</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>/job-search/warrington-halton/finance-accounts-jobs</t>
+          <t>/job-search/buckinghamshire/customer-service-jobs</t>
         </is>
       </c>
       <c r="F148" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>North East</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>/job-search/buckinghamshire/customer-service-jobs</t>
+          <t>/job-search/north-east/customer-service-jobs</t>
         </is>
       </c>
       <c r="F149" s="5" t="n">
@@ -6458,46 +6458,8 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>Detail</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>Regional/category</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>North East</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
-        <is>
-          <t>Customer Service &amp; Contact Centre</t>
-        </is>
-      </c>
-      <c r="E150" s="2" t="inlineStr">
-        <is>
-          <t>/job-search/north-east/customer-service-jobs</t>
-        </is>
-      </c>
-      <c r="F150" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G150" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H150"/>
+  <autoFilter ref="A1:H149"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6508,7 +6470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F267"/>
+  <dimension ref="A1:F300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6559,16 +6521,16 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Wakefield</t>
+          <t>Nottingham</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>0</v>
@@ -6583,16 +6545,16 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Bolton</t>
+          <t>Wakefield</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - Wigan &amp; Bolton</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>0</v>
@@ -6607,12 +6569,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Bolton</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Greater Manchester - Wigan &amp; Bolton</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
@@ -6631,16 +6593,16 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Chester</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>0</v>
@@ -6655,12 +6617,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Durham</t>
+          <t>Chester</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -6679,12 +6641,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Gateshead</t>
+          <t>Durham</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -6703,12 +6665,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Maidstone</t>
+          <t>Gateshead</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -6823,12 +6785,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Bracknell</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -6847,12 +6809,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Brighouse</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -6871,12 +6833,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Chelmsford</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Scotland Central - Tayside</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -6895,12 +6857,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Hemel Hempstead</t>
+          <t>Chester Le Street</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -6919,12 +6881,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>High Wycombe</t>
+          <t>Hemel Hempstead</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -6943,12 +6905,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Scarborough</t>
+          <t>High Wycombe</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -6967,12 +6929,12 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Swindon</t>
+          <t>Macclesfield</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -6991,7 +6953,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Tonbridge</t>
+          <t>Maidstone</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -7010,226 +6972,194 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Newtownabbey</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>/manchester/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Newcastle</t>
+          <t>Rotherham</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>/newcastle/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Scarborough</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>/birmingham/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Bristol</t>
+          <t>Stockport</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>/bristol/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Belfast</t>
+          <t>Stoke-on-trent</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>/belfast/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>/leeds/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Swindon</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Merseyside - Liverpool</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>/liverpool/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Hull</t>
+          <t>Tonbridge</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - East</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>/hull/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -7239,23 +7169,23 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Glasgow</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Scotland West - Glasgow</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>/glasgow/service-administrator-jobs</t>
+          <t>/manchester/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7267,23 +7197,23 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Bradford</t>
+          <t>Newcastle</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>/bradford/service-administrator-jobs</t>
+          <t>/newcastle/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7295,23 +7225,23 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Sheffield</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="E31" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>/sheffield/service-administrator-jobs</t>
+          <t>/birmingham/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7323,23 +7253,23 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Cardiff</t>
+          <t>Belfast</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Wales South - Cardiff &amp; Vale</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>/cardiff/service-administrator-jobs</t>
+          <t>/belfast/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7351,23 +7281,23 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Bristol</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Scotland Central - Edinburgh &amp; Lothians</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>/edinburgh/service-administrator-jobs</t>
+          <t>/bristol/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7379,23 +7309,23 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Leeds</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>/southampton/service-administrator-jobs, /southampton/support-worker</t>
+          <t>/leeds/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7407,23 +7337,23 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Oxford</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Merseyside - Liverpool</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E35" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>/oxford/service-administrator-jobs</t>
+          <t>/liverpool/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7435,23 +7365,23 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Cambridge</t>
+          <t>Hull</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Yorkshire - East</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>/cambridge/service-administrator-jobs</t>
+          <t>/hull/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7463,7 +7393,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Doncaster</t>
+          <t>Sheffield</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -7472,14 +7402,14 @@
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E37" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>/doncaster/service-administrator-jobs</t>
+          <t>/sheffield/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7491,23 +7421,23 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Peterborough</t>
+          <t>Glasgow</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Scotland West - Glasgow</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E38" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>/peterborough/service-administrator-jobs</t>
+          <t>/glasgow/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7519,23 +7449,23 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>York</t>
+          <t>Bradford</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E39" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>/york/service-administrator-jobs</t>
+          <t>/bradford/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7547,23 +7477,23 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove</t>
+          <t>Cardiff</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Wales South - Cardiff &amp; Vale</t>
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>/brighton-hove/service-administrator-jobs</t>
+          <t>/cardiff/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7575,23 +7505,23 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Warrington</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - Warrington &amp; Halton</t>
+          <t>Scotland Central - Edinburgh &amp; Lothians</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E41" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>/warrington/service-administrator-jobs</t>
+          <t>/edinburgh/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7603,23 +7533,23 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E42" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>/coventry/service-administrator-jobs</t>
+          <t>/southampton/service-administrator-jobs, /southampton/support-worker</t>
         </is>
       </c>
     </row>
@@ -7631,23 +7561,23 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Huddersfield</t>
+          <t>Cambridge</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E43" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>/huddersfield/service-administrator-jobs</t>
+          <t>/cambridge/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7659,213 +7589,245 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Barnsley</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr"/>
+          <t>Peterborough</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Cambridgeshire</t>
+        </is>
+      </c>
       <c r="D44" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>/barnsley/service-administrator-jobs</t>
+          <t>/peterborough/service-administrator-jobs</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Doncaster</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>/doncaster/service-administrator-jobs</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Wandsworth</t>
+          <t>Oxford</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>/oxford/service-administrator-jobs</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Borehamwood</t>
+          <t>York</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D47" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>/york/service-administrator-jobs</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Croydon</t>
+          <t>Brighton &amp; Hove</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>/brighton-hove/service-administrator-jobs</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Harrow</t>
+          <t>Huddersfield</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D49" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>/huddersfield/service-administrator-jobs</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Isleworth</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>/coventry/service-administrator-jobs</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Uxbridge</t>
+          <t>Warrington</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Cheshire - Warrington &amp; Halton</t>
         </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>/warrington/service-administrator-jobs</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Brentford</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>London</t>
-        </is>
-      </c>
+          <t>Barnsley</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr"/>
       <c r="D52" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>/barnsley/service-administrator-jobs</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -7875,7 +7837,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Sutton</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -7884,7 +7846,7 @@
         </is>
       </c>
       <c r="D53" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E53" s="5" t="n">
         <v>0</v>
@@ -7899,7 +7861,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Harrow</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -7908,7 +7870,7 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E54" s="3" t="n">
         <v>0</v>
@@ -7923,7 +7885,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Beckenham</t>
+          <t>Borehamwood</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -7932,7 +7894,7 @@
         </is>
       </c>
       <c r="D55" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E55" s="5" t="n">
         <v>0</v>
@@ -7947,7 +7909,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Bushey</t>
+          <t>Croydon</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -7956,7 +7918,7 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E56" s="3" t="n">
         <v>0</v>
@@ -7971,7 +7933,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Carshalton</t>
+          <t>Isleworth</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -7980,7 +7942,7 @@
         </is>
       </c>
       <c r="D57" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E57" s="5" t="n">
         <v>0</v>
@@ -7995,7 +7957,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Chessington</t>
+          <t>Sutton</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -8004,7 +7966,7 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E58" s="3" t="n">
         <v>0</v>
@@ -8019,7 +7981,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Dagenham</t>
+          <t>Uxbridge</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -8028,7 +7990,7 @@
         </is>
       </c>
       <c r="D59" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E59" s="5" t="n">
         <v>0</v>
@@ -8043,7 +8005,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Enfield</t>
+          <t>Wandsworth</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -8052,7 +8014,7 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E60" s="3" t="n">
         <v>0</v>
@@ -8067,7 +8029,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Hornchurch</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -8076,7 +8038,7 @@
         </is>
       </c>
       <c r="D61" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61" s="5" t="n">
         <v>0</v>
@@ -8091,7 +8053,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Ilford</t>
+          <t>Kingston Upon Thames</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -8100,7 +8062,7 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62" s="3" t="n">
         <v>0</v>
@@ -8115,7 +8077,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Islington</t>
+          <t>Morden</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -8124,7 +8086,7 @@
         </is>
       </c>
       <c r="D63" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63" s="5" t="n">
         <v>0</v>
@@ -8139,7 +8101,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Kingston Upon Thames</t>
+          <t>Southall</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -8148,7 +8110,7 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64" s="3" t="n">
         <v>0</v>
@@ -8163,7 +8125,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Lambeth</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -8187,7 +8149,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Morden</t>
+          <t>Beckenham</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -8211,7 +8173,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Rainham</t>
+          <t>Bushey</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -8235,7 +8197,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Sidcup</t>
+          <t>Carshalton</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -8259,7 +8221,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Southall</t>
+          <t>Chessington</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -8283,7 +8245,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Sutton-in-ashfield</t>
+          <t>Dagenham</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -8302,21 +8264,21 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>HOLD – LONDON</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Aylesbury</t>
+          <t>Enfield</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D71" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E71" s="5" t="n">
         <v>0</v>
@@ -8326,21 +8288,21 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>HOLD – LONDON</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Chelmsford</t>
+          <t>Hayes</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E72" s="3" t="n">
         <v>0</v>
@@ -8350,21 +8312,21 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>HOLD – LONDON</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Chester Le Street</t>
+          <t>Hornchurch</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D73" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E73" s="5" t="n">
         <v>0</v>
@@ -8374,21 +8336,21 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>HOLD – LONDON</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Crewe</t>
+          <t>Ilford</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E74" s="3" t="n">
         <v>0</v>
@@ -8398,21 +8360,21 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>HOLD – LONDON</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Darlington</t>
+          <t>Islington</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D75" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E75" s="5" t="n">
         <v>0</v>
@@ -8422,21 +8384,21 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>HOLD – LONDON</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Eastleigh</t>
+          <t>Lambeth</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E76" s="3" t="n">
         <v>0</v>
@@ -8446,21 +8408,21 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>HOLD – LONDON</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Epsom</t>
+          <t>Rainham</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D77" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E77" s="5" t="n">
         <v>0</v>
@@ -8470,21 +8432,21 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>HOLD – LONDON</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Fareham</t>
+          <t>Ruislip</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E78" s="3" t="n">
         <v>0</v>
@@ -8494,21 +8456,21 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>HOLD – LONDON</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Sidcup</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D79" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E79" s="5" t="n">
         <v>0</v>
@@ -8518,21 +8480,21 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>HOLD – LONDON</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Gloucester</t>
+          <t>Stanmore</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E80" s="3" t="n">
         <v>0</v>
@@ -8542,21 +8504,21 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>HOLD – LONDON</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Harrogate</t>
+          <t>Sutton-in-ashfield</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D81" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E81" s="5" t="n">
         <v>0</v>
@@ -8566,21 +8528,21 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>HOLD – LONDON</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Hastings</t>
+          <t>Worcester Park</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E82" s="3" t="n">
         <v>0</v>
@@ -8595,12 +8557,12 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Inverness</t>
+          <t>Aylesbury</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D83" s="5" t="n">
@@ -8619,12 +8581,12 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Leicester</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D84" s="3" t="n">
@@ -8643,12 +8605,12 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Macclesfield</t>
+          <t>Bracknell</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D85" s="5" t="n">
@@ -8667,12 +8629,12 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Milton Keynes</t>
+          <t>Brighouse</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D86" s="3" t="n">
@@ -8691,12 +8653,12 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Newry</t>
+          <t>Crawley</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D87" s="5" t="n">
@@ -8715,12 +8677,12 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Nottingham</t>
+          <t>Crewe</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Nottinghamshire</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D88" s="3" t="n">
@@ -8739,12 +8701,12 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Redhill</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D89" s="5" t="n">
@@ -8763,7 +8725,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Ringwood</t>
+          <t>Eastleigh</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -8787,12 +8749,12 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Rotherham</t>
+          <t>Epsom</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D91" s="5" t="n">
@@ -8811,12 +8773,12 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Solihull</t>
+          <t>Fareham</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D92" s="3" t="n">
@@ -8835,12 +8797,12 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Stoke-on-trent</t>
+          <t>Forfar</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D93" s="5" t="n">
@@ -8859,12 +8821,12 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Winchester</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D94" s="3" t="n">
@@ -8883,16 +8845,16 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Alresford</t>
+          <t>Gloucester</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D95" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E95" s="5" t="n">
         <v>0</v>
@@ -8907,16 +8869,16 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Barrow-in-furness</t>
+          <t>Harrogate</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Cumbria - South</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E96" s="3" t="n">
         <v>0</v>
@@ -8931,16 +8893,16 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hastings</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D97" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E97" s="5" t="n">
         <v>0</v>
@@ -8955,16 +8917,16 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Inverness</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E98" s="3" t="n">
         <v>0</v>
@@ -8979,16 +8941,16 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Berwick-upon-tweed</t>
+          <t>Leicester</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D99" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E99" s="5" t="n">
         <v>0</v>
@@ -9003,16 +8965,16 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Chelmsley Wood</t>
+          <t>Luton</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E100" s="3" t="n">
         <v>0</v>
@@ -9027,16 +8989,16 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Crawley</t>
+          <t>Newry</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D101" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E101" s="5" t="n">
         <v>0</v>
@@ -9051,16 +9013,16 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Dewsbury</t>
+          <t>Northwich</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E102" s="3" t="n">
         <v>0</v>
@@ -9075,16 +9037,16 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Dorking</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D103" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E103" s="5" t="n">
         <v>0</v>
@@ -9099,16 +9061,16 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Driffield</t>
+          <t>Redhill</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - East</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E104" s="3" t="n">
         <v>0</v>
@@ -9123,16 +9085,16 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Eastbourne</t>
+          <t>Ringwood</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D105" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E105" s="5" t="n">
         <v>0</v>
@@ -9147,16 +9109,16 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Ellesmere Port</t>
+          <t>Shrewsbury</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Shropshire</t>
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>0</v>
@@ -9171,16 +9133,16 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Exeter</t>
+          <t>Solihull</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D107" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E107" s="5" t="n">
         <v>0</v>
@@ -9195,16 +9157,16 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Forfar</t>
+          <t>Torquay</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Scotland Central - Tayside</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E108" s="3" t="n">
         <v>0</v>
@@ -9219,16 +9181,16 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Hebburn</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D109" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E109" s="5" t="n">
         <v>0</v>
@@ -9243,16 +9205,16 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Hessle</t>
+          <t>Winchester</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - East</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E110" s="3" t="n">
         <v>0</v>
@@ -9267,12 +9229,12 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Huntingdon</t>
+          <t>Alresford</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D111" s="5" t="n">
@@ -9291,12 +9253,12 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Kettering</t>
+          <t>Amersham</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D112" s="3" t="n">
@@ -9315,12 +9277,12 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Knaresborough</t>
+          <t>Ballyclare</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D113" s="5" t="n">
@@ -9339,12 +9301,12 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Knutsford</t>
+          <t>Ballymena</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D114" s="3" t="n">
@@ -9363,12 +9325,12 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Lichfield</t>
+          <t>Berwick-upon-tweed</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D115" s="5" t="n">
@@ -9387,12 +9349,12 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Bury St Edmunds</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D116" s="3" t="n">
@@ -9411,12 +9373,12 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Lingfield</t>
+          <t>Carrickfergus</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D117" s="5" t="n">
@@ -9435,12 +9397,12 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Newtownabbey</t>
+          <t>Cheadle</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D118" s="3" t="n">
@@ -9459,12 +9421,12 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Chelmsley Wood</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D119" s="5" t="n">
@@ -9483,12 +9445,12 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Romsey</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Derbyshire</t>
         </is>
       </c>
       <c r="D120" s="3" t="n">
@@ -9507,12 +9469,12 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Sale</t>
+          <t>Dewsbury</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D121" s="5" t="n">
@@ -9531,12 +9493,12 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Slough</t>
+          <t>Dorking</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D122" s="3" t="n">
@@ -9555,12 +9517,12 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Stafford</t>
+          <t>Driffield</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Yorkshire - East</t>
         </is>
       </c>
       <c r="D123" s="5" t="n">
@@ -9579,12 +9541,12 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Staines</t>
+          <t>Eastbourne</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D124" s="3" t="n">
@@ -9603,12 +9565,12 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Stockport</t>
+          <t>Ellesmere Port</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D125" s="5" t="n">
@@ -9627,12 +9589,12 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Tipton</t>
+          <t>Exeter</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D126" s="3" t="n">
@@ -9651,12 +9613,12 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Hebburn</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D127" s="5" t="n">
@@ -9675,12 +9637,12 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Weston-super-mare</t>
+          <t>Hessle</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Yorkshire - East</t>
         </is>
       </c>
       <c r="D128" s="3" t="n">
@@ -9699,12 +9661,12 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Worcester</t>
+          <t>Horsham</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Worcestershire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D129" s="5" t="n">
@@ -9723,16 +9685,16 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Huntingdon</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D130" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E130" s="3" t="n">
         <v>0</v>
@@ -9747,16 +9709,16 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Aldershot</t>
+          <t>Kettering</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D131" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E131" s="5" t="n">
         <v>0</v>
@@ -9771,16 +9733,16 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Alton</t>
+          <t>Knaresborough</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D132" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E132" s="3" t="n">
         <v>0</v>
@@ -9795,16 +9757,16 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Amersham</t>
+          <t>Knutsford</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D133" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E133" s="5" t="n">
         <v>0</v>
@@ -9819,16 +9781,16 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Ballyclare</t>
+          <t>Lichfield</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D134" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -9843,16 +9805,16 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Ballymena</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D135" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E135" s="5" t="n">
         <v>0</v>
@@ -9867,16 +9829,16 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Barry</t>
+          <t>Lingfield</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Wales South - Cardiff &amp; Vale</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D136" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E136" s="3" t="n">
         <v>0</v>
@@ -9891,16 +9853,16 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Basingstoke</t>
+          <t>Lisburn</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D137" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E137" s="5" t="n">
         <v>0</v>
@@ -9915,16 +9877,16 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Batley</t>
+          <t>Milton Keynes</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D138" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E138" s="3" t="n">
         <v>0</v>
@@ -9939,16 +9901,16 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Berkhamsted</t>
+          <t>Newbury</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D139" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E139" s="5" t="n">
         <v>0</v>
@@ -9963,16 +9925,16 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Bicester</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D140" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E140" s="3" t="n">
         <v>0</v>
@@ -9987,16 +9949,16 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Bingley</t>
+          <t>Rickmansworth</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D141" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E141" s="5" t="n">
         <v>0</v>
@@ -10011,16 +9973,16 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Bishop Auckland</t>
+          <t>Romsey</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D142" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E142" s="3" t="n">
         <v>0</v>
@@ -10035,16 +9997,16 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Bishop's Stortford</t>
+          <t>Salisbury</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D143" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E143" s="5" t="n">
         <v>0</v>
@@ -10059,16 +10021,16 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Bognor Regis</t>
+          <t>Slough</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D144" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E144" s="3" t="n">
         <v>0</v>
@@ -10083,16 +10045,16 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Staines</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D145" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E145" s="5" t="n">
         <v>0</v>
@@ -10107,16 +10069,16 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Stroud</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D146" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E146" s="3" t="n">
         <v>0</v>
@@ -10131,16 +10093,16 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Brentwood</t>
+          <t>Taunton</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D147" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E147" s="5" t="n">
         <v>0</v>
@@ -10155,16 +10117,16 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Bridport</t>
+          <t>Tipton</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D148" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E148" s="3" t="n">
         <v>0</v>
@@ -10179,16 +10141,16 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Brinsworth</t>
+          <t>Wellington</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>Shropshire</t>
         </is>
       </c>
       <c r="D149" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E149" s="5" t="n">
         <v>0</v>
@@ -10203,16 +10165,16 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Buckingham</t>
+          <t>Weston-super-mare</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D150" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E150" s="3" t="n">
         <v>0</v>
@@ -10227,7 +10189,7 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Bury St Edmunds</t>
+          <t>Woodbridge</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
@@ -10236,7 +10198,7 @@
         </is>
       </c>
       <c r="D151" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E151" s="5" t="n">
         <v>0</v>
@@ -10251,16 +10213,16 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Cannock</t>
+          <t>Worcester</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Worcestershire</t>
         </is>
       </c>
       <c r="D152" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E152" s="3" t="n">
         <v>0</v>
@@ -10275,16 +10237,16 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Canterbury</t>
+          <t>Yeovil</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D153" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E153" s="5" t="n">
         <v>0</v>
@@ -10299,12 +10261,12 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Cheadle</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D154" s="3" t="n">
@@ -10323,12 +10285,12 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Chertsey</t>
+          <t>Abingdon</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D155" s="5" t="n">
@@ -10347,12 +10309,12 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Chesham</t>
+          <t>Aldershot</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D156" s="3" t="n">
@@ -10371,12 +10333,12 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Alton</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Derbyshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D157" s="5" t="n">
@@ -10395,12 +10357,12 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Chichester</t>
+          <t>Banbury</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D158" s="3" t="n">
@@ -10419,12 +10381,12 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>Cirencester</t>
+          <t>Barrow-in-furness</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Cumbria - South</t>
         </is>
       </c>
       <c r="D159" s="5" t="n">
@@ -10443,12 +10405,12 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Colchester</t>
+          <t>Barry</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Wales South - Cardiff &amp; Vale</t>
         </is>
       </c>
       <c r="D160" s="3" t="n">
@@ -10467,12 +10429,12 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Cottingham</t>
+          <t>Basingstoke</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - East</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D161" s="5" t="n">
@@ -10491,12 +10453,12 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Cramlington</t>
+          <t>Batley</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D162" s="3" t="n">
@@ -10515,12 +10477,12 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>Cranbrook</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D163" s="5" t="n">
@@ -10539,12 +10501,12 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Dartford</t>
+          <t>Berkhamsted</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D164" s="3" t="n">
@@ -10563,12 +10525,12 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Droitwich</t>
+          <t>Bexhill-on-sea</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Worcestershire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D165" s="5" t="n">
@@ -10587,12 +10549,12 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Dudley</t>
+          <t>Bicester</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D166" s="3" t="n">
@@ -10611,12 +10573,12 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Fakenham</t>
+          <t>Biggleswade</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D167" s="5" t="n">
@@ -10635,12 +10597,12 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Falmouth</t>
+          <t>Bingley</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D168" s="3" t="n">
@@ -10659,12 +10621,12 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Farnham</t>
+          <t>Bishop Auckland</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D169" s="5" t="n">
@@ -10683,12 +10645,12 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Faversham</t>
+          <t>Bishop's Stortford</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D170" s="3" t="n">
@@ -10707,12 +10669,12 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Faygate</t>
+          <t>Brentwood</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D171" s="5" t="n">
@@ -10731,12 +10693,12 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Felixstowe</t>
+          <t>Bridport</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D172" s="3" t="n">
@@ -10755,12 +10717,12 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Fetcham</t>
+          <t>Brinsworth</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D173" s="5" t="n">
@@ -10779,12 +10741,12 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Frome</t>
+          <t>Buckingham</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D174" s="3" t="n">
@@ -10803,12 +10765,12 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Godalming</t>
+          <t>Cannock</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D175" s="5" t="n">
@@ -10827,12 +10789,12 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Gosport</t>
+          <t>Canterbury</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D176" s="3" t="n">
@@ -10851,12 +10813,12 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Great Yarmouth</t>
+          <t>Chatham</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D177" s="5" t="n">
@@ -10875,7 +10837,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Guildford</t>
+          <t>Chertsey</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -10899,7 +10861,7 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Hailsham</t>
+          <t>Chichester</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
@@ -10923,12 +10885,12 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Harlow</t>
+          <t>Chippenham</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D180" s="3" t="n">
@@ -10947,12 +10909,12 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Hartlepool</t>
+          <t>Cirencester</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D181" s="5" t="n">
@@ -10971,12 +10933,12 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Havant</t>
+          <t>Coalville</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D182" s="3" t="n">
@@ -10995,12 +10957,12 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Henley-on-thames</t>
+          <t>Cobham</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D183" s="5" t="n">
@@ -11019,12 +10981,12 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Horley</t>
+          <t>Colchester</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D184" s="3" t="n">
@@ -11043,12 +11005,12 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Horsham</t>
+          <t>Corby</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D185" s="5" t="n">
@@ -11067,12 +11029,12 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Hove</t>
+          <t>Cottingham</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Yorkshire - East</t>
         </is>
       </c>
       <c r="D186" s="3" t="n">
@@ -11091,12 +11053,12 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Keighley</t>
+          <t>Cramlington</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D187" s="5" t="n">
@@ -11115,12 +11077,12 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Kenilworth</t>
+          <t>Cranbrook</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D188" s="3" t="n">
@@ -11139,12 +11101,12 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Kings Langley</t>
+          <t>Darlington</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D189" s="5" t="n">
@@ -11163,12 +11125,12 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Knowle</t>
+          <t>Dartford</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D190" s="3" t="n">
@@ -11187,12 +11149,12 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Leamington Spa</t>
+          <t>Droitwich</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Worcestershire</t>
         </is>
       </c>
       <c r="D191" s="5" t="n">
@@ -11211,12 +11173,12 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Lisburn</t>
+          <t>Dudley</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D192" s="3" t="n">
@@ -11235,12 +11197,12 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>East Grinstead</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>Scotland Central - Edinburgh &amp; Lothians</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D193" s="5" t="n">
@@ -11259,12 +11221,12 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Loughborough</t>
+          <t>Ely</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D194" s="3" t="n">
@@ -11283,12 +11245,12 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Luton</t>
+          <t>Fakenham</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D195" s="5" t="n">
@@ -11307,12 +11269,12 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Maidenhead</t>
+          <t>Falmouth</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D196" s="3" t="n">
@@ -11331,12 +11293,12 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Mansfield</t>
+          <t>Farnham</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>Nottinghamshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D197" s="5" t="n">
@@ -11355,12 +11317,12 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Marlborough</t>
+          <t>Faygate</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D198" s="3" t="n">
@@ -11379,12 +11341,12 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Marlow</t>
+          <t>Felixstowe</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D199" s="5" t="n">
@@ -11403,12 +11365,12 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Montrose</t>
+          <t>Fetcham</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D200" s="3" t="n">
@@ -11427,12 +11389,12 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Nantwich</t>
+          <t>Frome</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D201" s="5" t="n">
@@ -11451,12 +11413,12 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Newbury</t>
+          <t>Gainsborough</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D202" s="3" t="n">
@@ -11475,12 +11437,12 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Normanton</t>
+          <t>Godalming</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D203" s="5" t="n">
@@ -11499,12 +11461,12 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Northampton</t>
+          <t>Godstone</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D204" s="3" t="n">
@@ -11523,12 +11485,12 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Northwich</t>
+          <t>Goole</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Yorkshire - East</t>
         </is>
       </c>
       <c r="D205" s="5" t="n">
@@ -11547,12 +11509,12 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Nuneaton</t>
+          <t>Gosport</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D206" s="3" t="n">
@@ -11571,12 +11533,12 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Okehampton</t>
+          <t>Great Yarmouth</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D207" s="5" t="n">
@@ -11595,12 +11557,12 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Otley</t>
+          <t>Grimsby</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D208" s="3" t="n">
@@ -11619,7 +11581,7 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Oxted</t>
+          <t>Guildford</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
@@ -11643,12 +11605,12 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Peterlee</t>
+          <t>Hailsham</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D210" s="3" t="n">
@@ -11667,12 +11629,12 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Pickering</t>
+          <t>Harlow</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D211" s="5" t="n">
@@ -11691,12 +11653,12 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Hartlepool</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D212" s="3" t="n">
@@ -11715,12 +11677,12 @@
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>Pontypridd</t>
+          <t>Hatfield</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>Wales South - Valleys</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D213" s="5" t="n">
@@ -11739,12 +11701,12 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Poole</t>
+          <t>Havant</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D214" s="3" t="n">
@@ -11763,12 +11725,12 @@
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>Portishead</t>
+          <t>Henley-on-thames</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D215" s="5" t="n">
@@ -11787,12 +11749,12 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Potters Bar</t>
+          <t>Horley</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D216" s="3" t="n">
@@ -11811,12 +11773,12 @@
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>Pudsey</t>
+          <t>Hove</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D217" s="5" t="n">
@@ -11835,12 +11797,12 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Ramsgate</t>
+          <t>Jarrow</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D218" s="3" t="n">
@@ -11859,12 +11821,12 @@
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>Redruth</t>
+          <t>Keighley</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D219" s="5" t="n">
@@ -11883,12 +11845,12 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Ripon</t>
+          <t>Kenilworth</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D220" s="3" t="n">
@@ -11907,12 +11869,12 @@
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Rochester</t>
+          <t>Kirriemuir</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D221" s="5" t="n">
@@ -11931,12 +11893,12 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Royston</t>
+          <t>Knowle</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D222" s="3" t="n">
@@ -11955,12 +11917,12 @@
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>Runcorn</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - Warrington &amp; Halton</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D223" s="5" t="n">
@@ -11979,12 +11941,12 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>Rushden</t>
+          <t>Leamington Spa</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D224" s="3" t="n">
@@ -12003,12 +11965,12 @@
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>Ryton</t>
+          <t>Leatherhead</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D225" s="5" t="n">
@@ -12027,12 +11989,12 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>Salisbury</t>
+          <t>Liskeard</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D226" s="3" t="n">
@@ -12051,12 +12013,12 @@
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>Sandy</t>
+          <t>Littlehampton</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D227" s="5" t="n">
@@ -12075,12 +12037,12 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>Scunthorpe</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Scotland Central - Edinburgh &amp; Lothians</t>
         </is>
       </c>
       <c r="D228" s="3" t="n">
@@ -12099,12 +12061,12 @@
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>Sevenoaks</t>
+          <t>Loughborough</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D229" s="5" t="n">
@@ -12123,12 +12085,12 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>Shepperton</t>
+          <t>Lutterworth</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D230" s="3" t="n">
@@ -12147,12 +12109,12 @@
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>Sherborne</t>
+          <t>Maidenhead</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D231" s="5" t="n">
@@ -12171,12 +12133,12 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Shrewsbury</t>
+          <t>Mansfield</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Shropshire</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D232" s="3" t="n">
@@ -12195,12 +12157,12 @@
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>Snodland</t>
+          <t>Marlborough</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D233" s="5" t="n">
@@ -12219,12 +12181,12 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Southam</t>
+          <t>Marlow</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D234" s="3" t="n">
@@ -12243,12 +12205,12 @@
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>Southend-on-sea</t>
+          <t>Nantwich</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D235" s="5" t="n">
@@ -12267,12 +12229,12 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Spalding</t>
+          <t>Newquay</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D236" s="3" t="n">
@@ -12291,12 +12253,12 @@
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>St. Ives</t>
+          <t>Newtownards</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D237" s="5" t="n">
@@ -12315,12 +12277,12 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>St. Neots</t>
+          <t>Northampton</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D238" s="3" t="n">
@@ -12339,12 +12301,12 @@
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>Stanley</t>
+          <t>Nuneaton</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D239" s="5" t="n">
@@ -12363,12 +12325,12 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Okehampton</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D240" s="3" t="n">
@@ -12387,12 +12349,12 @@
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>Stratford-upon-avon</t>
+          <t>Otley</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D241" s="5" t="n">
@@ -12411,12 +12373,12 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>Stretford</t>
+          <t>Oxted</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D242" s="3" t="n">
@@ -12435,12 +12397,12 @@
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>Stroud</t>
+          <t>Pickering</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D243" s="5" t="n">
@@ -12459,12 +12421,12 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Pontypridd</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Wales South - Valleys</t>
         </is>
       </c>
       <c r="D244" s="3" t="n">
@@ -12483,12 +12445,12 @@
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>Tadworth</t>
+          <t>Poole</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D245" s="5" t="n">
@@ -12507,12 +12469,12 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>Tamworth</t>
+          <t>Portishead</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D246" s="3" t="n">
@@ -12531,12 +12493,12 @@
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>Taunton</t>
+          <t>Potters Bar</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D247" s="5" t="n">
@@ -12555,12 +12517,12 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>Telford</t>
+          <t>Pudsey</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Shropshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D248" s="3" t="n">
@@ -12579,12 +12541,12 @@
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>Thatcham</t>
+          <t>Ramsgate</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D249" s="5" t="n">
@@ -12603,12 +12565,12 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>Thetford</t>
+          <t>Redditch</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Worcestershire</t>
         </is>
       </c>
       <c r="D250" s="3" t="n">
@@ -12627,7 +12589,7 @@
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>Truro</t>
+          <t>Redruth</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
@@ -12651,12 +12613,12 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>Tunbridge Wells</t>
+          <t>Reigate</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D252" s="3" t="n">
@@ -12675,12 +12637,12 @@
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Retford</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D253" s="5" t="n">
@@ -12699,12 +12661,12 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Walton-on-thames</t>
+          <t>Ripon</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D254" s="3" t="n">
@@ -12723,12 +12685,12 @@
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Rochester</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D255" s="5" t="n">
@@ -12747,12 +12709,12 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>Wellington</t>
+          <t>Royston</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Shropshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D256" s="3" t="n">
@@ -12771,12 +12733,12 @@
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>Welwyn Garden City</t>
+          <t>Runcorn</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Cheshire - Warrington &amp; Halton</t>
         </is>
       </c>
       <c r="D257" s="5" t="n">
@@ -12795,12 +12757,12 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>West Malling</t>
+          <t>Rushden</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D258" s="3" t="n">
@@ -12819,12 +12781,12 @@
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>Whitby</t>
+          <t>Ryton</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D259" s="5" t="n">
@@ -12843,12 +12805,12 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>Whitstable</t>
+          <t>Sale</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D260" s="3" t="n">
@@ -12867,12 +12829,12 @@
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>Wilmslow</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D261" s="5" t="n">
@@ -12891,12 +12853,12 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Scunthorpe</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D262" s="3" t="n">
@@ -12915,12 +12877,12 @@
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>Winsford</t>
+          <t>Sevenoaks</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D263" s="5" t="n">
@@ -12939,12 +12901,12 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>Wokingham</t>
+          <t>Shepperton</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D264" s="3" t="n">
@@ -12963,12 +12925,12 @@
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>Woodbridge</t>
+          <t>Sherborne</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D265" s="5" t="n">
@@ -12987,12 +12949,12 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>Worthing</t>
+          <t>Shirley</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D266" s="3" t="n">
@@ -13011,12 +12973,12 @@
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>Yeovil</t>
+          <t>Snodland</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D267" s="5" t="n">
@@ -13027,8 +12989,800 @@
       </c>
       <c r="F267" s="4" t="inlineStr"/>
     </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>Southam</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
+        </is>
+      </c>
+      <c r="D268" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E268" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F268" s="2" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="4" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B269" s="4" t="inlineStr">
+        <is>
+          <t>Southend-on-sea</t>
+        </is>
+      </c>
+      <c r="C269" s="4" t="inlineStr">
+        <is>
+          <t>Essex</t>
+        </is>
+      </c>
+      <c r="D269" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E269" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F269" s="4" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>Spalding</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>Lincolnshire</t>
+        </is>
+      </c>
+      <c r="D270" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E270" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F270" s="2" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="4" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B271" s="4" t="inlineStr">
+        <is>
+          <t>Spennymoor</t>
+        </is>
+      </c>
+      <c r="C271" s="4" t="inlineStr">
+        <is>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+        </is>
+      </c>
+      <c r="D271" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E271" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F271" s="4" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>St. Ives</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>Cambridgeshire</t>
+        </is>
+      </c>
+      <c r="D272" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E272" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F272" s="2" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="4" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B273" s="4" t="inlineStr">
+        <is>
+          <t>St. Neots</t>
+        </is>
+      </c>
+      <c r="C273" s="4" t="inlineStr">
+        <is>
+          <t>Cambridgeshire</t>
+        </is>
+      </c>
+      <c r="D273" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E273" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F273" s="4" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>Stafford</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>Staffordshire</t>
+        </is>
+      </c>
+      <c r="D274" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E274" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F274" s="2" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="4" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B275" s="4" t="inlineStr">
+        <is>
+          <t>Stanley</t>
+        </is>
+      </c>
+      <c r="C275" s="4" t="inlineStr">
+        <is>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+        </is>
+      </c>
+      <c r="D275" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E275" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F275" s="4" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>Stevenage</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>Hertfordshire</t>
+        </is>
+      </c>
+      <c r="D276" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E276" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F276" s="2" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="4" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B277" s="4" t="inlineStr">
+        <is>
+          <t>Stratford-upon-avon</t>
+        </is>
+      </c>
+      <c r="C277" s="4" t="inlineStr">
+        <is>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
+        </is>
+      </c>
+      <c r="D277" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E277" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F277" s="4" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>Stretford</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
+        </is>
+      </c>
+      <c r="D278" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E278" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" s="2" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="4" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B279" s="4" t="inlineStr">
+        <is>
+          <t>Tadworth</t>
+        </is>
+      </c>
+      <c r="C279" s="4" t="inlineStr">
+        <is>
+          <t>Surrey</t>
+        </is>
+      </c>
+      <c r="D279" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E279" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F279" s="4" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>Tamworth</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>Staffordshire</t>
+        </is>
+      </c>
+      <c r="D280" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E280" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" s="2" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="4" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B281" s="4" t="inlineStr">
+        <is>
+          <t>Telford</t>
+        </is>
+      </c>
+      <c r="C281" s="4" t="inlineStr">
+        <is>
+          <t>Shropshire</t>
+        </is>
+      </c>
+      <c r="D281" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E281" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" s="4" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>Thame</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>Oxfordshire</t>
+        </is>
+      </c>
+      <c r="D282" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E282" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F282" s="2" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="4" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B283" s="4" t="inlineStr">
+        <is>
+          <t>Thatcham</t>
+        </is>
+      </c>
+      <c r="C283" s="4" t="inlineStr">
+        <is>
+          <t>Berkshire</t>
+        </is>
+      </c>
+      <c r="D283" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E283" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F283" s="4" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>Thetford</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>Norfolk</t>
+        </is>
+      </c>
+      <c r="D284" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E284" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F284" s="2" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="4" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B285" s="4" t="inlineStr">
+        <is>
+          <t>Truro</t>
+        </is>
+      </c>
+      <c r="C285" s="4" t="inlineStr">
+        <is>
+          <t>Cornwall</t>
+        </is>
+      </c>
+      <c r="D285" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E285" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F285" s="4" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>Tunbridge Wells</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>Kent</t>
+        </is>
+      </c>
+      <c r="D286" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E286" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F286" s="2" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="4" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B287" s="4" t="inlineStr">
+        <is>
+          <t>Walsall</t>
+        </is>
+      </c>
+      <c r="C287" s="4" t="inlineStr">
+        <is>
+          <t>West Midlands - Black Country</t>
+        </is>
+      </c>
+      <c r="D287" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E287" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F287" s="4" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>Walton-on-thames</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>Surrey</t>
+        </is>
+      </c>
+      <c r="D288" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E288" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F288" s="2" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="4" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B289" s="4" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="C289" s="4" t="inlineStr">
+        <is>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+        </is>
+      </c>
+      <c r="D289" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E289" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F289" s="4" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>Wednesbury</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>West Midlands - Black Country</t>
+        </is>
+      </c>
+      <c r="D290" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E290" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F290" s="2" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="4" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B291" s="4" t="inlineStr">
+        <is>
+          <t>Wellingborough</t>
+        </is>
+      </c>
+      <c r="C291" s="4" t="inlineStr">
+        <is>
+          <t>Northamptonshire</t>
+        </is>
+      </c>
+      <c r="D291" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E291" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F291" s="4" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>Welwyn Garden City</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>Hertfordshire</t>
+        </is>
+      </c>
+      <c r="D292" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E292" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F292" s="2" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="4" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B293" s="4" t="inlineStr">
+        <is>
+          <t>West Malling</t>
+        </is>
+      </c>
+      <c r="C293" s="4" t="inlineStr">
+        <is>
+          <t>Kent</t>
+        </is>
+      </c>
+      <c r="D293" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E293" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F293" s="4" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>Weymouth</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>Dorset</t>
+        </is>
+      </c>
+      <c r="D294" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E294" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F294" s="2" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="4" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B295" s="4" t="inlineStr">
+        <is>
+          <t>Whitby</t>
+        </is>
+      </c>
+      <c r="C295" s="4" t="inlineStr">
+        <is>
+          <t>Yorkshire - North</t>
+        </is>
+      </c>
+      <c r="D295" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E295" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F295" s="4" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>Whitstable</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>Kent</t>
+        </is>
+      </c>
+      <c r="D296" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E296" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F296" s="2" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="4" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B297" s="4" t="inlineStr">
+        <is>
+          <t>Wilmslow</t>
+        </is>
+      </c>
+      <c r="C297" s="4" t="inlineStr">
+        <is>
+          <t>Cheshire - East</t>
+        </is>
+      </c>
+      <c r="D297" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E297" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F297" s="4" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>Windsor</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>Berkshire</t>
+        </is>
+      </c>
+      <c r="D298" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E298" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F298" s="2" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="4" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B299" s="4" t="inlineStr">
+        <is>
+          <t>Winsford</t>
+        </is>
+      </c>
+      <c r="C299" s="4" t="inlineStr">
+        <is>
+          <t>Cheshire - West</t>
+        </is>
+      </c>
+      <c r="D299" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E299" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F299" s="4" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>Worthing</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>Sussex</t>
+        </is>
+      </c>
+      <c r="D300" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E300" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F300" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F267"/>
+  <autoFilter ref="A1:F300"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13107,7 +13861,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr"/>
@@ -13124,15 +13878,15 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E3" s="4" t="inlineStr"/>
       <c r="F3" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
       <c r="H3" s="5" t="n">
@@ -13147,7 +13901,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="3" t="n">
@@ -13178,12 +13932,12 @@
       <c r="D5" s="4" t="inlineStr"/>
       <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr"/>
       <c r="I5" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -13193,13 +13947,13 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr"/>
@@ -13212,7 +13966,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr"/>
@@ -13235,8 +13989,10 @@
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="3" t="n">
-        <v>6</v>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr"/>
@@ -13248,13 +14004,13 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr"/>
       <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="4" t="inlineStr"/>
@@ -13267,7 +14023,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr"/>
@@ -13300,7 +14056,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
@@ -13348,7 +14104,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
       <c r="D15" s="4" t="inlineStr"/>
@@ -13369,7 +14125,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr"/>
@@ -13386,7 +14142,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
       <c r="D17" s="4" t="inlineStr"/>
@@ -13394,7 +14150,7 @@
         <v>5</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="4" t="inlineStr"/>
@@ -13407,7 +14163,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr"/>
@@ -13430,15 +14186,15 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
       <c r="D19" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="5" t="n">
@@ -13468,7 +14224,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C21" s="4" t="inlineStr"/>
       <c r="D21" s="4" t="inlineStr"/>
@@ -13485,7 +14241,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="2" t="inlineStr"/>
@@ -13502,10 +14258,10 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D23" s="4" t="inlineStr"/>
       <c r="E23" s="4" t="inlineStr"/>
@@ -13538,11 +14294,11 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
       <c r="D25" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
       <c r="F25" s="5" t="n">
@@ -13559,10 +14315,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>11</v>
@@ -13674,7 +14430,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C33" s="4" t="inlineStr"/>
       <c r="D33" s="4" t="inlineStr"/>
@@ -13691,28 +14447,28 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -13722,13 +14478,13 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
       <c r="D35" s="4" t="inlineStr"/>
       <c r="E35" s="4" t="inlineStr"/>
       <c r="F35" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G35" s="4" t="inlineStr"/>
       <c r="H35" s="4" t="inlineStr"/>
@@ -13786,7 +14542,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C39" s="4" t="inlineStr"/>
       <c r="D39" s="4" t="inlineStr"/>
@@ -13807,7 +14563,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>2</v>
@@ -13836,7 +14592,7 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C41" s="4" t="inlineStr"/>
       <c r="D41" s="4" t="inlineStr"/>
@@ -13883,7 +14639,7 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="inlineStr"/>
@@ -13900,7 +14656,7 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C45" s="4" t="inlineStr"/>
       <c r="D45" s="4" t="inlineStr"/>
@@ -13936,7 +14692,7 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="C47" s="4" t="inlineStr"/>
       <c r="D47" s="4" t="inlineStr"/>
@@ -13955,7 +14711,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>3</v>
@@ -13963,7 +14719,7 @@
       <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr"/>
@@ -14006,7 +14762,7 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C51" s="4" t="inlineStr"/>
       <c r="D51" s="4" t="inlineStr"/>
@@ -14053,7 +14809,7 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C54" s="2" t="inlineStr"/>
       <c r="D54" s="2" t="inlineStr"/>
@@ -14089,7 +14845,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr"/>
       <c r="D56" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr"/>
@@ -14134,7 +14890,7 @@
         </is>
       </c>
       <c r="B59" s="5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C59" s="4" t="inlineStr"/>
       <c r="D59" s="4" t="inlineStr"/>
@@ -14155,7 +14911,7 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C60" s="2" t="inlineStr"/>
       <c r="D60" s="2" t="inlineStr"/>
@@ -14172,7 +14928,7 @@
         </is>
       </c>
       <c r="B61" s="5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C61" s="4" t="inlineStr"/>
       <c r="D61" s="4" t="inlineStr"/>
@@ -14191,7 +14947,7 @@
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C62" s="2" t="inlineStr"/>
       <c r="D62" s="2" t="inlineStr"/>
@@ -14210,10 +14966,10 @@
         </is>
       </c>
       <c r="B63" s="5" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D63" s="5" t="n">
         <v>7</v>
@@ -14235,7 +14991,7 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C64" s="3" t="n">
         <v>4</v>
@@ -14288,7 +15044,7 @@
         </is>
       </c>
       <c r="B67" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C67" s="4" t="inlineStr"/>
       <c r="D67" s="4" t="inlineStr"/>
@@ -14352,17 +15108,17 @@
         </is>
       </c>
       <c r="B71" s="5" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C71" s="4" t="inlineStr"/>
       <c r="D71" s="4" t="inlineStr"/>
       <c r="E71" s="4" t="inlineStr"/>
       <c r="F71" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G71" s="4" t="inlineStr"/>
       <c r="H71" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I71" s="4" t="inlineStr"/>
     </row>
@@ -14373,7 +15129,7 @@
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C72" s="2" t="inlineStr"/>
       <c r="D72" s="2" t="inlineStr"/>
@@ -14390,7 +15146,7 @@
         </is>
       </c>
       <c r="B73" s="5" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C73" s="4" t="inlineStr"/>
       <c r="D73" s="4" t="inlineStr"/>
@@ -14407,7 +15163,7 @@
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C74" s="3" t="n">
         <v>2</v>
@@ -14481,7 +15237,7 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
@@ -14502,13 +15258,13 @@
         </is>
       </c>
       <c r="B79" s="5" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C79" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E79" s="4" t="inlineStr"/>
       <c r="F79" s="4" t="inlineStr"/>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sitewide'!$A$1:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'JobG8 categories'!$A$1:$C$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'PAGES'!$A$1:$H$149</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'PAGES'!$A$1:$H$159</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$F$300</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'LIVE'!$A$1:$I$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'NOT LIVE'!$A$1:$I$79</definedName>
@@ -645,10 +645,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2478</v>
+        <v>2450</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="3">
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1694</v>
+        <v>1673</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
@@ -671,10 +671,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1356</v>
+        <v>1360</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
     <row r="5">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>840</v>
+        <v>862</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>55</v>
@@ -697,10 +697,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8">
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>14</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>37</v>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>34</v>
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>11</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>22</v>
@@ -801,10 +801,10 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>1</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C17" s="8" t="inlineStr"/>
     </row>
@@ -854,7 +854,7 @@
         <v>10000</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>1501</v>
+        <v>1512</v>
       </c>
     </row>
   </sheetData>
@@ -869,7 +869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H149"/>
+  <dimension ref="A1:H159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -943,7 +943,7 @@
       <c r="D2" s="11" t="inlineStr"/>
       <c r="E2" s="11" t="inlineStr"/>
       <c r="F2" s="12" t="n">
-        <v>2043</v>
+        <v>2053</v>
       </c>
       <c r="G2" s="11" t="inlineStr"/>
       <c r="H2" s="11" t="inlineStr">
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="F5" s="12" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G5" s="11" t="inlineStr"/>
       <c r="H5" s="11" t="inlineStr">
@@ -3084,30 +3084,28 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Regional/category</t>
+          <t>City</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - East</t>
+          <t>Nottingham</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>All roles</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>/job-search/east-yorkshire/service-administrator-jobs</t>
+          <t>/nottingham/jobs</t>
         </is>
       </c>
       <c r="F61" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G61" s="5" t="n">
-        <v>22</v>
-      </c>
+      <c r="G61" s="4" t="inlineStr"/>
       <c r="H61" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3122,30 +3120,28 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Regional/category</t>
+          <t>City</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Wakefield</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>All roles</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>/job-search/northern-ireland-east/service-administrator-jobs</t>
+          <t>/wakefield/jobs</t>
         </is>
       </c>
       <c r="F62" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G62" s="3" t="n">
-        <v>51</v>
-      </c>
+      <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3160,30 +3156,28 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Regional/category</t>
+          <t>City</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Bolton</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Customer Service &amp; Contact Centre</t>
+          <t>All roles</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>/job-search/london/customer-service-jobs</t>
+          <t>/bolton/jobs</t>
         </is>
       </c>
       <c r="F63" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G63" s="5" t="n">
-        <v>3</v>
-      </c>
+      <c r="G63" s="4" t="inlineStr"/>
       <c r="H63" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3198,30 +3192,28 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Regional/category</t>
+          <t>City</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>HR &amp; Recruitment</t>
+          <t>All roles</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>/job-search/london/hr-recruitment-jobs</t>
+          <t>/reading/jobs</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G64" s="3" t="n">
-        <v>13</v>
-      </c>
+      <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3236,30 +3228,28 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Regional/category</t>
+          <t>City</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>Chester</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>All roles</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>/job-search/manchester-salford/service-administrator-jobs</t>
+          <t>/chester/jobs</t>
         </is>
       </c>
       <c r="F65" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G65" s="5" t="n">
-        <v>41</v>
-      </c>
+      <c r="G65" s="4" t="inlineStr"/>
       <c r="H65" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3274,30 +3264,28 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Regional/category</t>
+          <t>City</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Durham</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Finance &amp; Accounts</t>
+          <t>All roles</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>/job-search/london/finance-accounts-jobs</t>
+          <t>/durham/jobs</t>
         </is>
       </c>
       <c r="F66" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G66" s="3" t="n">
-        <v>6</v>
-      </c>
+      <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3312,30 +3300,28 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Regional/category</t>
+          <t>City</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Gateshead</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>All roles</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>/job-search/oxfordshire/service-administrator-jobs</t>
+          <t>/gateshead/jobs</t>
         </is>
       </c>
       <c r="F67" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G67" s="5" t="n">
-        <v>41</v>
-      </c>
+      <c r="G67" s="4" t="inlineStr"/>
       <c r="H67" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3350,30 +3336,28 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Regional/category</t>
+          <t>City</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Northallerton</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>All roles</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>/job-search/bristol-bath/service-administrator-jobs</t>
+          <t>/northallerton/jobs</t>
         </is>
       </c>
       <c r="F68" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G68" s="3" t="n">
-        <v>30</v>
-      </c>
+      <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3388,30 +3372,28 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Regional/category</t>
+          <t>City</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Norwich</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>All roles</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>/job-search/essex/service-administrator-jobs</t>
+          <t>/norwich/jobs</t>
         </is>
       </c>
       <c r="F69" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G69" s="5" t="n">
-        <v>40</v>
-      </c>
+      <c r="G69" s="4" t="inlineStr"/>
       <c r="H69" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3426,30 +3408,28 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Regional/category</t>
+          <t>City</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Salford</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Customer Service &amp; Contact Centre</t>
+          <t>All roles</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>/job-search/hampshire/customer-service-jobs</t>
+          <t>/salford/jobs</t>
         </is>
       </c>
       <c r="F70" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G70" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3469,7 +3449,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Yorkshire - East</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -3479,7 +3459,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>/job-search/cambridgeshire/service-administrator-jobs</t>
+          <t>/job-search/east-yorkshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F71" s="5" t="n">
@@ -3507,7 +3487,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -3517,14 +3497,14 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>/job-search/gloucestershire/service-administrator-jobs</t>
+          <t>/job-search/northern-ireland-east/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3550,19 +3530,19 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Support Worker</t>
+          <t>Customer Service &amp; Contact Centre</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>/job-search/london/support-worker</t>
+          <t>/job-search/london/customer-service-jobs</t>
         </is>
       </c>
       <c r="F73" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
@@ -3583,24 +3563,24 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>HR &amp; Recruitment</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>/job-search/dorset/service-administrator-jobs</t>
+          <t>/job-search/london/hr-recruitment-jobs</t>
         </is>
       </c>
       <c r="F74" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -3621,24 +3601,24 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Customer Service &amp; Contact Centre</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>/job-search/staffordshire/customer-service-jobs</t>
+          <t>/job-search/manchester-salford/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F75" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
@@ -3659,24 +3639,24 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Finance &amp; Accounts</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>/job-search/devon/service-administrator-jobs</t>
+          <t>/job-search/london/finance-accounts-jobs</t>
         </is>
       </c>
       <c r="F76" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -3697,24 +3677,24 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Customer Service &amp; Contact Centre</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>/job-search/surrey/customer-service-jobs</t>
+          <t>/job-search/oxfordshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F77" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
@@ -3735,7 +3715,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -3745,14 +3725,14 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>/job-search/wiltshire/service-administrator-jobs</t>
+          <t>/job-search/bristol-bath/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F78" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -3773,7 +3753,7 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -3783,14 +3763,14 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>/job-search/northamptonshire/service-administrator-jobs</t>
+          <t>/job-search/essex/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F79" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
@@ -3811,24 +3791,24 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Customer Service &amp; Contact Centre</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>/job-search/berkshire/service-administrator-jobs</t>
+          <t>/job-search/hampshire/customer-service-jobs</t>
         </is>
       </c>
       <c r="F80" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -3849,7 +3829,7 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Nottinghamshire</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -3859,14 +3839,14 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>/job-search/nottinghamshire/service-administrator-jobs</t>
+          <t>/job-search/cambridgeshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F81" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
@@ -3887,7 +3867,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -3897,14 +3877,14 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>/job-search/buckinghamshire/service-administrator-jobs</t>
+          <t>/job-search/gloucestershire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F82" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -3925,7 +3905,7 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -3935,14 +3915,14 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>/job-search/surrey/support-worker</t>
+          <t>/job-search/london/support-worker</t>
         </is>
       </c>
       <c r="F83" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
@@ -3963,7 +3943,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -3973,14 +3953,14 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>/job-search/hertfordshire/service-administrator-jobs</t>
+          <t>/job-search/dorset/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F84" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -4006,19 +3986,19 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Customer Service &amp; Contact Centre</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>/job-search/staffordshire/service-administrator-jobs</t>
+          <t>/job-search/staffordshire/customer-service-jobs</t>
         </is>
       </c>
       <c r="F85" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
@@ -4039,7 +4019,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -4049,14 +4029,14 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>/job-search/norfolk/service-administrator-jobs</t>
+          <t>/job-search/devon/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F86" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4077,24 +4057,24 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Customer Service &amp; Contact Centre</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>/job-search/birmingham-solihull/service-administrator-jobs</t>
+          <t>/job-search/surrey/customer-service-jobs</t>
         </is>
       </c>
       <c r="F87" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
@@ -4115,24 +4095,24 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>HR &amp; Recruitment</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>/job-search/west-yorkshire/hr-recruitment-jobs</t>
+          <t>/job-search/wiltshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F88" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4153,7 +4133,7 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -4163,14 +4143,14 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>/job-search/greater-manchester-south/service-administrator-jobs</t>
+          <t>/job-search/northamptonshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F89" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
@@ -4191,24 +4171,24 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Support Worker</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>/job-search/wiltshire/support-worker</t>
+          <t>/job-search/berkshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F90" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4229,7 +4209,7 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -4239,14 +4219,14 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>/job-search/somerset/service-administrator-jobs</t>
+          <t>/job-search/nottinghamshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F91" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
@@ -4267,24 +4247,24 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>/job-search/london/customer-sales-jobs</t>
+          <t>/job-search/buckinghamshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F92" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -4305,17 +4285,17 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Support Worker</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>/job-search/west-yorkshire/customer-sales-jobs</t>
+          <t>/job-search/surrey/support-worker</t>
         </is>
       </c>
       <c r="F93" s="5" t="n">
@@ -4343,24 +4323,24 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>/job-search/manchester-salford/customer-sales-jobs</t>
+          <t>/job-search/hertfordshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F94" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -4381,7 +4361,7 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -4391,14 +4371,14 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>/job-search/leicestershire/service-administrator-jobs</t>
+          <t>/job-search/staffordshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F95" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
@@ -4419,7 +4399,7 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - Warrington &amp; Halton</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -4429,14 +4409,14 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>/job-search/warrington-halton/service-administrator-jobs</t>
+          <t>/job-search/norfolk/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F96" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -4457,7 +4437,7 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -4467,14 +4447,14 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>/job-search/cornwall/service-administrator-jobs</t>
+          <t>/job-search/birmingham-solihull/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F97" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
@@ -4495,24 +4475,24 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>HR &amp; Recruitment</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>/job-search/suffolk/service-administrator-jobs</t>
+          <t>/job-search/west-yorkshire/hr-recruitment-jobs</t>
         </is>
       </c>
       <c r="F98" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -4533,7 +4513,7 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Derbyshire</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -4543,7 +4523,7 @@
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>/job-search/derbyshire/service-administrator-jobs</t>
+          <t>/job-search/greater-manchester-south/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F99" s="5" t="n">
@@ -4571,24 +4551,24 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Support Worker</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>/job-search/cheshire-east/service-administrator-jobs</t>
+          <t>/job-search/wiltshire/support-worker</t>
         </is>
       </c>
       <c r="F100" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -4609,7 +4589,7 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -4619,14 +4599,14 @@
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>/job-search/lincolnshire/service-administrator-jobs</t>
+          <t>/job-search/somerset/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F101" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
@@ -4647,24 +4627,24 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Merseyside - Liverpool</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>/job-search/merseyside-liverpool/service-administrator-jobs</t>
+          <t>/job-search/london/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F102" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -4685,24 +4665,24 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Shropshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>/job-search/shropshire/service-administrator-jobs</t>
+          <t>/job-search/west-yorkshire/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F103" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
@@ -4723,24 +4703,24 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - Wigan &amp; Bolton</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>/job-search/wigan-bolton/service-administrator-jobs</t>
+          <t>/job-search/manchester-salford/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F104" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -4761,7 +4741,7 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
@@ -4771,14 +4751,14 @@
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>/job-search/black-country/service-administrator-jobs</t>
+          <t>/job-search/leicestershire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F105" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
@@ -4799,24 +4779,24 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Cheshire - Warrington &amp; Halton</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Legal Assistant &amp; Paralegal</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>/job-search/london/paralegal-jobs</t>
+          <t>/job-search/warrington-halton/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F106" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -4837,24 +4817,24 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Legal Assistant &amp; Paralegal</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>/job-search/suffolk/paralegal-jobs</t>
+          <t>/job-search/cornwall/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F107" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
@@ -4875,24 +4855,24 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Legal Assistant &amp; Paralegal</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>/job-search/essex/paralegal-jobs</t>
+          <t>/job-search/suffolk/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F108" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -4913,24 +4893,24 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Derbyshire</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>/job-search/london/marketing-jobs</t>
+          <t>/job-search/derbyshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F109" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
@@ -4951,24 +4931,24 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>/job-search/surrey/marketing-jobs</t>
+          <t>/job-search/cheshire-east/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F110" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -4989,24 +4969,24 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>/job-search/manchester-salford/marketing-jobs</t>
+          <t>/job-search/lincolnshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F111" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
@@ -5027,24 +5007,24 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Merseyside - Liverpool</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>/job-search/birmingham-solihull/marketing-jobs</t>
+          <t>/job-search/merseyside-liverpool/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F112" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5065,24 +5045,24 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Shropshire</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>HR &amp; Recruitment</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>/job-search/berkshire/hr-recruitment-jobs</t>
+          <t>/job-search/shropshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F113" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
@@ -5103,24 +5083,24 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>Greater Manchester - Wigan &amp; Bolton</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>HR &amp; Recruitment</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>/job-search/manchester-salford/hr-recruitment-jobs</t>
+          <t>/job-search/wigan-bolton/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F114" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -5141,24 +5121,24 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Nottinghamshire</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>HR &amp; Recruitment</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>/job-search/nottinghamshire/hr-recruitment-jobs</t>
+          <t>/job-search/black-country/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F115" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
@@ -5179,24 +5159,24 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>HR &amp; Recruitment</t>
+          <t>Legal Assistant &amp; Paralegal</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>/job-search/birmingham-solihull/hr-recruitment-jobs</t>
+          <t>/job-search/london/paralegal-jobs</t>
         </is>
       </c>
       <c r="F116" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5217,24 +5197,24 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>HR &amp; Recruitment</t>
+          <t>Legal Assistant &amp; Paralegal</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>/job-search/sussex/hr-recruitment-jobs</t>
+          <t>/job-search/suffolk/paralegal-jobs</t>
         </is>
       </c>
       <c r="F117" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
@@ -5255,24 +5235,24 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Legal Assistant &amp; Paralegal</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>/job-search/cheshire-west/service-administrator-jobs</t>
+          <t>/job-search/essex/paralegal-jobs</t>
         </is>
       </c>
       <c r="F118" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -5293,24 +5273,24 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Scotland Central - Edinburgh &amp; Lothians</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>/job-search/edinburgh-lothians/service-administrator-jobs</t>
+          <t>/job-search/london/marketing-jobs</t>
         </is>
       </c>
       <c r="F119" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
@@ -5331,24 +5311,24 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Worcestershire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>/job-search/worcestershire/service-administrator-jobs</t>
+          <t>/job-search/surrey/marketing-jobs</t>
         </is>
       </c>
       <c r="F120" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -5369,7 +5349,7 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
@@ -5379,14 +5359,14 @@
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>/job-search/berkshire/marketing-jobs</t>
+          <t>/job-search/manchester-salford/marketing-jobs</t>
         </is>
       </c>
       <c r="F121" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
@@ -5407,24 +5387,24 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Support Worker</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>/job-search/kent/support-worker</t>
+          <t>/job-search/birmingham-solihull/marketing-jobs</t>
         </is>
       </c>
       <c r="F122" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -5445,24 +5425,24 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>North East</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>HR &amp; Recruitment</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>/job-search/north-east/customer-sales-jobs</t>
+          <t>/job-search/berkshire/hr-recruitment-jobs</t>
         </is>
       </c>
       <c r="F123" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
@@ -5483,24 +5463,24 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Support Worker</t>
+          <t>HR &amp; Recruitment</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>/job-search/oxfordshire/support-worker</t>
+          <t>/job-search/manchester-salford/hr-recruitment-jobs</t>
         </is>
       </c>
       <c r="F124" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -5521,24 +5501,24 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>HR &amp; Recruitment</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>/job-search/bedfordshire/service-administrator-jobs</t>
+          <t>/job-search/nottinghamshire/hr-recruitment-jobs</t>
         </is>
       </c>
       <c r="F125" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
@@ -5559,24 +5539,24 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>HR &amp; Recruitment</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>/job-search/bristol-bath/customer-sales-jobs</t>
+          <t>/job-search/birmingham-solihull/hr-recruitment-jobs</t>
         </is>
       </c>
       <c r="F126" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -5597,24 +5577,24 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>HR &amp; Recruitment</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>/job-search/buckinghamshire/marketing-jobs</t>
+          <t>/job-search/sussex/hr-recruitment-jobs</t>
         </is>
       </c>
       <c r="F127" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
@@ -5635,7 +5615,7 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Wales South - Cardiff &amp; Vale</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -5645,14 +5625,14 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>/job-search/cardiff-vale/service-administrator-jobs</t>
+          <t>/job-search/cheshire-west/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F128" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -5673,24 +5653,24 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Scotland Central - Edinburgh &amp; Lothians</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>/job-search/berkshire/customer-sales-jobs</t>
+          <t>/job-search/edinburgh-lothians/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F129" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
@@ -5711,24 +5691,24 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Worcestershire</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>/job-search/hertfordshire/customer-sales-jobs</t>
+          <t>/job-search/worcestershire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F130" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -5749,24 +5729,24 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>/job-search/kent/customer-sales-jobs</t>
+          <t>/job-search/berkshire/marketing-jobs</t>
         </is>
       </c>
       <c r="F131" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
@@ -5787,24 +5767,24 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Scotland West - Glasgow</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Support Worker</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>/job-search/glasgow/customer-sales-jobs</t>
+          <t>/job-search/kent/support-worker</t>
         </is>
       </c>
       <c r="F132" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -5825,7 +5805,7 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>North East</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
@@ -5835,14 +5815,14 @@
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>/job-search/surrey/customer-sales-jobs</t>
+          <t>/job-search/north-east/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F133" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
@@ -5863,24 +5843,24 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Support Worker</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>/job-search/sussex/customer-sales-jobs</t>
+          <t>/job-search/oxfordshire/support-worker</t>
         </is>
       </c>
       <c r="F134" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -5901,24 +5881,24 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>/job-search/bristol-bath/marketing-jobs</t>
+          <t>/job-search/bedfordshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F135" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
@@ -5939,24 +5919,24 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>/job-search/gloucestershire/marketing-jobs</t>
+          <t>/job-search/bristol-bath/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F136" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -5977,7 +5957,7 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
@@ -5987,14 +5967,14 @@
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>/job-search/hertfordshire/marketing-jobs</t>
+          <t>/job-search/buckinghamshire/marketing-jobs</t>
         </is>
       </c>
       <c r="F137" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
@@ -6015,24 +5995,24 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Wales South - Cardiff &amp; Vale</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>/job-search/kent/marketing-jobs</t>
+          <t>/job-search/cardiff-vale/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F138" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -6053,24 +6033,24 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>/job-search/oxfordshire/marketing-jobs</t>
+          <t>/job-search/berkshire/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F139" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
@@ -6091,24 +6071,24 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>/job-search/north-scotland/service-administrator-jobs</t>
+          <t>/job-search/hertfordshire/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F140" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -6129,24 +6109,24 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Scotland Central - Tayside</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>/job-search/tayside/service-administrator-jobs</t>
+          <t>/job-search/kent/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F141" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
@@ -6167,24 +6147,24 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Wales South - Valleys</t>
+          <t>Scotland West - Glasgow</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>/job-search/south-wales-valleys/service-administrator-jobs</t>
+          <t>/job-search/glasgow/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F142" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -6205,24 +6185,24 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>/job-search/cambridgeshire/marketing-jobs</t>
+          <t>/job-search/surrey/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F143" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
@@ -6243,24 +6223,24 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>/job-search/cheshire-west/marketing-jobs</t>
+          <t>/job-search/sussex/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F144" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6281,7 +6261,7 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
@@ -6291,14 +6271,14 @@
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>/job-search/essex/marketing-jobs</t>
+          <t>/job-search/bristol-bath/marketing-jobs</t>
         </is>
       </c>
       <c r="F145" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
@@ -6319,7 +6299,7 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Merseyside - Liverpool</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -6329,14 +6309,14 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>/job-search/merseyside-liverpool/marketing-jobs</t>
+          <t>/job-search/gloucestershire/marketing-jobs</t>
         </is>
       </c>
       <c r="F146" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -6357,7 +6337,7 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>North East</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
@@ -6367,14 +6347,14 @@
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>/job-search/north-east/marketing-jobs</t>
+          <t>/job-search/hertfordshire/marketing-jobs</t>
         </is>
       </c>
       <c r="F147" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
@@ -6395,24 +6375,24 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Customer Service &amp; Contact Centre</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>/job-search/buckinghamshire/customer-service-jobs</t>
+          <t>/job-search/kent/marketing-jobs</t>
         </is>
       </c>
       <c r="F148" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -6433,17 +6413,17 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>North East</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Customer Service &amp; Contact Centre</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>/job-search/north-east/customer-service-jobs</t>
+          <t>/job-search/oxfordshire/marketing-jobs</t>
         </is>
       </c>
       <c r="F149" s="5" t="n">
@@ -6458,8 +6438,388 @@
         </is>
       </c>
     </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Regional/category</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>North Scotland</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Admin &amp; Customer Service</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>/job-search/north-scotland/service-administrator-jobs</t>
+        </is>
+      </c>
+      <c r="F150" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G150" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>Regional/category</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>Scotland Central - Tayside</t>
+        </is>
+      </c>
+      <c r="D151" s="4" t="inlineStr">
+        <is>
+          <t>Admin &amp; Customer Service</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t>/job-search/tayside/service-administrator-jobs</t>
+        </is>
+      </c>
+      <c r="F151" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G151" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H151" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>Regional/category</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Wales South - Valleys</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Admin &amp; Customer Service</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>/job-search/south-wales-valleys/service-administrator-jobs</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G152" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>Regional/category</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>Cambridgeshire</t>
+        </is>
+      </c>
+      <c r="D153" s="4" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>/job-search/cambridgeshire/marketing-jobs</t>
+        </is>
+      </c>
+      <c r="F153" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G153" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H153" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Regional/category</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Cheshire - West</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>/job-search/cheshire-west/marketing-jobs</t>
+        </is>
+      </c>
+      <c r="F154" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G154" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="4" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>Regional/category</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>Essex</t>
+        </is>
+      </c>
+      <c r="D155" s="4" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E155" s="4" t="inlineStr">
+        <is>
+          <t>/job-search/essex/marketing-jobs</t>
+        </is>
+      </c>
+      <c r="F155" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G155" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H155" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>Regional/category</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Merseyside - Liverpool</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>/job-search/merseyside-liverpool/marketing-jobs</t>
+        </is>
+      </c>
+      <c r="F156" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G156" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="4" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>Regional/category</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="inlineStr">
+        <is>
+          <t>North East</t>
+        </is>
+      </c>
+      <c r="D157" s="4" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E157" s="4" t="inlineStr">
+        <is>
+          <t>/job-search/north-east/marketing-jobs</t>
+        </is>
+      </c>
+      <c r="F157" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G157" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H157" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Regional/category</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Buckinghamshire</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Customer Service &amp; Contact Centre</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>/job-search/buckinghamshire/customer-service-jobs</t>
+        </is>
+      </c>
+      <c r="F158" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G158" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>Regional/category</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="inlineStr">
+        <is>
+          <t>North East</t>
+        </is>
+      </c>
+      <c r="D159" s="4" t="inlineStr">
+        <is>
+          <t>Customer Service &amp; Contact Centre</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="inlineStr">
+        <is>
+          <t>/job-search/north-east/customer-service-jobs</t>
+        </is>
+      </c>
+      <c r="F159" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G159" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H159" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H149"/>
+  <autoFilter ref="A1:H159"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6521,16 +6881,16 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Nottingham</t>
+          <t>Altrincham</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nottinghamshire</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>0</v>
@@ -6545,16 +6905,16 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Wakefield</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>0</v>
@@ -6569,16 +6929,16 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Bolton</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - Wigan &amp; Bolton</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
@@ -6593,16 +6953,16 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Chelmsford</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>0</v>
@@ -6617,16 +6977,16 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Chester</t>
+          <t>Chester Le Street</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
@@ -6641,16 +7001,16 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Durham</t>
+          <t>Hemel Hempstead</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>0</v>
@@ -6665,16 +7025,16 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Gateshead</t>
+          <t>High Wycombe</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>0</v>
@@ -6689,16 +7049,16 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Northallerton</t>
+          <t>Macclesfield</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>0</v>
@@ -6713,16 +7073,16 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Norwich</t>
+          <t>Maidstone</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0</v>
@@ -6737,16 +7097,16 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Salford</t>
+          <t>Newtownabbey</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>0</v>
@@ -6761,12 +7121,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Altrincham</t>
+          <t>Rotherham</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -6785,12 +7145,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Scarborough</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -6809,12 +7169,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Stockport</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -6833,12 +7193,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Chelmsford</t>
+          <t>Stoke-on-trent</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -6857,12 +7217,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Chester Le Street</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -6881,12 +7241,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Hemel Hempstead</t>
+          <t>Swindon</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -6905,12 +7265,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>High Wycombe</t>
+          <t>Tonbridge</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -6924,242 +7284,282 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>CREATE</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Macclesfield</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>/manchester/service-administrator-jobs</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>CREATE</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Maidstone</t>
+          <t>Newcastle</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>/newcastle/service-administrator-jobs</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>CREATE</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Newtownabbey</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>/birmingham/service-administrator-jobs</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>CREATE</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Rotherham</t>
+          <t>Belfast</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>/belfast/service-administrator-jobs</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>CREATE</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Scarborough</t>
+          <t>Bristol</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>/bristol/service-administrator-jobs</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>CREATE</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Stockport</t>
+          <t>Leeds</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>/leeds/service-administrator-jobs</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>CREATE</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Stoke-on-trent</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Merseyside - Liverpool</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>/liverpool/service-administrator-jobs</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>CREATE</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Hull</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Yorkshire - East</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>/hull/service-administrator-jobs</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>CREATE</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Swindon</t>
+          <t>Sheffield</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>/sheffield/service-administrator-jobs</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>CREATE</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Tonbridge</t>
+          <t>Glasgow</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Scotland West - Glasgow</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>/glasgow/service-administrator-jobs</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -7169,23 +7569,23 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Nottingham</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>/manchester/service-administrator-jobs</t>
+          <t>/nottingham/jobs</t>
         </is>
       </c>
     </row>
@@ -7197,23 +7597,23 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Newcastle</t>
+          <t>Bradford</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>/newcastle/service-administrator-jobs</t>
+          <t>/bradford/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7225,23 +7625,23 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Cardiff</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Wales South - Cardiff &amp; Vale</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="E31" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>/birmingham/service-administrator-jobs</t>
+          <t>/cardiff/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7253,23 +7653,23 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Belfast</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Scotland Central - Edinburgh &amp; Lothians</t>
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>/belfast/service-administrator-jobs</t>
+          <t>/edinburgh/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7281,23 +7681,23 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Bristol</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>/bristol/service-administrator-jobs</t>
+          <t>/southampton/service-administrator-jobs, /southampton/support-worker</t>
         </is>
       </c>
     </row>
@@ -7309,7 +7709,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Wakefield</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -7318,14 +7718,14 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>/leeds/service-administrator-jobs</t>
+          <t>/wakefield/jobs</t>
         </is>
       </c>
     </row>
@@ -7337,23 +7737,23 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Cambridge</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Merseyside - Liverpool</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E35" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>/liverpool/service-administrator-jobs</t>
+          <t>/cambridge/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7365,23 +7765,23 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Hull</t>
+          <t>Peterborough</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - East</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>/hull/service-administrator-jobs</t>
+          <t>/peterborough/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7393,7 +7793,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Sheffield</t>
+          <t>Doncaster</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -7402,14 +7802,14 @@
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E37" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>/sheffield/service-administrator-jobs</t>
+          <t>/doncaster/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7421,23 +7821,23 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Glasgow</t>
+          <t>Oxford</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Scotland West - Glasgow</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E38" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>/glasgow/service-administrator-jobs</t>
+          <t>/oxford/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7449,23 +7849,23 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Bradford</t>
+          <t>Bolton</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Greater Manchester - Wigan &amp; Bolton</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E39" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>/bradford/service-administrator-jobs</t>
+          <t>/bolton/jobs</t>
         </is>
       </c>
     </row>
@@ -7477,23 +7877,23 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Cardiff</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Wales South - Cardiff &amp; Vale</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>/cardiff/service-administrator-jobs</t>
+          <t>/reading/jobs</t>
         </is>
       </c>
     </row>
@@ -7505,23 +7905,23 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Chester</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Scotland Central - Edinburgh &amp; Lothians</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E41" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>/edinburgh/service-administrator-jobs</t>
+          <t>/chester/jobs</t>
         </is>
       </c>
     </row>
@@ -7533,23 +7933,23 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Durham</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>/southampton/service-administrator-jobs, /southampton/support-worker</t>
+          <t>/durham/jobs</t>
         </is>
       </c>
     </row>
@@ -7561,23 +7961,23 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Cambridge</t>
+          <t>Gateshead</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E43" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>/cambridge/service-administrator-jobs</t>
+          <t>/gateshead/jobs</t>
         </is>
       </c>
     </row>
@@ -7589,23 +7989,23 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Peterborough</t>
+          <t>Northallerton</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>/peterborough/service-administrator-jobs</t>
+          <t>/northallerton/jobs</t>
         </is>
       </c>
     </row>
@@ -7617,23 +8017,23 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Doncaster</t>
+          <t>Norwich</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E45" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>/doncaster/service-administrator-jobs</t>
+          <t>/norwich/jobs</t>
         </is>
       </c>
     </row>
@@ -7645,23 +8045,23 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Oxford</t>
+          <t>Salford</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E46" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>/oxford/service-administrator-jobs</t>
+          <t>/salford/jobs</t>
         </is>
       </c>
     </row>
@@ -15403,7 +15803,7 @@
       <c r="B3" s="14" t="inlineStr"/>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>4 / 3.1 / 3/14</t>
+          <t>2 / 3.0 / 3/14</t>
         </is>
       </c>
       <c r="D3" s="14" t="inlineStr"/>
@@ -15434,7 +15834,7 @@
       <c r="B4" s="13" t="inlineStr"/>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/14</t>
+          <t>1 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr"/>
@@ -15447,7 +15847,7 @@
       <c r="G4" s="13" t="inlineStr"/>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.0 / 0/12</t>
+          <t>1 / 1.9 / 0/12</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
@@ -15544,7 +15944,7 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.9 / 0/14</t>
+          <t>4 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -15569,7 +15969,7 @@
       </c>
       <c r="I7" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.0 / 0/9</t>
+          <t>3 / 2.1 / 0/9</t>
         </is>
       </c>
     </row>
@@ -15690,7 +16090,7 @@
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/9</t>
+          <t>1 / 0.8 / 0/9</t>
         </is>
       </c>
     </row>
@@ -15749,7 +16149,7 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr"/>
@@ -15775,7 +16175,7 @@
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/12</t>
+          <t>0 / 0.3 / 0/12</t>
         </is>
       </c>
       <c r="I12" s="13" t="inlineStr">
@@ -15898,7 +16298,7 @@
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>5 / 2.5 / 2/13</t>
+          <t>6 / 2.5 / 3/13</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr"/>
@@ -15977,7 +16377,7 @@
       <c r="F17" s="14" t="inlineStr"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>5 / 5.5 / 2/10</t>
+          <t>6 / 5.6 / 3/10</t>
         </is>
       </c>
       <c r="H17" s="14" t="inlineStr">
@@ -16005,7 +16405,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>5 / 2.0 / 0/14</t>
+          <t>6 / 2.1 / 1/14</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
@@ -16210,7 +16610,7 @@
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>7 / 6.2 / 6/13</t>
+          <t>6 / 6.1 / 6/13</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
@@ -16393,7 +16793,7 @@
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.7 / 0/14</t>
+          <t>3 / 2.8 / 0/14</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
@@ -16450,7 +16850,7 @@
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/14</t>
+          <t>0 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
@@ -16487,7 +16887,7 @@
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.4 / 0/14</t>
+          <t>1 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
@@ -16517,7 +16917,7 @@
       </c>
       <c r="H30" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/12</t>
+          <t>0 / 0.3 / 0/12</t>
         </is>
       </c>
       <c r="I30" s="13" t="inlineStr">
@@ -16587,7 +16987,7 @@
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 0/14</t>
+          <t>2 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
@@ -16597,7 +16997,7 @@
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.2 / 0/13</t>
+          <t>0 / 1.0 / 0/13</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr">
@@ -16835,7 +17235,7 @@
       </c>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>3 / 0.9 / 0/13</t>
+          <t>2 / 0.8 / 0/13</t>
         </is>
       </c>
       <c r="G38" s="13" t="inlineStr">
@@ -16874,7 +17274,7 @@
       <c r="E39" s="14" t="inlineStr"/>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.3 / 0/13</t>
+          <t>0 / 1.2 / 0/13</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
@@ -16930,7 +17330,7 @@
       </c>
       <c r="D41" s="14" t="inlineStr">
         <is>
-          <t>6 / 3.9 / 5/14</t>
+          <t>7 / 3.9 / 5/14</t>
         </is>
       </c>
       <c r="E41" s="14" t="inlineStr">
@@ -16987,7 +17387,7 @@
       </c>
       <c r="F42" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.8 / 0/13</t>
+          <t>3 / 0.8 / 0/13</t>
         </is>
       </c>
       <c r="G42" s="13" t="inlineStr">
@@ -17115,7 +17515,7 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>14 / 3.2 / 2/13</t>
+          <t>15 / 3.3 / 2/13</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr">
@@ -17126,7 +17526,7 @@
       <c r="G45" s="14" t="inlineStr"/>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>6 / 1.2 / 2/12</t>
+          <t>5 / 1.2 / 1/12</t>
         </is>
       </c>
       <c r="I45" s="14" t="inlineStr">
@@ -17143,7 +17543,7 @@
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>24 / 7.8 / 3/14</t>
+          <t>25 / 7.9 / 3/14</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
@@ -17168,7 +17568,7 @@
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/10</t>
+          <t>1 / 0.3 / 0/10</t>
         </is>
       </c>
       <c r="H46" s="13" t="inlineStr">
@@ -17201,7 +17601,7 @@
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.2 / 0/13</t>
+          <t>2 / 2.1 / 0/13</t>
         </is>
       </c>
       <c r="F47" s="14" t="inlineStr">
@@ -17231,7 +17631,7 @@
       <c r="C48" s="13" t="inlineStr"/>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.4 / 0/14</t>
+          <t>5 / 3.5 / 0/14</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
@@ -17311,7 +17711,7 @@
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.6 / 0/14</t>
+          <t>2 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
@@ -17336,7 +17736,7 @@
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/10</t>
+          <t>0 / 0.1 / 0/10</t>
         </is>
       </c>
       <c r="H50" s="13" t="inlineStr">
@@ -17401,7 +17801,7 @@
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.2 / 0/14</t>
+          <t>2 / 2.3 / 0/14</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
@@ -17773,7 +18173,7 @@
       </c>
       <c r="F60" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.5 / 0/13</t>
+          <t>4 / 1.6 / 0/13</t>
         </is>
       </c>
       <c r="G60" s="13" t="inlineStr">
@@ -17826,7 +18226,7 @@
       </c>
       <c r="H61" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/12</t>
+          <t>1 / 0.2 / 0/12</t>
         </is>
       </c>
       <c r="I61" s="14" t="inlineStr"/>
@@ -17845,7 +18245,7 @@
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.8 / 0/14</t>
+          <t>4 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr"/>
@@ -17881,13 +18281,13 @@
       <c r="D63" s="14" t="inlineStr"/>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>5 / 4.2 / 0/13</t>
+          <t>6 / 4.3 / 1/13</t>
         </is>
       </c>
       <c r="F63" s="14" t="inlineStr"/>
       <c r="G63" s="14" t="inlineStr">
         <is>
-          <t>3 / 4.3 / 2/10</t>
+          <t>4 / 4.4 / 2/10</t>
         </is>
       </c>
       <c r="H63" s="14" t="inlineStr">
@@ -18130,7 +18530,7 @@
       </c>
       <c r="D69" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.6 / 0/14</t>
+          <t>2 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="E69" s="14" t="inlineStr">
@@ -18221,7 +18621,7 @@
       </c>
       <c r="E71" s="14" t="inlineStr">
         <is>
-          <t>4 / 4.0 / 2/13</t>
+          <t>2 / 3.8 / 2/13</t>
         </is>
       </c>
       <c r="F71" s="14" t="inlineStr"/>
@@ -18276,7 +18676,7 @@
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/9</t>
+          <t>2 / 1.1 / 0/9</t>
         </is>
       </c>
     </row>
@@ -18304,7 +18704,7 @@
       </c>
       <c r="F73" s="14" t="inlineStr">
         <is>
-          <t>5 / 3.0 / 0/13</t>
+          <t>6 / 3.1 / 1/13</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
@@ -18314,7 +18714,7 @@
       </c>
       <c r="H73" s="14" t="inlineStr">
         <is>
-          <t>3 / 3.1 / 0/12</t>
+          <t>4 / 3.2 / 0/12</t>
         </is>
       </c>
       <c r="I73" s="14" t="inlineStr">
@@ -18396,7 +18796,7 @@
       </c>
       <c r="H75" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/12</t>
+          <t>1 / 0.2 / 0/12</t>
         </is>
       </c>
       <c r="I75" s="14" t="inlineStr">
@@ -18444,7 +18844,7 @@
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
-          <t>3 / 3.2 / 0/9</t>
+          <t>2 / 3.1 / 0/9</t>
         </is>
       </c>
     </row>
@@ -18472,7 +18872,7 @@
       </c>
       <c r="F77" s="14" t="inlineStr">
         <is>
-          <t>7 / 4.8 / 5/13</t>
+          <t>8 / 4.8 / 5/13</t>
         </is>
       </c>
       <c r="G77" s="14" t="inlineStr"/>
@@ -18507,12 +18907,12 @@
       </c>
       <c r="F78" s="13" t="inlineStr">
         <is>
-          <t>6 / 3.1 / 3/13</t>
+          <t>5 / 3.0 / 2/13</t>
         </is>
       </c>
       <c r="G78" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.4 / 2/10</t>
+          <t>1 / 1.5 / 2/10</t>
         </is>
       </c>
       <c r="H78" s="13" t="inlineStr">
@@ -18542,7 +18942,7 @@
       </c>
       <c r="F79" s="14" t="inlineStr">
         <is>
-          <t>19 / 9.3 / 7/13</t>
+          <t>18 / 9.2 / 7/13</t>
         </is>
       </c>
       <c r="G79" s="14" t="inlineStr"/>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1916</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="3">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="5">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1993</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="6">
@@ -645,10 +645,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2450</v>
+        <v>2484</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3">
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1673</v>
+        <v>1677</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -671,10 +671,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1360</v>
+        <v>1356</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>736</v>
+        <v>741</v>
       </c>
     </row>
     <row r="5">
@@ -684,10 +684,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>862</v>
+        <v>847</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6">
@@ -697,10 +697,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>39</v>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>11</v>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>14</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>37</v>
@@ -762,10 +762,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>11</v>
@@ -788,10 +788,10 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>8</v>
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>1</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C17" s="8" t="inlineStr"/>
     </row>
@@ -854,7 +854,7 @@
         <v>10000</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>1512</v>
+        <v>1520</v>
       </c>
     </row>
   </sheetData>
@@ -7298,7 +7298,7 @@
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>1</v>
@@ -9341,12 +9341,12 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Leicester</t>
+          <t>Luton</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D99" s="5" t="n">
@@ -9365,12 +9365,12 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Luton</t>
+          <t>Newry</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D100" s="3" t="n">
@@ -9389,12 +9389,12 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Newry</t>
+          <t>Northwich</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D101" s="5" t="n">
@@ -9413,12 +9413,12 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Northwich</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D102" s="3" t="n">
@@ -9437,12 +9437,12 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Redhill</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D103" s="5" t="n">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Redhill</t>
+          <t>Ringwood</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D104" s="3" t="n">
@@ -9485,12 +9485,12 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Ringwood</t>
+          <t>Shrewsbury</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Shropshire</t>
         </is>
       </c>
       <c r="D105" s="5" t="n">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Shrewsbury</t>
+          <t>Solihull</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Shropshire</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D106" s="3" t="n">
@@ -9533,12 +9533,12 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Solihull</t>
+          <t>Torquay</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D107" s="5" t="n">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Torquay</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D108" s="3" t="n">
@@ -9581,12 +9581,12 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Winchester</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D109" s="5" t="n">
@@ -9605,7 +9605,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Winchester</t>
+          <t>Alresford</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -9614,7 +9614,7 @@
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E110" s="3" t="n">
         <v>0</v>
@@ -9629,12 +9629,12 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Alresford</t>
+          <t>Amersham</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D111" s="5" t="n">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Amersham</t>
+          <t>Ballyclare</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D112" s="3" t="n">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Ballyclare</t>
+          <t>Ballymena</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
@@ -9701,12 +9701,12 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Ballymena</t>
+          <t>Berwick-upon-tweed</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D114" s="3" t="n">
@@ -9725,12 +9725,12 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Berwick-upon-tweed</t>
+          <t>Bury St Edmunds</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D115" s="5" t="n">
@@ -9749,12 +9749,12 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Bury St Edmunds</t>
+          <t>Carrickfergus</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D116" s="3" t="n">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Carrickfergus</t>
+          <t>Cheadle</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D117" s="5" t="n">
@@ -9797,12 +9797,12 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Cheadle</t>
+          <t>Chelmsley Wood</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D118" s="3" t="n">
@@ -9821,12 +9821,12 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Chelmsley Wood</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Derbyshire</t>
         </is>
       </c>
       <c r="D119" s="5" t="n">
@@ -9845,12 +9845,12 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Dewsbury</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Derbyshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D120" s="3" t="n">
@@ -9869,12 +9869,12 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Dewsbury</t>
+          <t>Dorking</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D121" s="5" t="n">
@@ -9893,12 +9893,12 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Dorking</t>
+          <t>Driffield</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Yorkshire - East</t>
         </is>
       </c>
       <c r="D122" s="3" t="n">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Driffield</t>
+          <t>Eastbourne</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - East</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D123" s="5" t="n">
@@ -9941,12 +9941,12 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Eastbourne</t>
+          <t>Ellesmere Port</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D124" s="3" t="n">
@@ -9965,12 +9965,12 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Ellesmere Port</t>
+          <t>Exeter</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D125" s="5" t="n">
@@ -9989,12 +9989,12 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Exeter</t>
+          <t>Hebburn</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D126" s="3" t="n">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Hebburn</t>
+          <t>Hessle</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Yorkshire - East</t>
         </is>
       </c>
       <c r="D127" s="5" t="n">
@@ -10037,12 +10037,12 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Hessle</t>
+          <t>Horsham</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - East</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D128" s="3" t="n">
@@ -10061,12 +10061,12 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Horsham</t>
+          <t>Huntingdon</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D129" s="5" t="n">
@@ -10085,12 +10085,12 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Huntingdon</t>
+          <t>Kettering</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D130" s="3" t="n">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Kettering</t>
+          <t>Knaresborough</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D131" s="5" t="n">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Knaresborough</t>
+          <t>Knutsford</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D132" s="3" t="n">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Knutsford</t>
+          <t>Leicester</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D133" s="5" t="n">
@@ -14586,7 +14586,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
       <c r="D19" s="5" t="n">
@@ -14813,7 +14813,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="inlineStr"/>
@@ -14847,7 +14847,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>19</v>
@@ -15760,37 +15760,37 @@
       <c r="B2" s="13" t="inlineStr"/>
       <c r="C2" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="D2" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.8 / 0/14</t>
+          <t>0 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="E2" s="13" t="inlineStr">
         <is>
-          <t>3 / 3.7 / 0/13</t>
+          <t>3 / 3.6 / 0/14</t>
         </is>
       </c>
       <c r="F2" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/13</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="G2" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/10</t>
+          <t>1 / 0.8 / 0/11</t>
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/12</t>
+          <t>2 / 1.2 / 0/13</t>
         </is>
       </c>
       <c r="I2" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/9</t>
+          <t>1 / 1.0 / 0/10</t>
         </is>
       </c>
     </row>
@@ -15803,25 +15803,25 @@
       <c r="B3" s="14" t="inlineStr"/>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>2 / 3.0 / 3/14</t>
+          <t>2 / 3.1 / 3/14</t>
         </is>
       </c>
       <c r="D3" s="14" t="inlineStr"/>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/13</t>
+          <t>2 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="F3" s="14" t="inlineStr"/>
       <c r="G3" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/10</t>
+          <t>1 / 0.7 / 0/11</t>
         </is>
       </c>
       <c r="H3" s="14" t="inlineStr"/>
       <c r="I3" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/9</t>
+          <t>1 / 0.6 / 0/10</t>
         </is>
       </c>
     </row>
@@ -15834,25 +15834,25 @@
       <c r="B4" s="13" t="inlineStr"/>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/14</t>
+          <t>0 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr"/>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.8 / 1/13</t>
+          <t>3 / 2.9 / 1/14</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr"/>
       <c r="G4" s="13" t="inlineStr"/>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.9 / 0/12</t>
+          <t>2 / 1.9 / 0/13</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
-          <t>5 / 3.3 / 0/9</t>
+          <t>5 / 3.5 / 0/10</t>
         </is>
       </c>
     </row>
@@ -15865,7 +15865,7 @@
       <c r="B5" s="14" t="inlineStr"/>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>0 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
@@ -15875,18 +15875,18 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/13</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr"/>
       <c r="G5" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.1 / 0/10</t>
+          <t>2 / 2.1 / 0/11</t>
         </is>
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/12</t>
+          <t>0 / 0.6 / 0/13</t>
         </is>
       </c>
       <c r="I5" s="14" t="inlineStr"/>
@@ -15905,28 +15905,28 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.5 / 0/14</t>
+          <t>3 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/13</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr"/>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.6 / 2/10</t>
+          <t>2 / 3.5 / 2/11</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/12</t>
+          <t>0 / 0.1 / 0/13</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/9</t>
+          <t>0 / 0.6 / 0/10</t>
         </is>
       </c>
     </row>
@@ -15944,32 +15944,32 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>4 / 2.0 / 0/14</t>
+          <t>4 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/13</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.2 / 0/13</t>
+          <t>2 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/10</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/12</t>
+          <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
       <c r="I7" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.1 / 0/9</t>
+          <t>3 / 2.2 / 0/10</t>
         </is>
       </c>
     </row>
@@ -15982,33 +15982,33 @@
       <c r="B8" s="13" t="inlineStr"/>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.3 / 0/14</t>
+          <t>1 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.7 / 1/14</t>
+          <t>1 / 1.6 / 1/14</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/13</t>
+          <t>2 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/13</t>
+          <t>0 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr"/>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/12</t>
+          <t>1 / 0.2 / 0/13</t>
         </is>
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
     </row>
@@ -16021,33 +16021,33 @@
       <c r="B9" s="14" t="inlineStr"/>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.1 / 0/14</t>
+          <t>0 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.6 / 0/14</t>
+          <t>1 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.3 / 0/13</t>
+          <t>2 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr"/>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.7 / 0/10</t>
+          <t>1 / 1.6 / 0/11</t>
         </is>
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/12</t>
+          <t>1 / 0.5 / 0/13</t>
         </is>
       </c>
       <c r="I9" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/9</t>
+          <t>1 / 0.6 / 0/10</t>
         </is>
       </c>
     </row>
@@ -16070,27 +16070,27 @@
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/14</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/11</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.2 / 0/13</t>
-        </is>
-      </c>
-      <c r="G10" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.2 / 0/10</t>
-        </is>
-      </c>
-      <c r="H10" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/9</t>
+          <t>1 / 0.8 / 0/10</t>
         </is>
       </c>
     </row>
@@ -16107,7 +16107,7 @@
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.8 / 2/14</t>
+          <t>0 / 1.4 / 1/14</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
@@ -16117,27 +16117,27 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/11</t>
+        </is>
+      </c>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/13</t>
-        </is>
-      </c>
-      <c r="G11" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.1 / 0/10</t>
-        </is>
-      </c>
-      <c r="H11" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
       <c r="I11" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
     </row>
@@ -16149,7 +16149,7 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr"/>
@@ -16160,27 +16160,27 @@
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/13</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.0 / 0/13</t>
+          <t>2 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/10</t>
+          <t>0 / 0.4 / 0/11</t>
         </is>
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/12</t>
+          <t>0 / 0.3 / 0/13</t>
         </is>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
     </row>
@@ -16192,12 +16192,12 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.3 / 0/14</t>
+          <t>0 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/14</t>
+          <t>0 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
@@ -16207,27 +16207,27 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.3 / 0/11</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/13</t>
-        </is>
-      </c>
-      <c r="G13" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.3 / 0/10</t>
-        </is>
-      </c>
-      <c r="H13" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
     </row>
@@ -16245,32 +16245,32 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.5 / 0/14</t>
+          <t>3 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.0 / 0/13</t>
+          <t>2 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.2 / 0/13</t>
+          <t>2 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.7 / 0/10</t>
+          <t>2 / 2.6 / 0/11</t>
         </is>
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/12</t>
+          <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.7 / 0/9</t>
+          <t>1 / 1.6 / 0/10</t>
         </is>
       </c>
     </row>
@@ -16283,33 +16283,33 @@
       <c r="B15" s="14" t="inlineStr"/>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/14</t>
+          <t>1 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>7 / 4.1 / 3/14</t>
+          <t>7 / 4.4 / 4/14</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.9 / 0/13</t>
+          <t>1 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>6 / 2.5 / 3/13</t>
+          <t>6 / 2.8 / 4/14</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr"/>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/12</t>
+          <t>0 / 0.8 / 0/13</t>
         </is>
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.4 / 0/9</t>
+          <t>2 / 1.5 / 0/10</t>
         </is>
       </c>
     </row>
@@ -16322,7 +16322,7 @@
       <c r="B16" s="13" t="inlineStr"/>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
@@ -16332,27 +16332,27 @@
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/13</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 0/13</t>
+          <t>1 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>0 / 2.1 / 0/10</t>
+          <t>0 / 1.9 / 0/11</t>
         </is>
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/12</t>
+          <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
       <c r="I16" s="13" t="inlineStr">
         <is>
-          <t>4 / 1.4 / 0/9</t>
+          <t>4 / 1.7 / 0/10</t>
         </is>
       </c>
     </row>
@@ -16365,7 +16365,7 @@
       <c r="B17" s="14" t="inlineStr"/>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
@@ -16377,17 +16377,17 @@
       <c r="F17" s="14" t="inlineStr"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>6 / 5.6 / 3/10</t>
+          <t>6 / 5.6 / 4/11</t>
         </is>
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/12</t>
+          <t>1 / 1.1 / 0/13</t>
         </is>
       </c>
       <c r="I17" s="14" t="inlineStr">
         <is>
-          <t>4 / 3.0 / 0/9</t>
+          <t>4 / 3.1 / 0/10</t>
         </is>
       </c>
     </row>
@@ -16400,29 +16400,29 @@
       <c r="B18" s="13" t="inlineStr"/>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/14</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>6 / 2.1 / 1/14</t>
+          <t>6 / 2.3 / 2/14</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/13</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr"/>
       <c r="G18" s="13" t="inlineStr"/>
       <c r="H18" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/12</t>
+          <t>0 / 0.8 / 0/13</t>
         </is>
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.4 / 0/9</t>
+          <t>4 / 2.6 / 0/10</t>
         </is>
       </c>
     </row>
@@ -16435,25 +16435,25 @@
       <c r="B19" s="14" t="inlineStr"/>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/14</t>
+          <t>2 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr"/>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>5 / 4.2 / 3/13</t>
+          <t>5 / 4.2 / 3/14</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr"/>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>5 / 4.0 / 0/10</t>
+          <t>5 / 4.1 / 0/11</t>
         </is>
       </c>
       <c r="H19" s="14" t="inlineStr"/>
       <c r="I19" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.6 / 0/9</t>
+          <t>3 / 2.6 / 0/10</t>
         </is>
       </c>
     </row>
@@ -16475,32 +16475,32 @@
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/13</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/13</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/10</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="H20" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/12</t>
+          <t>0 / 0.1 / 0/13</t>
         </is>
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/9</t>
+          <t>1 / 0.6 / 0/10</t>
         </is>
       </c>
     </row>
@@ -16513,37 +16513,37 @@
       <c r="B21" s="14" t="inlineStr"/>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/14</t>
+          <t>0 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/13</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.8 / 0/13</t>
+          <t>2 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/10</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/12</t>
+          <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
       <c r="I21" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.4 / 0/9</t>
+          <t>2 / 1.5 / 0/10</t>
         </is>
       </c>
     </row>
@@ -16561,32 +16561,32 @@
       </c>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/14</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/13</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/13</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/10</t>
+          <t>0 / 0.2 / 0/11</t>
         </is>
       </c>
       <c r="H22" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/12</t>
+          <t>1 / 1.0 / 0/13</t>
         </is>
       </c>
       <c r="I22" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/9</t>
+          <t>1 / 1.0 / 0/10</t>
         </is>
       </c>
     </row>
@@ -16600,27 +16600,27 @@
       <c r="C23" s="14" t="inlineStr"/>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>12 / 9.3 / 11/14</t>
+          <t>12 / 9.9 / 12/14</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.3 / 0/13</t>
+          <t>1 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>6 / 6.1 / 6/13</t>
+          <t>6 / 6.1 / 7/14</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.1 / 0/10</t>
+          <t>1 / 2.0 / 0/11</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>5 / 3.8 / 0/12</t>
+          <t>5 / 3.8 / 0/13</t>
         </is>
       </c>
       <c r="I23" s="14" t="inlineStr"/>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
@@ -16648,27 +16648,27 @@
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.6 / 0/11</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
-      <c r="F24" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/13</t>
-        </is>
-      </c>
-      <c r="G24" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.7 / 0/10</t>
-        </is>
-      </c>
-      <c r="H24" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
       <c r="I24" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
     </row>
@@ -16681,29 +16681,29 @@
       <c r="B25" s="14" t="inlineStr"/>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.2 / 0/14</t>
+          <t>0 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr"/>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 0/13</t>
+          <t>1 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/10</t>
+          <t>2 / 1.1 / 0/11</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/12</t>
+          <t>1 / 0.5 / 0/13</t>
         </is>
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
-          <t>4 / 2.4 / 0/9</t>
+          <t>4 / 2.6 / 0/10</t>
         </is>
       </c>
     </row>
@@ -16718,23 +16718,23 @@
       <c r="D26" s="13" t="inlineStr"/>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>5 / 4.4 / 2/13</t>
+          <t>5 / 4.4 / 2/14</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr"/>
       <c r="G26" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.8 / 1/10</t>
+          <t>0 / 1.6 / 1/11</t>
         </is>
       </c>
       <c r="H26" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.6 / 0/12</t>
+          <t>1 / 1.5 / 0/13</t>
         </is>
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.9 / 0/9</t>
+          <t>3 / 2.0 / 0/10</t>
         </is>
       </c>
     </row>
@@ -16761,27 +16761,27 @@
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>2 / 1.3 / 0/14</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/11</t>
+        </is>
+      </c>
+      <c r="H27" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>2 / 1.2 / 0/13</t>
-        </is>
-      </c>
-      <c r="G27" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.2 / 0/10</t>
-        </is>
-      </c>
-      <c r="H27" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
       <c r="I27" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
     </row>
@@ -16798,37 +16798,37 @@
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/14</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/13</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/13</t>
+          <t>1 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/10</t>
+          <t>0 / 0.5 / 0/11</t>
         </is>
       </c>
       <c r="H28" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/12</t>
+          <t>0 / 0.2 / 0/13</t>
         </is>
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
     </row>
@@ -16840,12 +16840,12 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.5 / 0/14</t>
+          <t>3 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.9 / 0/14</t>
+          <t>2 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="D29" s="14" t="inlineStr">
@@ -16855,27 +16855,27 @@
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/13</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.7 / 0/13</t>
+          <t>3 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/10</t>
+          <t>0 / 0.8 / 0/11</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/12</t>
+          <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
       <c r="I29" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
     </row>
@@ -16892,37 +16892,37 @@
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/14</t>
+          <t>1 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/13</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/13</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="H30" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.3 / 0/13</t>
+        </is>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/10</t>
-        </is>
-      </c>
-      <c r="H30" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.3 / 0/12</t>
-        </is>
-      </c>
-      <c r="I30" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
     </row>
@@ -16934,42 +16934,42 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="D31" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>1 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="E31" s="14" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
-      <c r="F31" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/13</t>
-        </is>
-      </c>
-      <c r="G31" s="14" t="inlineStr">
+      <c r="I31" s="14" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/10</t>
-        </is>
-      </c>
-      <c r="H31" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
-      <c r="I31" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
     </row>
@@ -16992,27 +16992,27 @@
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.4 / 0/13</t>
+          <t>1 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.0 / 0/13</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.8 / 1/10</t>
+          <t>3 / 2.8 / 1/11</t>
         </is>
       </c>
       <c r="H32" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.8 / 0/12</t>
+          <t>0 / 0.7 / 0/13</t>
         </is>
       </c>
       <c r="I32" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.3 / 0/9</t>
+          <t>1 / 2.2 / 0/10</t>
         </is>
       </c>
     </row>
@@ -17025,37 +17025,37 @@
       <c r="B33" s="14" t="inlineStr"/>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.3 / 0/14</t>
+          <t>0 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
-          <t>4 / 2.1 / 0/14</t>
+          <t>4 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.7 / 0/13</t>
+          <t>2 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.5 / 0/13</t>
+          <t>2 / 2.5 / 0/14</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.1 / 0/10</t>
+          <t>1 / 2.0 / 0/11</t>
         </is>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.6 / 0/12</t>
+          <t>2 / 1.6 / 0/13</t>
         </is>
       </c>
       <c r="I33" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/9</t>
+          <t>1 / 1.0 / 0/10</t>
         </is>
       </c>
     </row>
@@ -17083,33 +17083,33 @@
       <c r="B35" s="14" t="inlineStr"/>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.8 / 0/13</t>
+          <t>2 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="F35" s="14" t="inlineStr"/>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.2 / 0/10</t>
+          <t>3 / 1.4 / 0/11</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/12</t>
+          <t>0 / 0.1 / 0/13</t>
         </is>
       </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
     </row>
@@ -17121,7 +17121,7 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
@@ -17136,27 +17136,27 @@
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="G36" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="H36" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
-      <c r="F36" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/13</t>
-        </is>
-      </c>
-      <c r="G36" s="13" t="inlineStr">
+      <c r="I36" s="13" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/10</t>
-        </is>
-      </c>
-      <c r="H36" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
-      <c r="I36" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
     </row>
@@ -17168,7 +17168,7 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.7 / 0/14</t>
+          <t>1 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="C37" s="14" t="inlineStr">
@@ -17183,27 +17183,27 @@
       </c>
       <c r="E37" s="14" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="F37" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>0 / 1.2 / 0/11</t>
+        </is>
+      </c>
+      <c r="H37" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
-      <c r="F37" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/13</t>
-        </is>
-      </c>
-      <c r="G37" s="14" t="inlineStr">
-        <is>
-          <t>0 / 1.3 / 0/10</t>
-        </is>
-      </c>
-      <c r="H37" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
       <c r="I37" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
     </row>
@@ -17215,7 +17215,7 @@
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.4 / 0/14</t>
+          <t>1 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
@@ -17230,27 +17230,27 @@
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/13</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.8 / 0/13</t>
+          <t>2 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/10</t>
+          <t>1 / 0.5 / 0/11</t>
         </is>
       </c>
       <c r="H38" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/12</t>
+          <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/9</t>
+          <t>1 / 1.0 / 0/10</t>
         </is>
       </c>
     </row>
@@ -17268,28 +17268,28 @@
       </c>
       <c r="D39" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/14</t>
+          <t>1 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="E39" s="14" t="inlineStr"/>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.2 / 0/13</t>
+          <t>0 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>1 / 3.1 / 2/10</t>
+          <t>1 / 2.9 / 2/11</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/12</t>
+          <t>0 / 0.2 / 0/13</t>
         </is>
       </c>
       <c r="I39" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/9</t>
+          <t>1 / 0.9 / 0/10</t>
         </is>
       </c>
     </row>
@@ -17304,14 +17304,14 @@
       <c r="D40" s="13" t="inlineStr"/>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/13</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="F40" s="13" t="inlineStr"/>
       <c r="G40" s="13" t="inlineStr"/>
       <c r="H40" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/12</t>
+          <t>1 / 1.1 / 0/13</t>
         </is>
       </c>
       <c r="I40" s="13" t="inlineStr"/>
@@ -17330,32 +17330,32 @@
       </c>
       <c r="D41" s="14" t="inlineStr">
         <is>
-          <t>7 / 3.9 / 5/14</t>
+          <t>6 / 4.3 / 6/14</t>
         </is>
       </c>
       <c r="E41" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/13</t>
+          <t>1 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="F41" s="14" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.4 / 0/11</t>
+        </is>
+      </c>
+      <c r="H41" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
-      <c r="G41" s="14" t="inlineStr">
-        <is>
-          <t>1 / 1.4 / 0/10</t>
-        </is>
-      </c>
-      <c r="H41" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
       <c r="I41" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
     </row>
@@ -17367,7 +17367,7 @@
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>3 / 4.3 / 1/14</t>
+          <t>3 / 4.1 / 0/14</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
@@ -17377,32 +17377,32 @@
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.4 / 0/14</t>
+          <t>1 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="F42" s="13" t="inlineStr">
+        <is>
+          <t>3 / 1.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="G42" s="13" t="inlineStr">
+        <is>
+          <t>2 / 1.5 / 0/11</t>
+        </is>
+      </c>
+      <c r="H42" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
-      <c r="F42" s="13" t="inlineStr">
-        <is>
-          <t>3 / 0.8 / 0/13</t>
-        </is>
-      </c>
-      <c r="G42" s="13" t="inlineStr">
-        <is>
-          <t>2 / 1.5 / 0/10</t>
-        </is>
-      </c>
-      <c r="H42" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
       <c r="I42" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/9</t>
+          <t>1 / 1.0 / 0/10</t>
         </is>
       </c>
     </row>
@@ -17414,7 +17414,7 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>4 / 2.3 / 0/14</t>
+          <t>4 / 2.5 / 0/14</t>
         </is>
       </c>
       <c r="C43" s="14" t="inlineStr">
@@ -17429,27 +17429,27 @@
       </c>
       <c r="E43" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/13</t>
+          <t>1 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/13</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/10</t>
+          <t>0 / 0.0 / 0/11</t>
         </is>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/12</t>
+          <t>1 / 0.5 / 0/13</t>
         </is>
       </c>
       <c r="I43" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/9</t>
+          <t>1 / 0.7 / 0/10</t>
         </is>
       </c>
     </row>
@@ -17462,37 +17462,37 @@
       <c r="B44" s="13" t="inlineStr"/>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>1 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>9 / 5.1 / 5/14</t>
+          <t>9 / 5.5 / 6/14</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/13</t>
+          <t>1 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="F44" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.5 / 0/13</t>
+          <t>3 / 2.5 / 0/14</t>
         </is>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.6 / 2/10</t>
+          <t>2 / 2.5 / 2/11</t>
         </is>
       </c>
       <c r="H44" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.4 / 1/12</t>
+          <t>2 / 2.4 / 1/13</t>
         </is>
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/9</t>
+          <t>1 / 0.6 / 0/10</t>
         </is>
       </c>
     </row>
@@ -17505,7 +17505,7 @@
       <c r="B45" s="14" t="inlineStr"/>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.4 / 0/14</t>
+          <t>0 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="D45" s="14" t="inlineStr">
@@ -17515,23 +17515,23 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>15 / 3.3 / 2/13</t>
+          <t>16 / 4.2 / 3/14</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.4 / 0/13</t>
+          <t>2 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr"/>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>5 / 1.2 / 1/12</t>
+          <t>5 / 1.5 / 1/13</t>
         </is>
       </c>
       <c r="I45" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.2 / 0/9</t>
+          <t>2 / 1.3 / 0/10</t>
         </is>
       </c>
     </row>
@@ -17543,7 +17543,7 @@
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>25 / 7.9 / 3/14</t>
+          <t>25 / 9.4 / 4/14</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
@@ -17553,32 +17553,32 @@
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.6 / 0/14</t>
+          <t>3 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/13</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="F46" s="13" t="inlineStr">
         <is>
+          <t>1 / 0.2 / 0/14</t>
+        </is>
+      </c>
+      <c r="G46" s="13" t="inlineStr">
+        <is>
+          <t>1 / 0.4 / 0/11</t>
+        </is>
+      </c>
+      <c r="H46" s="13" t="inlineStr">
+        <is>
           <t>1 / 0.2 / 0/13</t>
         </is>
       </c>
-      <c r="G46" s="13" t="inlineStr">
-        <is>
-          <t>1 / 0.3 / 0/10</t>
-        </is>
-      </c>
-      <c r="H46" s="13" t="inlineStr">
-        <is>
-          <t>1 / 0.1 / 0/12</t>
-        </is>
-      </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.4 / 0/9</t>
+          <t>2 / 0.6 / 0/10</t>
         </is>
       </c>
     </row>
@@ -17601,23 +17601,23 @@
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.1 / 0/13</t>
+          <t>2 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>4 / 2.5 / 0/13</t>
+          <t>4 / 2.6 / 0/14</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.6 / 2/10</t>
+          <t>1 / 2.5 / 2/11</t>
         </is>
       </c>
       <c r="H47" s="14" t="inlineStr"/>
       <c r="I47" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/9</t>
+          <t>1 / 1.0 / 0/10</t>
         </is>
       </c>
     </row>
@@ -17631,28 +17631,28 @@
       <c r="C48" s="13" t="inlineStr"/>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>5 / 3.5 / 0/14</t>
+          <t>5 / 3.8 / 0/14</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.6 / 0/13</t>
+          <t>1 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="F48" s="13" t="inlineStr"/>
       <c r="G48" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.1 / 0/10</t>
+          <t>0 / 1.9 / 0/11</t>
         </is>
       </c>
       <c r="H48" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/12</t>
+          <t>1 / 0.6 / 0/13</t>
         </is>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.8 / 0/9</t>
+          <t>3 / 1.9 / 0/10</t>
         </is>
       </c>
     </row>
@@ -17679,27 +17679,27 @@
       </c>
       <c r="E49" s="14" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="H49" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
-      <c r="F49" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/13</t>
-        </is>
-      </c>
-      <c r="G49" s="14" t="inlineStr">
+      <c r="I49" s="14" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/10</t>
-        </is>
-      </c>
-      <c r="H49" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
-      <c r="I49" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
     </row>
@@ -17711,7 +17711,7 @@
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/14</t>
+          <t>2 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
@@ -17726,27 +17726,27 @@
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="F50" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="G50" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/11</t>
+        </is>
+      </c>
+      <c r="H50" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
-      <c r="F50" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/13</t>
-        </is>
-      </c>
-      <c r="G50" s="13" t="inlineStr">
+      <c r="I50" s="13" t="inlineStr">
         <is>
           <t>0 / 0.1 / 0/10</t>
-        </is>
-      </c>
-      <c r="H50" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
-      <c r="I50" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.1 / 0/9</t>
         </is>
       </c>
     </row>
@@ -17759,37 +17759,37 @@
       <c r="B51" s="14" t="inlineStr"/>
       <c r="C51" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="D51" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.5 / 0/14</t>
+          <t>3 / 2.6 / 0/14</t>
         </is>
       </c>
       <c r="E51" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.6 / 0/13</t>
+          <t>3 / 2.6 / 0/14</t>
         </is>
       </c>
       <c r="F51" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/13</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/10</t>
+          <t>1 / 1.1 / 0/11</t>
         </is>
       </c>
       <c r="H51" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/12</t>
+          <t>1 / 0.6 / 0/13</t>
         </is>
       </c>
       <c r="I51" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/9</t>
+          <t>1 / 0.6 / 0/10</t>
         </is>
       </c>
     </row>
@@ -17801,7 +17801,7 @@
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.3 / 0/14</t>
+          <t>2 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
@@ -17816,27 +17816,27 @@
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="F52" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="G52" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.7 / 0/11</t>
+        </is>
+      </c>
+      <c r="H52" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
-      <c r="F52" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/13</t>
-        </is>
-      </c>
-      <c r="G52" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.8 / 0/10</t>
-        </is>
-      </c>
-      <c r="H52" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
     </row>
@@ -17848,7 +17848,7 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.6 / 0/14</t>
+          <t>2 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="C53" s="14" t="inlineStr">
@@ -17863,27 +17863,27 @@
       </c>
       <c r="E53" s="14" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="F53" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.4 / 0/11</t>
+        </is>
+      </c>
+      <c r="H53" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
-      <c r="F53" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/13</t>
-        </is>
-      </c>
-      <c r="G53" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.4 / 0/10</t>
-        </is>
-      </c>
-      <c r="H53" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
       <c r="I53" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
     </row>
@@ -17906,27 +17906,27 @@
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/13</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="F54" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/13</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="G54" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/10</t>
+          <t>0 / 0.4 / 0/11</t>
         </is>
       </c>
       <c r="H54" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/12</t>
+          <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
       <c r="I54" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/9</t>
+          <t>0 / 0.3 / 0/10</t>
         </is>
       </c>
     </row>
@@ -17938,42 +17938,42 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
+          <t>1 / 0.7 / 0/14</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="D55" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="E55" s="14" t="inlineStr">
+        <is>
           <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
-      <c r="C55" s="14" t="inlineStr">
+      <c r="F55" s="14" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
-      <c r="D55" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/14</t>
-        </is>
-      </c>
-      <c r="E55" s="14" t="inlineStr">
-        <is>
-          <t>1 / 0.6 / 0/13</t>
-        </is>
-      </c>
-      <c r="F55" s="14" t="inlineStr">
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="H55" s="14" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
-      <c r="G55" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/10</t>
-        </is>
-      </c>
-      <c r="H55" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
       <c r="I55" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/9</t>
+          <t>1 / 0.8 / 0/10</t>
         </is>
       </c>
     </row>
@@ -17992,27 +17992,27 @@
       <c r="D56" s="13" t="inlineStr"/>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/13</t>
+          <t>1 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="F56" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/13</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/10</t>
+          <t>0 / 0.2 / 0/11</t>
         </is>
       </c>
       <c r="H56" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/12</t>
+          <t>1 / 0.7 / 0/13</t>
         </is>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.7 / 1/9</t>
+          <t>1 / 2.5 / 1/10</t>
         </is>
       </c>
     </row>
@@ -18029,7 +18029,7 @@
       </c>
       <c r="C57" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="D57" s="14" t="inlineStr">
@@ -18039,27 +18039,27 @@
       </c>
       <c r="E57" s="14" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="F57" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.4 / 0/11</t>
+        </is>
+      </c>
+      <c r="H57" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
-      <c r="F57" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/13</t>
-        </is>
-      </c>
-      <c r="G57" s="14" t="inlineStr">
-        <is>
-          <t>1 / 0.3 / 0/10</t>
-        </is>
-      </c>
-      <c r="H57" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
       <c r="I57" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
     </row>
@@ -18071,7 +18071,7 @@
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>2 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="C58" s="13" t="inlineStr">
@@ -18086,27 +18086,27 @@
       </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="F58" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="G58" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.4 / 0/11</t>
+        </is>
+      </c>
+      <c r="H58" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
-      <c r="F58" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/13</t>
-        </is>
-      </c>
-      <c r="G58" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.4 / 0/10</t>
-        </is>
-      </c>
-      <c r="H58" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
     </row>
@@ -18119,33 +18119,33 @@
       <c r="B59" s="14" t="inlineStr"/>
       <c r="C59" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.4 / 0/14</t>
+          <t>0 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="D59" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>1 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="E59" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.7 / 0/13</t>
+          <t>1 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="F59" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/13</t>
+          <t>1 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="G59" s="14" t="inlineStr"/>
       <c r="H59" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.9 / 0/12</t>
+          <t>2 / 1.9 / 0/13</t>
         </is>
       </c>
       <c r="I59" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
     </row>
@@ -18158,37 +18158,37 @@
       <c r="B60" s="13" t="inlineStr"/>
       <c r="C60" s="13" t="inlineStr">
         <is>
-          <t>0 / 2.9 / 3/14</t>
+          <t>0 / 2.7 / 3/14</t>
         </is>
       </c>
       <c r="D60" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.1 / 0/14</t>
+          <t>4 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/13</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="F60" s="13" t="inlineStr">
         <is>
-          <t>4 / 1.6 / 0/13</t>
+          <t>3 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="G60" s="13" t="inlineStr">
         <is>
-          <t>0 / 2.2 / 1/10</t>
+          <t>0 / 2.0 / 1/11</t>
         </is>
       </c>
       <c r="H60" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/12</t>
+          <t>1 / 0.4 / 0/13</t>
         </is>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/9</t>
+          <t>2 / 1.2 / 0/10</t>
         </is>
       </c>
     </row>
@@ -18206,27 +18206,27 @@
       </c>
       <c r="D61" s="14" t="inlineStr">
         <is>
+          <t>2 / 1.8 / 0/14</t>
+        </is>
+      </c>
+      <c r="E61" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="F61" s="14" t="inlineStr">
+        <is>
           <t>2 / 1.6 / 0/14</t>
         </is>
       </c>
-      <c r="E61" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/13</t>
-        </is>
-      </c>
-      <c r="F61" s="14" t="inlineStr">
-        <is>
-          <t>2 / 1.5 / 0/13</t>
-        </is>
-      </c>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.7 / 0/10</t>
+          <t>3 / 2.7 / 0/11</t>
         </is>
       </c>
       <c r="H61" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/12</t>
+          <t>1 / 0.2 / 0/13</t>
         </is>
       </c>
       <c r="I61" s="14" t="inlineStr"/>
@@ -18240,33 +18240,33 @@
       <c r="B62" s="13" t="inlineStr"/>
       <c r="C62" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
-          <t>4 / 1.9 / 0/14</t>
+          <t>4 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr"/>
       <c r="F62" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/13</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="G62" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 0/10</t>
+          <t>2 / 1.5 / 0/11</t>
         </is>
       </c>
       <c r="H62" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.8 / 0/12</t>
+          <t>0 / 0.7 / 0/13</t>
         </is>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/9</t>
+          <t>1 / 0.7 / 0/10</t>
         </is>
       </c>
     </row>
@@ -18281,18 +18281,18 @@
       <c r="D63" s="14" t="inlineStr"/>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>6 / 4.3 / 1/13</t>
+          <t>6 / 4.4 / 2/14</t>
         </is>
       </c>
       <c r="F63" s="14" t="inlineStr"/>
       <c r="G63" s="14" t="inlineStr">
         <is>
-          <t>4 / 4.4 / 2/10</t>
+          <t>4 / 4.4 / 2/11</t>
         </is>
       </c>
       <c r="H63" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.3 / 0/12</t>
+          <t>3 / 2.4 / 0/13</t>
         </is>
       </c>
       <c r="I63" s="14" t="inlineStr"/>
@@ -18308,23 +18308,23 @@
       <c r="D64" s="13" t="inlineStr"/>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.6 / 0/13</t>
+          <t>4 / 2.7 / 0/14</t>
         </is>
       </c>
       <c r="F64" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.9 / 0/13</t>
+          <t>3 / 2.9 / 0/14</t>
         </is>
       </c>
       <c r="G64" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.4 / 0/10</t>
+          <t>2 / 3.3 / 0/11</t>
         </is>
       </c>
       <c r="H64" s="13" t="inlineStr"/>
       <c r="I64" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.3 / 0/9</t>
+          <t>4 / 3.4 / 0/10</t>
         </is>
       </c>
     </row>
@@ -18336,7 +18336,7 @@
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="C65" s="14" t="inlineStr">
@@ -18351,27 +18351,27 @@
       </c>
       <c r="E65" s="14" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="F65" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="G65" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/11</t>
+        </is>
+      </c>
+      <c r="H65" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
-      <c r="F65" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/13</t>
-        </is>
-      </c>
-      <c r="G65" s="14" t="inlineStr">
+      <c r="I65" s="14" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/10</t>
-        </is>
-      </c>
-      <c r="H65" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
-      <c r="I65" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/9</t>
         </is>
       </c>
     </row>
@@ -18383,7 +18383,7 @@
       </c>
       <c r="B66" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.3 / 0/14</t>
+          <t>3 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="C66" s="13" t="inlineStr">
@@ -18398,27 +18398,27 @@
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/13</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="F66" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/13</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="G66" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/10</t>
+          <t>0 / 0.4 / 0/11</t>
         </is>
       </c>
       <c r="H66" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/12</t>
+          <t>1 / 0.5 / 0/13</t>
         </is>
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
     </row>
@@ -18436,32 +18436,32 @@
       </c>
       <c r="D67" s="14" t="inlineStr">
         <is>
-          <t>4 / 2.2 / 0/14</t>
+          <t>4 / 2.3 / 0/14</t>
         </is>
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/13</t>
+          <t>2 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="F67" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/13</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/10</t>
+          <t>0 / 0.6 / 0/11</t>
         </is>
       </c>
       <c r="H67" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/12</t>
+          <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
       <c r="I67" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/9</t>
+          <t>0 / 0.3 / 0/10</t>
         </is>
       </c>
     </row>
@@ -18473,42 +18473,42 @@
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.4 / 0/14</t>
+          <t>3 / 2.3 / 0/14</t>
         </is>
       </c>
       <c r="C68" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="D68" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
-      <c r="D68" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.2 / 0/14</t>
-        </is>
-      </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/13</t>
+          <t>2 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="F68" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="G68" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.4 / 0/11</t>
+        </is>
+      </c>
+      <c r="H68" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
-      <c r="G68" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.4 / 0/10</t>
-        </is>
-      </c>
-      <c r="H68" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/12</t>
-        </is>
-      </c>
       <c r="I68" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
     </row>
@@ -18520,42 +18520,42 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>2 / 3.1 / 1/14</t>
+          <t>2 / 2.6 / 0/14</t>
         </is>
       </c>
       <c r="C69" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="D69" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.6 / 0/14</t>
+          <t>2 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="E69" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/13</t>
+          <t>1 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="F69" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/13</t>
+          <t>1 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="G69" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/10</t>
+          <t>0 / 0.2 / 0/11</t>
         </is>
       </c>
       <c r="H69" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/12</t>
+          <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
       <c r="I69" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/9</t>
+          <t>0 / 0.0 / 0/10</t>
         </is>
       </c>
     </row>
@@ -18573,32 +18573,32 @@
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/14</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.0 / 0/13</t>
+          <t>4 / 3.1 / 0/14</t>
         </is>
       </c>
       <c r="F70" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/13</t>
+          <t>0 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="G70" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/10</t>
+          <t>0 / 0.1 / 0/11</t>
         </is>
       </c>
       <c r="H70" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/12</t>
+          <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
       <c r="I70" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/9</t>
+          <t>1 / 1.1 / 0/10</t>
         </is>
       </c>
     </row>
@@ -18616,24 +18616,24 @@
       </c>
       <c r="D71" s="14" t="inlineStr">
         <is>
-          <t>9 / 5.6 / 5/14</t>
+          <t>9 / 5.9 / 6/14</t>
         </is>
       </c>
       <c r="E71" s="14" t="inlineStr">
         <is>
-          <t>2 / 3.8 / 2/13</t>
+          <t>2 / 3.7 / 2/14</t>
         </is>
       </c>
       <c r="F71" s="14" t="inlineStr"/>
       <c r="G71" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.8 / 0/10</t>
+          <t>3 / 2.8 / 0/11</t>
         </is>
       </c>
       <c r="H71" s="14" t="inlineStr"/>
       <c r="I71" s="14" t="inlineStr">
         <is>
-          <t>3 / 3.8 / 0/9</t>
+          <t>3 / 3.7 / 0/10</t>
         </is>
       </c>
     </row>
@@ -18656,27 +18656,27 @@
       </c>
       <c r="E72" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.0 / 0/13</t>
+          <t>4 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="F72" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/13</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="G72" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/10</t>
+          <t>1 / 1.2 / 0/11</t>
         </is>
       </c>
       <c r="H72" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/12</t>
+          <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/9</t>
+          <t>2 / 1.2 / 0/10</t>
         </is>
       </c>
     </row>
@@ -18689,37 +18689,37 @@
       <c r="B73" s="14" t="inlineStr"/>
       <c r="C73" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/14</t>
+          <t>1 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="D73" s="14" t="inlineStr">
         <is>
-          <t>7 / 2.7 / 5/14</t>
+          <t>7 / 3.1 / 6/14</t>
         </is>
       </c>
       <c r="E73" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/13</t>
+          <t>1 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="F73" s="14" t="inlineStr">
         <is>
-          <t>6 / 3.1 / 1/13</t>
+          <t>6 / 3.3 / 2/14</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.4 / 0/10</t>
+          <t>3 / 2.5 / 0/11</t>
         </is>
       </c>
       <c r="H73" s="14" t="inlineStr">
         <is>
-          <t>4 / 3.2 / 0/12</t>
+          <t>4 / 3.2 / 0/13</t>
         </is>
       </c>
       <c r="I73" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/9</t>
+          <t>0 / 0.3 / 0/10</t>
         </is>
       </c>
     </row>
@@ -18738,27 +18738,27 @@
       </c>
       <c r="E74" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.2 / 0/13</t>
+          <t>4 / 3.3 / 0/14</t>
         </is>
       </c>
       <c r="F74" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/13</t>
+          <t>2 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="G74" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.7 / 0/10</t>
+          <t>0 / 1.5 / 0/11</t>
         </is>
       </c>
       <c r="H74" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/12</t>
+          <t>1 / 0.6 / 0/13</t>
         </is>
       </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.4 / 0/9</t>
+          <t>2 / 1.5 / 0/10</t>
         </is>
       </c>
     </row>
@@ -18771,37 +18771,37 @@
       <c r="B75" s="14" t="inlineStr"/>
       <c r="C75" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="D75" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.9 / 0/14</t>
+          <t>2 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="E75" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.9 / 0/13</t>
+          <t>2 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="F75" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/13</t>
+          <t>1 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="G75" s="14" t="inlineStr">
         <is>
+          <t>1 / 0.8 / 0/11</t>
+        </is>
+      </c>
+      <c r="H75" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.3 / 0/13</t>
+        </is>
+      </c>
+      <c r="I75" s="14" t="inlineStr">
+        <is>
           <t>1 / 0.8 / 0/10</t>
-        </is>
-      </c>
-      <c r="H75" s="14" t="inlineStr">
-        <is>
-          <t>1 / 0.2 / 0/12</t>
-        </is>
-      </c>
-      <c r="I75" s="14" t="inlineStr">
-        <is>
-          <t>1 / 0.8 / 0/9</t>
         </is>
       </c>
     </row>
@@ -18814,37 +18814,37 @@
       <c r="B76" s="13" t="inlineStr"/>
       <c r="C76" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.4 / 0/14</t>
+        </is>
+      </c>
+      <c r="D76" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.5 / 0/14</t>
         </is>
       </c>
-      <c r="D76" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.7 / 0/14</t>
-        </is>
-      </c>
       <c r="E76" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.3 / 0/13</t>
+          <t>2 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="F76" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.9 / 0/13</t>
+          <t>2 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="G76" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.2 / 0/10</t>
+          <t>2 / 3.1 / 0/11</t>
         </is>
       </c>
       <c r="H76" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/12</t>
+          <t>1 / 1.2 / 0/13</t>
         </is>
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.1 / 0/9</t>
+          <t>2 / 3.0 / 0/10</t>
         </is>
       </c>
     </row>
@@ -18857,33 +18857,33 @@
       <c r="B77" s="14" t="inlineStr"/>
       <c r="C77" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.7 / 0/14</t>
+          <t>1 / 2.5 / 0/14</t>
         </is>
       </c>
       <c r="D77" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.6 / 0/14</t>
+          <t>3 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="E77" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/13</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="F77" s="14" t="inlineStr">
         <is>
-          <t>8 / 4.8 / 5/13</t>
+          <t>8 / 5.1 / 6/14</t>
         </is>
       </c>
       <c r="G77" s="14" t="inlineStr"/>
       <c r="H77" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 0/12</t>
+          <t>1 / 1.5 / 0/13</t>
         </is>
       </c>
       <c r="I77" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.3 / 0/9</t>
+          <t>2 / 1.4 / 0/10</t>
         </is>
       </c>
     </row>
@@ -18897,32 +18897,32 @@
       <c r="C78" s="13" t="inlineStr"/>
       <c r="D78" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.4 / 0/14</t>
+          <t>4 / 2.3 / 0/14</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
         <is>
-          <t>3 / 3.1 / 0/13</t>
+          <t>3 / 3.1 / 0/14</t>
         </is>
       </c>
       <c r="F78" s="13" t="inlineStr">
         <is>
-          <t>5 / 3.0 / 2/13</t>
+          <t>5 / 3.1 / 2/14</t>
         </is>
       </c>
       <c r="G78" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 2/10</t>
+          <t>1 / 1.5 / 2/11</t>
         </is>
       </c>
       <c r="H78" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/12</t>
+          <t>0 / 0.0 / 0/13</t>
         </is>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/9</t>
+          <t>1 / 1.2 / 0/10</t>
         </is>
       </c>
     </row>
@@ -18937,19 +18937,19 @@
       <c r="D79" s="14" t="inlineStr"/>
       <c r="E79" s="14" t="inlineStr">
         <is>
-          <t>4 / 4.2 / 0/13</t>
+          <t>4 / 4.1 / 0/14</t>
         </is>
       </c>
       <c r="F79" s="14" t="inlineStr">
         <is>
-          <t>18 / 9.2 / 7/13</t>
+          <t>18 / 9.9 / 8/14</t>
         </is>
       </c>
       <c r="G79" s="14" t="inlineStr"/>
       <c r="H79" s="14" t="inlineStr"/>
       <c r="I79" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.8 / 0/9</t>
+          <t>3 / 2.8 / 0/10</t>
         </is>
       </c>
     </row>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -17,8 +17,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sitewide'!$A$1:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'JobG8 categories'!$A$1:$C$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'PAGES'!$A$1:$H$159</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$F$300</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'PAGES'!$A$1:$H$160</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$F$303</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'LIVE'!$A$1:$I$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'NOT LIVE'!$A$1:$I$79</definedName>
   </definedNames>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1913</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="3">
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1501</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="4">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="5">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1990</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="6">
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8">
@@ -674,7 +674,7 @@
         <v>1356</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>741</v>
+        <v>746</v>
       </c>
     </row>
     <row r="5">
@@ -726,7 +726,7 @@
         <v>413</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -854,7 +854,7 @@
         <v>10000</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>1520</v>
+        <v>1526</v>
       </c>
     </row>
   </sheetData>
@@ -869,7 +869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H159"/>
+  <dimension ref="A1:H160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -943,7 +943,7 @@
       <c r="D2" s="11" t="inlineStr"/>
       <c r="E2" s="11" t="inlineStr"/>
       <c r="F2" s="12" t="n">
-        <v>2053</v>
+        <v>2079</v>
       </c>
       <c r="G2" s="11" t="inlineStr"/>
       <c r="H2" s="11" t="inlineStr">
@@ -975,10 +975,10 @@
         </is>
       </c>
       <c r="F3" s="12" t="n">
-        <v>1900</v>
+        <v>1925</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>1900</v>
+        <v>1925</v>
       </c>
       <c r="H3" s="11" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="F4" s="12" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G4" s="11" t="inlineStr"/>
       <c r="H4" s="11" t="inlineStr">
@@ -1368,7 +1368,7 @@
         <v>1</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>1</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>1</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>1</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>1</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>1</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>1</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>1</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>1</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>1</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>1</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>1</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>1</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>1</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>1</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>1</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>1</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>1</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>1</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>1</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>1</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>1</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>1</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>1</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>1</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>1</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>1</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>1</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>1</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>1</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>1</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>1</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>1</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>1</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>1</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>1</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>1</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>1</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>1</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>1</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>1</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>1</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>1</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
@@ -5881,24 +5881,24 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Finance &amp; Accounts</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>/job-search/bedfordshire/service-administrator-jobs</t>
+          <t>/job-search/northern-ireland-east/finance-accounts-jobs</t>
         </is>
       </c>
       <c r="F135" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
@@ -5919,24 +5919,24 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>/job-search/bristol-bath/customer-sales-jobs</t>
+          <t>/job-search/bedfordshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F136" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -5957,24 +5957,24 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>/job-search/buckinghamshire/marketing-jobs</t>
+          <t>/job-search/bristol-bath/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F137" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
@@ -5995,17 +5995,17 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Wales South - Cardiff &amp; Vale</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>/job-search/cardiff-vale/service-administrator-jobs</t>
+          <t>/job-search/buckinghamshire/marketing-jobs</t>
         </is>
       </c>
       <c r="F138" s="3" t="n">
@@ -6033,24 +6033,24 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Wales South - Cardiff &amp; Vale</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>/job-search/berkshire/customer-sales-jobs</t>
+          <t>/job-search/cardiff-vale/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F139" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -6081,14 +6081,14 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>/job-search/hertfordshire/customer-sales-jobs</t>
+          <t>/job-search/berkshire/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F140" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
@@ -6119,14 +6119,14 @@
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>/job-search/kent/customer-sales-jobs</t>
+          <t>/job-search/hertfordshire/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F141" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Scotland West - Glasgow</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -6157,14 +6157,14 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>/job-search/glasgow/customer-sales-jobs</t>
+          <t>/job-search/kent/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F142" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Scotland West - Glasgow</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
@@ -6195,14 +6195,14 @@
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>/job-search/surrey/customer-sales-jobs</t>
+          <t>/job-search/glasgow/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F143" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -6233,14 +6233,14 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>/job-search/sussex/customer-sales-jobs</t>
+          <t>/job-search/surrey/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F144" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6261,24 +6261,24 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>/job-search/bristol-bath/marketing-jobs</t>
+          <t>/job-search/sussex/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F145" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>/job-search/gloucestershire/marketing-jobs</t>
+          <t>/job-search/bristol-bath/marketing-jobs</t>
         </is>
       </c>
       <c r="F146" s="3" t="n">
@@ -6337,7 +6337,7 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
@@ -6347,14 +6347,14 @@
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>/job-search/hertfordshire/marketing-jobs</t>
+          <t>/job-search/gloucestershire/marketing-jobs</t>
         </is>
       </c>
       <c r="F147" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -6385,14 +6385,14 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>/job-search/kent/marketing-jobs</t>
+          <t>/job-search/hertfordshire/marketing-jobs</t>
         </is>
       </c>
       <c r="F148" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
@@ -6423,14 +6423,14 @@
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>/job-search/oxfordshire/marketing-jobs</t>
+          <t>/job-search/kent/marketing-jobs</t>
         </is>
       </c>
       <c r="F149" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H149" s="4" t="inlineStr">
         <is>
@@ -6451,24 +6451,24 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>/job-search/north-scotland/service-administrator-jobs</t>
+          <t>/job-search/oxfordshire/marketing-jobs</t>
         </is>
       </c>
       <c r="F150" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Scotland Central - Tayside</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
@@ -6499,14 +6499,14 @@
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>/job-search/tayside/service-administrator-jobs</t>
+          <t>/job-search/north-scotland/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F151" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H151" s="4" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Wales South - Valleys</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -6537,14 +6537,14 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>/job-search/south-wales-valleys/service-administrator-jobs</t>
+          <t>/job-search/tayside/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F152" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -6565,24 +6565,24 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Wales South - Valleys</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>/job-search/cambridgeshire/marketing-jobs</t>
+          <t>/job-search/south-wales-valleys/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F153" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G153" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H153" s="4" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -6613,14 +6613,14 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>/job-search/cheshire-west/marketing-jobs</t>
+          <t>/job-search/cambridgeshire/marketing-jobs</t>
         </is>
       </c>
       <c r="F154" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
@@ -6651,14 +6651,14 @@
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>/job-search/essex/marketing-jobs</t>
+          <t>/job-search/cheshire-west/marketing-jobs</t>
         </is>
       </c>
       <c r="F155" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Merseyside - Liverpool</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -6689,14 +6689,14 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>/job-search/merseyside-liverpool/marketing-jobs</t>
+          <t>/job-search/essex/marketing-jobs</t>
         </is>
       </c>
       <c r="F156" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>North East</t>
+          <t>Merseyside - Liverpool</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
@@ -6727,14 +6727,14 @@
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>/job-search/north-east/marketing-jobs</t>
+          <t>/job-search/merseyside-liverpool/marketing-jobs</t>
         </is>
       </c>
       <c r="F157" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G157" s="5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
@@ -6755,24 +6755,24 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>North East</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Customer Service &amp; Contact Centre</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>/job-search/buckinghamshire/customer-service-jobs</t>
+          <t>/job-search/north-east/marketing-jobs</t>
         </is>
       </c>
       <c r="F158" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -6793,33 +6793,71 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
+          <t>Buckinghamshire</t>
+        </is>
+      </c>
+      <c r="D159" s="4" t="inlineStr">
+        <is>
+          <t>Customer Service &amp; Contact Centre</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="inlineStr">
+        <is>
+          <t>/job-search/buckinghamshire/customer-service-jobs</t>
+        </is>
+      </c>
+      <c r="F159" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G159" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H159" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>Regional/category</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
           <t>North East</t>
         </is>
       </c>
-      <c r="D159" s="4" t="inlineStr">
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Customer Service &amp; Contact Centre</t>
         </is>
       </c>
-      <c r="E159" s="4" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>/job-search/north-east/customer-service-jobs</t>
         </is>
       </c>
-      <c r="F159" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G159" s="5" t="n">
+      <c r="F160" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G160" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H159" s="4" t="inlineStr">
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H159"/>
+  <autoFilter ref="A1:H160"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6830,7 +6868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F300"/>
+  <dimension ref="A1:F303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6881,16 +6919,16 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Altrincham</t>
+          <t>High Wycombe</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>0</v>
@@ -6905,16 +6943,16 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Newtownabbey</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>0</v>
@@ -6929,12 +6967,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Altrincham</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
@@ -6953,12 +6991,12 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Chelmsford</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -6977,12 +7015,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Chester Le Street</t>
+          <t>Chelmsford</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -7001,12 +7039,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Hemel Hempstead</t>
+          <t>Chester Le Street</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -7025,12 +7063,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>High Wycombe</t>
+          <t>Hemel Hempstead</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -7097,12 +7135,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Newtownabbey</t>
+          <t>Rotherham</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -7121,12 +7159,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Rotherham</t>
+          <t>Scarborough</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -7145,12 +7183,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Scarborough</t>
+          <t>Stockport</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -7169,12 +7207,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Stockport</t>
+          <t>Stoke-on-trent</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -7193,12 +7231,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Stoke-on-trent</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -7217,12 +7255,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Swindon</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -7241,12 +7279,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Swindon</t>
+          <t>Tonbridge</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -7260,26 +7298,30 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>CREATE</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Tonbridge</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>/manchester/service-administrator-jobs</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -7289,23 +7331,23 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Newcastle</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>/manchester/service-administrator-jobs</t>
+          <t>/newcastle/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7317,23 +7359,23 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Newcastle</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>/newcastle/service-administrator-jobs</t>
+          <t>/birmingham/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7345,12 +7387,12 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Belfast</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -7361,7 +7403,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>/birmingham/service-administrator-jobs</t>
+          <t>/belfast/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7373,23 +7415,23 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Belfast</t>
+          <t>Bristol</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>/belfast/service-administrator-jobs</t>
+          <t>/bristol/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7401,23 +7443,23 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Bristol</t>
+          <t>Leeds</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>/bristol/service-administrator-jobs</t>
+          <t>/leeds/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7429,23 +7471,23 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Merseyside - Liverpool</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>/leeds/service-administrator-jobs</t>
+          <t>/liverpool/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7457,12 +7499,12 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sheffield</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Merseyside - Liverpool</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -7473,7 +7515,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>/liverpool/service-administrator-jobs</t>
+          <t>/sheffield/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7513,23 +7555,23 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Sheffield</t>
+          <t>Glasgow</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>Scotland West - Glasgow</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E27" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>/sheffield/service-administrator-jobs</t>
+          <t>/glasgow/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7541,23 +7583,23 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Glasgow</t>
+          <t>Nottingham</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Scotland West - Glasgow</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>/glasgow/service-administrator-jobs</t>
+          <t>/nottingham/jobs</t>
         </is>
       </c>
     </row>
@@ -7569,23 +7611,23 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Nottingham</t>
+          <t>Bradford</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Nottinghamshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>/nottingham/jobs</t>
+          <t>/bradford/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7597,23 +7639,23 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Bradford</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Scotland Central - Edinburgh &amp; Lothians</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>/bradford/service-administrator-jobs</t>
+          <t>/edinburgh/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7653,23 +7695,23 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Scotland Central - Edinburgh &amp; Lothians</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D32" s="3" t="n">
         <v>10</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>/edinburgh/service-administrator-jobs</t>
+          <t>/southampton/service-administrator-jobs, /southampton/support-worker</t>
         </is>
       </c>
     </row>
@@ -7681,23 +7723,23 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Peterborough</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>/southampton/service-administrator-jobs, /southampton/support-worker</t>
+          <t>/peterborough/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7709,23 +7751,23 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Wakefield</t>
+          <t>Cambridge</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>/wakefield/jobs</t>
+          <t>/cambridge/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7737,23 +7779,23 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Cambridge</t>
+          <t>Doncaster</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E35" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>/cambridge/service-administrator-jobs</t>
+          <t>/doncaster/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7765,23 +7807,23 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Peterborough</t>
+          <t>Oxford</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>/peterborough/service-administrator-jobs</t>
+          <t>/oxford/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7835,12 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Doncaster</t>
+          <t>Wakefield</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
@@ -7809,7 +7851,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>/doncaster/service-administrator-jobs</t>
+          <t>/wakefield/jobs</t>
         </is>
       </c>
     </row>
@@ -7821,23 +7863,23 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Oxford</t>
+          <t>Bolton</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Greater Manchester - Wigan &amp; Bolton</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E38" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>/oxford/service-administrator-jobs</t>
+          <t>/bolton/jobs</t>
         </is>
       </c>
     </row>
@@ -7849,12 +7891,12 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Bolton</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - Wigan &amp; Bolton</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
@@ -7865,7 +7907,7 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>/bolton/jobs</t>
+          <t>/reading/jobs</t>
         </is>
       </c>
     </row>
@@ -7877,23 +7919,23 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Chester</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>/reading/jobs</t>
+          <t>/chester/jobs</t>
         </is>
       </c>
     </row>
@@ -7905,12 +7947,12 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Chester</t>
+          <t>Durham</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
@@ -7921,7 +7963,7 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>/chester/jobs</t>
+          <t>/durham/jobs</t>
         </is>
       </c>
     </row>
@@ -7933,12 +7975,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Durham</t>
+          <t>Gateshead</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
@@ -7949,7 +7991,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>/durham/jobs</t>
+          <t>/gateshead/jobs</t>
         </is>
       </c>
     </row>
@@ -7961,12 +8003,12 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Gateshead</t>
+          <t>Northallerton</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
@@ -7977,7 +8019,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>/gateshead/jobs</t>
+          <t>/northallerton/jobs</t>
         </is>
       </c>
     </row>
@@ -7989,12 +8031,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Northallerton</t>
+          <t>Norwich</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
@@ -8005,7 +8047,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>/northallerton/jobs</t>
+          <t>/norwich/jobs</t>
         </is>
       </c>
     </row>
@@ -8017,12 +8059,12 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Norwich</t>
+          <t>Salford</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
@@ -8033,7 +8075,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>/norwich/jobs</t>
+          <t>/salford/jobs</t>
         </is>
       </c>
     </row>
@@ -8045,12 +8087,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Salford</t>
+          <t>York</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D46" s="3" t="n">
@@ -8061,7 +8103,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>/salford/jobs</t>
+          <t>/york/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -8073,23 +8115,23 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>York</t>
+          <t>Brighton &amp; Hove</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D47" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E47" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>/york/service-administrator-jobs</t>
+          <t>/brighton-hove/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -8101,23 +8143,23 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove</t>
+          <t>Huddersfield</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>/brighton-hove/service-administrator-jobs</t>
+          <t>/huddersfield/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -8129,23 +8171,23 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Huddersfield</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D49" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E49" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>/huddersfield/service-administrator-jobs</t>
+          <t>/coventry/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -8157,12 +8199,12 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>Warrington</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Cheshire - Warrington &amp; Halton</t>
         </is>
       </c>
       <c r="D50" s="3" t="n">
@@ -8173,7 +8215,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>/coventry/service-administrator-jobs</t>
+          <t>/warrington/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -8185,49 +8227,49 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Warrington</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - Warrington &amp; Halton</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E51" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>/warrington/service-administrator-jobs</t>
+          <t>/barnsley/service-administrator-jobs</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>HOLD – LONDON</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Barnsley</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr"/>
+          <t>Bromley</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
       <c r="D52" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>/barnsley/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -8237,7 +8279,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Harrow</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -8246,7 +8288,7 @@
         </is>
       </c>
       <c r="D53" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E53" s="5" t="n">
         <v>0</v>
@@ -8261,7 +8303,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Harrow</t>
+          <t>Borehamwood</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -8270,7 +8312,7 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E54" s="3" t="n">
         <v>0</v>
@@ -8285,7 +8327,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Borehamwood</t>
+          <t>Croydon</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -8309,7 +8351,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Croydon</t>
+          <t>Isleworth</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -8333,7 +8375,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Isleworth</t>
+          <t>Sutton</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -8357,7 +8399,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Sutton</t>
+          <t>Uxbridge</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -8381,7 +8423,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Uxbridge</t>
+          <t>Wandsworth</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -8405,7 +8447,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Wandsworth</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -8414,7 +8456,7 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E60" s="3" t="n">
         <v>0</v>
@@ -8429,7 +8471,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Kingston Upon Thames</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -8453,7 +8495,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Kingston Upon Thames</t>
+          <t>Morden</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -8477,7 +8519,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Morden</t>
+          <t>Southall</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -8501,7 +8543,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Southall</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -8510,7 +8552,7 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64" s="3" t="n">
         <v>0</v>
@@ -8525,7 +8567,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Beckenham</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -8549,7 +8591,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Beckenham</t>
+          <t>Bushey</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -8573,7 +8615,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Bushey</t>
+          <t>Carshalton</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -8597,7 +8639,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Carshalton</t>
+          <t>Chessington</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -8621,7 +8663,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Chessington</t>
+          <t>Dagenham</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -8645,7 +8687,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Dagenham</t>
+          <t>Enfield</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -8669,7 +8711,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Enfield</t>
+          <t>Hayes</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -8693,7 +8735,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Hayes</t>
+          <t>Hornchurch</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -8717,7 +8759,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Hornchurch</t>
+          <t>Ilford</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -8741,7 +8783,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Ilford</t>
+          <t>Islington</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -8765,7 +8807,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Islington</t>
+          <t>Lambeth</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -8789,7 +8831,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Lambeth</t>
+          <t>Rainham</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -8813,7 +8855,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Rainham</t>
+          <t>Ruislip</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -8837,7 +8879,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Ruislip</t>
+          <t>Sidcup</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -8861,7 +8903,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Sidcup</t>
+          <t>Stanmore</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -8885,7 +8927,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Stanmore</t>
+          <t>Sutton-in-ashfield</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -8909,7 +8951,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Sutton-in-ashfield</t>
+          <t>Worcester Park</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -8928,21 +8970,21 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>MONITOR</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Worcester Park</t>
+          <t>Aylesbury</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E82" s="3" t="n">
         <v>0</v>
@@ -8957,12 +8999,12 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Aylesbury</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D83" s="5" t="n">
@@ -9053,7 +9095,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Crawley</t>
+          <t>Chichester</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -9077,12 +9119,12 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Crewe</t>
+          <t>Crawley</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D88" s="3" t="n">
@@ -9101,12 +9143,12 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Eastleigh</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Scotland Central - Tayside</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D89" s="5" t="n">
@@ -9125,12 +9167,12 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Eastleigh</t>
+          <t>Epsom</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D90" s="3" t="n">
@@ -9149,12 +9191,12 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Epsom</t>
+          <t>Fareham</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D91" s="5" t="n">
@@ -9173,12 +9215,12 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Fareham</t>
+          <t>Forfar</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D92" s="3" t="n">
@@ -9197,12 +9239,12 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Forfar</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Scotland Central - Tayside</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D93" s="5" t="n">
@@ -9221,12 +9263,12 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Gloucester</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D94" s="3" t="n">
@@ -9245,12 +9287,12 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Gloucester</t>
+          <t>Harrogate</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D95" s="5" t="n">
@@ -9269,12 +9311,12 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Harrogate</t>
+          <t>Hastings</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D96" s="3" t="n">
@@ -9293,12 +9335,12 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Hastings</t>
+          <t>Inverness</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D97" s="5" t="n">
@@ -9317,12 +9359,12 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Inverness</t>
+          <t>Lisburn</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D98" s="3" t="n">
@@ -9365,12 +9407,12 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Newry</t>
+          <t>Northwich</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D100" s="3" t="n">
@@ -9389,12 +9431,12 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Northwich</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D101" s="5" t="n">
@@ -9413,12 +9455,12 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Redhill</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D102" s="3" t="n">
@@ -9437,12 +9479,12 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Redhill</t>
+          <t>Ringwood</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D103" s="5" t="n">
@@ -9461,12 +9503,12 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Ringwood</t>
+          <t>Shrewsbury</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Shropshire</t>
         </is>
       </c>
       <c r="D104" s="3" t="n">
@@ -9485,12 +9527,12 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Shrewsbury</t>
+          <t>Solihull</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Shropshire</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D105" s="5" t="n">
@@ -9509,12 +9551,12 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Solihull</t>
+          <t>Torquay</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D106" s="3" t="n">
@@ -9533,12 +9575,12 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Torquay</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D107" s="5" t="n">
@@ -9557,12 +9599,12 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Winchester</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D108" s="3" t="n">
@@ -9581,16 +9623,16 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Winchester</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D109" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E109" s="5" t="n">
         <v>0</v>
@@ -9701,12 +9743,12 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Berwick-upon-tweed</t>
+          <t>Bury St Edmunds</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D114" s="3" t="n">
@@ -9725,12 +9767,12 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Bury St Edmunds</t>
+          <t>Carrickfergus</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D115" s="5" t="n">
@@ -9749,12 +9791,12 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Carrickfergus</t>
+          <t>Cheadle</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D116" s="3" t="n">
@@ -9773,12 +9815,12 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Cheadle</t>
+          <t>Chelmsley Wood</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D117" s="5" t="n">
@@ -9797,12 +9839,12 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Chelmsley Wood</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Derbyshire</t>
         </is>
       </c>
       <c r="D118" s="3" t="n">
@@ -9821,12 +9863,12 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Crewe</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Derbyshire</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D119" s="5" t="n">
@@ -9893,12 +9935,12 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Driffield</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - East</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D122" s="3" t="n">
@@ -10253,12 +10295,12 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Lisburn</t>
+          <t>Marlborough</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D137" s="5" t="n">
@@ -10325,12 +10367,12 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Newry</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D140" s="3" t="n">
@@ -10349,12 +10391,12 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Rickmansworth</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D141" s="5" t="n">
@@ -10373,12 +10415,12 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Romsey</t>
+          <t>Rickmansworth</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D142" s="3" t="n">
@@ -10397,12 +10439,12 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Salisbury</t>
+          <t>Romsey</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D143" s="5" t="n">
@@ -10421,12 +10463,12 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Slough</t>
+          <t>Salisbury</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D144" s="3" t="n">
@@ -10445,12 +10487,12 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Staines</t>
+          <t>Slough</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D145" s="5" t="n">
@@ -10469,12 +10511,12 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Stroud</t>
+          <t>Staines</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D146" s="3" t="n">
@@ -10493,12 +10535,12 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Taunton</t>
+          <t>Stroud</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D147" s="5" t="n">
@@ -10517,12 +10559,12 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Tipton</t>
+          <t>Taunton</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D148" s="3" t="n">
@@ -10541,12 +10583,12 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Wellington</t>
+          <t>Tipton</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Shropshire</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D149" s="5" t="n">
@@ -10565,12 +10607,12 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Weston-super-mare</t>
+          <t>Truro</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D150" s="3" t="n">
@@ -10589,12 +10631,12 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Woodbridge</t>
+          <t>Wellington</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Shropshire</t>
         </is>
       </c>
       <c r="D151" s="5" t="n">
@@ -10613,12 +10655,12 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Worcester</t>
+          <t>Weston-super-mare</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Worcestershire</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D152" s="3" t="n">
@@ -10637,12 +10679,12 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Yeovil</t>
+          <t>Woodbridge</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D153" s="5" t="n">
@@ -10661,16 +10703,16 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Yeovil</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D154" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E154" s="3" t="n">
         <v>0</v>
@@ -10925,12 +10967,12 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Bexhill-on-sea</t>
+          <t>Berwick-upon-tweed</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D165" s="5" t="n">
@@ -10949,12 +10991,12 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Bicester</t>
+          <t>Bexhill-on-sea</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D166" s="3" t="n">
@@ -10973,12 +11015,12 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Biggleswade</t>
+          <t>Bicester</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D167" s="5" t="n">
@@ -10997,12 +11039,12 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Bingley</t>
+          <t>Biggleswade</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D168" s="3" t="n">
@@ -11021,12 +11063,12 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Bishop Auckland</t>
+          <t>Bingley</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D169" s="5" t="n">
@@ -11045,12 +11087,12 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Bishop's Stortford</t>
+          <t>Bishop Auckland</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D170" s="3" t="n">
@@ -11069,12 +11111,12 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Brentwood</t>
+          <t>Bishop's Stortford</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D171" s="5" t="n">
@@ -11093,12 +11135,12 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Bridport</t>
+          <t>Brentwood</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D172" s="3" t="n">
@@ -11117,12 +11159,12 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Brinsworth</t>
+          <t>Bridport</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D173" s="5" t="n">
@@ -11141,12 +11183,12 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Buckingham</t>
+          <t>Brinsworth</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D174" s="3" t="n">
@@ -11165,12 +11207,12 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Cannock</t>
+          <t>Buckingham</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D175" s="5" t="n">
@@ -11189,12 +11231,12 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Canterbury</t>
+          <t>Cannock</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D176" s="3" t="n">
@@ -11213,7 +11255,7 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Chatham</t>
+          <t>Canterbury</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
@@ -11237,12 +11279,12 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Chertsey</t>
+          <t>Chatham</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D178" s="3" t="n">
@@ -11261,12 +11303,12 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Chichester</t>
+          <t>Chertsey</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D179" s="5" t="n">
@@ -11285,12 +11327,12 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Chippenham</t>
+          <t>Chesham</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D180" s="3" t="n">
@@ -11309,12 +11351,12 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Cirencester</t>
+          <t>Chippenham</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D181" s="5" t="n">
@@ -11333,12 +11375,12 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Coalville</t>
+          <t>Cirencester</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D182" s="3" t="n">
@@ -11357,12 +11399,12 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Cobham</t>
+          <t>Coalville</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D183" s="5" t="n">
@@ -11405,12 +11447,12 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Corby</t>
+          <t>Congleton</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D185" s="5" t="n">
@@ -11429,12 +11471,12 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Cottingham</t>
+          <t>Corby</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - East</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D186" s="3" t="n">
@@ -11453,12 +11495,12 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Cramlington</t>
+          <t>Cottingham</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Yorkshire - East</t>
         </is>
       </c>
       <c r="D187" s="5" t="n">
@@ -11477,12 +11519,12 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Cranbrook</t>
+          <t>Cramlington</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D188" s="3" t="n">
@@ -11501,12 +11543,12 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Darlington</t>
+          <t>Cranbrook</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D189" s="5" t="n">
@@ -11525,12 +11567,12 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Dartford</t>
+          <t>Darlington</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D190" s="3" t="n">
@@ -11549,12 +11591,12 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Droitwich</t>
+          <t>Dartford</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Worcestershire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D191" s="5" t="n">
@@ -11573,12 +11615,12 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Dudley</t>
+          <t>Driffield</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Yorkshire - East</t>
         </is>
       </c>
       <c r="D192" s="3" t="n">
@@ -11597,12 +11639,12 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>East Grinstead</t>
+          <t>Droitwich</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Worcestershire</t>
         </is>
       </c>
       <c r="D193" s="5" t="n">
@@ -11621,12 +11663,12 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Ely</t>
+          <t>East Grinstead</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D194" s="3" t="n">
@@ -11645,12 +11687,12 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Fakenham</t>
+          <t>Ely</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D195" s="5" t="n">
@@ -11669,12 +11711,12 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Falmouth</t>
+          <t>Fakenham</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D196" s="3" t="n">
@@ -11693,12 +11735,12 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Farnham</t>
+          <t>Falmouth</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D197" s="5" t="n">
@@ -11717,12 +11759,12 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Faygate</t>
+          <t>Farnham</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D198" s="3" t="n">
@@ -11741,12 +11783,12 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Felixstowe</t>
+          <t>Faygate</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D199" s="5" t="n">
@@ -11765,12 +11807,12 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Fetcham</t>
+          <t>Felixstowe</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D200" s="3" t="n">
@@ -11789,12 +11831,12 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Frome</t>
+          <t>Fetcham</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D201" s="5" t="n">
@@ -11813,12 +11855,12 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Gainsborough</t>
+          <t>Frome</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D202" s="3" t="n">
@@ -11837,12 +11879,12 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Godalming</t>
+          <t>Gainsborough</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D203" s="5" t="n">
@@ -11861,7 +11903,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Godstone</t>
+          <t>Godalming</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
@@ -11885,12 +11927,12 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Goole</t>
+          <t>Godstone</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - East</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D205" s="5" t="n">
@@ -11909,12 +11951,12 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Gosport</t>
+          <t>Goole</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Yorkshire - East</t>
         </is>
       </c>
       <c r="D206" s="3" t="n">
@@ -11933,12 +11975,12 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Great Yarmouth</t>
+          <t>Gosport</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D207" s="5" t="n">
@@ -11957,12 +11999,12 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Grimsby</t>
+          <t>Great Yarmouth</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D208" s="3" t="n">
@@ -11981,12 +12023,12 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Guildford</t>
+          <t>Grimsby</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D209" s="5" t="n">
@@ -12005,12 +12047,12 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Hailsham</t>
+          <t>Guildford</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D210" s="3" t="n">
@@ -12029,12 +12071,12 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Harlow</t>
+          <t>Hailsham</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D211" s="5" t="n">
@@ -12053,12 +12095,12 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Hartlepool</t>
+          <t>Halesowen</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D212" s="3" t="n">
@@ -12077,12 +12119,12 @@
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>Hatfield</t>
+          <t>Harlow</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D213" s="5" t="n">
@@ -12101,12 +12143,12 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Havant</t>
+          <t>Hartlepool</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D214" s="3" t="n">
@@ -12125,12 +12167,12 @@
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>Henley-on-thames</t>
+          <t>Hatfield</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D215" s="5" t="n">
@@ -12149,12 +12191,12 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Horley</t>
+          <t>Havant</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D216" s="3" t="n">
@@ -12173,12 +12215,12 @@
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>Hove</t>
+          <t>Henley-on-thames</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D217" s="5" t="n">
@@ -12197,12 +12239,12 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Jarrow</t>
+          <t>Holywood</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D218" s="3" t="n">
@@ -12221,12 +12263,12 @@
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>Keighley</t>
+          <t>Horley</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D219" s="5" t="n">
@@ -12245,12 +12287,12 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Kenilworth</t>
+          <t>Hove</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D220" s="3" t="n">
@@ -12269,12 +12311,12 @@
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Kirriemuir</t>
+          <t>Jarrow</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>Scotland Central - Tayside</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D221" s="5" t="n">
@@ -12293,12 +12335,12 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Knowle</t>
+          <t>Keighley</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D222" s="3" t="n">
@@ -12317,12 +12359,12 @@
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Kenilworth</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D223" s="5" t="n">
@@ -12341,12 +12383,12 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>Leamington Spa</t>
+          <t>Kirriemuir</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D224" s="3" t="n">
@@ -12365,12 +12407,12 @@
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>Leatherhead</t>
+          <t>Knowle</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D225" s="5" t="n">
@@ -12389,12 +12431,12 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>Liskeard</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D226" s="3" t="n">
@@ -12413,12 +12455,12 @@
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>Littlehampton</t>
+          <t>Leamington Spa</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D227" s="5" t="n">
@@ -12437,12 +12479,12 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Leatherhead</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Scotland Central - Edinburgh &amp; Lothians</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D228" s="3" t="n">
@@ -12461,12 +12503,12 @@
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>Loughborough</t>
+          <t>Liskeard</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D229" s="5" t="n">
@@ -12485,12 +12527,12 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>Lutterworth</t>
+          <t>Littlehampton</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D230" s="3" t="n">
@@ -12509,12 +12551,12 @@
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>Maidenhead</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Scotland Central - Edinburgh &amp; Lothians</t>
         </is>
       </c>
       <c r="D231" s="5" t="n">
@@ -12533,12 +12575,12 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Mansfield</t>
+          <t>Loughborough</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Nottinghamshire</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D232" s="3" t="n">
@@ -12557,12 +12599,12 @@
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>Marlborough</t>
+          <t>Lutterworth</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D233" s="5" t="n">
@@ -12581,12 +12623,12 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Marlow</t>
+          <t>Maidenhead</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D234" s="3" t="n">
@@ -12605,12 +12647,12 @@
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>Nantwich</t>
+          <t>Mansfield</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D235" s="5" t="n">
@@ -12629,12 +12671,12 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Newquay</t>
+          <t>Marlow</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D236" s="3" t="n">
@@ -12653,12 +12695,12 @@
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>Newtownards</t>
+          <t>Nantwich</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D237" s="5" t="n">
@@ -12677,12 +12719,12 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>Northampton</t>
+          <t>Newquay</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D238" s="3" t="n">
@@ -12701,12 +12743,12 @@
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>Nuneaton</t>
+          <t>Newtownards</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D239" s="5" t="n">
@@ -12725,12 +12767,12 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Okehampton</t>
+          <t>Northampton</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D240" s="3" t="n">
@@ -12749,12 +12791,12 @@
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>Otley</t>
+          <t>Nuneaton</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D241" s="5" t="n">
@@ -12773,12 +12815,12 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>Oxted</t>
+          <t>Okehampton</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D242" s="3" t="n">
@@ -12797,12 +12839,12 @@
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>Pickering</t>
+          <t>Otley</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D243" s="5" t="n">
@@ -12821,12 +12863,12 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>Pontypridd</t>
+          <t>Oxted</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Wales South - Valleys</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D244" s="3" t="n">
@@ -12845,12 +12887,12 @@
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>Poole</t>
+          <t>Pickering</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D245" s="5" t="n">
@@ -12869,12 +12911,12 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>Portishead</t>
+          <t>Pontypridd</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Wales South - Valleys</t>
         </is>
       </c>
       <c r="D246" s="3" t="n">
@@ -12893,12 +12935,12 @@
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>Potters Bar</t>
+          <t>Poole</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D247" s="5" t="n">
@@ -12917,12 +12959,12 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>Pudsey</t>
+          <t>Portishead</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D248" s="3" t="n">
@@ -12941,12 +12983,12 @@
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>Ramsgate</t>
+          <t>Potters Bar</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D249" s="5" t="n">
@@ -12965,12 +13007,12 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>Redditch</t>
+          <t>Pudsey</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Worcestershire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D250" s="3" t="n">
@@ -12989,12 +13031,12 @@
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>Redruth</t>
+          <t>Ramsgate</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D251" s="5" t="n">
@@ -13013,12 +13055,12 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>Reigate</t>
+          <t>Redditch</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Worcestershire</t>
         </is>
       </c>
       <c r="D252" s="3" t="n">
@@ -13037,12 +13079,12 @@
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>Retford</t>
+          <t>Redruth</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>Nottinghamshire</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D253" s="5" t="n">
@@ -13061,12 +13103,12 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Ripon</t>
+          <t>Reigate</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D254" s="3" t="n">
@@ -13085,12 +13127,12 @@
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>Rochester</t>
+          <t>Retford</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D255" s="5" t="n">
@@ -13109,12 +13151,12 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>Royston</t>
+          <t>Ripon</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D256" s="3" t="n">
@@ -13133,12 +13175,12 @@
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>Runcorn</t>
+          <t>Rochester</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - Warrington &amp; Halton</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D257" s="5" t="n">
@@ -13157,12 +13199,12 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>Rushden</t>
+          <t>Royston</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D258" s="3" t="n">
@@ -13181,12 +13223,12 @@
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>Ryton</t>
+          <t>Runcorn</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Cheshire - Warrington &amp; Halton</t>
         </is>
       </c>
       <c r="D259" s="5" t="n">
@@ -13205,12 +13247,12 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>Sale</t>
+          <t>Rushden</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D260" s="3" t="n">
@@ -13229,12 +13271,12 @@
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>Sandy</t>
+          <t>Ryton</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D261" s="5" t="n">
@@ -13253,12 +13295,12 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>Scunthorpe</t>
+          <t>Sale</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D262" s="3" t="n">
@@ -13277,12 +13319,12 @@
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>Sevenoaks</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D263" s="5" t="n">
@@ -13301,12 +13343,12 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>Shepperton</t>
+          <t>Scunthorpe</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D264" s="3" t="n">
@@ -13325,12 +13367,12 @@
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>Sherborne</t>
+          <t>Sevenoaks</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D265" s="5" t="n">
@@ -13349,12 +13391,12 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>Shirley</t>
+          <t>Shepperton</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D266" s="3" t="n">
@@ -13373,12 +13415,12 @@
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>Snodland</t>
+          <t>Sherborne</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D267" s="5" t="n">
@@ -13397,12 +13439,12 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>Southam</t>
+          <t>Shirley</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D268" s="3" t="n">
@@ -13421,12 +13463,12 @@
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>Southend-on-sea</t>
+          <t>Snodland</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D269" s="5" t="n">
@@ -13445,12 +13487,12 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>Spalding</t>
+          <t>Southam</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D270" s="3" t="n">
@@ -13469,12 +13511,12 @@
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>Spennymoor</t>
+          <t>Southend-on-sea</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D271" s="5" t="n">
@@ -13493,12 +13535,12 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>St. Ives</t>
+          <t>Spalding</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D272" s="3" t="n">
@@ -13517,12 +13559,12 @@
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>St. Neots</t>
+          <t>Spennymoor</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D273" s="5" t="n">
@@ -13541,12 +13583,12 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>Stafford</t>
+          <t>St. Ives</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D274" s="3" t="n">
@@ -13565,12 +13607,12 @@
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>Stanley</t>
+          <t>St. Neots</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D275" s="5" t="n">
@@ -13589,12 +13631,12 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Stafford</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D276" s="3" t="n">
@@ -13613,12 +13655,12 @@
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>Stratford-upon-avon</t>
+          <t>Stanley</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D277" s="5" t="n">
@@ -13637,12 +13679,12 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>Stretford</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D278" s="3" t="n">
@@ -13661,12 +13703,12 @@
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>Tadworth</t>
+          <t>Stratford-upon-avon</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D279" s="5" t="n">
@@ -13685,12 +13727,12 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>Tamworth</t>
+          <t>Stretford</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D280" s="3" t="n">
@@ -13709,12 +13751,12 @@
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>Telford</t>
+          <t>Tadworth</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>Shropshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D281" s="5" t="n">
@@ -13733,12 +13775,12 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>Thame</t>
+          <t>Tamworth</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D282" s="3" t="n">
@@ -13757,12 +13799,12 @@
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>Thatcham</t>
+          <t>Telford</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Shropshire</t>
         </is>
       </c>
       <c r="D283" s="5" t="n">
@@ -13781,12 +13823,12 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>Thetford</t>
+          <t>Thame</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D284" s="3" t="n">
@@ -13805,12 +13847,12 @@
       </c>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>Truro</t>
+          <t>Thatcham</t>
         </is>
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D285" s="5" t="n">
@@ -13829,12 +13871,12 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>Tunbridge Wells</t>
+          <t>Thetford</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D286" s="3" t="n">
@@ -13853,12 +13895,12 @@
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Thurso</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D287" s="5" t="n">
@@ -13877,12 +13919,12 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>Walton-on-thames</t>
+          <t>Tunbridge Wells</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D288" s="3" t="n">
@@ -13901,12 +13943,12 @@
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D289" s="5" t="n">
@@ -13925,12 +13967,12 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>Wednesbury</t>
+          <t>Walton-on-thames</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D290" s="3" t="n">
@@ -13949,12 +13991,12 @@
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>Wellingborough</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D291" s="5" t="n">
@@ -13973,12 +14015,12 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>Welwyn Garden City</t>
+          <t>Wednesbury</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D292" s="3" t="n">
@@ -13997,12 +14039,12 @@
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>West Malling</t>
+          <t>Wellingborough</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D293" s="5" t="n">
@@ -14021,12 +14063,12 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>Weymouth</t>
+          <t>Welwyn Garden City</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D294" s="3" t="n">
@@ -14045,12 +14087,12 @@
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>Whitby</t>
+          <t>West Malling</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D295" s="5" t="n">
@@ -14069,12 +14111,12 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>Whitstable</t>
+          <t>Weymouth</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D296" s="3" t="n">
@@ -14093,12 +14135,12 @@
       </c>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>Wilmslow</t>
+          <t>Whitby</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D297" s="5" t="n">
@@ -14117,12 +14159,12 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Whitstable</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D298" s="3" t="n">
@@ -14141,12 +14183,12 @@
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>Winsford</t>
+          <t>Wilmslow</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D299" s="5" t="n">
@@ -14165,24 +14207,96 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
+          <t>Windsor</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>Berkshire</t>
+        </is>
+      </c>
+      <c r="D300" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E300" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F300" s="2" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="4" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B301" s="4" t="inlineStr">
+        <is>
+          <t>Winsford</t>
+        </is>
+      </c>
+      <c r="C301" s="4" t="inlineStr">
+        <is>
+          <t>Cheshire - West</t>
+        </is>
+      </c>
+      <c r="D301" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E301" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F301" s="4" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>Worcester</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>Worcestershire</t>
+        </is>
+      </c>
+      <c r="D302" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E302" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F302" s="2" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="4" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B303" s="4" t="inlineStr">
+        <is>
           <t>Worthing</t>
         </is>
       </c>
-      <c r="C300" s="2" t="inlineStr">
+      <c r="C303" s="4" t="inlineStr">
         <is>
           <t>Sussex</t>
         </is>
       </c>
-      <c r="D300" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E300" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F300" s="2" t="inlineStr"/>
+      <c r="D303" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E303" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F303" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F300"/>
+  <autoFilter ref="A1:F303"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14278,7 +14392,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="5" t="n">
@@ -14301,7 +14415,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="3" t="n">
@@ -14326,7 +14440,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
       <c r="D5" s="4" t="inlineStr"/>
@@ -14347,7 +14461,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr"/>
@@ -14423,7 +14537,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr"/>
@@ -14487,7 +14601,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr"/>
@@ -14504,7 +14618,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
       <c r="D15" s="4" t="inlineStr"/>
@@ -14525,7 +14639,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr"/>
@@ -14542,7 +14656,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
       <c r="D17" s="4" t="inlineStr"/>
@@ -14550,7 +14664,7 @@
         <v>5</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="4" t="inlineStr"/>
@@ -14569,7 +14683,7 @@
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
@@ -14586,15 +14700,15 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
       <c r="D19" s="5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="5" t="n">
@@ -14658,7 +14772,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C23" s="5" t="n">
         <v>9</v>
@@ -14715,10 +14829,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>11</v>
@@ -14813,7 +14927,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="inlineStr"/>
@@ -14847,22 +14961,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>18</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>13</v>
@@ -14942,7 +15056,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C39" s="4" t="inlineStr"/>
       <c r="D39" s="4" t="inlineStr"/>
@@ -14969,7 +15083,7 @@
         <v>2</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="3" t="n">
@@ -14992,7 +15106,7 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C41" s="4" t="inlineStr"/>
       <c r="D41" s="4" t="inlineStr"/>
@@ -15039,7 +15153,7 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="inlineStr"/>
@@ -15056,16 +15170,14 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C45" s="4" t="inlineStr"/>
       <c r="D45" s="4" t="inlineStr"/>
       <c r="E45" s="4" t="inlineStr"/>
       <c r="F45" s="4" t="inlineStr"/>
-      <c r="G45" s="4" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
+      <c r="G45" s="5" t="n">
+        <v>9</v>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
       <c r="I45" s="4" t="inlineStr"/>
@@ -15162,7 +15274,7 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C51" s="4" t="inlineStr"/>
       <c r="D51" s="4" t="inlineStr"/>
@@ -15209,7 +15321,7 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C54" s="2" t="inlineStr"/>
       <c r="D54" s="2" t="inlineStr"/>
@@ -15241,7 +15353,7 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C56" s="2" t="inlineStr"/>
       <c r="D56" s="3" t="n">
@@ -15290,7 +15402,7 @@
         </is>
       </c>
       <c r="B59" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C59" s="4" t="inlineStr"/>
       <c r="D59" s="4" t="inlineStr"/>
@@ -15311,7 +15423,7 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C60" s="2" t="inlineStr"/>
       <c r="D60" s="2" t="inlineStr"/>
@@ -15328,7 +15440,7 @@
         </is>
       </c>
       <c r="B61" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C61" s="4" t="inlineStr"/>
       <c r="D61" s="4" t="inlineStr"/>
@@ -15369,7 +15481,7 @@
         <v>61</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D63" s="5" t="n">
         <v>7</v>
@@ -15391,13 +15503,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C64" s="3" t="n">
         <v>4</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr"/>
@@ -15514,7 +15626,7 @@
       <c r="D71" s="4" t="inlineStr"/>
       <c r="E71" s="4" t="inlineStr"/>
       <c r="F71" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G71" s="4" t="inlineStr"/>
       <c r="H71" s="5" t="n">
@@ -15546,7 +15658,7 @@
         </is>
       </c>
       <c r="B73" s="5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C73" s="4" t="inlineStr"/>
       <c r="D73" s="4" t="inlineStr"/>
@@ -15563,7 +15675,7 @@
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C74" s="3" t="n">
         <v>2</v>
@@ -15582,7 +15694,7 @@
         </is>
       </c>
       <c r="B75" s="5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C75" s="4" t="inlineStr"/>
       <c r="D75" s="4" t="inlineStr"/>
@@ -15599,7 +15711,7 @@
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C76" s="2" t="inlineStr"/>
       <c r="D76" s="2" t="inlineStr"/>
@@ -15637,7 +15749,7 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
@@ -15658,10 +15770,10 @@
         </is>
       </c>
       <c r="B79" s="5" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C79" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D79" s="5" t="n">
         <v>4</v>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sitewide'!$A$1:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'JobG8 categories'!$A$1:$C$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'PAGES'!$A$1:$H$160</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$F$303</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$F$357</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'LIVE'!$A$1:$I$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'NOT LIVE'!$A$1:$I$79</definedName>
   </definedNames>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1941</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="3">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>415</v>
+        <v>395</v>
       </c>
     </row>
     <row r="5">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>2016</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="6">
@@ -943,7 +943,7 @@
       <c r="D2" s="11" t="inlineStr"/>
       <c r="E2" s="11" t="inlineStr"/>
       <c r="F2" s="12" t="n">
-        <v>2079</v>
+        <v>2059</v>
       </c>
       <c r="G2" s="11" t="inlineStr"/>
       <c r="H2" s="11" t="inlineStr">
@@ -975,10 +975,10 @@
         </is>
       </c>
       <c r="F3" s="12" t="n">
-        <v>1925</v>
+        <v>1905</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>1925</v>
+        <v>1905</v>
       </c>
       <c r="H3" s="11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>1</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>1</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>1</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>1</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>1</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>1</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>1</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>1</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>1</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>1</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>1</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>1</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>1</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>1</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>1</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>1</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>1</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>1</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
         <v>1</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>1</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>1</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F303"/>
+  <dimension ref="A1:F357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6919,16 +6919,16 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>High Wycombe</t>
+          <t>Exeter</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>0</v>
@@ -6943,16 +6943,16 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Newtownabbey</t>
+          <t>Hemel Hempstead</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>0</v>
@@ -6967,16 +6967,16 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Altrincham</t>
+          <t>Farnham</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
@@ -6991,16 +6991,16 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Milton Keynes</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>0</v>
@@ -7015,16 +7015,16 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Chelmsford</t>
+          <t>Newbury</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
@@ -7039,16 +7039,16 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Chester Le Street</t>
+          <t>Northampton</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>0</v>
@@ -7063,16 +7063,16 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Hemel Hempstead</t>
+          <t>Poole</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>0</v>
@@ -7087,16 +7087,16 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Macclesfield</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>0</v>
@@ -7111,16 +7111,16 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Maidstone</t>
+          <t>Stoke-on-trent</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0</v>
@@ -7135,16 +7135,16 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Rotherham</t>
+          <t>High Wycombe</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>0</v>
@@ -7159,16 +7159,16 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Scarborough</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -7183,16 +7183,16 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Stockport</t>
+          <t>Basingstoke</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>0</v>
@@ -7207,16 +7207,16 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Stoke-on-trent</t>
+          <t>Bracknell</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>0</v>
@@ -7231,16 +7231,16 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelmsford</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>0</v>
@@ -7255,16 +7255,16 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Swindon</t>
+          <t>Crawley</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>0</v>
@@ -7279,16 +7279,16 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Tonbridge</t>
+          <t>Gloucester</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" s="5" t="n">
         <v>0</v>
@@ -7298,96 +7298,84 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Leicester</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>/manchester/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Newcastle</t>
+          <t>Lisburn</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>/newcastle/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Maidstone</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>/birmingham/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Belfast</t>
+          <t>Newtownabbey</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -7396,800 +7384,684 @@
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>/belfast/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Bristol</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>/bristol/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>/leeds/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Warwick</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Merseyside - Liverpool</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>/liverpool/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Sheffield</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>/sheffield/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Hull</t>
+          <t>Worcester</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - East</t>
+          <t>Worcestershire</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>/hull/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Glasgow</t>
+          <t>Altrincham</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Scotland West - Glasgow</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>/glasgow/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Nottingham</t>
+          <t>Ashford</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Nottinghamshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>/nottingham/jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Bradford</t>
+          <t>Aylesbury</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>/bradford/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Scotland Central - Edinburgh &amp; Lothians</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>/edinburgh/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Cardiff</t>
+          <t>Bishop's Stortford</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Wales South - Cardiff &amp; Vale</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>/cardiff/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>/southampton/service-administrator-jobs, /southampton/support-worker</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Peterborough</t>
+          <t>Burgess Hill</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>/peterborough/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Cambridge</t>
+          <t>Chester Le Street</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>/cambridge/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Doncaster</t>
+          <t>Eastleigh</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>/doncaster/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Oxford</t>
+          <t>Epsom</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>/oxford/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Wakefield</t>
+          <t>Fareham</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>/wakefield/jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Bolton</t>
+          <t>Guildford</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - Wigan &amp; Bolton</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>/bolton/jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Horsham</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>/reading/jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Chester</t>
+          <t>Ipswich</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>/chester/jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Durham</t>
+          <t>Macclesfield</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>/durham/jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Gateshead</t>
+          <t>Mansfield</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>/gateshead/jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Northallerton</t>
+          <t>Rotherham</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>/northallerton/jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Norwich</t>
+          <t>Scarborough</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>/norwich/jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Salford</t>
+          <t>Shrewsbury</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>Shropshire</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>/salford/jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>York</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>/york/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove</t>
+          <t>Swindon</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D47" s="5" t="n">
         <v>4</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>/brighton-hove/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Huddersfield</t>
+          <t>Tonbridge</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>/huddersfield/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>Wigston</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D49" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>/coventry/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -8199,23 +8071,23 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Warrington</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - Warrington &amp; Halton</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="E50" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>/warrington/service-administrator-jobs</t>
+          <t>/manchester/service-administrator-jobs</t>
         </is>
       </c>
     </row>
@@ -8227,812 +8099,940 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Newcastle</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="E51" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>/barnsley/service-administrator-jobs</t>
+          <t>/newcastle/service-administrator-jobs</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Belfast</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>/belfast/service-administrator-jobs</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Harrow</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D53" s="5" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>/birmingham/service-administrator-jobs</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Borehamwood</t>
+          <t>Bristol</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>/bristol/service-administrator-jobs</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Croydon</t>
+          <t>Leeds</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D55" s="5" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>/leeds/service-administrator-jobs</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Isleworth</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Merseyside - Liverpool</t>
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>/liverpool/service-administrator-jobs</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Sutton</t>
+          <t>Nottingham</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D57" s="5" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>/nottingham/jobs</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Uxbridge</t>
+          <t>Sheffield</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>/sheffield/service-administrator-jobs</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Wandsworth</t>
+          <t>Hull</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Yorkshire - East</t>
         </is>
       </c>
       <c r="D59" s="5" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>/hull/service-administrator-jobs</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Glasgow</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Scotland West - Glasgow</t>
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>/glasgow/service-administrator-jobs</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Kingston Upon Thames</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D61" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E61" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>/southampton/service-administrator-jobs, /southampton/support-worker</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Morden</t>
+          <t>Bradford</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Yorkshire - West</t>
         